--- a/Docs/Units.xlsx
+++ b/Docs/Units.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="208">
   <si>
     <t>Name</t>
   </si>
@@ -589,6 +589,57 @@
   </si>
   <si>
     <t>Plaguebearers</t>
+  </si>
+  <si>
+    <t>Tallyman of deathguard</t>
+  </si>
+  <si>
+    <t>Crowd-dependant</t>
+  </si>
+  <si>
+    <t>Virus rat</t>
+  </si>
+  <si>
+    <t>Giant rat</t>
+  </si>
+  <si>
+    <t>Ratbearer</t>
+  </si>
+  <si>
+    <t>Tallyman</t>
+  </si>
+  <si>
+    <t>Ratling</t>
+  </si>
+  <si>
+    <t>Skaven basic troop</t>
+  </si>
+  <si>
+    <t>Plague mage</t>
+  </si>
+  <si>
+    <t>1 normal, 2 only diagonals</t>
+  </si>
+  <si>
+    <t>The Nurgle sloppity guy</t>
+  </si>
+  <si>
+    <t>Bombshoom</t>
+  </si>
+  <si>
+    <t>Explosive (1)</t>
+  </si>
+  <si>
+    <t>Gladiator</t>
+  </si>
+  <si>
+    <t>World eater jackal</t>
+  </si>
+  <si>
+    <t>Battle-hungry</t>
+  </si>
+  <si>
+    <t>Bomb squig made out of mushrooms</t>
   </si>
 </sst>
 </file>
@@ -729,7 +780,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -801,6 +852,12 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -819,16 +876,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -837,10 +885,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1150,56 +1204,56 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AB178"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.85546875" style="1"/>
-    <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" style="1"/>
-    <col min="6" max="6" width="17.28515625" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="23.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" style="1"/>
-    <col min="12" max="12" width="20.28515625" style="1" customWidth="1"/>
-    <col min="13" max="14" width="8.85546875" style="1"/>
-    <col min="15" max="15" width="10.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.85546875" style="1"/>
-    <col min="17" max="17" width="14.140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="17.85546875" style="1" customWidth="1"/>
-    <col min="19" max="20" width="8.85546875" style="1"/>
-    <col min="21" max="21" width="16.5703125" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="2" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="20.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23.5546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" style="1"/>
+    <col min="12" max="12" width="20.33203125" style="1" customWidth="1"/>
+    <col min="13" max="14" width="8.88671875" style="1"/>
+    <col min="15" max="15" width="10.5546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.88671875" style="1"/>
+    <col min="17" max="17" width="14.109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="17.88671875" style="1" customWidth="1"/>
+    <col min="19" max="20" width="8.88671875" style="1"/>
+    <col min="21" max="21" width="16.5546875" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-    </row>
-    <row r="2" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-    </row>
-    <row r="3" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+    </row>
+    <row r="2" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1210,7 +1264,7 @@
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -1220,10 +1274,34 @@
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
     </row>
-    <row r="5" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>14</v>
       </c>
+      <c r="C5" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>19</v>
+      </c>
       <c r="L5" s="6" t="s">
         <v>0</v>
       </c>
@@ -1273,10 +1351,34 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
+      <c r="C6" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="D6" s="24">
+        <v>2</v>
+      </c>
+      <c r="E6" s="24">
+        <v>1</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" s="24">
+        <v>20</v>
+      </c>
       <c r="L6" s="6" t="s">
         <v>26</v>
       </c>
@@ -1326,70 +1428,118 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>110</v>
       </c>
+      <c r="C7" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
       <c r="L7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="37" t="s">
+      <c r="M7" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="37"/>
-      <c r="S7" s="37"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="33"/>
+      <c r="P7" s="33"/>
+      <c r="Q7" s="33"/>
+      <c r="R7" s="33"/>
+      <c r="S7" s="33"/>
       <c r="U7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V7" s="36" t="s">
+      <c r="V7" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="W7" s="36"/>
-      <c r="X7" s="36"/>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="36"/>
-      <c r="AA7" s="36"/>
-      <c r="AB7" s="36"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="W7" s="35"/>
+      <c r="X7" s="35"/>
+      <c r="Y7" s="35"/>
+      <c r="Z7" s="35"/>
+      <c r="AA7" s="35"/>
+      <c r="AB7" s="35"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="5"/>
+      <c r="C8" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
       <c r="L8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="37" t="s">
+      <c r="M8" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="37"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="33"/>
+      <c r="S8" s="33"/>
       <c r="U8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="36" t="s">
+      <c r="V8" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="W8" s="36"/>
-      <c r="X8" s="36"/>
-      <c r="Y8" s="36"/>
-      <c r="Z8" s="36"/>
-      <c r="AA8" s="36"/>
-      <c r="AB8" s="36"/>
-    </row>
-    <row r="9" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="W8" s="35"/>
+      <c r="X8" s="35"/>
+      <c r="Y8" s="35"/>
+      <c r="Z8" s="35"/>
+      <c r="AA8" s="35"/>
+      <c r="AB8" s="35"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="O9"/>
       <c r="X9"/>
     </row>
-    <row r="10" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C10" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>19</v>
+      </c>
       <c r="L10" s="6" t="s">
         <v>0</v>
       </c>
@@ -1439,7 +1589,31 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="14">
+        <v>12</v>
+      </c>
+      <c r="E11" s="14">
+        <v>3</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="14">
+        <v>100</v>
+      </c>
       <c r="L11" s="6" t="s">
         <v>28</v>
       </c>
@@ -1489,63 +1663,111 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="C12" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="29"/>
       <c r="L12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="37" t="s">
+      <c r="M12" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
-      <c r="S12" s="37"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="33"/>
+      <c r="S12" s="33"/>
       <c r="U12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V12" s="36" t="s">
+      <c r="V12" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="W12" s="36"/>
-      <c r="X12" s="36"/>
-      <c r="Y12" s="36"/>
-      <c r="Z12" s="36"/>
-      <c r="AA12" s="36"/>
-      <c r="AB12" s="36"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="W12" s="35"/>
+      <c r="X12" s="35"/>
+      <c r="Y12" s="35"/>
+      <c r="Z12" s="35"/>
+      <c r="AA12" s="35"/>
+      <c r="AB12" s="35"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="C13" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="29"/>
       <c r="L13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="37" t="s">
+      <c r="M13" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
-      <c r="S13" s="37"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="33"/>
+      <c r="Q13" s="33"/>
+      <c r="R13" s="33"/>
+      <c r="S13" s="33"/>
       <c r="U13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V13" s="36" t="s">
+      <c r="V13" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="W13" s="36"/>
-      <c r="X13" s="36"/>
-      <c r="Y13" s="36"/>
-      <c r="Z13" s="36"/>
-      <c r="AA13" s="36"/>
-      <c r="AB13" s="36"/>
-    </row>
-    <row r="14" spans="1:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="W13" s="35"/>
+      <c r="X13" s="35"/>
+      <c r="Y13" s="35"/>
+      <c r="Z13" s="35"/>
+      <c r="AA13" s="35"/>
+      <c r="AB13" s="35"/>
+    </row>
+    <row r="14" spans="1:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="O14"/>
       <c r="X14"/>
     </row>
-    <row r="15" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C15" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>19</v>
+      </c>
       <c r="L15" s="6" t="s">
         <v>0</v>
       </c>
@@ -1595,7 +1817,31 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C16" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="D16" s="25">
+        <v>2</v>
+      </c>
+      <c r="E16" s="25">
+        <v>1</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="25">
+        <v>25</v>
+      </c>
       <c r="L16" s="6" t="s">
         <v>32</v>
       </c>
@@ -1645,59 +1891,83 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="C17" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
       <c r="L17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="37" t="s">
+      <c r="M17" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
-      <c r="S17" s="37"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="33"/>
+      <c r="S17" s="33"/>
       <c r="U17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V17" s="36" t="s">
+      <c r="V17" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="W17" s="36"/>
-      <c r="X17" s="36"/>
-      <c r="Y17" s="36"/>
-      <c r="Z17" s="36"/>
-      <c r="AA17" s="36"/>
-      <c r="AB17" s="36"/>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="W17" s="35"/>
+      <c r="X17" s="35"/>
+      <c r="Y17" s="35"/>
+      <c r="Z17" s="35"/>
+      <c r="AA17" s="35"/>
+      <c r="AB17" s="35"/>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="C18" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
       <c r="L18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="37" t="s">
+      <c r="M18" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
-      <c r="S18" s="37"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="33"/>
+      <c r="S18" s="33"/>
       <c r="U18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V18" s="36" t="s">
+      <c r="V18" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="W18" s="36"/>
-      <c r="X18" s="36"/>
-      <c r="Y18" s="36"/>
-      <c r="Z18" s="36"/>
-      <c r="AA18" s="36"/>
-      <c r="AB18" s="36"/>
-    </row>
-    <row r="19" spans="3:28" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="W18" s="35"/>
+      <c r="X18" s="35"/>
+      <c r="Y18" s="35"/>
+      <c r="Z18" s="35"/>
+      <c r="AA18" s="35"/>
+      <c r="AB18" s="35"/>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
@@ -1758,7 +2028,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="16" t="s">
         <v>184</v>
       </c>
@@ -1808,59 +2078,59 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="31" t="s">
+      <c r="D22" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="33"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="39"/>
       <c r="L22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="37" t="s">
+      <c r="M22" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="37"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="37"/>
-      <c r="S22" s="37"/>
-    </row>
-    <row r="23" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N22" s="33"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="33"/>
+      <c r="Q22" s="33"/>
+      <c r="R22" s="33"/>
+      <c r="S22" s="33"/>
+    </row>
+    <row r="23" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="31" t="s">
+      <c r="D23" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="33"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="39"/>
       <c r="L23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="37" t="s">
+      <c r="M23" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="N23" s="37"/>
-      <c r="O23" s="37"/>
-      <c r="P23" s="37"/>
-      <c r="Q23" s="37"/>
-      <c r="R23" s="37"/>
-      <c r="S23" s="37"/>
-    </row>
-    <row r="25" spans="3:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N23" s="33"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="33"/>
+      <c r="R23" s="33"/>
+      <c r="S23" s="33"/>
+    </row>
+    <row r="25" spans="3:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="16" t="s">
         <v>0</v>
       </c>
@@ -1910,7 +2180,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="16" t="s">
         <v>172</v>
       </c>
@@ -1960,59 +2230,59 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="31" t="s">
+      <c r="D27" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="33"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="39"/>
       <c r="L27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M27" s="37" t="s">
+      <c r="M27" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="N27" s="37"/>
-      <c r="O27" s="37"/>
-      <c r="P27" s="37"/>
-      <c r="Q27" s="37"/>
-      <c r="R27" s="37"/>
-      <c r="S27" s="37"/>
-    </row>
-    <row r="28" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="33"/>
+      <c r="S27" s="33"/>
+    </row>
+    <row r="28" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="31" t="s">
+      <c r="D28" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="33"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="39"/>
       <c r="L28" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
-    </row>
-    <row r="30" spans="3:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N28" s="36"/>
+      <c r="O28" s="36"/>
+      <c r="P28" s="36"/>
+      <c r="Q28" s="36"/>
+      <c r="R28" s="36"/>
+      <c r="S28" s="36"/>
+    </row>
+    <row r="30" spans="3:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C30" s="16" t="s">
         <v>0</v>
       </c>
@@ -2062,7 +2332,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C31" s="16" t="s">
         <v>85</v>
       </c>
@@ -2116,55 +2386,79 @@
       <c r="C32" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="31" t="s">
+      <c r="D32" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="33"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="39"/>
       <c r="L32" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M32" s="28" t="s">
+      <c r="M32" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="30"/>
-    </row>
-    <row r="33" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="32"/>
+    </row>
+    <row r="33" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C33" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="31" t="s">
+      <c r="D33" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="33"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
+      <c r="J33" s="39"/>
       <c r="L33" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M33" s="28" t="s">
+      <c r="M33" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="N33" s="29"/>
-      <c r="O33" s="29"/>
-      <c r="P33" s="29"/>
-      <c r="Q33" s="29"/>
-      <c r="R33" s="29"/>
-      <c r="S33" s="30"/>
-    </row>
-    <row r="35" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="31"/>
+      <c r="S33" s="32"/>
+    </row>
+    <row r="35" spans="3:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="21" t="s">
+        <v>19</v>
+      </c>
       <c r="L35" s="11" t="s">
         <v>0</v>
       </c>
@@ -2190,7 +2484,31 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="D36" s="21">
+        <v>2</v>
+      </c>
+      <c r="E36" s="21">
+        <v>1</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="H36" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="I36" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="J36" s="21">
+        <v>25</v>
+      </c>
       <c r="L36" s="11" t="s">
         <v>50</v>
       </c>
@@ -2216,57 +2534,81 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
       <c r="L37" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M37" s="28" t="s">
+      <c r="M37" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="30"/>
-    </row>
-    <row r="38" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="31"/>
+      <c r="S37" s="32"/>
+    </row>
+    <row r="38" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="26"/>
       <c r="L38" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M38" s="34" t="s">
+      <c r="M38" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="N38" s="34"/>
-      <c r="O38" s="34"/>
-      <c r="P38" s="34"/>
-      <c r="Q38" s="34"/>
-      <c r="R38" s="34"/>
-      <c r="S38" s="34"/>
-    </row>
-    <row r="40" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="D40" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="F40" s="24" t="s">
+      <c r="N38" s="36"/>
+      <c r="O38" s="36"/>
+      <c r="P38" s="36"/>
+      <c r="Q38" s="36"/>
+      <c r="R38" s="36"/>
+      <c r="S38" s="36"/>
+    </row>
+    <row r="40" spans="3:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F40" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="G40" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="H40" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="I40" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="J40" s="24" t="s">
+      <c r="G40" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="H40" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I40" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="J40" s="25" t="s">
         <v>19</v>
       </c>
       <c r="L40" s="11" t="s">
@@ -2294,30 +2636,30 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="D41" s="24">
-        <v>2</v>
-      </c>
-      <c r="E41" s="24">
-        <v>1</v>
-      </c>
-      <c r="F41" s="24" t="s">
+    <row r="41" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="D41" s="25">
+        <v>2</v>
+      </c>
+      <c r="E41" s="25">
+        <v>2</v>
+      </c>
+      <c r="F41" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="G41" s="24" t="s">
+      <c r="G41" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="H41" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="I41" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="J41" s="24">
-        <v>20</v>
+      <c r="H41" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="25">
+        <v>30</v>
       </c>
       <c r="L41" s="11" t="s">
         <v>52</v>
@@ -2344,59 +2686,59 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="24" t="s">
+    <row r="42" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="D42" s="38" t="s">
-        <v>189</v>
-      </c>
-      <c r="E42" s="38"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="38"/>
-      <c r="I42" s="38"/>
-      <c r="J42" s="38"/>
+      <c r="D42" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
       <c r="L42" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M42" s="28" t="s">
+      <c r="M42" s="30" t="s">
         <v>187</v>
       </c>
-      <c r="N42" s="29"/>
-      <c r="O42" s="29"/>
-      <c r="P42" s="29"/>
-      <c r="Q42" s="29"/>
-      <c r="R42" s="29"/>
-      <c r="S42" s="30"/>
-    </row>
-    <row r="43" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="24" t="s">
+      <c r="N42" s="31"/>
+      <c r="O42" s="31"/>
+      <c r="P42" s="31"/>
+      <c r="Q42" s="31"/>
+      <c r="R42" s="31"/>
+      <c r="S42" s="32"/>
+    </row>
+    <row r="43" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C43" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
-      <c r="J43" s="38"/>
+      <c r="D43" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
       <c r="L43" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M43" s="28" t="s">
+      <c r="M43" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="30"/>
-    </row>
-    <row r="45" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+      <c r="R43" s="31"/>
+      <c r="S43" s="32"/>
+    </row>
+    <row r="45" spans="3:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="13" t="s">
         <v>0</v>
       </c>
@@ -2446,7 +2788,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="13" t="s">
         <v>150</v>
       </c>
@@ -2496,59 +2838,59 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="38" t="s">
+      <c r="D47" s="26" t="s">
         <v>151</v>
       </c>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="38"/>
-      <c r="I47" s="38"/>
-      <c r="J47" s="38"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="26"/>
       <c r="L47" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="28" t="s">
+      <c r="M47" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="N47" s="29"/>
-      <c r="O47" s="29"/>
-      <c r="P47" s="29"/>
-      <c r="Q47" s="29"/>
-      <c r="R47" s="29"/>
-      <c r="S47" s="30"/>
-    </row>
-    <row r="48" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N47" s="31"/>
+      <c r="O47" s="31"/>
+      <c r="P47" s="31"/>
+      <c r="Q47" s="31"/>
+      <c r="R47" s="31"/>
+      <c r="S47" s="32"/>
+    </row>
+    <row r="48" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="38" t="s">
+      <c r="D48" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="E48" s="38"/>
-      <c r="F48" s="38"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="38"/>
-      <c r="I48" s="38"/>
-      <c r="J48" s="38"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="26"/>
       <c r="L48" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M48" s="28" t="s">
+      <c r="M48" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="N48" s="29"/>
-      <c r="O48" s="29"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="29"/>
-      <c r="S48" s="30"/>
-    </row>
-    <row r="50" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N48" s="31"/>
+      <c r="O48" s="31"/>
+      <c r="P48" s="31"/>
+      <c r="Q48" s="31"/>
+      <c r="R48" s="31"/>
+      <c r="S48" s="32"/>
+    </row>
+    <row r="50" spans="3:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="14" t="s">
         <v>0</v>
       </c>
@@ -2598,7 +2940,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="14" t="s">
         <v>143</v>
       </c>
@@ -2652,53 +2994,53 @@
       <c r="C52" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D52" s="25" t="s">
+      <c r="D52" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="26"/>
-      <c r="H52" s="26"/>
-      <c r="I52" s="26"/>
-      <c r="J52" s="27"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="29"/>
       <c r="L52" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M52" s="34" t="s">
+      <c r="M52" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="N52" s="34"/>
-      <c r="O52" s="34"/>
-      <c r="P52" s="34"/>
-      <c r="Q52" s="34"/>
-      <c r="R52" s="34"/>
-      <c r="S52" s="34"/>
-    </row>
-    <row r="53" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N52" s="36"/>
+      <c r="O52" s="36"/>
+      <c r="P52" s="36"/>
+      <c r="Q52" s="36"/>
+      <c r="R52" s="36"/>
+      <c r="S52" s="36"/>
+    </row>
+    <row r="53" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="25" t="s">
+      <c r="D53" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26"/>
-      <c r="H53" s="26"/>
-      <c r="I53" s="26"/>
-      <c r="J53" s="27"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="28"/>
+      <c r="I53" s="28"/>
+      <c r="J53" s="29"/>
       <c r="L53" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M53" s="34" t="s">
+      <c r="M53" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="N53" s="34"/>
-      <c r="O53" s="34"/>
-      <c r="P53" s="34"/>
-      <c r="Q53" s="34"/>
-      <c r="R53" s="34"/>
-      <c r="S53" s="34"/>
+      <c r="N53" s="36"/>
+      <c r="O53" s="36"/>
+      <c r="P53" s="36"/>
+      <c r="Q53" s="36"/>
+      <c r="R53" s="36"/>
+      <c r="S53" s="36"/>
     </row>
     <row r="55" spans="3:19" ht="30" x14ac:dyDescent="0.25">
       <c r="C55" s="14" t="s">
@@ -2750,7 +3092,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:19" ht="15" x14ac:dyDescent="0.25">
       <c r="C56" s="14" t="s">
         <v>146</v>
       </c>
@@ -2800,57 +3142,57 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C57" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="25" t="s">
+      <c r="D57" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
-      <c r="G57" s="26"/>
-      <c r="H57" s="26"/>
-      <c r="I57" s="26"/>
-      <c r="J57" s="27"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="29"/>
       <c r="L57" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M57" s="28" t="s">
+      <c r="M57" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="N57" s="29"/>
-      <c r="O57" s="29"/>
-      <c r="P57" s="29"/>
-      <c r="Q57" s="29"/>
-      <c r="R57" s="29"/>
-      <c r="S57" s="30"/>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="N57" s="31"/>
+      <c r="O57" s="31"/>
+      <c r="P57" s="31"/>
+      <c r="Q57" s="31"/>
+      <c r="R57" s="31"/>
+      <c r="S57" s="32"/>
+    </row>
+    <row r="58" spans="3:19" ht="15" x14ac:dyDescent="0.25">
       <c r="C58" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="25" t="s">
+      <c r="D58" s="27" t="s">
         <v>166</v>
       </c>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26"/>
-      <c r="H58" s="26"/>
-      <c r="I58" s="26"/>
-      <c r="J58" s="27"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="29"/>
       <c r="L58" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M58" s="28" t="s">
+      <c r="M58" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="N58" s="29"/>
-      <c r="O58" s="29"/>
-      <c r="P58" s="29"/>
-      <c r="Q58" s="29"/>
-      <c r="R58" s="29"/>
-      <c r="S58" s="30"/>
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
+      <c r="P58" s="31"/>
+      <c r="Q58" s="31"/>
+      <c r="R58" s="31"/>
+      <c r="S58" s="32"/>
     </row>
     <row r="60" spans="3:19" ht="30" x14ac:dyDescent="0.25">
       <c r="C60" s="14" t="s">
@@ -2952,59 +3294,59 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D62" s="25" t="s">
+      <c r="D62" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="E62" s="26"/>
-      <c r="F62" s="26"/>
-      <c r="G62" s="26"/>
-      <c r="H62" s="26"/>
-      <c r="I62" s="26"/>
-      <c r="J62" s="27"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
+      <c r="G62" s="28"/>
+      <c r="H62" s="28"/>
+      <c r="I62" s="28"/>
+      <c r="J62" s="29"/>
       <c r="L62" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M62" s="34" t="s">
+      <c r="M62" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="N62" s="34"/>
-      <c r="O62" s="34"/>
-      <c r="P62" s="34"/>
-      <c r="Q62" s="34"/>
-      <c r="R62" s="34"/>
-      <c r="S62" s="34"/>
-    </row>
-    <row r="63" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N62" s="36"/>
+      <c r="O62" s="36"/>
+      <c r="P62" s="36"/>
+      <c r="Q62" s="36"/>
+      <c r="R62" s="36"/>
+      <c r="S62" s="36"/>
+    </row>
+    <row r="63" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C63" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="25" t="s">
+      <c r="D63" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="E63" s="26"/>
-      <c r="F63" s="26"/>
-      <c r="G63" s="26"/>
-      <c r="H63" s="26"/>
-      <c r="I63" s="26"/>
-      <c r="J63" s="27"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
+      <c r="G63" s="28"/>
+      <c r="H63" s="28"/>
+      <c r="I63" s="28"/>
+      <c r="J63" s="29"/>
       <c r="L63" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M63" s="34" t="s">
+      <c r="M63" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="N63" s="34"/>
-      <c r="O63" s="34"/>
-      <c r="P63" s="34"/>
-      <c r="Q63" s="34"/>
-      <c r="R63" s="34"/>
-      <c r="S63" s="34"/>
-    </row>
-    <row r="65" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N63" s="36"/>
+      <c r="O63" s="36"/>
+      <c r="P63" s="36"/>
+      <c r="Q63" s="36"/>
+      <c r="R63" s="36"/>
+      <c r="S63" s="36"/>
+    </row>
+    <row r="65" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C65" s="14" t="s">
         <v>0</v>
       </c>
@@ -3054,7 +3396,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C66" s="14" t="s">
         <v>156</v>
       </c>
@@ -3104,59 +3446,59 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="25" t="s">
+      <c r="D67" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="E67" s="26"/>
-      <c r="F67" s="26"/>
-      <c r="G67" s="26"/>
-      <c r="H67" s="26"/>
-      <c r="I67" s="26"/>
-      <c r="J67" s="27"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="H67" s="28"/>
+      <c r="I67" s="28"/>
+      <c r="J67" s="29"/>
       <c r="L67" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M67" s="28" t="s">
+      <c r="M67" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="N67" s="29"/>
-      <c r="O67" s="29"/>
-      <c r="P67" s="29"/>
-      <c r="Q67" s="29"/>
-      <c r="R67" s="29"/>
-      <c r="S67" s="30"/>
-    </row>
-    <row r="68" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N67" s="31"/>
+      <c r="O67" s="31"/>
+      <c r="P67" s="31"/>
+      <c r="Q67" s="31"/>
+      <c r="R67" s="31"/>
+      <c r="S67" s="32"/>
+    </row>
+    <row r="68" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="25" t="s">
+      <c r="D68" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="E68" s="26"/>
-      <c r="F68" s="26"/>
-      <c r="G68" s="26"/>
-      <c r="H68" s="26"/>
-      <c r="I68" s="26"/>
-      <c r="J68" s="27"/>
+      <c r="E68" s="28"/>
+      <c r="F68" s="28"/>
+      <c r="G68" s="28"/>
+      <c r="H68" s="28"/>
+      <c r="I68" s="28"/>
+      <c r="J68" s="29"/>
       <c r="L68" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M68" s="28" t="s">
+      <c r="M68" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="N68" s="29"/>
-      <c r="O68" s="29"/>
-      <c r="P68" s="29"/>
-      <c r="Q68" s="29"/>
-      <c r="R68" s="29"/>
-      <c r="S68" s="30"/>
-    </row>
-    <row r="70" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N68" s="31"/>
+      <c r="O68" s="31"/>
+      <c r="P68" s="31"/>
+      <c r="Q68" s="31"/>
+      <c r="R68" s="31"/>
+      <c r="S68" s="32"/>
+    </row>
+    <row r="70" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C70" s="14" t="s">
         <v>0</v>
       </c>
@@ -3206,7 +3548,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C71" s="14" t="s">
         <v>160</v>
       </c>
@@ -3256,59 +3598,59 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C72" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="25" t="s">
+      <c r="D72" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="E72" s="26"/>
-      <c r="F72" s="26"/>
-      <c r="G72" s="26"/>
-      <c r="H72" s="26"/>
-      <c r="I72" s="26"/>
-      <c r="J72" s="27"/>
+      <c r="E72" s="28"/>
+      <c r="F72" s="28"/>
+      <c r="G72" s="28"/>
+      <c r="H72" s="28"/>
+      <c r="I72" s="28"/>
+      <c r="J72" s="29"/>
       <c r="L72" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M72" s="28" t="s">
+      <c r="M72" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="N72" s="29"/>
-      <c r="O72" s="29"/>
-      <c r="P72" s="29"/>
-      <c r="Q72" s="29"/>
-      <c r="R72" s="29"/>
-      <c r="S72" s="30"/>
-    </row>
-    <row r="73" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N72" s="31"/>
+      <c r="O72" s="31"/>
+      <c r="P72" s="31"/>
+      <c r="Q72" s="31"/>
+      <c r="R72" s="31"/>
+      <c r="S72" s="32"/>
+    </row>
+    <row r="73" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C73" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="25" t="s">
+      <c r="D73" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="E73" s="26"/>
-      <c r="F73" s="26"/>
-      <c r="G73" s="26"/>
-      <c r="H73" s="26"/>
-      <c r="I73" s="26"/>
-      <c r="J73" s="27"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
+      <c r="G73" s="28"/>
+      <c r="H73" s="28"/>
+      <c r="I73" s="28"/>
+      <c r="J73" s="29"/>
       <c r="L73" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M73" s="34" t="s">
+      <c r="M73" s="36" t="s">
         <v>148</v>
       </c>
-      <c r="N73" s="34"/>
-      <c r="O73" s="34"/>
-      <c r="P73" s="34"/>
-      <c r="Q73" s="34"/>
-      <c r="R73" s="34"/>
-      <c r="S73" s="34"/>
-    </row>
-    <row r="75" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N73" s="36"/>
+      <c r="O73" s="36"/>
+      <c r="P73" s="36"/>
+      <c r="Q73" s="36"/>
+      <c r="R73" s="36"/>
+      <c r="S73" s="36"/>
+    </row>
+    <row r="75" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C75" s="14" t="s">
         <v>0</v>
       </c>
@@ -3358,7 +3700,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C76" s="14" t="s">
         <v>82</v>
       </c>
@@ -3408,81 +3750,81 @@
         <v>60</v>
       </c>
     </row>
-    <row r="77" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C77" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="25" t="s">
+      <c r="D77" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="E77" s="26"/>
-      <c r="F77" s="26"/>
-      <c r="G77" s="26"/>
-      <c r="H77" s="26"/>
-      <c r="I77" s="26"/>
-      <c r="J77" s="27"/>
+      <c r="E77" s="28"/>
+      <c r="F77" s="28"/>
+      <c r="G77" s="28"/>
+      <c r="H77" s="28"/>
+      <c r="I77" s="28"/>
+      <c r="J77" s="29"/>
       <c r="L77" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M77" s="28" t="s">
+      <c r="M77" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="N77" s="29"/>
-      <c r="O77" s="29"/>
-      <c r="P77" s="29"/>
-      <c r="Q77" s="29"/>
-      <c r="R77" s="29"/>
-      <c r="S77" s="30"/>
-    </row>
-    <row r="78" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N77" s="31"/>
+      <c r="O77" s="31"/>
+      <c r="P77" s="31"/>
+      <c r="Q77" s="31"/>
+      <c r="R77" s="31"/>
+      <c r="S77" s="32"/>
+    </row>
+    <row r="78" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C78" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="25" t="s">
+      <c r="D78" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="E78" s="26"/>
-      <c r="F78" s="26"/>
-      <c r="G78" s="26"/>
-      <c r="H78" s="26"/>
-      <c r="I78" s="26"/>
-      <c r="J78" s="27"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="28"/>
+      <c r="G78" s="28"/>
+      <c r="H78" s="28"/>
+      <c r="I78" s="28"/>
+      <c r="J78" s="29"/>
       <c r="L78" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="M78" s="28" t="s">
+      <c r="M78" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="N78" s="29"/>
-      <c r="O78" s="29"/>
-      <c r="P78" s="29"/>
-      <c r="Q78" s="29"/>
-      <c r="R78" s="29"/>
-      <c r="S78" s="30"/>
-    </row>
-    <row r="80" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C80" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="D80" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="E80" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="F80" s="21" t="s">
+      <c r="N78" s="31"/>
+      <c r="O78" s="31"/>
+      <c r="P78" s="31"/>
+      <c r="Q78" s="31"/>
+      <c r="R78" s="31"/>
+      <c r="S78" s="32"/>
+    </row>
+    <row r="80" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C80" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D80" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E80" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F80" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="G80" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="H80" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="I80" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="J80" s="21" t="s">
+      <c r="G80" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="H80" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I80" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="J80" s="25" t="s">
         <v>19</v>
       </c>
       <c r="L80" s="20" t="s">
@@ -3510,30 +3852,30 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C81" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="D81" s="21">
-        <v>2</v>
-      </c>
-      <c r="E81" s="21">
-        <v>1</v>
-      </c>
-      <c r="F81" s="21" t="s">
+    <row r="81" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C81" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="D81" s="25">
+        <v>5</v>
+      </c>
+      <c r="E81" s="25">
+        <v>1</v>
+      </c>
+      <c r="F81" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="G81" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="H81" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="I81" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="J81" s="21">
-        <v>25</v>
+      <c r="G81" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H81" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="25">
+        <v>50</v>
       </c>
       <c r="L81" s="20" t="s">
         <v>98</v>
@@ -3560,84 +3902,84 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C82" s="21" t="s">
+    <row r="82" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C82" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="E82" s="38"/>
-      <c r="F82" s="38"/>
-      <c r="G82" s="38"/>
-      <c r="H82" s="38"/>
-      <c r="I82" s="38"/>
-      <c r="J82" s="38"/>
+      <c r="D82" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="E82" s="28"/>
+      <c r="F82" s="28"/>
+      <c r="G82" s="28"/>
+      <c r="H82" s="28"/>
+      <c r="I82" s="28"/>
+      <c r="J82" s="29"/>
       <c r="L82" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M82" s="28" t="s">
+      <c r="M82" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="N82" s="29"/>
-      <c r="O82" s="29"/>
-      <c r="P82" s="29"/>
-      <c r="Q82" s="29"/>
-      <c r="R82" s="29"/>
-      <c r="S82" s="30"/>
-    </row>
-    <row r="83" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C83" s="21" t="s">
+      <c r="N82" s="31"/>
+      <c r="O82" s="31"/>
+      <c r="P82" s="31"/>
+      <c r="Q82" s="31"/>
+      <c r="R82" s="31"/>
+      <c r="S82" s="32"/>
+    </row>
+    <row r="83" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C83" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D83" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="E83" s="38"/>
-      <c r="F83" s="38"/>
-      <c r="G83" s="38"/>
-      <c r="H83" s="38"/>
-      <c r="I83" s="38"/>
-      <c r="J83" s="38"/>
+      <c r="D83" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="E83" s="28"/>
+      <c r="F83" s="28"/>
+      <c r="G83" s="28"/>
+      <c r="H83" s="28"/>
+      <c r="I83" s="28"/>
+      <c r="J83" s="29"/>
       <c r="L83" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="M83" s="28" t="s">
+      <c r="M83" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="N83" s="29"/>
-      <c r="O83" s="29"/>
-      <c r="P83" s="29"/>
-      <c r="Q83" s="29"/>
-      <c r="R83" s="29"/>
-      <c r="S83" s="30"/>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="N83" s="31"/>
+      <c r="O83" s="31"/>
+      <c r="P83" s="31"/>
+      <c r="Q83" s="31"/>
+      <c r="R83" s="31"/>
+      <c r="S83" s="32"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.3">
       <c r="O84"/>
     </row>
-    <row r="85" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C85" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D85" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E85" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="F85" s="14" t="s">
+    <row r="85" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C85" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D85" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E85" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F85" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="G85" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="H85" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="I85" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="J85" s="14" t="s">
+      <c r="G85" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="H85" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I85" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="J85" s="25" t="s">
         <v>19</v>
       </c>
       <c r="L85" s="20" t="s">
@@ -3665,30 +4007,30 @@
         <v>19</v>
       </c>
     </row>
-    <row r="86" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C86" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D86" s="14">
-        <v>12</v>
-      </c>
-      <c r="E86" s="14">
-        <v>3</v>
-      </c>
-      <c r="F86" s="14" t="s">
+    <row r="86" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C86" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D86" s="25">
+        <v>3</v>
+      </c>
+      <c r="E86" s="25">
+        <v>1</v>
+      </c>
+      <c r="F86" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="G86" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="H86" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="I86" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="J86" s="14">
-        <v>100</v>
+      <c r="G86" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="H86" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I86" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J86" s="25">
+        <v>45</v>
       </c>
       <c r="L86" s="20" t="s">
         <v>99</v>
@@ -3715,59 +4057,59 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C87" s="14" t="s">
+    <row r="87" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C87" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="D87" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="E87" s="26"/>
-      <c r="F87" s="26"/>
-      <c r="G87" s="26"/>
-      <c r="H87" s="26"/>
-      <c r="I87" s="26"/>
-      <c r="J87" s="27"/>
+      <c r="D87" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="E87" s="28"/>
+      <c r="F87" s="28"/>
+      <c r="G87" s="28"/>
+      <c r="H87" s="28"/>
+      <c r="I87" s="28"/>
+      <c r="J87" s="29"/>
       <c r="L87" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M87" s="28" t="s">
+      <c r="M87" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="N87" s="29"/>
-      <c r="O87" s="29"/>
-      <c r="P87" s="29"/>
-      <c r="Q87" s="29"/>
-      <c r="R87" s="29"/>
-      <c r="S87" s="30"/>
-    </row>
-    <row r="88" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C88" s="14" t="s">
+      <c r="N87" s="31"/>
+      <c r="O87" s="31"/>
+      <c r="P87" s="31"/>
+      <c r="Q87" s="31"/>
+      <c r="R87" s="31"/>
+      <c r="S87" s="32"/>
+    </row>
+    <row r="88" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C88" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D88" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="E88" s="26"/>
-      <c r="F88" s="26"/>
-      <c r="G88" s="26"/>
-      <c r="H88" s="26"/>
-      <c r="I88" s="26"/>
-      <c r="J88" s="27"/>
+      <c r="D88" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="E88" s="28"/>
+      <c r="F88" s="28"/>
+      <c r="G88" s="28"/>
+      <c r="H88" s="28"/>
+      <c r="I88" s="28"/>
+      <c r="J88" s="29"/>
       <c r="L88" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="M88" s="28" t="s">
+      <c r="M88" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="N88" s="29"/>
-      <c r="O88" s="29"/>
-      <c r="P88" s="29"/>
-      <c r="Q88" s="29"/>
-      <c r="R88" s="29"/>
-      <c r="S88" s="30"/>
-    </row>
-    <row r="90" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N88" s="31"/>
+      <c r="O88" s="31"/>
+      <c r="P88" s="31"/>
+      <c r="Q88" s="31"/>
+      <c r="R88" s="31"/>
+      <c r="S88" s="32"/>
+    </row>
+    <row r="90" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C90" s="14" t="s">
         <v>0</v>
       </c>
@@ -3817,7 +4159,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="91" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C91" s="14" t="s">
         <v>89</v>
       </c>
@@ -3867,59 +4209,59 @@
         <v>80</v>
       </c>
     </row>
-    <row r="92" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C92" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D92" s="25" t="s">
+      <c r="D92" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="E92" s="26"/>
-      <c r="F92" s="26"/>
-      <c r="G92" s="26"/>
-      <c r="H92" s="26"/>
-      <c r="I92" s="26"/>
-      <c r="J92" s="27"/>
+      <c r="E92" s="28"/>
+      <c r="F92" s="28"/>
+      <c r="G92" s="28"/>
+      <c r="H92" s="28"/>
+      <c r="I92" s="28"/>
+      <c r="J92" s="29"/>
       <c r="L92" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M92" s="28" t="s">
+      <c r="M92" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="N92" s="29"/>
-      <c r="O92" s="29"/>
-      <c r="P92" s="29"/>
-      <c r="Q92" s="29"/>
-      <c r="R92" s="29"/>
-      <c r="S92" s="30"/>
-    </row>
-    <row r="93" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N92" s="31"/>
+      <c r="O92" s="31"/>
+      <c r="P92" s="31"/>
+      <c r="Q92" s="31"/>
+      <c r="R92" s="31"/>
+      <c r="S92" s="32"/>
+    </row>
+    <row r="93" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C93" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="25" t="s">
+      <c r="D93" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="E93" s="26"/>
-      <c r="F93" s="26"/>
-      <c r="G93" s="26"/>
-      <c r="H93" s="26"/>
-      <c r="I93" s="26"/>
-      <c r="J93" s="27"/>
+      <c r="E93" s="28"/>
+      <c r="F93" s="28"/>
+      <c r="G93" s="28"/>
+      <c r="H93" s="28"/>
+      <c r="I93" s="28"/>
+      <c r="J93" s="29"/>
       <c r="L93" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="M93" s="28" t="s">
+      <c r="M93" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="N93" s="29"/>
-      <c r="O93" s="29"/>
-      <c r="P93" s="29"/>
-      <c r="Q93" s="29"/>
-      <c r="R93" s="29"/>
-      <c r="S93" s="30"/>
-    </row>
-    <row r="95" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N93" s="31"/>
+      <c r="O93" s="31"/>
+      <c r="P93" s="31"/>
+      <c r="Q93" s="31"/>
+      <c r="R93" s="31"/>
+      <c r="S93" s="32"/>
+    </row>
+    <row r="95" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C95" s="14" t="s">
         <v>0</v>
       </c>
@@ -3969,7 +4311,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C96" s="14" t="s">
         <v>105</v>
       </c>
@@ -4019,62 +4361,62 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C97" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="25" t="s">
+      <c r="D97" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="E97" s="26"/>
-      <c r="F97" s="26"/>
-      <c r="G97" s="26"/>
-      <c r="H97" s="26"/>
-      <c r="I97" s="26"/>
-      <c r="J97" s="27"/>
+      <c r="E97" s="28"/>
+      <c r="F97" s="28"/>
+      <c r="G97" s="28"/>
+      <c r="H97" s="28"/>
+      <c r="I97" s="28"/>
+      <c r="J97" s="29"/>
       <c r="L97" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M97" s="28" t="s">
+      <c r="M97" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="N97" s="29"/>
-      <c r="O97" s="29"/>
-      <c r="P97" s="29"/>
-      <c r="Q97" s="29"/>
-      <c r="R97" s="29"/>
-      <c r="S97" s="30"/>
-    </row>
-    <row r="98" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N97" s="31"/>
+      <c r="O97" s="31"/>
+      <c r="P97" s="31"/>
+      <c r="Q97" s="31"/>
+      <c r="R97" s="31"/>
+      <c r="S97" s="32"/>
+    </row>
+    <row r="98" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C98" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D98" s="25" t="s">
+      <c r="D98" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="E98" s="26"/>
-      <c r="F98" s="26"/>
-      <c r="G98" s="26"/>
-      <c r="H98" s="26"/>
-      <c r="I98" s="26"/>
-      <c r="J98" s="27"/>
+      <c r="E98" s="28"/>
+      <c r="F98" s="28"/>
+      <c r="G98" s="28"/>
+      <c r="H98" s="28"/>
+      <c r="I98" s="28"/>
+      <c r="J98" s="29"/>
       <c r="L98" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="M98" s="28" t="s">
+      <c r="M98" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="N98" s="29"/>
-      <c r="O98" s="29"/>
-      <c r="P98" s="29"/>
-      <c r="Q98" s="29"/>
-      <c r="R98" s="29"/>
-      <c r="S98" s="30"/>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="N98" s="31"/>
+      <c r="O98" s="31"/>
+      <c r="P98" s="31"/>
+      <c r="Q98" s="31"/>
+      <c r="R98" s="31"/>
+      <c r="S98" s="32"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.3">
       <c r="O99"/>
     </row>
-    <row r="100" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C100" s="14" t="s">
         <v>0</v>
       </c>
@@ -4124,7 +4466,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="101" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C101" s="14" t="s">
         <v>109</v>
       </c>
@@ -4174,62 +4516,62 @@
         <v>40</v>
       </c>
     </row>
-    <row r="102" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C102" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D102" s="25" t="s">
+      <c r="D102" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="E102" s="26"/>
-      <c r="F102" s="26"/>
-      <c r="G102" s="26"/>
-      <c r="H102" s="26"/>
-      <c r="I102" s="26"/>
-      <c r="J102" s="27"/>
+      <c r="E102" s="28"/>
+      <c r="F102" s="28"/>
+      <c r="G102" s="28"/>
+      <c r="H102" s="28"/>
+      <c r="I102" s="28"/>
+      <c r="J102" s="29"/>
       <c r="L102" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M102" s="28" t="s">
+      <c r="M102" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="N102" s="29"/>
-      <c r="O102" s="29"/>
-      <c r="P102" s="29"/>
-      <c r="Q102" s="29"/>
-      <c r="R102" s="29"/>
-      <c r="S102" s="30"/>
-    </row>
-    <row r="103" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N102" s="31"/>
+      <c r="O102" s="31"/>
+      <c r="P102" s="31"/>
+      <c r="Q102" s="31"/>
+      <c r="R102" s="31"/>
+      <c r="S102" s="32"/>
+    </row>
+    <row r="103" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C103" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D103" s="25" t="s">
+      <c r="D103" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="E103" s="26"/>
-      <c r="F103" s="26"/>
-      <c r="G103" s="26"/>
-      <c r="H103" s="26"/>
-      <c r="I103" s="26"/>
-      <c r="J103" s="27"/>
+      <c r="E103" s="28"/>
+      <c r="F103" s="28"/>
+      <c r="G103" s="28"/>
+      <c r="H103" s="28"/>
+      <c r="I103" s="28"/>
+      <c r="J103" s="29"/>
       <c r="L103" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="M103" s="28" t="s">
+      <c r="M103" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="N103" s="29"/>
-      <c r="O103" s="29"/>
-      <c r="P103" s="29"/>
-      <c r="Q103" s="29"/>
-      <c r="R103" s="29"/>
-      <c r="S103" s="30"/>
-    </row>
-    <row r="104" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="N103" s="31"/>
+      <c r="O103" s="31"/>
+      <c r="P103" s="31"/>
+      <c r="Q103" s="31"/>
+      <c r="R103" s="31"/>
+      <c r="S103" s="32"/>
+    </row>
+    <row r="104" spans="3:19" x14ac:dyDescent="0.3">
       <c r="O104"/>
     </row>
-    <row r="105" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C105" s="14" t="s">
         <v>0</v>
       </c>
@@ -4279,7 +4621,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C106" s="14" t="s">
         <v>116</v>
       </c>
@@ -4329,59 +4671,59 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C107" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="25" t="s">
+      <c r="D107" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="E107" s="26"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="26"/>
-      <c r="H107" s="26"/>
-      <c r="I107" s="26"/>
-      <c r="J107" s="27"/>
+      <c r="E107" s="28"/>
+      <c r="F107" s="28"/>
+      <c r="G107" s="28"/>
+      <c r="H107" s="28"/>
+      <c r="I107" s="28"/>
+      <c r="J107" s="29"/>
       <c r="L107" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M107" s="34" t="s">
+      <c r="M107" s="36" t="s">
         <v>176</v>
       </c>
-      <c r="N107" s="34"/>
-      <c r="O107" s="34"/>
-      <c r="P107" s="34"/>
-      <c r="Q107" s="34"/>
-      <c r="R107" s="34"/>
-      <c r="S107" s="34"/>
-    </row>
-    <row r="108" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N107" s="36"/>
+      <c r="O107" s="36"/>
+      <c r="P107" s="36"/>
+      <c r="Q107" s="36"/>
+      <c r="R107" s="36"/>
+      <c r="S107" s="36"/>
+    </row>
+    <row r="108" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C108" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="25" t="s">
+      <c r="D108" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="E108" s="26"/>
-      <c r="F108" s="26"/>
-      <c r="G108" s="26"/>
-      <c r="H108" s="26"/>
-      <c r="I108" s="26"/>
-      <c r="J108" s="27"/>
+      <c r="E108" s="28"/>
+      <c r="F108" s="28"/>
+      <c r="G108" s="28"/>
+      <c r="H108" s="28"/>
+      <c r="I108" s="28"/>
+      <c r="J108" s="29"/>
       <c r="L108" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="M108" s="34" t="s">
+      <c r="M108" s="36" t="s">
         <v>177</v>
       </c>
-      <c r="N108" s="34"/>
-      <c r="O108" s="34"/>
-      <c r="P108" s="34"/>
-      <c r="Q108" s="34"/>
-      <c r="R108" s="34"/>
-      <c r="S108" s="34"/>
-    </row>
-    <row r="110" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N108" s="36"/>
+      <c r="O108" s="36"/>
+      <c r="P108" s="36"/>
+      <c r="Q108" s="36"/>
+      <c r="R108" s="36"/>
+      <c r="S108" s="36"/>
+    </row>
+    <row r="110" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C110" s="14" t="s">
         <v>0</v>
       </c>
@@ -4431,7 +4773,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="111" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C111" s="14" t="s">
         <v>118</v>
       </c>
@@ -4481,59 +4823,59 @@
         <v>30</v>
       </c>
     </row>
-    <row r="112" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C112" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D112" s="25" t="s">
+      <c r="D112" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="E112" s="26"/>
-      <c r="F112" s="26"/>
-      <c r="G112" s="26"/>
-      <c r="H112" s="26"/>
-      <c r="I112" s="26"/>
-      <c r="J112" s="27"/>
+      <c r="E112" s="28"/>
+      <c r="F112" s="28"/>
+      <c r="G112" s="28"/>
+      <c r="H112" s="28"/>
+      <c r="I112" s="28"/>
+      <c r="J112" s="29"/>
       <c r="L112" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M112" s="28" t="s">
+      <c r="M112" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="N112" s="29"/>
-      <c r="O112" s="29"/>
-      <c r="P112" s="29"/>
-      <c r="Q112" s="29"/>
-      <c r="R112" s="29"/>
-      <c r="S112" s="30"/>
-    </row>
-    <row r="113" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N112" s="31"/>
+      <c r="O112" s="31"/>
+      <c r="P112" s="31"/>
+      <c r="Q112" s="31"/>
+      <c r="R112" s="31"/>
+      <c r="S112" s="32"/>
+    </row>
+    <row r="113" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C113" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D113" s="25" t="s">
+      <c r="D113" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="E113" s="26"/>
-      <c r="F113" s="26"/>
-      <c r="G113" s="26"/>
-      <c r="H113" s="26"/>
-      <c r="I113" s="26"/>
-      <c r="J113" s="27"/>
+      <c r="E113" s="28"/>
+      <c r="F113" s="28"/>
+      <c r="G113" s="28"/>
+      <c r="H113" s="28"/>
+      <c r="I113" s="28"/>
+      <c r="J113" s="29"/>
       <c r="L113" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="M113" s="28" t="s">
+      <c r="M113" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="N113" s="29"/>
-      <c r="O113" s="29"/>
-      <c r="P113" s="29"/>
-      <c r="Q113" s="29"/>
-      <c r="R113" s="29"/>
-      <c r="S113" s="30"/>
-    </row>
-    <row r="115" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N113" s="31"/>
+      <c r="O113" s="31"/>
+      <c r="P113" s="31"/>
+      <c r="Q113" s="31"/>
+      <c r="R113" s="31"/>
+      <c r="S113" s="32"/>
+    </row>
+    <row r="115" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C115" s="14" t="s">
         <v>0</v>
       </c>
@@ -4583,7 +4925,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="116" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C116" s="14" t="s">
         <v>121</v>
       </c>
@@ -4633,59 +4975,59 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C117" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D117" s="25" t="s">
+      <c r="D117" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="E117" s="26"/>
-      <c r="F117" s="26"/>
-      <c r="G117" s="26"/>
-      <c r="H117" s="26"/>
-      <c r="I117" s="26"/>
-      <c r="J117" s="27"/>
+      <c r="E117" s="28"/>
+      <c r="F117" s="28"/>
+      <c r="G117" s="28"/>
+      <c r="H117" s="28"/>
+      <c r="I117" s="28"/>
+      <c r="J117" s="29"/>
       <c r="L117" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M117" s="28" t="s">
+      <c r="M117" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="N117" s="29"/>
-      <c r="O117" s="29"/>
-      <c r="P117" s="29"/>
-      <c r="Q117" s="29"/>
-      <c r="R117" s="29"/>
-      <c r="S117" s="30"/>
-    </row>
-    <row r="118" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N117" s="31"/>
+      <c r="O117" s="31"/>
+      <c r="P117" s="31"/>
+      <c r="Q117" s="31"/>
+      <c r="R117" s="31"/>
+      <c r="S117" s="32"/>
+    </row>
+    <row r="118" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C118" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D118" s="25" t="s">
+      <c r="D118" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="E118" s="26"/>
-      <c r="F118" s="26"/>
-      <c r="G118" s="26"/>
-      <c r="H118" s="26"/>
-      <c r="I118" s="26"/>
-      <c r="J118" s="27"/>
+      <c r="E118" s="28"/>
+      <c r="F118" s="28"/>
+      <c r="G118" s="28"/>
+      <c r="H118" s="28"/>
+      <c r="I118" s="28"/>
+      <c r="J118" s="29"/>
       <c r="L118" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="M118" s="28" t="s">
+      <c r="M118" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="N118" s="29"/>
-      <c r="O118" s="29"/>
-      <c r="P118" s="29"/>
-      <c r="Q118" s="29"/>
-      <c r="R118" s="29"/>
-      <c r="S118" s="30"/>
-    </row>
-    <row r="120" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N118" s="31"/>
+      <c r="O118" s="31"/>
+      <c r="P118" s="31"/>
+      <c r="Q118" s="31"/>
+      <c r="R118" s="31"/>
+      <c r="S118" s="32"/>
+    </row>
+    <row r="120" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C120" s="14" t="s">
         <v>0</v>
       </c>
@@ -4735,7 +5077,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="121" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C121" s="12" t="s">
         <v>124</v>
       </c>
@@ -4785,59 +5127,59 @@
         <v>40</v>
       </c>
     </row>
-    <row r="122" spans="3:19" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:19" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C122" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D122" s="25" t="s">
+      <c r="D122" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="E122" s="26"/>
-      <c r="F122" s="26"/>
-      <c r="G122" s="26"/>
-      <c r="H122" s="26"/>
-      <c r="I122" s="26"/>
-      <c r="J122" s="27"/>
+      <c r="E122" s="28"/>
+      <c r="F122" s="28"/>
+      <c r="G122" s="28"/>
+      <c r="H122" s="28"/>
+      <c r="I122" s="28"/>
+      <c r="J122" s="29"/>
       <c r="L122" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="M122" s="34" t="s">
+      <c r="M122" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="N122" s="34"/>
-      <c r="O122" s="34"/>
-      <c r="P122" s="34"/>
-      <c r="Q122" s="34"/>
-      <c r="R122" s="34"/>
-      <c r="S122" s="34"/>
-    </row>
-    <row r="123" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N122" s="36"/>
+      <c r="O122" s="36"/>
+      <c r="P122" s="36"/>
+      <c r="Q122" s="36"/>
+      <c r="R122" s="36"/>
+      <c r="S122" s="36"/>
+    </row>
+    <row r="123" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C123" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D123" s="25" t="s">
+      <c r="D123" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="E123" s="26"/>
-      <c r="F123" s="26"/>
-      <c r="G123" s="26"/>
-      <c r="H123" s="26"/>
-      <c r="I123" s="26"/>
-      <c r="J123" s="27"/>
+      <c r="E123" s="28"/>
+      <c r="F123" s="28"/>
+      <c r="G123" s="28"/>
+      <c r="H123" s="28"/>
+      <c r="I123" s="28"/>
+      <c r="J123" s="29"/>
       <c r="L123" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="M123" s="34" t="s">
+      <c r="M123" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="N123" s="34"/>
-      <c r="O123" s="34"/>
-      <c r="P123" s="34"/>
-      <c r="Q123" s="34"/>
-      <c r="R123" s="34"/>
-      <c r="S123" s="34"/>
-    </row>
-    <row r="125" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N123" s="36"/>
+      <c r="O123" s="36"/>
+      <c r="P123" s="36"/>
+      <c r="Q123" s="36"/>
+      <c r="R123" s="36"/>
+      <c r="S123" s="36"/>
+    </row>
+    <row r="125" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C125" s="14" t="s">
         <v>0</v>
       </c>
@@ -4887,7 +5229,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C126" s="14" t="s">
         <v>129</v>
       </c>
@@ -4937,59 +5279,59 @@
         <v>40</v>
       </c>
     </row>
-    <row r="127" spans="3:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:19" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C127" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D127" s="25" t="s">
+      <c r="D127" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="E127" s="26"/>
-      <c r="F127" s="26"/>
-      <c r="G127" s="26"/>
-      <c r="H127" s="26"/>
-      <c r="I127" s="26"/>
-      <c r="J127" s="27"/>
+      <c r="E127" s="28"/>
+      <c r="F127" s="28"/>
+      <c r="G127" s="28"/>
+      <c r="H127" s="28"/>
+      <c r="I127" s="28"/>
+      <c r="J127" s="29"/>
       <c r="L127" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="M127" s="28" t="s">
+      <c r="M127" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="N127" s="29"/>
-      <c r="O127" s="29"/>
-      <c r="P127" s="29"/>
-      <c r="Q127" s="29"/>
-      <c r="R127" s="29"/>
-      <c r="S127" s="30"/>
-    </row>
-    <row r="128" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N127" s="31"/>
+      <c r="O127" s="31"/>
+      <c r="P127" s="31"/>
+      <c r="Q127" s="31"/>
+      <c r="R127" s="31"/>
+      <c r="S127" s="32"/>
+    </row>
+    <row r="128" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C128" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D128" s="25" t="s">
+      <c r="D128" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E128" s="26"/>
-      <c r="F128" s="26"/>
-      <c r="G128" s="26"/>
-      <c r="H128" s="26"/>
-      <c r="I128" s="26"/>
-      <c r="J128" s="27"/>
+      <c r="E128" s="28"/>
+      <c r="F128" s="28"/>
+      <c r="G128" s="28"/>
+      <c r="H128" s="28"/>
+      <c r="I128" s="28"/>
+      <c r="J128" s="29"/>
       <c r="L128" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="M128" s="28" t="s">
+      <c r="M128" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="N128" s="29"/>
-      <c r="O128" s="29"/>
-      <c r="P128" s="29"/>
-      <c r="Q128" s="29"/>
-      <c r="R128" s="29"/>
-      <c r="S128" s="30"/>
-    </row>
-    <row r="130" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N128" s="31"/>
+      <c r="O128" s="31"/>
+      <c r="P128" s="31"/>
+      <c r="Q128" s="31"/>
+      <c r="R128" s="31"/>
+      <c r="S128" s="32"/>
+    </row>
+    <row r="130" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C130" s="14" t="s">
         <v>0</v>
       </c>
@@ -5039,7 +5381,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="131" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C131" s="14" t="s">
         <v>133</v>
       </c>
@@ -5089,59 +5431,59 @@
         <v>50</v>
       </c>
     </row>
-    <row r="132" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C132" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D132" s="25" t="s">
+      <c r="D132" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="E132" s="26"/>
-      <c r="F132" s="26"/>
-      <c r="G132" s="26"/>
-      <c r="H132" s="26"/>
-      <c r="I132" s="26"/>
-      <c r="J132" s="27"/>
+      <c r="E132" s="28"/>
+      <c r="F132" s="28"/>
+      <c r="G132" s="28"/>
+      <c r="H132" s="28"/>
+      <c r="I132" s="28"/>
+      <c r="J132" s="29"/>
       <c r="L132" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="M132" s="28" t="s">
+      <c r="M132" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="N132" s="29"/>
-      <c r="O132" s="29"/>
-      <c r="P132" s="29"/>
-      <c r="Q132" s="29"/>
-      <c r="R132" s="29"/>
-      <c r="S132" s="30"/>
-    </row>
-    <row r="133" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N132" s="31"/>
+      <c r="O132" s="31"/>
+      <c r="P132" s="31"/>
+      <c r="Q132" s="31"/>
+      <c r="R132" s="31"/>
+      <c r="S132" s="32"/>
+    </row>
+    <row r="133" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C133" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D133" s="25" t="s">
+      <c r="D133" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="E133" s="26"/>
-      <c r="F133" s="26"/>
-      <c r="G133" s="26"/>
-      <c r="H133" s="26"/>
-      <c r="I133" s="26"/>
-      <c r="J133" s="27"/>
+      <c r="E133" s="28"/>
+      <c r="F133" s="28"/>
+      <c r="G133" s="28"/>
+      <c r="H133" s="28"/>
+      <c r="I133" s="28"/>
+      <c r="J133" s="29"/>
       <c r="L133" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="M133" s="28" t="s">
+      <c r="M133" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="N133" s="29"/>
-      <c r="O133" s="29"/>
-      <c r="P133" s="29"/>
-      <c r="Q133" s="29"/>
-      <c r="R133" s="29"/>
-      <c r="S133" s="30"/>
-    </row>
-    <row r="134" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N133" s="31"/>
+      <c r="O133" s="31"/>
+      <c r="P133" s="31"/>
+      <c r="Q133" s="31"/>
+      <c r="R133" s="31"/>
+      <c r="S133" s="32"/>
+    </row>
+    <row r="134" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C134" s="17"/>
       <c r="D134" s="17"/>
       <c r="E134" s="17"/>
@@ -5156,7 +5498,7 @@
       <c r="P134"/>
       <c r="Q134"/>
     </row>
-    <row r="135" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C135" s="14" t="s">
         <v>0</v>
       </c>
@@ -5206,7 +5548,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="136" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C136" s="14" t="s">
         <v>135</v>
       </c>
@@ -5256,59 +5598,59 @@
         <v>50</v>
       </c>
     </row>
-    <row r="137" spans="3:19" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:19" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D137" s="25" t="s">
+      <c r="D137" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="E137" s="26"/>
-      <c r="F137" s="26"/>
-      <c r="G137" s="26"/>
-      <c r="H137" s="26"/>
-      <c r="I137" s="26"/>
-      <c r="J137" s="27"/>
+      <c r="E137" s="28"/>
+      <c r="F137" s="28"/>
+      <c r="G137" s="28"/>
+      <c r="H137" s="28"/>
+      <c r="I137" s="28"/>
+      <c r="J137" s="29"/>
       <c r="L137" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="M137" s="28" t="s">
+      <c r="M137" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="N137" s="29"/>
-      <c r="O137" s="29"/>
-      <c r="P137" s="29"/>
-      <c r="Q137" s="29"/>
-      <c r="R137" s="29"/>
-      <c r="S137" s="30"/>
-    </row>
-    <row r="138" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N137" s="31"/>
+      <c r="O137" s="31"/>
+      <c r="P137" s="31"/>
+      <c r="Q137" s="31"/>
+      <c r="R137" s="31"/>
+      <c r="S137" s="32"/>
+    </row>
+    <row r="138" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C138" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D138" s="25" t="s">
+      <c r="D138" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="E138" s="26"/>
-      <c r="F138" s="26"/>
-      <c r="G138" s="26"/>
-      <c r="H138" s="26"/>
-      <c r="I138" s="26"/>
-      <c r="J138" s="27"/>
+      <c r="E138" s="28"/>
+      <c r="F138" s="28"/>
+      <c r="G138" s="28"/>
+      <c r="H138" s="28"/>
+      <c r="I138" s="28"/>
+      <c r="J138" s="29"/>
       <c r="L138" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="M138" s="28" t="s">
+      <c r="M138" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="N138" s="29"/>
-      <c r="O138" s="29"/>
-      <c r="P138" s="29"/>
-      <c r="Q138" s="29"/>
-      <c r="R138" s="29"/>
-      <c r="S138" s="30"/>
-    </row>
-    <row r="139" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N138" s="31"/>
+      <c r="O138" s="31"/>
+      <c r="P138" s="31"/>
+      <c r="Q138" s="31"/>
+      <c r="R138" s="31"/>
+      <c r="S138" s="32"/>
+    </row>
+    <row r="139" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C139" s="17"/>
       <c r="D139" s="17"/>
       <c r="E139" s="17"/>
@@ -5323,185 +5665,412 @@
       <c r="P139"/>
       <c r="Q139"/>
     </row>
-    <row r="140" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C140" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D140" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E140" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F140" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G140" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="H140" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I140" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="J140" s="25" t="s">
+        <v>19</v>
+      </c>
       <c r="M140"/>
       <c r="N140"/>
       <c r="O140"/>
       <c r="P140"/>
       <c r="Q140"/>
     </row>
-    <row r="141" spans="3:19" ht="47.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="3:19" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C145" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="D145" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="E145" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="F145" s="21" t="s">
+    <row r="141" spans="3:19" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C141" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="D141" s="25">
+        <v>3</v>
+      </c>
+      <c r="E141" s="25">
+        <v>1</v>
+      </c>
+      <c r="F141" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="G141" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="H141" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="I141" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J141" s="25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="142" spans="3:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C142" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D142" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="E142" s="28"/>
+      <c r="F142" s="28"/>
+      <c r="G142" s="28"/>
+      <c r="H142" s="28"/>
+      <c r="I142" s="28"/>
+      <c r="J142" s="29"/>
+    </row>
+    <row r="143" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C143" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D143" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="E143" s="28"/>
+      <c r="F143" s="28"/>
+      <c r="G143" s="28"/>
+      <c r="H143" s="28"/>
+      <c r="I143" s="28"/>
+      <c r="J143" s="29"/>
+    </row>
+    <row r="145" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C145" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D145" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E145" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F145" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="G145" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="H145" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="I145" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="J145" s="21" t="s">
+      <c r="G145" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="H145" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I145" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="J145" s="25" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="146" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C146" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="D146" s="21">
-        <v>5</v>
-      </c>
-      <c r="E146" s="21">
-        <v>1</v>
-      </c>
-      <c r="F146" s="21" t="s">
+    <row r="146" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C146" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="D146" s="25">
+        <v>5</v>
+      </c>
+      <c r="E146" s="25">
+        <v>1</v>
+      </c>
+      <c r="F146" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="G146" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="H146" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I146" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="J146" s="25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="147" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C147" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D147" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="E147" s="28"/>
+      <c r="F147" s="28"/>
+      <c r="G147" s="28"/>
+      <c r="H147" s="28"/>
+      <c r="I147" s="28"/>
+      <c r="J147" s="29"/>
+    </row>
+    <row r="148" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C148" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D148" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="E148" s="28"/>
+      <c r="F148" s="28"/>
+      <c r="G148" s="28"/>
+      <c r="H148" s="28"/>
+      <c r="I148" s="28"/>
+      <c r="J148" s="29"/>
+    </row>
+    <row r="150" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C150" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D150" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E150" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F150" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G150" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="H150" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I150" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="J150" s="25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="151" spans="3:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C151" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="D151" s="25">
+        <v>2</v>
+      </c>
+      <c r="E151" s="25">
+        <v>1</v>
+      </c>
+      <c r="F151" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="G146" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="H146" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="I146" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="J146" s="21">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="147" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C147" s="21" t="s">
+      <c r="G151" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="H151" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I151" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J151" s="25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="152" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C152" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="D147" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="E147" s="26"/>
-      <c r="F147" s="26"/>
-      <c r="G147" s="26"/>
-      <c r="H147" s="26"/>
-      <c r="I147" s="26"/>
-      <c r="J147" s="27"/>
-    </row>
-    <row r="148" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C148" s="21" t="s">
+      <c r="D152" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="E152" s="28"/>
+      <c r="F152" s="28"/>
+      <c r="G152" s="28"/>
+      <c r="H152" s="28"/>
+      <c r="I152" s="28"/>
+      <c r="J152" s="29"/>
+    </row>
+    <row r="153" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C153" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D148" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="E148" s="26"/>
-      <c r="F148" s="26"/>
-      <c r="G148" s="26"/>
-      <c r="H148" s="26"/>
-      <c r="I148" s="26"/>
-      <c r="J148" s="27"/>
-    </row>
-    <row r="150" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C150" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D150" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E150" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="F150" s="14" t="s">
+      <c r="D153" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="E153" s="28"/>
+      <c r="F153" s="28"/>
+      <c r="G153" s="28"/>
+      <c r="H153" s="28"/>
+      <c r="I153" s="28"/>
+      <c r="J153" s="29"/>
+    </row>
+    <row r="155" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C155" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D155" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E155" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F155" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="G150" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="H150" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="I150" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="J150" s="14" t="s">
+      <c r="G155" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="H155" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I155" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="J155" s="25" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="151" spans="3:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D151" s="14">
-        <v>3</v>
-      </c>
-      <c r="E151" s="14">
-        <v>1</v>
-      </c>
-      <c r="F151" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G151" s="14" t="s">
+    <row r="156" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C156" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="D156" s="25">
+        <v>1</v>
+      </c>
+      <c r="E156" s="25">
+        <v>1</v>
+      </c>
+      <c r="F156" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G156" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="H151" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="I151" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="J151" s="14">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="152" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="14" t="s">
+      <c r="H156" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I156" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J156" s="25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C157" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="D152" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="E152" s="26"/>
-      <c r="F152" s="26"/>
-      <c r="G152" s="26"/>
-      <c r="H152" s="26"/>
-      <c r="I152" s="26"/>
-      <c r="J152" s="27"/>
-    </row>
-    <row r="153" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="14" t="s">
+      <c r="D157" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="E157" s="28"/>
+      <c r="F157" s="28"/>
+      <c r="G157" s="28"/>
+      <c r="H157" s="28"/>
+      <c r="I157" s="28"/>
+      <c r="J157" s="29"/>
+    </row>
+    <row r="158" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C158" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D153" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="E153" s="26"/>
-      <c r="F153" s="26"/>
-      <c r="G153" s="26"/>
-      <c r="H153" s="26"/>
-      <c r="I153" s="26"/>
-      <c r="J153" s="27"/>
-    </row>
-    <row r="155" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D158" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="E158" s="28"/>
+      <c r="F158" s="28"/>
+      <c r="G158" s="28"/>
+      <c r="H158" s="28"/>
+      <c r="I158" s="28"/>
+      <c r="J158" s="29"/>
+    </row>
+    <row r="160" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C160" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D160" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E160" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F160" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G160" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="H160" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I160" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="J160" s="25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C161" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="D161" s="25">
+        <v>1</v>
+      </c>
+      <c r="E161" s="25">
+        <v>1</v>
+      </c>
+      <c r="F161" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G161" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="H161" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I161" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J161" s="25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C162" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D162" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="E162" s="26"/>
+      <c r="F162" s="26"/>
+      <c r="G162" s="26"/>
+      <c r="H162" s="26"/>
+      <c r="I162" s="26"/>
+      <c r="J162" s="26"/>
+    </row>
+    <row r="163" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C163" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D163" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="E163" s="26"/>
+      <c r="F163" s="26"/>
+      <c r="G163" s="26"/>
+      <c r="H163" s="26"/>
+      <c r="I163" s="26"/>
+      <c r="J163" s="26"/>
+    </row>
+    <row r="165" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L165"/>
       <c r="M165"/>
       <c r="N165"/>
@@ -5511,7 +6080,7 @@
       <c r="R165"/>
       <c r="S165"/>
     </row>
-    <row r="166" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L166"/>
       <c r="M166"/>
       <c r="N166"/>
@@ -5521,48 +6090,44 @@
       <c r="R166"/>
       <c r="S166"/>
     </row>
-    <row r="167" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L167"/>
-      <c r="M167" s="39"/>
-      <c r="N167" s="39"/>
-      <c r="O167" s="39"/>
-      <c r="P167" s="39"/>
-      <c r="Q167" s="39"/>
-      <c r="R167" s="39"/>
-      <c r="S167" s="39"/>
-    </row>
-    <row r="168" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M167" s="40"/>
+      <c r="N167" s="40"/>
+      <c r="O167" s="40"/>
+      <c r="P167" s="40"/>
+      <c r="Q167" s="40"/>
+      <c r="R167" s="40"/>
+      <c r="S167" s="40"/>
+    </row>
+    <row r="168" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L168"/>
-      <c r="M168" s="39"/>
-      <c r="N168" s="39"/>
-      <c r="O168" s="39"/>
-      <c r="P168" s="39"/>
-      <c r="Q168" s="39"/>
-      <c r="R168" s="39"/>
-      <c r="S168" s="39"/>
-    </row>
-    <row r="170" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="M168" s="40"/>
+      <c r="N168" s="40"/>
+      <c r="O168" s="40"/>
+      <c r="P168" s="40"/>
+      <c r="Q168" s="40"/>
+      <c r="R168" s="40"/>
+      <c r="S168" s="40"/>
+    </row>
+    <row r="170" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="113">
+  <mergeCells count="127">
+    <mergeCell ref="D142:J142"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D162:J162"/>
+    <mergeCell ref="D163:J163"/>
+    <mergeCell ref="D17:J17"/>
+    <mergeCell ref="D18:J18"/>
     <mergeCell ref="D42:J42"/>
     <mergeCell ref="D43:J43"/>
-    <mergeCell ref="M103:S103"/>
-    <mergeCell ref="M98:S98"/>
-    <mergeCell ref="M38:S38"/>
-    <mergeCell ref="M53:S53"/>
-    <mergeCell ref="M62:S62"/>
-    <mergeCell ref="M68:S68"/>
-    <mergeCell ref="M102:S102"/>
-    <mergeCell ref="M63:S63"/>
-    <mergeCell ref="M127:S127"/>
-    <mergeCell ref="M128:S128"/>
     <mergeCell ref="M167:S167"/>
     <mergeCell ref="M168:S168"/>
     <mergeCell ref="D63:J63"/>
@@ -5575,8 +6140,6 @@
     <mergeCell ref="M108:S108"/>
     <mergeCell ref="D82:J82"/>
     <mergeCell ref="D83:J83"/>
-    <mergeCell ref="D147:J147"/>
-    <mergeCell ref="D148:J148"/>
     <mergeCell ref="M112:S112"/>
     <mergeCell ref="M113:S113"/>
     <mergeCell ref="M82:S82"/>
@@ -5585,10 +6148,34 @@
     <mergeCell ref="D128:J128"/>
     <mergeCell ref="M117:S117"/>
     <mergeCell ref="M118:S118"/>
-    <mergeCell ref="D132:J132"/>
-    <mergeCell ref="M92:S92"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="M103:S103"/>
+    <mergeCell ref="M98:S98"/>
+    <mergeCell ref="M68:S68"/>
+    <mergeCell ref="M102:S102"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="M132:S132"/>
+    <mergeCell ref="D72:J72"/>
+    <mergeCell ref="D73:J73"/>
+    <mergeCell ref="D52:J52"/>
+    <mergeCell ref="D53:J53"/>
+    <mergeCell ref="D57:J57"/>
+    <mergeCell ref="D58:J58"/>
+    <mergeCell ref="D62:J62"/>
+    <mergeCell ref="M127:S127"/>
+    <mergeCell ref="M128:S128"/>
+    <mergeCell ref="D37:J37"/>
+    <mergeCell ref="D38:J38"/>
+    <mergeCell ref="M38:S38"/>
+    <mergeCell ref="M53:S53"/>
+    <mergeCell ref="M62:S62"/>
+    <mergeCell ref="M63:S63"/>
+    <mergeCell ref="D47:J47"/>
+    <mergeCell ref="D48:J48"/>
+    <mergeCell ref="M57:S57"/>
+    <mergeCell ref="M58:S58"/>
+    <mergeCell ref="M97:S97"/>
+    <mergeCell ref="M72:S72"/>
+    <mergeCell ref="M73:S73"/>
     <mergeCell ref="V17:AB17"/>
     <mergeCell ref="V18:AB18"/>
     <mergeCell ref="M17:S17"/>
@@ -5599,12 +6186,6 @@
     <mergeCell ref="M27:S27"/>
     <mergeCell ref="M28:S28"/>
     <mergeCell ref="M33:S33"/>
-    <mergeCell ref="D27:J27"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="M132:S132"/>
-    <mergeCell ref="M137:S137"/>
-    <mergeCell ref="M138:S138"/>
-    <mergeCell ref="M22:S22"/>
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="V12:AB12"/>
     <mergeCell ref="V13:AB13"/>
@@ -5614,29 +6195,42 @@
     <mergeCell ref="M13:S13"/>
     <mergeCell ref="V7:AB7"/>
     <mergeCell ref="V8:AB8"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D98:J98"/>
+    <mergeCell ref="D102:J102"/>
+    <mergeCell ref="M87:S87"/>
+    <mergeCell ref="M88:S88"/>
+    <mergeCell ref="M77:S77"/>
+    <mergeCell ref="M78:S78"/>
+    <mergeCell ref="M137:S137"/>
+    <mergeCell ref="M138:S138"/>
+    <mergeCell ref="M22:S22"/>
     <mergeCell ref="M122:S122"/>
     <mergeCell ref="M123:S123"/>
     <mergeCell ref="D32:J32"/>
     <mergeCell ref="D33:J33"/>
-    <mergeCell ref="D87:J87"/>
-    <mergeCell ref="D88:J88"/>
     <mergeCell ref="D92:J92"/>
     <mergeCell ref="D103:J103"/>
     <mergeCell ref="M43:S43"/>
     <mergeCell ref="M47:S47"/>
     <mergeCell ref="M48:S48"/>
     <mergeCell ref="M52:S52"/>
-    <mergeCell ref="D72:J72"/>
-    <mergeCell ref="D73:J73"/>
-    <mergeCell ref="D52:J52"/>
-    <mergeCell ref="D53:J53"/>
-    <mergeCell ref="D57:J57"/>
-    <mergeCell ref="D58:J58"/>
-    <mergeCell ref="D62:J62"/>
-    <mergeCell ref="D47:J47"/>
-    <mergeCell ref="D48:J48"/>
+    <mergeCell ref="D132:J132"/>
+    <mergeCell ref="M92:S92"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="D27:J27"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D158:J158"/>
     <mergeCell ref="D152:J152"/>
     <mergeCell ref="D153:J153"/>
+    <mergeCell ref="D147:J147"/>
+    <mergeCell ref="D148:J148"/>
+    <mergeCell ref="D87:J87"/>
+    <mergeCell ref="D88:J88"/>
     <mergeCell ref="M42:S42"/>
     <mergeCell ref="M93:S93"/>
     <mergeCell ref="M67:S67"/>
@@ -5653,17 +6247,6 @@
     <mergeCell ref="D93:J93"/>
     <mergeCell ref="M133:S133"/>
     <mergeCell ref="D97:J97"/>
-    <mergeCell ref="D98:J98"/>
-    <mergeCell ref="D102:J102"/>
-    <mergeCell ref="M87:S87"/>
-    <mergeCell ref="M88:S88"/>
-    <mergeCell ref="M77:S77"/>
-    <mergeCell ref="M78:S78"/>
-    <mergeCell ref="M57:S57"/>
-    <mergeCell ref="M58:S58"/>
-    <mergeCell ref="M97:S97"/>
-    <mergeCell ref="M72:S72"/>
-    <mergeCell ref="M73:S73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5673,42 +6256,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="35"/>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="35"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-    </row>
-    <row r="4" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="34"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
     </row>
   </sheetData>
@@ -5722,7 +6305,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/Units.xlsx
+++ b/Docs/Units.xlsx
@@ -123,9 +123,6 @@
     <t>Either Astropath or some old psyker model</t>
   </si>
   <si>
-    <t>Knight of corn</t>
-  </si>
-  <si>
     <t>2, normal</t>
   </si>
   <si>
@@ -621,9 +618,6 @@
     <t>The Nurgle sloppity guy</t>
   </si>
   <si>
-    <t>Bombshoom</t>
-  </si>
-  <si>
     <t>Explosive (1)</t>
   </si>
   <si>
@@ -640,6 +634,12 @@
   </si>
   <si>
     <t>Oliokinesis, Oozing</t>
+  </si>
+  <si>
+    <t>Bombshroom</t>
+  </si>
+  <si>
+    <t>Corn knight</t>
   </si>
 </sst>
 </file>
@@ -780,7 +780,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -849,6 +849,31 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -856,13 +881,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
@@ -874,13 +892,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
@@ -890,9 +902,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1225,30 +1234,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
     </row>
     <row r="2" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
+      <c r="A2" s="42"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
     </row>
     <row r="3" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
@@ -1275,28 +1284,28 @@
       <c r="A5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="15" t="s">
+      <c r="C5" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="13" t="s">
         <v>19</v>
       </c>
       <c r="L5" s="6" t="s">
@@ -1352,29 +1361,29 @@
       <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="D6" s="15">
-        <v>2</v>
-      </c>
-      <c r="E6" s="15">
-        <v>1</v>
-      </c>
-      <c r="F6" s="15" t="s">
+      <c r="C6" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" s="13">
+        <v>3</v>
+      </c>
+      <c r="E6" s="13">
+        <v>1</v>
+      </c>
+      <c r="F6" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J6" s="15">
-        <v>20</v>
+      <c r="H6" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" s="13">
+        <v>50</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>26</v>
@@ -1427,86 +1436,86 @@
     </row>
     <row r="7" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="39" t="s">
-        <v>188</v>
-      </c>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
+      <c r="D7" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="35"/>
       <c r="L7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="37" t="s">
+      <c r="M7" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="37"/>
-      <c r="S7" s="37"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="41"/>
       <c r="U7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V7" s="36" t="s">
+      <c r="V7" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="W7" s="36"/>
-      <c r="X7" s="36"/>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="36"/>
-      <c r="AA7" s="36"/>
-      <c r="AB7" s="36"/>
+      <c r="W7" s="40"/>
+      <c r="X7" s="40"/>
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="40"/>
+      <c r="AA7" s="40"/>
+      <c r="AB7" s="40"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="5"/>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
+      <c r="D8" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="35"/>
       <c r="L8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="37" t="s">
+      <c r="M8" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="37"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="41"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="41"/>
       <c r="U8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="36" t="s">
+      <c r="V8" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="W8" s="36"/>
-      <c r="X8" s="36"/>
-      <c r="Y8" s="36"/>
-      <c r="Z8" s="36"/>
-      <c r="AA8" s="36"/>
-      <c r="AB8" s="36"/>
+      <c r="W8" s="40"/>
+      <c r="X8" s="40"/>
+      <c r="Y8" s="40"/>
+      <c r="Z8" s="40"/>
+      <c r="AA8" s="40"/>
+      <c r="AB8" s="40"/>
     </row>
     <row r="9" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
       <c r="O9"/>
@@ -1588,7 +1597,7 @@
     </row>
     <row r="11" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D11" s="15">
         <v>3</v>
@@ -1597,13 +1606,13 @@
         <v>1</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G11" s="15" t="s">
         <v>7</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>8</v>
@@ -1636,7 +1645,7 @@
         <v>50</v>
       </c>
       <c r="U11" s="20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V11" s="2">
         <v>3</v>
@@ -1664,77 +1673,77 @@
       <c r="C12" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="35"/>
+      <c r="D12" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="32"/>
       <c r="L12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="37" t="s">
+      <c r="M12" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
-      <c r="S12" s="37"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="41"/>
+      <c r="P12" s="41"/>
+      <c r="Q12" s="41"/>
+      <c r="R12" s="41"/>
+      <c r="S12" s="41"/>
       <c r="U12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V12" s="36" t="s">
+      <c r="V12" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="W12" s="36"/>
-      <c r="X12" s="36"/>
-      <c r="Y12" s="36"/>
-      <c r="Z12" s="36"/>
-      <c r="AA12" s="36"/>
-      <c r="AB12" s="36"/>
+      <c r="W12" s="40"/>
+      <c r="X12" s="40"/>
+      <c r="Y12" s="40"/>
+      <c r="Z12" s="40"/>
+      <c r="AA12" s="40"/>
+      <c r="AB12" s="40"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="C13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="33" t="s">
-        <v>191</v>
-      </c>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="35"/>
+      <c r="D13" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="32"/>
       <c r="L13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="37" t="s">
+      <c r="M13" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
-      <c r="S13" s="37"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="41"/>
+      <c r="Q13" s="41"/>
+      <c r="R13" s="41"/>
+      <c r="S13" s="41"/>
       <c r="U13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V13" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="W13" s="36"/>
-      <c r="X13" s="36"/>
-      <c r="Y13" s="36"/>
-      <c r="Z13" s="36"/>
-      <c r="AA13" s="36"/>
-      <c r="AB13" s="36"/>
+      <c r="V13" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="W13" s="40"/>
+      <c r="X13" s="40"/>
+      <c r="Y13" s="40"/>
+      <c r="Z13" s="40"/>
+      <c r="AA13" s="40"/>
+      <c r="AB13" s="40"/>
     </row>
     <row r="14" spans="1:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O14"/>
@@ -1816,7 +1825,7 @@
     </row>
     <row r="16" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="C16" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D16" s="15">
         <v>3</v>
@@ -1825,7 +1834,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G16" s="15" t="s">
         <v>7</v>
@@ -1892,77 +1901,77 @@
       <c r="C17" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
+      <c r="D17" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
       <c r="L17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="37" t="s">
+      <c r="M17" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
-      <c r="S17" s="37"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="41"/>
+      <c r="P17" s="41"/>
+      <c r="Q17" s="41"/>
+      <c r="R17" s="41"/>
+      <c r="S17" s="41"/>
       <c r="U17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V17" s="36" t="s">
+      <c r="V17" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="W17" s="36"/>
-      <c r="X17" s="36"/>
-      <c r="Y17" s="36"/>
-      <c r="Z17" s="36"/>
-      <c r="AA17" s="36"/>
-      <c r="AB17" s="36"/>
+      <c r="W17" s="40"/>
+      <c r="X17" s="40"/>
+      <c r="Y17" s="40"/>
+      <c r="Z17" s="40"/>
+      <c r="AA17" s="40"/>
+      <c r="AB17" s="40"/>
     </row>
     <row r="18" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
+      <c r="D18" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
       <c r="L18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="37" t="s">
+      <c r="M18" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
-      <c r="S18" s="37"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="41"/>
+      <c r="P18" s="41"/>
+      <c r="Q18" s="41"/>
+      <c r="R18" s="41"/>
+      <c r="S18" s="41"/>
       <c r="U18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V18" s="36" t="s">
+      <c r="V18" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="W18" s="36"/>
-      <c r="X18" s="36"/>
-      <c r="Y18" s="36"/>
-      <c r="Z18" s="36"/>
-      <c r="AA18" s="36"/>
-      <c r="AB18" s="36"/>
+      <c r="W18" s="40"/>
+      <c r="X18" s="40"/>
+      <c r="Y18" s="40"/>
+      <c r="Z18" s="40"/>
+      <c r="AA18" s="40"/>
+      <c r="AB18" s="40"/>
     </row>
     <row r="19" spans="3:28" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C19" s="16"/>
@@ -1976,28 +1985,28 @@
       <c r="O19"/>
     </row>
     <row r="20" spans="3:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="C20" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J20" s="15" t="s">
+      <c r="C20" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="26" t="s">
         <v>19</v>
       </c>
       <c r="L20" s="6" t="s">
@@ -2026,32 +2035,32 @@
       </c>
     </row>
     <row r="21" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="D21" s="15">
-        <v>2</v>
-      </c>
-      <c r="E21" s="15">
-        <v>1</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="15" t="s">
+      <c r="C21" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="D21" s="26">
+        <v>2</v>
+      </c>
+      <c r="E21" s="26">
+        <v>1</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J21" s="15">
+      <c r="H21" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="26">
         <v>25</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>35</v>
+        <v>207</v>
       </c>
       <c r="M21" s="6">
         <v>3</v>
@@ -2063,10 +2072,10 @@
         <v>21</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>8</v>
@@ -2076,56 +2085,56 @@
       </c>
     </row>
     <row r="22" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="33" t="s">
-        <v>184</v>
-      </c>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="35"/>
+      <c r="D22" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
       <c r="L22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="37"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="37"/>
-      <c r="S22" s="37"/>
+      <c r="M22" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="N22" s="41"/>
+      <c r="O22" s="41"/>
+      <c r="P22" s="41"/>
+      <c r="Q22" s="41"/>
+      <c r="R22" s="41"/>
+      <c r="S22" s="41"/>
     </row>
     <row r="23" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="35"/>
+      <c r="D23" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
       <c r="L23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="N23" s="37"/>
-      <c r="O23" s="37"/>
-      <c r="P23" s="37"/>
-      <c r="Q23" s="37"/>
-      <c r="R23" s="37"/>
-      <c r="S23" s="37"/>
+      <c r="M23" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="N23" s="41"/>
+      <c r="O23" s="41"/>
+      <c r="P23" s="41"/>
+      <c r="Q23" s="41"/>
+      <c r="R23" s="41"/>
+      <c r="S23" s="41"/>
     </row>
     <row r="25" spans="3:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="15" t="s">
@@ -2179,7 +2188,7 @@
     </row>
     <row r="26" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D26" s="15">
         <v>6</v>
@@ -2188,7 +2197,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G26" s="15" t="s">
         <v>29</v>
@@ -2197,13 +2206,13 @@
         <v>8</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J26" s="15">
         <v>50</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M26" s="6">
         <v>5</v>
@@ -2221,7 +2230,7 @@
         <v>8</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S26" s="6">
         <v>60</v>
@@ -2231,77 +2240,77 @@
       <c r="C27" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="35"/>
+      <c r="D27" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="32"/>
       <c r="L27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M27" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="N27" s="37"/>
-      <c r="O27" s="37"/>
-      <c r="P27" s="37"/>
-      <c r="Q27" s="37"/>
-      <c r="R27" s="37"/>
-      <c r="S27" s="37"/>
+      <c r="M27" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="N27" s="41"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="41"/>
+      <c r="S27" s="41"/>
     </row>
     <row r="28" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="35"/>
+      <c r="D28" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="32"/>
       <c r="L28" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M28" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="N28" s="29"/>
-      <c r="O28" s="29"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-    </row>
-    <row r="30" spans="3:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I30" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J30" s="15" t="s">
+      <c r="M28" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="N28" s="39"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="39"/>
+      <c r="R28" s="39"/>
+      <c r="S28" s="39"/>
+    </row>
+    <row r="30" spans="3:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="J30" s="13" t="s">
         <v>19</v>
       </c>
       <c r="L30" s="11" t="s">
@@ -2329,42 +2338,42 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="D31" s="15">
-        <v>6</v>
-      </c>
-      <c r="E31" s="15">
-        <v>1</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="H31" s="15">
-        <v>0</v>
-      </c>
-      <c r="I31" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="J31" s="15">
-        <v>50</v>
+    <row r="31" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="13">
+        <v>3</v>
+      </c>
+      <c r="E31" s="13">
+        <v>1</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J31" s="13">
+        <v>60</v>
       </c>
       <c r="L31" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M31" s="11">
+        <v>3</v>
+      </c>
+      <c r="N31" s="11">
+        <v>1</v>
+      </c>
+      <c r="O31" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="M31" s="11">
-        <v>3</v>
-      </c>
-      <c r="N31" s="11">
-        <v>1</v>
-      </c>
-      <c r="O31" s="11" t="s">
-        <v>45</v>
       </c>
       <c r="P31" s="11" t="s">
         <v>7</v>
@@ -2379,12 +2388,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="3:28" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="15" t="s">
+    <row r="32" spans="3:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="13" t="s">
         <v>11</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="E32" s="34"/>
       <c r="F32" s="34"/>
@@ -2395,22 +2404,22 @@
       <c r="L32" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M32" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="32"/>
-    </row>
-    <row r="33" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="15" t="s">
+      <c r="M32" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="N32" s="37"/>
+      <c r="O32" s="37"/>
+      <c r="P32" s="37"/>
+      <c r="Q32" s="37"/>
+      <c r="R32" s="37"/>
+      <c r="S32" s="38"/>
+    </row>
+    <row r="33" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="E33" s="34"/>
       <c r="F33" s="34"/>
@@ -2421,15 +2430,15 @@
       <c r="L33" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M33" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="31"/>
-      <c r="Q33" s="31"/>
-      <c r="R33" s="31"/>
-      <c r="S33" s="32"/>
+      <c r="M33" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="N33" s="37"/>
+      <c r="O33" s="37"/>
+      <c r="P33" s="37"/>
+      <c r="Q33" s="37"/>
+      <c r="R33" s="37"/>
+      <c r="S33" s="38"/>
     </row>
     <row r="35" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="15" t="s">
@@ -2483,7 +2492,7 @@
     </row>
     <row r="36" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D36" s="15">
         <v>2</v>
@@ -2507,7 +2516,7 @@
         <v>25</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M36" s="11">
         <v>3</v>
@@ -2525,7 +2534,7 @@
         <v>8</v>
       </c>
       <c r="R36" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S36" s="11">
         <v>50</v>
@@ -2535,53 +2544,53 @@
       <c r="C37" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="39" t="s">
-        <v>185</v>
-      </c>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="39"/>
-      <c r="H37" s="39"/>
-      <c r="I37" s="39"/>
-      <c r="J37" s="39"/>
+      <c r="D37" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
       <c r="L37" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M37" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="N37" s="31"/>
-      <c r="O37" s="31"/>
-      <c r="P37" s="31"/>
-      <c r="Q37" s="31"/>
-      <c r="R37" s="31"/>
-      <c r="S37" s="32"/>
+      <c r="M37" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="N37" s="37"/>
+      <c r="O37" s="37"/>
+      <c r="P37" s="37"/>
+      <c r="Q37" s="37"/>
+      <c r="R37" s="37"/>
+      <c r="S37" s="38"/>
     </row>
     <row r="38" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="39" t="s">
-        <v>178</v>
-      </c>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="39"/>
+      <c r="D38" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="28"/>
       <c r="L38" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M38" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="N38" s="29"/>
-      <c r="O38" s="29"/>
-      <c r="P38" s="29"/>
-      <c r="Q38" s="29"/>
-      <c r="R38" s="29"/>
-      <c r="S38" s="29"/>
+      <c r="M38" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="N38" s="39"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="39"/>
+      <c r="Q38" s="39"/>
+      <c r="R38" s="39"/>
+      <c r="S38" s="39"/>
     </row>
     <row r="40" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="15" t="s">
@@ -2635,7 +2644,7 @@
     </row>
     <row r="41" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D41" s="15">
         <v>3</v>
@@ -2653,13 +2662,13 @@
         <v>8</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J41" s="15">
         <v>35</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M41" s="11">
         <v>2</v>
@@ -2687,53 +2696,53 @@
       <c r="C42" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D42" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="35"/>
+      <c r="D42" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="32"/>
       <c r="L42" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M42" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="N42" s="31"/>
-      <c r="O42" s="31"/>
-      <c r="P42" s="31"/>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="31"/>
-      <c r="S42" s="32"/>
+      <c r="M42" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="N42" s="37"/>
+      <c r="O42" s="37"/>
+      <c r="P42" s="37"/>
+      <c r="Q42" s="37"/>
+      <c r="R42" s="37"/>
+      <c r="S42" s="38"/>
     </row>
     <row r="43" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-      <c r="J43" s="35"/>
+      <c r="D43" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="32"/>
       <c r="L43" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M43" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="N43" s="31"/>
-      <c r="O43" s="31"/>
-      <c r="P43" s="31"/>
-      <c r="Q43" s="31"/>
-      <c r="R43" s="31"/>
-      <c r="S43" s="32"/>
+      <c r="M43" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="N43" s="37"/>
+      <c r="O43" s="37"/>
+      <c r="P43" s="37"/>
+      <c r="Q43" s="37"/>
+      <c r="R43" s="37"/>
+      <c r="S43" s="38"/>
     </row>
     <row r="45" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="13" t="s">
@@ -2786,32 +2795,32 @@
       </c>
     </row>
     <row r="46" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="13" t="s">
-        <v>116</v>
+      <c r="C46" s="12" t="s">
+        <v>123</v>
       </c>
       <c r="D46" s="13">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E46" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="13" t="s">
         <v>21</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="I46" s="13" t="s">
         <v>8</v>
       </c>
       <c r="J46" s="13">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="L46" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M46" s="11">
         <v>3</v>
@@ -2826,7 +2835,7 @@
         <v>7</v>
       </c>
       <c r="Q46" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R46" s="11" t="s">
         <v>8</v>
@@ -2839,53 +2848,53 @@
       <c r="C47" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="25"/>
-      <c r="I47" s="25"/>
-      <c r="J47" s="26"/>
+      <c r="D47" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="34"/>
+      <c r="H47" s="34"/>
+      <c r="I47" s="34"/>
+      <c r="J47" s="35"/>
       <c r="L47" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="N47" s="31"/>
-      <c r="O47" s="31"/>
-      <c r="P47" s="31"/>
-      <c r="Q47" s="31"/>
-      <c r="R47" s="31"/>
-      <c r="S47" s="32"/>
+      <c r="M47" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="N47" s="37"/>
+      <c r="O47" s="37"/>
+      <c r="P47" s="37"/>
+      <c r="Q47" s="37"/>
+      <c r="R47" s="37"/>
+      <c r="S47" s="38"/>
     </row>
     <row r="48" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25"/>
-      <c r="H48" s="25"/>
-      <c r="I48" s="25"/>
-      <c r="J48" s="26"/>
+      <c r="D48" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E48" s="34"/>
+      <c r="F48" s="34"/>
+      <c r="G48" s="34"/>
+      <c r="H48" s="34"/>
+      <c r="I48" s="34"/>
+      <c r="J48" s="35"/>
       <c r="L48" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M48" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="N48" s="31"/>
-      <c r="O48" s="31"/>
-      <c r="P48" s="31"/>
-      <c r="Q48" s="31"/>
-      <c r="R48" s="31"/>
-      <c r="S48" s="32"/>
+      <c r="M48" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="N48" s="37"/>
+      <c r="O48" s="37"/>
+      <c r="P48" s="37"/>
+      <c r="Q48" s="37"/>
+      <c r="R48" s="37"/>
+      <c r="S48" s="38"/>
     </row>
     <row r="50" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="13" t="s">
@@ -2939,7 +2948,7 @@
     </row>
     <row r="51" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D51" s="13">
         <v>3</v>
@@ -2954,16 +2963,16 @@
         <v>7</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J51" s="13">
         <v>35</v>
       </c>
       <c r="L51" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M51" s="11">
         <v>2</v>
@@ -2991,53 +3000,53 @@
       <c r="C52" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D52" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E52" s="25"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="25"/>
-      <c r="H52" s="25"/>
-      <c r="I52" s="25"/>
-      <c r="J52" s="26"/>
+      <c r="D52" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="E52" s="34"/>
+      <c r="F52" s="34"/>
+      <c r="G52" s="34"/>
+      <c r="H52" s="34"/>
+      <c r="I52" s="34"/>
+      <c r="J52" s="35"/>
       <c r="L52" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M52" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="N52" s="29"/>
-      <c r="O52" s="29"/>
-      <c r="P52" s="29"/>
-      <c r="Q52" s="29"/>
-      <c r="R52" s="29"/>
-      <c r="S52" s="29"/>
+      <c r="M52" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="N52" s="39"/>
+      <c r="O52" s="39"/>
+      <c r="P52" s="39"/>
+      <c r="Q52" s="39"/>
+      <c r="R52" s="39"/>
+      <c r="S52" s="39"/>
     </row>
     <row r="53" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="E53" s="25"/>
-      <c r="F53" s="25"/>
-      <c r="G53" s="25"/>
-      <c r="H53" s="25"/>
-      <c r="I53" s="25"/>
-      <c r="J53" s="26"/>
+      <c r="D53" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="34"/>
+      <c r="I53" s="34"/>
+      <c r="J53" s="35"/>
       <c r="L53" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M53" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="N53" s="29"/>
-      <c r="O53" s="29"/>
-      <c r="P53" s="29"/>
-      <c r="Q53" s="29"/>
-      <c r="R53" s="29"/>
-      <c r="S53" s="29"/>
+      <c r="M53" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="N53" s="39"/>
+      <c r="O53" s="39"/>
+      <c r="P53" s="39"/>
+      <c r="Q53" s="39"/>
+      <c r="R53" s="39"/>
+      <c r="S53" s="39"/>
     </row>
     <row r="55" spans="3:19" ht="30" x14ac:dyDescent="0.25">
       <c r="C55" s="13" t="s">
@@ -3091,7 +3100,7 @@
     </row>
     <row r="56" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C56" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D56" s="13">
         <v>3</v>
@@ -3109,13 +3118,13 @@
         <v>8</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J56" s="13">
         <v>30</v>
       </c>
       <c r="L56" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M56" s="17">
         <v>3</v>
@@ -3143,53 +3152,53 @@
       <c r="C57" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="E57" s="25"/>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25"/>
-      <c r="H57" s="25"/>
-      <c r="I57" s="25"/>
-      <c r="J57" s="26"/>
+      <c r="D57" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="E57" s="34"/>
+      <c r="F57" s="34"/>
+      <c r="G57" s="34"/>
+      <c r="H57" s="34"/>
+      <c r="I57" s="34"/>
+      <c r="J57" s="35"/>
       <c r="L57" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M57" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="N57" s="31"/>
-      <c r="O57" s="31"/>
-      <c r="P57" s="31"/>
-      <c r="Q57" s="31"/>
-      <c r="R57" s="31"/>
-      <c r="S57" s="32"/>
+      <c r="M57" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="N57" s="37"/>
+      <c r="O57" s="37"/>
+      <c r="P57" s="37"/>
+      <c r="Q57" s="37"/>
+      <c r="R57" s="37"/>
+      <c r="S57" s="38"/>
     </row>
     <row r="58" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C58" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="E58" s="25"/>
-      <c r="F58" s="25"/>
-      <c r="G58" s="25"/>
-      <c r="H58" s="25"/>
-      <c r="I58" s="25"/>
-      <c r="J58" s="26"/>
+      <c r="D58" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="E58" s="34"/>
+      <c r="F58" s="34"/>
+      <c r="G58" s="34"/>
+      <c r="H58" s="34"/>
+      <c r="I58" s="34"/>
+      <c r="J58" s="35"/>
       <c r="L58" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M58" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="N58" s="31"/>
-      <c r="O58" s="31"/>
-      <c r="P58" s="31"/>
-      <c r="Q58" s="31"/>
-      <c r="R58" s="31"/>
-      <c r="S58" s="32"/>
+      <c r="M58" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="N58" s="37"/>
+      <c r="O58" s="37"/>
+      <c r="P58" s="37"/>
+      <c r="Q58" s="37"/>
+      <c r="R58" s="37"/>
+      <c r="S58" s="38"/>
     </row>
     <row r="60" spans="3:19" ht="30" x14ac:dyDescent="0.25">
       <c r="C60" s="13" t="s">
@@ -3243,7 +3252,7 @@
     </row>
     <row r="61" spans="3:19" ht="45" x14ac:dyDescent="0.25">
       <c r="C61" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D61" s="13">
         <v>3</v>
@@ -3252,7 +3261,7 @@
         <v>1</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G61" s="13" t="s">
         <v>7</v>
@@ -3267,7 +3276,7 @@
         <v>30</v>
       </c>
       <c r="L61" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M61" s="17">
         <v>2</v>
@@ -3285,7 +3294,7 @@
         <v>8</v>
       </c>
       <c r="R61" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S61" s="17">
         <v>60</v>
@@ -3295,53 +3304,53 @@
       <c r="C62" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D62" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="E62" s="25"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
-      <c r="H62" s="25"/>
-      <c r="I62" s="25"/>
-      <c r="J62" s="26"/>
+      <c r="D62" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="E62" s="34"/>
+      <c r="F62" s="34"/>
+      <c r="G62" s="34"/>
+      <c r="H62" s="34"/>
+      <c r="I62" s="34"/>
+      <c r="J62" s="35"/>
       <c r="L62" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M62" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="N62" s="29"/>
-      <c r="O62" s="29"/>
-      <c r="P62" s="29"/>
-      <c r="Q62" s="29"/>
-      <c r="R62" s="29"/>
-      <c r="S62" s="29"/>
+      <c r="M62" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="N62" s="39"/>
+      <c r="O62" s="39"/>
+      <c r="P62" s="39"/>
+      <c r="Q62" s="39"/>
+      <c r="R62" s="39"/>
+      <c r="S62" s="39"/>
     </row>
     <row r="63" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
-      <c r="H63" s="25"/>
-      <c r="I63" s="25"/>
-      <c r="J63" s="26"/>
+      <c r="D63" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="E63" s="34"/>
+      <c r="F63" s="34"/>
+      <c r="G63" s="34"/>
+      <c r="H63" s="34"/>
+      <c r="I63" s="34"/>
+      <c r="J63" s="35"/>
       <c r="L63" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M63" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="N63" s="29"/>
-      <c r="O63" s="29"/>
-      <c r="P63" s="29"/>
-      <c r="Q63" s="29"/>
-      <c r="R63" s="29"/>
-      <c r="S63" s="29"/>
+      <c r="M63" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="N63" s="39"/>
+      <c r="O63" s="39"/>
+      <c r="P63" s="39"/>
+      <c r="Q63" s="39"/>
+      <c r="R63" s="39"/>
+      <c r="S63" s="39"/>
     </row>
     <row r="65" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="13" t="s">
@@ -3395,7 +3404,7 @@
     </row>
     <row r="66" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D66" s="13">
         <v>4</v>
@@ -3413,13 +3422,13 @@
         <v>8</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J66" s="13">
         <v>40</v>
       </c>
       <c r="L66" s="18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M66" s="18">
         <v>3</v>
@@ -3428,13 +3437,13 @@
         <v>1</v>
       </c>
       <c r="O66" s="18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P66" s="18" t="s">
         <v>7</v>
       </c>
       <c r="Q66" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R66" s="18" t="s">
         <v>8</v>
@@ -3447,53 +3456,53 @@
       <c r="C67" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="E67" s="25"/>
-      <c r="F67" s="25"/>
-      <c r="G67" s="25"/>
-      <c r="H67" s="25"/>
-      <c r="I67" s="25"/>
-      <c r="J67" s="26"/>
+      <c r="D67" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="E67" s="34"/>
+      <c r="F67" s="34"/>
+      <c r="G67" s="34"/>
+      <c r="H67" s="34"/>
+      <c r="I67" s="34"/>
+      <c r="J67" s="35"/>
       <c r="L67" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M67" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="N67" s="31"/>
-      <c r="O67" s="31"/>
-      <c r="P67" s="31"/>
-      <c r="Q67" s="31"/>
-      <c r="R67" s="31"/>
-      <c r="S67" s="32"/>
+      <c r="M67" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="N67" s="37"/>
+      <c r="O67" s="37"/>
+      <c r="P67" s="37"/>
+      <c r="Q67" s="37"/>
+      <c r="R67" s="37"/>
+      <c r="S67" s="38"/>
     </row>
     <row r="68" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="E68" s="25"/>
-      <c r="F68" s="25"/>
-      <c r="G68" s="25"/>
-      <c r="H68" s="25"/>
-      <c r="I68" s="25"/>
-      <c r="J68" s="26"/>
+      <c r="D68" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="E68" s="34"/>
+      <c r="F68" s="34"/>
+      <c r="G68" s="34"/>
+      <c r="H68" s="34"/>
+      <c r="I68" s="34"/>
+      <c r="J68" s="35"/>
       <c r="L68" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M68" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="N68" s="31"/>
-      <c r="O68" s="31"/>
-      <c r="P68" s="31"/>
-      <c r="Q68" s="31"/>
-      <c r="R68" s="31"/>
-      <c r="S68" s="32"/>
+      <c r="M68" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="N68" s="37"/>
+      <c r="O68" s="37"/>
+      <c r="P68" s="37"/>
+      <c r="Q68" s="37"/>
+      <c r="R68" s="37"/>
+      <c r="S68" s="38"/>
     </row>
     <row r="70" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="13" t="s">
@@ -3547,7 +3556,7 @@
     </row>
     <row r="71" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D71" s="13">
         <v>3</v>
@@ -3562,7 +3571,7 @@
         <v>7</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I71" s="13" t="s">
         <v>24</v>
@@ -3571,7 +3580,7 @@
         <v>30</v>
       </c>
       <c r="L71" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M71" s="18">
         <v>2</v>
@@ -3580,13 +3589,13 @@
         <v>1</v>
       </c>
       <c r="O71" s="18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P71" s="18" t="s">
         <v>7</v>
       </c>
       <c r="Q71" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R71" s="18" t="s">
         <v>8</v>
@@ -3599,53 +3608,53 @@
       <c r="C72" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="E72" s="25"/>
-      <c r="F72" s="25"/>
-      <c r="G72" s="25"/>
-      <c r="H72" s="25"/>
-      <c r="I72" s="25"/>
-      <c r="J72" s="26"/>
+      <c r="D72" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="E72" s="34"/>
+      <c r="F72" s="34"/>
+      <c r="G72" s="34"/>
+      <c r="H72" s="34"/>
+      <c r="I72" s="34"/>
+      <c r="J72" s="35"/>
       <c r="L72" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M72" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="N72" s="31"/>
-      <c r="O72" s="31"/>
-      <c r="P72" s="31"/>
-      <c r="Q72" s="31"/>
-      <c r="R72" s="31"/>
-      <c r="S72" s="32"/>
+      <c r="M72" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="N72" s="37"/>
+      <c r="O72" s="37"/>
+      <c r="P72" s="37"/>
+      <c r="Q72" s="37"/>
+      <c r="R72" s="37"/>
+      <c r="S72" s="38"/>
     </row>
     <row r="73" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="25"/>
-      <c r="H73" s="25"/>
-      <c r="I73" s="25"/>
-      <c r="J73" s="26"/>
+      <c r="D73" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="E73" s="34"/>
+      <c r="F73" s="34"/>
+      <c r="G73" s="34"/>
+      <c r="H73" s="34"/>
+      <c r="I73" s="34"/>
+      <c r="J73" s="35"/>
       <c r="L73" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M73" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="N73" s="29"/>
-      <c r="O73" s="29"/>
-      <c r="P73" s="29"/>
-      <c r="Q73" s="29"/>
-      <c r="R73" s="29"/>
-      <c r="S73" s="29"/>
+      <c r="M73" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="N73" s="39"/>
+      <c r="O73" s="39"/>
+      <c r="P73" s="39"/>
+      <c r="Q73" s="39"/>
+      <c r="R73" s="39"/>
+      <c r="S73" s="39"/>
     </row>
     <row r="75" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="13" t="s">
@@ -3699,7 +3708,7 @@
     </row>
     <row r="76" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C76" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D76" s="13">
         <v>2</v>
@@ -3723,7 +3732,7 @@
         <v>40</v>
       </c>
       <c r="L76" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M76" s="19">
         <v>4</v>
@@ -3732,7 +3741,7 @@
         <v>1</v>
       </c>
       <c r="O76" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P76" s="19" t="s">
         <v>7</v>
@@ -3741,7 +3750,7 @@
         <v>8</v>
       </c>
       <c r="R76" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="S76" s="19">
         <v>60</v>
@@ -3751,53 +3760,53 @@
       <c r="C77" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="E77" s="25"/>
-      <c r="F77" s="25"/>
-      <c r="G77" s="25"/>
-      <c r="H77" s="25"/>
-      <c r="I77" s="25"/>
-      <c r="J77" s="26"/>
+      <c r="D77" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="E77" s="34"/>
+      <c r="F77" s="34"/>
+      <c r="G77" s="34"/>
+      <c r="H77" s="34"/>
+      <c r="I77" s="34"/>
+      <c r="J77" s="35"/>
       <c r="L77" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M77" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="N77" s="31"/>
-      <c r="O77" s="31"/>
-      <c r="P77" s="31"/>
-      <c r="Q77" s="31"/>
-      <c r="R77" s="31"/>
-      <c r="S77" s="32"/>
+      <c r="M77" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="N77" s="37"/>
+      <c r="O77" s="37"/>
+      <c r="P77" s="37"/>
+      <c r="Q77" s="37"/>
+      <c r="R77" s="37"/>
+      <c r="S77" s="38"/>
     </row>
     <row r="78" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C78" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="E78" s="25"/>
-      <c r="F78" s="25"/>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25"/>
-      <c r="I78" s="25"/>
-      <c r="J78" s="26"/>
+      <c r="D78" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="E78" s="34"/>
+      <c r="F78" s="34"/>
+      <c r="G78" s="34"/>
+      <c r="H78" s="34"/>
+      <c r="I78" s="34"/>
+      <c r="J78" s="35"/>
       <c r="L78" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M78" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="N78" s="31"/>
-      <c r="O78" s="31"/>
-      <c r="P78" s="31"/>
-      <c r="Q78" s="31"/>
-      <c r="R78" s="31"/>
-      <c r="S78" s="32"/>
+      <c r="M78" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="N78" s="37"/>
+      <c r="O78" s="37"/>
+      <c r="P78" s="37"/>
+      <c r="Q78" s="37"/>
+      <c r="R78" s="37"/>
+      <c r="S78" s="38"/>
     </row>
     <row r="80" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C80" s="23" t="s">
@@ -3851,7 +3860,7 @@
     </row>
     <row r="81" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C81" s="23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D81" s="23">
         <v>5</v>
@@ -3875,7 +3884,7 @@
         <v>50</v>
       </c>
       <c r="L81" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M81" s="19">
         <v>2</v>
@@ -3893,7 +3902,7 @@
         <v>8</v>
       </c>
       <c r="R81" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S81" s="19">
         <v>20</v>
@@ -3903,53 +3912,53 @@
       <c r="C82" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="E82" s="25"/>
-      <c r="F82" s="25"/>
-      <c r="G82" s="25"/>
-      <c r="H82" s="25"/>
-      <c r="I82" s="25"/>
-      <c r="J82" s="26"/>
+      <c r="D82" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="E82" s="34"/>
+      <c r="F82" s="34"/>
+      <c r="G82" s="34"/>
+      <c r="H82" s="34"/>
+      <c r="I82" s="34"/>
+      <c r="J82" s="35"/>
       <c r="L82" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M82" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="N82" s="31"/>
-      <c r="O82" s="31"/>
-      <c r="P82" s="31"/>
-      <c r="Q82" s="31"/>
-      <c r="R82" s="31"/>
-      <c r="S82" s="32"/>
+      <c r="M82" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="N82" s="37"/>
+      <c r="O82" s="37"/>
+      <c r="P82" s="37"/>
+      <c r="Q82" s="37"/>
+      <c r="R82" s="37"/>
+      <c r="S82" s="38"/>
     </row>
     <row r="83" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C83" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D83" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="E83" s="25"/>
-      <c r="F83" s="25"/>
-      <c r="G83" s="25"/>
-      <c r="H83" s="25"/>
-      <c r="I83" s="25"/>
-      <c r="J83" s="26"/>
+      <c r="D83" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="E83" s="34"/>
+      <c r="F83" s="34"/>
+      <c r="G83" s="34"/>
+      <c r="H83" s="34"/>
+      <c r="I83" s="34"/>
+      <c r="J83" s="35"/>
       <c r="L83" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M83" s="30" t="s">
+      <c r="M83" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="N83" s="31"/>
-      <c r="O83" s="31"/>
-      <c r="P83" s="31"/>
-      <c r="Q83" s="31"/>
-      <c r="R83" s="31"/>
-      <c r="S83" s="32"/>
+      <c r="N83" s="37"/>
+      <c r="O83" s="37"/>
+      <c r="P83" s="37"/>
+      <c r="Q83" s="37"/>
+      <c r="R83" s="37"/>
+      <c r="S83" s="38"/>
     </row>
     <row r="84" spans="3:19" x14ac:dyDescent="0.25">
       <c r="O84"/>
@@ -4006,7 +4015,7 @@
     </row>
     <row r="86" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C86" s="23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D86" s="23">
         <v>3</v>
@@ -4015,7 +4024,7 @@
         <v>1</v>
       </c>
       <c r="F86" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G86" s="23" t="s">
         <v>7</v>
@@ -4030,7 +4039,7 @@
         <v>45</v>
       </c>
       <c r="L86" s="19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M86" s="19">
         <v>1</v>
@@ -4045,10 +4054,10 @@
         <v>7</v>
       </c>
       <c r="Q86" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R86" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S86" s="19">
         <v>20</v>
@@ -4058,53 +4067,53 @@
       <c r="C87" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D87" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="E87" s="25"/>
-      <c r="F87" s="25"/>
-      <c r="G87" s="25"/>
-      <c r="H87" s="25"/>
-      <c r="I87" s="25"/>
-      <c r="J87" s="26"/>
+      <c r="D87" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="E87" s="34"/>
+      <c r="F87" s="34"/>
+      <c r="G87" s="34"/>
+      <c r="H87" s="34"/>
+      <c r="I87" s="34"/>
+      <c r="J87" s="35"/>
       <c r="L87" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M87" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="N87" s="31"/>
-      <c r="O87" s="31"/>
-      <c r="P87" s="31"/>
-      <c r="Q87" s="31"/>
-      <c r="R87" s="31"/>
-      <c r="S87" s="32"/>
+      <c r="M87" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="N87" s="37"/>
+      <c r="O87" s="37"/>
+      <c r="P87" s="37"/>
+      <c r="Q87" s="37"/>
+      <c r="R87" s="37"/>
+      <c r="S87" s="38"/>
     </row>
     <row r="88" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C88" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D88" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25"/>
-      <c r="H88" s="25"/>
-      <c r="I88" s="25"/>
-      <c r="J88" s="26"/>
+      <c r="D88" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="E88" s="34"/>
+      <c r="F88" s="34"/>
+      <c r="G88" s="34"/>
+      <c r="H88" s="34"/>
+      <c r="I88" s="34"/>
+      <c r="J88" s="35"/>
       <c r="L88" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M88" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="N88" s="31"/>
-      <c r="O88" s="31"/>
-      <c r="P88" s="31"/>
-      <c r="Q88" s="31"/>
-      <c r="R88" s="31"/>
-      <c r="S88" s="32"/>
+      <c r="M88" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="N88" s="37"/>
+      <c r="O88" s="37"/>
+      <c r="P88" s="37"/>
+      <c r="Q88" s="37"/>
+      <c r="R88" s="37"/>
+      <c r="S88" s="38"/>
     </row>
     <row r="90" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="13" t="s">
@@ -4158,7 +4167,7 @@
     </row>
     <row r="91" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C91" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D91" s="13">
         <v>1</v>
@@ -4167,7 +4176,7 @@
         <v>2</v>
       </c>
       <c r="F91" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G91" s="13" t="s">
         <v>7</v>
@@ -4182,7 +4191,7 @@
         <v>30</v>
       </c>
       <c r="L91" s="19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M91" s="19">
         <v>5</v>
@@ -4191,10 +4200,10 @@
         <v>2</v>
       </c>
       <c r="O91" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P91" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q91" s="19" t="s">
         <v>8</v>
@@ -4210,53 +4219,53 @@
       <c r="C92" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D92" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="E92" s="25"/>
-      <c r="F92" s="25"/>
-      <c r="G92" s="25"/>
-      <c r="H92" s="25"/>
-      <c r="I92" s="25"/>
-      <c r="J92" s="26"/>
+      <c r="D92" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="E92" s="34"/>
+      <c r="F92" s="34"/>
+      <c r="G92" s="34"/>
+      <c r="H92" s="34"/>
+      <c r="I92" s="34"/>
+      <c r="J92" s="35"/>
       <c r="L92" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M92" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="N92" s="31"/>
-      <c r="O92" s="31"/>
-      <c r="P92" s="31"/>
-      <c r="Q92" s="31"/>
-      <c r="R92" s="31"/>
-      <c r="S92" s="32"/>
+      <c r="M92" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="N92" s="37"/>
+      <c r="O92" s="37"/>
+      <c r="P92" s="37"/>
+      <c r="Q92" s="37"/>
+      <c r="R92" s="37"/>
+      <c r="S92" s="38"/>
     </row>
     <row r="93" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C93" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="E93" s="25"/>
-      <c r="F93" s="25"/>
-      <c r="G93" s="25"/>
-      <c r="H93" s="25"/>
-      <c r="I93" s="25"/>
-      <c r="J93" s="26"/>
+      <c r="D93" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="E93" s="34"/>
+      <c r="F93" s="34"/>
+      <c r="G93" s="34"/>
+      <c r="H93" s="34"/>
+      <c r="I93" s="34"/>
+      <c r="J93" s="35"/>
       <c r="L93" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M93" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="N93" s="31"/>
-      <c r="O93" s="31"/>
-      <c r="P93" s="31"/>
-      <c r="Q93" s="31"/>
-      <c r="R93" s="31"/>
-      <c r="S93" s="32"/>
+      <c r="M93" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="N93" s="37"/>
+      <c r="O93" s="37"/>
+      <c r="P93" s="37"/>
+      <c r="Q93" s="37"/>
+      <c r="R93" s="37"/>
+      <c r="S93" s="38"/>
     </row>
     <row r="95" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C95" s="13" t="s">
@@ -4310,7 +4319,7 @@
     </row>
     <row r="96" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C96" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D96" s="13">
         <v>7</v>
@@ -4334,7 +4343,7 @@
         <v>50</v>
       </c>
       <c r="L96" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M96" s="19">
         <v>3</v>
@@ -4362,53 +4371,53 @@
       <c r="C97" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="E97" s="25"/>
-      <c r="F97" s="25"/>
-      <c r="G97" s="25"/>
-      <c r="H97" s="25"/>
-      <c r="I97" s="25"/>
-      <c r="J97" s="26"/>
+      <c r="D97" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="E97" s="34"/>
+      <c r="F97" s="34"/>
+      <c r="G97" s="34"/>
+      <c r="H97" s="34"/>
+      <c r="I97" s="34"/>
+      <c r="J97" s="35"/>
       <c r="L97" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M97" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="N97" s="31"/>
-      <c r="O97" s="31"/>
-      <c r="P97" s="31"/>
-      <c r="Q97" s="31"/>
-      <c r="R97" s="31"/>
-      <c r="S97" s="32"/>
+      <c r="M97" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="N97" s="37"/>
+      <c r="O97" s="37"/>
+      <c r="P97" s="37"/>
+      <c r="Q97" s="37"/>
+      <c r="R97" s="37"/>
+      <c r="S97" s="38"/>
     </row>
     <row r="98" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C98" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D98" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="E98" s="25"/>
-      <c r="F98" s="25"/>
-      <c r="G98" s="25"/>
-      <c r="H98" s="25"/>
-      <c r="I98" s="25"/>
-      <c r="J98" s="26"/>
+      <c r="D98" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="E98" s="34"/>
+      <c r="F98" s="34"/>
+      <c r="G98" s="34"/>
+      <c r="H98" s="34"/>
+      <c r="I98" s="34"/>
+      <c r="J98" s="35"/>
       <c r="L98" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M98" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="N98" s="31"/>
-      <c r="O98" s="31"/>
-      <c r="P98" s="31"/>
-      <c r="Q98" s="31"/>
-      <c r="R98" s="31"/>
-      <c r="S98" s="32"/>
+      <c r="M98" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="N98" s="37"/>
+      <c r="O98" s="37"/>
+      <c r="P98" s="37"/>
+      <c r="Q98" s="37"/>
+      <c r="R98" s="37"/>
+      <c r="S98" s="38"/>
     </row>
     <row r="99" spans="3:19" x14ac:dyDescent="0.25">
       <c r="O99"/>
@@ -4465,7 +4474,7 @@
     </row>
     <row r="101" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C101" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D101" s="13">
         <v>2</v>
@@ -4489,7 +4498,7 @@
         <v>50</v>
       </c>
       <c r="L101" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M101" s="19">
         <v>3</v>
@@ -4517,53 +4526,53 @@
       <c r="C102" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D102" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="E102" s="25"/>
-      <c r="F102" s="25"/>
-      <c r="G102" s="25"/>
-      <c r="H102" s="25"/>
-      <c r="I102" s="25"/>
-      <c r="J102" s="26"/>
+      <c r="D102" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="E102" s="34"/>
+      <c r="F102" s="34"/>
+      <c r="G102" s="34"/>
+      <c r="H102" s="34"/>
+      <c r="I102" s="34"/>
+      <c r="J102" s="35"/>
       <c r="L102" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M102" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="N102" s="31"/>
-      <c r="O102" s="31"/>
-      <c r="P102" s="31"/>
-      <c r="Q102" s="31"/>
-      <c r="R102" s="31"/>
-      <c r="S102" s="32"/>
+      <c r="M102" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="N102" s="37"/>
+      <c r="O102" s="37"/>
+      <c r="P102" s="37"/>
+      <c r="Q102" s="37"/>
+      <c r="R102" s="37"/>
+      <c r="S102" s="38"/>
     </row>
     <row r="103" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C103" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D103" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="E103" s="25"/>
-      <c r="F103" s="25"/>
-      <c r="G103" s="25"/>
-      <c r="H103" s="25"/>
-      <c r="I103" s="25"/>
-      <c r="J103" s="26"/>
+      <c r="D103" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E103" s="34"/>
+      <c r="F103" s="34"/>
+      <c r="G103" s="34"/>
+      <c r="H103" s="34"/>
+      <c r="I103" s="34"/>
+      <c r="J103" s="35"/>
       <c r="L103" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M103" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="N103" s="31"/>
-      <c r="O103" s="31"/>
-      <c r="P103" s="31"/>
-      <c r="Q103" s="31"/>
-      <c r="R103" s="31"/>
-      <c r="S103" s="32"/>
+      <c r="M103" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="N103" s="37"/>
+      <c r="O103" s="37"/>
+      <c r="P103" s="37"/>
+      <c r="Q103" s="37"/>
+      <c r="R103" s="37"/>
+      <c r="S103" s="38"/>
     </row>
     <row r="104" spans="3:19" x14ac:dyDescent="0.25">
       <c r="O104"/>
@@ -4618,21 +4627,21 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:19" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C106" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D106" s="13">
+        <v>12</v>
+      </c>
+      <c r="E106" s="13">
+        <v>3</v>
+      </c>
+      <c r="F106" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G106" s="13" t="s">
         <v>87</v>
-      </c>
-      <c r="D106" s="13">
-        <v>12</v>
-      </c>
-      <c r="E106" s="13">
-        <v>3</v>
-      </c>
-      <c r="F106" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G106" s="13" t="s">
-        <v>88</v>
       </c>
       <c r="H106" s="13" t="s">
         <v>8</v>
@@ -4644,7 +4653,7 @@
         <v>100</v>
       </c>
       <c r="L106" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M106" s="21">
         <v>3</v>
@@ -4672,53 +4681,53 @@
       <c r="C107" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="E107" s="25"/>
-      <c r="F107" s="25"/>
-      <c r="G107" s="25"/>
-      <c r="H107" s="25"/>
-      <c r="I107" s="25"/>
-      <c r="J107" s="26"/>
+      <c r="D107" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="E107" s="34"/>
+      <c r="F107" s="34"/>
+      <c r="G107" s="34"/>
+      <c r="H107" s="34"/>
+      <c r="I107" s="34"/>
+      <c r="J107" s="35"/>
       <c r="L107" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M107" s="29" t="s">
-        <v>175</v>
-      </c>
-      <c r="N107" s="29"/>
-      <c r="O107" s="29"/>
-      <c r="P107" s="29"/>
-      <c r="Q107" s="29"/>
-      <c r="R107" s="29"/>
-      <c r="S107" s="29"/>
+      <c r="M107" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="N107" s="39"/>
+      <c r="O107" s="39"/>
+      <c r="P107" s="39"/>
+      <c r="Q107" s="39"/>
+      <c r="R107" s="39"/>
+      <c r="S107" s="39"/>
     </row>
     <row r="108" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C108" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="E108" s="25"/>
-      <c r="F108" s="25"/>
-      <c r="G108" s="25"/>
-      <c r="H108" s="25"/>
-      <c r="I108" s="25"/>
-      <c r="J108" s="26"/>
+      <c r="D108" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="E108" s="34"/>
+      <c r="F108" s="34"/>
+      <c r="G108" s="34"/>
+      <c r="H108" s="34"/>
+      <c r="I108" s="34"/>
+      <c r="J108" s="35"/>
       <c r="L108" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M108" s="29" t="s">
-        <v>176</v>
-      </c>
-      <c r="N108" s="29"/>
-      <c r="O108" s="29"/>
-      <c r="P108" s="29"/>
-      <c r="Q108" s="29"/>
-      <c r="R108" s="29"/>
-      <c r="S108" s="29"/>
+      <c r="M108" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="N108" s="39"/>
+      <c r="O108" s="39"/>
+      <c r="P108" s="39"/>
+      <c r="Q108" s="39"/>
+      <c r="R108" s="39"/>
+      <c r="S108" s="39"/>
     </row>
     <row r="110" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C110" s="13" t="s">
@@ -4772,31 +4781,31 @@
     </row>
     <row r="111" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C111" s="13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D111" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E111" s="13">
         <v>1</v>
       </c>
       <c r="F111" s="13" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="G111" s="13" t="s">
         <v>7</v>
       </c>
       <c r="H111" s="13" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="I111" s="13" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="J111" s="13">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L111" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M111" s="21">
         <v>1</v>
@@ -4824,77 +4833,77 @@
       <c r="C112" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D112" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="E112" s="25"/>
-      <c r="F112" s="25"/>
-      <c r="G112" s="25"/>
-      <c r="H112" s="25"/>
-      <c r="I112" s="25"/>
-      <c r="J112" s="26"/>
+      <c r="D112" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="E112" s="34"/>
+      <c r="F112" s="34"/>
+      <c r="G112" s="34"/>
+      <c r="H112" s="34"/>
+      <c r="I112" s="34"/>
+      <c r="J112" s="35"/>
       <c r="L112" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M112" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="N112" s="31"/>
-      <c r="O112" s="31"/>
-      <c r="P112" s="31"/>
-      <c r="Q112" s="31"/>
-      <c r="R112" s="31"/>
-      <c r="S112" s="32"/>
+      <c r="M112" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="N112" s="37"/>
+      <c r="O112" s="37"/>
+      <c r="P112" s="37"/>
+      <c r="Q112" s="37"/>
+      <c r="R112" s="37"/>
+      <c r="S112" s="38"/>
     </row>
     <row r="113" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C113" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D113" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="E113" s="25"/>
-      <c r="F113" s="25"/>
-      <c r="G113" s="25"/>
-      <c r="H113" s="25"/>
-      <c r="I113" s="25"/>
-      <c r="J113" s="26"/>
+      <c r="D113" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="E113" s="34"/>
+      <c r="F113" s="34"/>
+      <c r="G113" s="34"/>
+      <c r="H113" s="34"/>
+      <c r="I113" s="34"/>
+      <c r="J113" s="35"/>
       <c r="L113" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M113" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="N113" s="31"/>
-      <c r="O113" s="31"/>
-      <c r="P113" s="31"/>
-      <c r="Q113" s="31"/>
-      <c r="R113" s="31"/>
-      <c r="S113" s="32"/>
+      <c r="M113" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="N113" s="37"/>
+      <c r="O113" s="37"/>
+      <c r="P113" s="37"/>
+      <c r="Q113" s="37"/>
+      <c r="R113" s="37"/>
+      <c r="S113" s="38"/>
     </row>
     <row r="115" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C115" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D115" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E115" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F115" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G115" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H115" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I115" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="J115" s="13" t="s">
+      <c r="C115" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D115" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="E115" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="F115" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G115" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="H115" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="I115" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="J115" s="24" t="s">
         <v>19</v>
       </c>
       <c r="L115" s="21" t="s">
@@ -4923,32 +4932,32 @@
       </c>
     </row>
     <row r="116" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C116" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D116" s="13">
-        <v>2</v>
-      </c>
-      <c r="E116" s="13">
-        <v>1</v>
-      </c>
-      <c r="F116" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G116" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="H116" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I116" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="J116" s="13">
-        <v>40</v>
+      <c r="C116" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="D116" s="24">
+        <v>2</v>
+      </c>
+      <c r="E116" s="24">
+        <v>0</v>
+      </c>
+      <c r="F116" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G116" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="H116" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="I116" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="J116" s="24">
+        <v>10</v>
       </c>
       <c r="L116" s="21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M116" s="21">
         <v>3</v>
@@ -4957,96 +4966,96 @@
         <v>1</v>
       </c>
       <c r="O116" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P116" s="21" t="s">
         <v>7</v>
       </c>
       <c r="Q116" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R116" s="21" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S116" s="21">
         <v>25</v>
       </c>
     </row>
     <row r="117" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C117" s="13" t="s">
+      <c r="C117" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D117" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="E117" s="25"/>
-      <c r="F117" s="25"/>
-      <c r="G117" s="25"/>
-      <c r="H117" s="25"/>
-      <c r="I117" s="25"/>
-      <c r="J117" s="26"/>
+      <c r="D117" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="E117" s="34"/>
+      <c r="F117" s="34"/>
+      <c r="G117" s="34"/>
+      <c r="H117" s="34"/>
+      <c r="I117" s="34"/>
+      <c r="J117" s="35"/>
       <c r="L117" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M117" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="N117" s="31"/>
-      <c r="O117" s="31"/>
-      <c r="P117" s="31"/>
-      <c r="Q117" s="31"/>
-      <c r="R117" s="31"/>
-      <c r="S117" s="32"/>
+      <c r="M117" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="N117" s="37"/>
+      <c r="O117" s="37"/>
+      <c r="P117" s="37"/>
+      <c r="Q117" s="37"/>
+      <c r="R117" s="37"/>
+      <c r="S117" s="38"/>
     </row>
     <row r="118" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C118" s="13" t="s">
+      <c r="C118" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="D118" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="E118" s="25"/>
-      <c r="F118" s="25"/>
-      <c r="G118" s="25"/>
-      <c r="H118" s="25"/>
-      <c r="I118" s="25"/>
-      <c r="J118" s="26"/>
+      <c r="D118" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="E118" s="34"/>
+      <c r="F118" s="34"/>
+      <c r="G118" s="34"/>
+      <c r="H118" s="34"/>
+      <c r="I118" s="34"/>
+      <c r="J118" s="35"/>
       <c r="L118" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M118" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="N118" s="31"/>
-      <c r="O118" s="31"/>
-      <c r="P118" s="31"/>
-      <c r="Q118" s="31"/>
-      <c r="R118" s="31"/>
-      <c r="S118" s="32"/>
+      <c r="M118" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="N118" s="37"/>
+      <c r="O118" s="37"/>
+      <c r="P118" s="37"/>
+      <c r="Q118" s="37"/>
+      <c r="R118" s="37"/>
+      <c r="S118" s="38"/>
     </row>
     <row r="120" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C120" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D120" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E120" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F120" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G120" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H120" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I120" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="J120" s="13" t="s">
+      <c r="C120" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D120" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E120" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F120" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G120" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="H120" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="I120" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J120" s="23" t="s">
         <v>19</v>
       </c>
       <c r="L120" s="22" t="s">
@@ -5075,32 +5084,32 @@
       </c>
     </row>
     <row r="121" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C121" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="D121" s="13">
-        <v>12</v>
-      </c>
-      <c r="E121" s="13">
-        <v>2</v>
-      </c>
-      <c r="F121" s="13" t="s">
+      <c r="C121" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="D121" s="23">
+        <v>2</v>
+      </c>
+      <c r="E121" s="23">
+        <v>2</v>
+      </c>
+      <c r="F121" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="G121" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="H121" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="I121" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="J121" s="13">
-        <v>80</v>
+      <c r="G121" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="H121" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="I121" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="J121" s="23">
+        <v>30</v>
       </c>
       <c r="L121" s="22" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M121" s="22">
         <v>2</v>
@@ -5125,56 +5134,66 @@
       </c>
     </row>
     <row r="122" spans="3:19" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C122" s="13" t="s">
+      <c r="C122" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D122" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="E122" s="25"/>
-      <c r="F122" s="25"/>
-      <c r="G122" s="25"/>
-      <c r="H122" s="25"/>
-      <c r="I122" s="25"/>
-      <c r="J122" s="26"/>
+      <c r="D122" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="E122" s="27"/>
+      <c r="F122" s="27"/>
+      <c r="G122" s="27"/>
+      <c r="H122" s="27"/>
+      <c r="I122" s="27"/>
+      <c r="J122" s="27"/>
       <c r="L122" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M122" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="N122" s="29"/>
-      <c r="O122" s="29"/>
-      <c r="P122" s="29"/>
-      <c r="Q122" s="29"/>
-      <c r="R122" s="29"/>
-      <c r="S122" s="29"/>
+      <c r="M122" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="N122" s="39"/>
+      <c r="O122" s="39"/>
+      <c r="P122" s="39"/>
+      <c r="Q122" s="39"/>
+      <c r="R122" s="39"/>
+      <c r="S122" s="39"/>
     </row>
     <row r="123" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C123" s="13" t="s">
+      <c r="C123" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D123" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="E123" s="25"/>
-      <c r="F123" s="25"/>
-      <c r="G123" s="25"/>
-      <c r="H123" s="25"/>
-      <c r="I123" s="25"/>
-      <c r="J123" s="26"/>
+      <c r="D123" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="E123" s="27"/>
+      <c r="F123" s="27"/>
+      <c r="G123" s="27"/>
+      <c r="H123" s="27"/>
+      <c r="I123" s="27"/>
+      <c r="J123" s="27"/>
       <c r="L123" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="M123" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="N123" s="29"/>
-      <c r="O123" s="29"/>
-      <c r="P123" s="29"/>
-      <c r="Q123" s="29"/>
-      <c r="R123" s="29"/>
-      <c r="S123" s="29"/>
+      <c r="M123" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="N123" s="39"/>
+      <c r="O123" s="39"/>
+      <c r="P123" s="39"/>
+      <c r="Q123" s="39"/>
+      <c r="R123" s="39"/>
+      <c r="S123" s="39"/>
+    </row>
+    <row r="124" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C124" s="16"/>
+      <c r="D124" s="16"/>
+      <c r="E124" s="16"/>
+      <c r="F124" s="14"/>
+      <c r="G124" s="16"/>
+      <c r="H124" s="16"/>
+      <c r="I124" s="16"/>
+      <c r="J124" s="16"/>
     </row>
     <row r="125" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C125" s="13" t="s">
@@ -5228,31 +5247,31 @@
     </row>
     <row r="126" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C126" s="13" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D126" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E126" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G126" s="13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H126" s="13" t="s">
         <v>8</v>
       </c>
       <c r="I126" s="13" t="s">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="J126" s="13">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="L126" s="22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M126" s="22">
         <v>3</v>
@@ -5267,7 +5286,7 @@
         <v>7</v>
       </c>
       <c r="Q126" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R126" s="22" t="s">
         <v>8</v>
@@ -5280,53 +5299,53 @@
       <c r="C127" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D127" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="E127" s="25"/>
-      <c r="F127" s="25"/>
-      <c r="G127" s="25"/>
-      <c r="H127" s="25"/>
-      <c r="I127" s="25"/>
-      <c r="J127" s="26"/>
+      <c r="D127" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="E127" s="34"/>
+      <c r="F127" s="34"/>
+      <c r="G127" s="34"/>
+      <c r="H127" s="34"/>
+      <c r="I127" s="34"/>
+      <c r="J127" s="35"/>
       <c r="L127" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M127" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="N127" s="31"/>
-      <c r="O127" s="31"/>
-      <c r="P127" s="31"/>
-      <c r="Q127" s="31"/>
-      <c r="R127" s="31"/>
-      <c r="S127" s="32"/>
+      <c r="M127" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="N127" s="37"/>
+      <c r="O127" s="37"/>
+      <c r="P127" s="37"/>
+      <c r="Q127" s="37"/>
+      <c r="R127" s="37"/>
+      <c r="S127" s="38"/>
     </row>
     <row r="128" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C128" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D128" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E128" s="25"/>
-      <c r="F128" s="25"/>
-      <c r="G128" s="25"/>
-      <c r="H128" s="25"/>
-      <c r="I128" s="25"/>
-      <c r="J128" s="26"/>
+      <c r="D128" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E128" s="34"/>
+      <c r="F128" s="34"/>
+      <c r="G128" s="34"/>
+      <c r="H128" s="34"/>
+      <c r="I128" s="34"/>
+      <c r="J128" s="35"/>
       <c r="L128" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="M128" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="N128" s="31"/>
-      <c r="O128" s="31"/>
-      <c r="P128" s="31"/>
-      <c r="Q128" s="31"/>
-      <c r="R128" s="31"/>
-      <c r="S128" s="32"/>
+      <c r="M128" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="N128" s="37"/>
+      <c r="O128" s="37"/>
+      <c r="P128" s="37"/>
+      <c r="Q128" s="37"/>
+      <c r="R128" s="37"/>
+      <c r="S128" s="38"/>
     </row>
     <row r="130" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C130" s="23" t="s">
@@ -5380,16 +5399,16 @@
     </row>
     <row r="131" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C131" s="23" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D131" s="23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E131" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F131" s="23" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="G131" s="23" t="s">
         <v>7</v>
@@ -5398,13 +5417,13 @@
         <v>8</v>
       </c>
       <c r="I131" s="23" t="s">
-        <v>8</v>
+        <v>198</v>
       </c>
       <c r="J131" s="23">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="L131" s="22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M131" s="22">
         <v>3</v>
@@ -5419,7 +5438,7 @@
         <v>7</v>
       </c>
       <c r="Q131" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R131" s="22" t="s">
         <v>8</v>
@@ -5432,63 +5451,55 @@
       <c r="C132" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D132" s="27" t="s">
-        <v>204</v>
-      </c>
-      <c r="E132" s="27"/>
-      <c r="F132" s="27"/>
-      <c r="G132" s="27"/>
-      <c r="H132" s="27"/>
-      <c r="I132" s="27"/>
-      <c r="J132" s="27"/>
+      <c r="D132" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="E132" s="34"/>
+      <c r="F132" s="34"/>
+      <c r="G132" s="34"/>
+      <c r="H132" s="34"/>
+      <c r="I132" s="34"/>
+      <c r="J132" s="35"/>
       <c r="L132" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M132" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="N132" s="31"/>
-      <c r="O132" s="31"/>
-      <c r="P132" s="31"/>
-      <c r="Q132" s="31"/>
-      <c r="R132" s="31"/>
-      <c r="S132" s="32"/>
+      <c r="M132" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="N132" s="37"/>
+      <c r="O132" s="37"/>
+      <c r="P132" s="37"/>
+      <c r="Q132" s="37"/>
+      <c r="R132" s="37"/>
+      <c r="S132" s="38"/>
     </row>
     <row r="133" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C133" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D133" s="27" t="s">
-        <v>205</v>
-      </c>
-      <c r="E133" s="27"/>
-      <c r="F133" s="27"/>
-      <c r="G133" s="27"/>
-      <c r="H133" s="27"/>
-      <c r="I133" s="27"/>
-      <c r="J133" s="27"/>
+      <c r="D133" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="E133" s="34"/>
+      <c r="F133" s="34"/>
+      <c r="G133" s="34"/>
+      <c r="H133" s="34"/>
+      <c r="I133" s="34"/>
+      <c r="J133" s="35"/>
       <c r="L133" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="M133" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="N133" s="31"/>
-      <c r="O133" s="31"/>
-      <c r="P133" s="31"/>
-      <c r="Q133" s="31"/>
-      <c r="R133" s="31"/>
-      <c r="S133" s="32"/>
+      <c r="M133" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="N133" s="37"/>
+      <c r="O133" s="37"/>
+      <c r="P133" s="37"/>
+      <c r="Q133" s="37"/>
+      <c r="R133" s="37"/>
+      <c r="S133" s="38"/>
     </row>
     <row r="134" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C134" s="16"/>
-      <c r="D134" s="16"/>
-      <c r="E134" s="16"/>
-      <c r="F134" s="14"/>
-      <c r="G134" s="16"/>
-      <c r="H134" s="16"/>
-      <c r="I134" s="16"/>
-      <c r="J134" s="16"/>
       <c r="M134"/>
       <c r="N134"/>
       <c r="O134"/>
@@ -5496,28 +5507,28 @@
       <c r="Q134"/>
     </row>
     <row r="135" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D135" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E135" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F135" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G135" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H135" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I135" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="J135" s="13" t="s">
+      <c r="C135" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D135" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E135" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F135" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G135" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="H135" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="I135" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J135" s="23" t="s">
         <v>19</v>
       </c>
       <c r="L135" s="22" t="s">
@@ -5546,32 +5557,32 @@
       </c>
     </row>
     <row r="136" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="D136" s="13">
-        <v>4</v>
-      </c>
-      <c r="E136" s="13">
-        <v>1</v>
-      </c>
-      <c r="F136" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G136" s="13" t="s">
+      <c r="C136" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="D136" s="23">
+        <v>2</v>
+      </c>
+      <c r="E136" s="23">
+        <v>1</v>
+      </c>
+      <c r="F136" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G136" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="H136" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I136" s="13" t="s">
+      <c r="H136" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="I136" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="J136" s="23">
+        <v>25</v>
+      </c>
+      <c r="L136" s="22" t="s">
         <v>138</v>
-      </c>
-      <c r="J136" s="13">
-        <v>50</v>
-      </c>
-      <c r="L136" s="22" t="s">
-        <v>139</v>
       </c>
       <c r="M136" s="22">
         <v>3</v>
@@ -5586,7 +5597,7 @@
         <v>7</v>
       </c>
       <c r="Q136" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R136" s="22" t="s">
         <v>8</v>
@@ -5596,66 +5607,58 @@
       </c>
     </row>
     <row r="137" spans="3:19" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C137" s="13" t="s">
+      <c r="C137" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D137" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="E137" s="25"/>
-      <c r="F137" s="25"/>
-      <c r="G137" s="25"/>
-      <c r="H137" s="25"/>
-      <c r="I137" s="25"/>
-      <c r="J137" s="26"/>
+      <c r="D137" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="E137" s="34"/>
+      <c r="F137" s="34"/>
+      <c r="G137" s="34"/>
+      <c r="H137" s="34"/>
+      <c r="I137" s="34"/>
+      <c r="J137" s="35"/>
       <c r="L137" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M137" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="N137" s="31"/>
-      <c r="O137" s="31"/>
-      <c r="P137" s="31"/>
-      <c r="Q137" s="31"/>
-      <c r="R137" s="31"/>
-      <c r="S137" s="32"/>
+      <c r="M137" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="N137" s="37"/>
+      <c r="O137" s="37"/>
+      <c r="P137" s="37"/>
+      <c r="Q137" s="37"/>
+      <c r="R137" s="37"/>
+      <c r="S137" s="38"/>
     </row>
     <row r="138" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C138" s="13" t="s">
+      <c r="C138" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D138" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="E138" s="25"/>
-      <c r="F138" s="25"/>
-      <c r="G138" s="25"/>
-      <c r="H138" s="25"/>
-      <c r="I138" s="25"/>
-      <c r="J138" s="26"/>
+      <c r="D138" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="E138" s="34"/>
+      <c r="F138" s="34"/>
+      <c r="G138" s="34"/>
+      <c r="H138" s="34"/>
+      <c r="I138" s="34"/>
+      <c r="J138" s="35"/>
       <c r="L138" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="M138" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="N138" s="31"/>
-      <c r="O138" s="31"/>
-      <c r="P138" s="31"/>
-      <c r="Q138" s="31"/>
-      <c r="R138" s="31"/>
-      <c r="S138" s="32"/>
+      <c r="M138" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="N138" s="37"/>
+      <c r="O138" s="37"/>
+      <c r="P138" s="37"/>
+      <c r="Q138" s="37"/>
+      <c r="R138" s="37"/>
+      <c r="S138" s="38"/>
     </row>
     <row r="139" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C139" s="16"/>
-      <c r="D139" s="16"/>
-      <c r="E139" s="16"/>
-      <c r="F139" s="14"/>
-      <c r="G139" s="16"/>
-      <c r="H139" s="16"/>
-      <c r="I139" s="16"/>
-      <c r="J139" s="16"/>
       <c r="M139"/>
       <c r="N139"/>
       <c r="O139"/>
@@ -5687,19 +5690,43 @@
       <c r="J140" s="23" t="s">
         <v>19</v>
       </c>
+      <c r="L140" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="M140" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="N140" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="O140" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="P140" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q140" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="R140" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S140" s="25" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="141" spans="3:19" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C141" s="23" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D141" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E141" s="23">
         <v>1</v>
       </c>
       <c r="F141" s="23" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G141" s="23" t="s">
         <v>7</v>
@@ -5711,6 +5738,30 @@
         <v>8</v>
       </c>
       <c r="J141" s="23">
+        <v>10</v>
+      </c>
+      <c r="L141" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="M141" s="25">
+        <v>2</v>
+      </c>
+      <c r="N141" s="25">
+        <v>1</v>
+      </c>
+      <c r="O141" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="P141" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q141" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="R141" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="S141" s="25">
         <v>25</v>
       </c>
     </row>
@@ -5718,31 +5769,55 @@
       <c r="C142" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D142" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="E142" s="27"/>
-      <c r="F142" s="27"/>
-      <c r="G142" s="27"/>
-      <c r="H142" s="27"/>
-      <c r="I142" s="27"/>
-      <c r="J142" s="27"/>
+      <c r="D142" s="33" t="s">
+        <v>192</v>
+      </c>
+      <c r="E142" s="34"/>
+      <c r="F142" s="34"/>
+      <c r="G142" s="34"/>
+      <c r="H142" s="34"/>
+      <c r="I142" s="34"/>
+      <c r="J142" s="35"/>
+      <c r="L142" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="M142" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="N142" s="37"/>
+      <c r="O142" s="37"/>
+      <c r="P142" s="37"/>
+      <c r="Q142" s="37"/>
+      <c r="R142" s="37"/>
+      <c r="S142" s="38"/>
     </row>
     <row r="143" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C143" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D143" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="E143" s="27"/>
-      <c r="F143" s="27"/>
-      <c r="G143" s="27"/>
-      <c r="H143" s="27"/>
-      <c r="I143" s="27"/>
-      <c r="J143" s="27"/>
-    </row>
-    <row r="145" spans="3:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D143" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="E143" s="34"/>
+      <c r="F143" s="34"/>
+      <c r="G143" s="34"/>
+      <c r="H143" s="34"/>
+      <c r="I143" s="34"/>
+      <c r="J143" s="35"/>
+      <c r="L143" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="M143" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="N143" s="37"/>
+      <c r="O143" s="37"/>
+      <c r="P143" s="37"/>
+      <c r="Q143" s="37"/>
+      <c r="R143" s="37"/>
+      <c r="S143" s="38"/>
+    </row>
+    <row r="145" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C145" s="23" t="s">
         <v>0</v>
       </c>
@@ -5767,20 +5842,43 @@
       <c r="J145" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="O145"/>
-    </row>
-    <row r="146" spans="3:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L145" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="M145" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="N145" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="O145" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="P145" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q145" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="R145" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S145" s="25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="146" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="23" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D146" s="23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E146" s="23">
         <v>1</v>
       </c>
       <c r="F146" s="23" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="G146" s="23" t="s">
         <v>7</v>
@@ -5789,281 +5887,177 @@
         <v>8</v>
       </c>
       <c r="I146" s="23" t="s">
-        <v>199</v>
+        <v>8</v>
       </c>
       <c r="J146" s="23">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="147" spans="3:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="L146" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="M146" s="25">
+        <v>2</v>
+      </c>
+      <c r="N146" s="25">
+        <v>1</v>
+      </c>
+      <c r="O146" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="P146" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q146" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="R146" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="S146" s="25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="147" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C147" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D147" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="E147" s="25"/>
-      <c r="F147" s="25"/>
-      <c r="G147" s="25"/>
-      <c r="H147" s="25"/>
-      <c r="I147" s="25"/>
-      <c r="J147" s="26"/>
-    </row>
-    <row r="148" spans="3:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D147" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="E147" s="27"/>
+      <c r="F147" s="27"/>
+      <c r="G147" s="27"/>
+      <c r="H147" s="27"/>
+      <c r="I147" s="27"/>
+      <c r="J147" s="27"/>
+      <c r="L147" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="M147" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="N147" s="39"/>
+      <c r="O147" s="39"/>
+      <c r="P147" s="39"/>
+      <c r="Q147" s="39"/>
+      <c r="R147" s="39"/>
+      <c r="S147" s="39"/>
+    </row>
+    <row r="148" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C148" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D148" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="E148" s="25"/>
-      <c r="F148" s="25"/>
-      <c r="G148" s="25"/>
-      <c r="H148" s="25"/>
-      <c r="I148" s="25"/>
-      <c r="J148" s="26"/>
-    </row>
-    <row r="150" spans="3:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C150" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D150" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E150" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F150" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G150" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="H150" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I150" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="J150" s="23" t="s">
+      <c r="D148" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="E148" s="27"/>
+      <c r="F148" s="27"/>
+      <c r="G148" s="27"/>
+      <c r="H148" s="27"/>
+      <c r="I148" s="27"/>
+      <c r="J148" s="27"/>
+      <c r="L148" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="M148" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="N148" s="39"/>
+      <c r="O148" s="39"/>
+      <c r="P148" s="39"/>
+      <c r="Q148" s="39"/>
+      <c r="R148" s="39"/>
+      <c r="S148" s="39"/>
+    </row>
+    <row r="150" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L150" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="M150" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="N150" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="O150" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="P150" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q150" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="R150" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S150" s="25" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="151" spans="3:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="D151" s="23">
-        <v>2</v>
-      </c>
-      <c r="E151" s="23">
-        <v>1</v>
-      </c>
-      <c r="F151" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G151" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="H151" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="I151" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="J151" s="23">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="152" spans="3:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="23" t="s">
+    <row r="151" spans="3:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L151" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="M151" s="25">
+        <v>6</v>
+      </c>
+      <c r="N151" s="25">
+        <v>1</v>
+      </c>
+      <c r="O151" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="P151" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q151" s="25">
+        <v>0</v>
+      </c>
+      <c r="R151" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="S151" s="25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="152" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L152" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="D152" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="E152" s="25"/>
-      <c r="F152" s="25"/>
-      <c r="G152" s="25"/>
-      <c r="H152" s="25"/>
-      <c r="I152" s="25"/>
-      <c r="J152" s="26"/>
-    </row>
-    <row r="153" spans="3:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="23" t="s">
+      <c r="M152" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="N152" s="37"/>
+      <c r="O152" s="37"/>
+      <c r="P152" s="37"/>
+      <c r="Q152" s="37"/>
+      <c r="R152" s="37"/>
+      <c r="S152" s="38"/>
+    </row>
+    <row r="153" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L153" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D153" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="E153" s="25"/>
-      <c r="F153" s="25"/>
-      <c r="G153" s="25"/>
-      <c r="H153" s="25"/>
-      <c r="I153" s="25"/>
-      <c r="J153" s="26"/>
-    </row>
-    <row r="155" spans="3:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C155" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D155" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E155" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F155" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G155" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="H155" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I155" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="J155" s="23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="156" spans="3:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C156" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="D156" s="23">
-        <v>1</v>
-      </c>
-      <c r="E156" s="23">
-        <v>1</v>
-      </c>
-      <c r="F156" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G156" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="H156" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="I156" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="J156" s="23">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="157" spans="3:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C157" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D157" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="E157" s="25"/>
-      <c r="F157" s="25"/>
-      <c r="G157" s="25"/>
-      <c r="H157" s="25"/>
-      <c r="I157" s="25"/>
-      <c r="J157" s="26"/>
-    </row>
-    <row r="158" spans="3:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C158" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D158" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="E158" s="25"/>
-      <c r="F158" s="25"/>
-      <c r="G158" s="25"/>
-      <c r="H158" s="25"/>
-      <c r="I158" s="25"/>
-      <c r="J158" s="26"/>
-    </row>
-    <row r="160" spans="3:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C160" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D160" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E160" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F160" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G160" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="H160" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I160" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="J160" s="23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="161" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C161" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="D161" s="23">
-        <v>1</v>
-      </c>
-      <c r="E161" s="23">
-        <v>1</v>
-      </c>
-      <c r="F161" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G161" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="H161" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="I161" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="J161" s="23">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="162" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C162" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D162" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="E162" s="27"/>
-      <c r="F162" s="27"/>
-      <c r="G162" s="27"/>
-      <c r="H162" s="27"/>
-      <c r="I162" s="27"/>
-      <c r="J162" s="27"/>
-    </row>
-    <row r="163" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C163" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D163" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="E163" s="27"/>
-      <c r="F163" s="27"/>
-      <c r="G163" s="27"/>
-      <c r="H163" s="27"/>
-      <c r="I163" s="27"/>
-      <c r="J163" s="27"/>
-    </row>
-    <row r="165" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M153" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="N153" s="37"/>
+      <c r="O153" s="37"/>
+      <c r="P153" s="37"/>
+      <c r="Q153" s="37"/>
+      <c r="R153" s="37"/>
+      <c r="S153" s="38"/>
+    </row>
+    <row r="155" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L165"/>
       <c r="M165"/>
       <c r="N165"/>
@@ -6073,7 +6067,7 @@
       <c r="R165"/>
       <c r="S165"/>
     </row>
-    <row r="166" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L166"/>
       <c r="M166"/>
       <c r="N166"/>
@@ -6083,60 +6077,91 @@
       <c r="R166"/>
       <c r="S166"/>
     </row>
-    <row r="167" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L167"/>
-      <c r="M167" s="28"/>
-      <c r="N167" s="28"/>
-      <c r="O167" s="28"/>
-      <c r="P167" s="28"/>
-      <c r="Q167" s="28"/>
-      <c r="R167" s="28"/>
-      <c r="S167" s="28"/>
-    </row>
-    <row r="168" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M167" s="29"/>
+      <c r="N167" s="29"/>
+      <c r="O167" s="29"/>
+      <c r="P167" s="29"/>
+      <c r="Q167" s="29"/>
+      <c r="R167" s="29"/>
+      <c r="S167" s="29"/>
+    </row>
+    <row r="168" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L168"/>
-      <c r="M168" s="28"/>
-      <c r="N168" s="28"/>
-      <c r="O168" s="28"/>
-      <c r="P168" s="28"/>
-      <c r="Q168" s="28"/>
-      <c r="R168" s="28"/>
-      <c r="S168" s="28"/>
-    </row>
-    <row r="170" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="M168" s="29"/>
+      <c r="N168" s="29"/>
+      <c r="O168" s="29"/>
+      <c r="P168" s="29"/>
+      <c r="Q168" s="29"/>
+      <c r="R168" s="29"/>
+      <c r="S168" s="29"/>
+    </row>
+    <row r="170" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="177" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="178" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="127">
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D158:J158"/>
-    <mergeCell ref="D152:J152"/>
-    <mergeCell ref="D153:J153"/>
-    <mergeCell ref="D147:J147"/>
-    <mergeCell ref="D148:J148"/>
+    <mergeCell ref="D32:J32"/>
+    <mergeCell ref="D33:J33"/>
+    <mergeCell ref="D112:J112"/>
+    <mergeCell ref="D77:J77"/>
+    <mergeCell ref="D78:J78"/>
+    <mergeCell ref="D93:J93"/>
+    <mergeCell ref="M133:S133"/>
+    <mergeCell ref="D97:J97"/>
+    <mergeCell ref="M152:S152"/>
+    <mergeCell ref="M153:S153"/>
+    <mergeCell ref="D92:J92"/>
+    <mergeCell ref="D103:J103"/>
+    <mergeCell ref="M43:S43"/>
+    <mergeCell ref="M47:S47"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M52:S52"/>
+    <mergeCell ref="D42:J42"/>
+    <mergeCell ref="M92:S92"/>
+    <mergeCell ref="M142:S142"/>
+    <mergeCell ref="M143:S143"/>
+    <mergeCell ref="D142:J142"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D137:J137"/>
+    <mergeCell ref="D138:J138"/>
+    <mergeCell ref="D132:J132"/>
+    <mergeCell ref="D133:J133"/>
     <mergeCell ref="D87:J87"/>
     <mergeCell ref="D88:J88"/>
     <mergeCell ref="M42:S42"/>
     <mergeCell ref="M93:S93"/>
     <mergeCell ref="M67:S67"/>
-    <mergeCell ref="D118:J118"/>
-    <mergeCell ref="D122:J122"/>
-    <mergeCell ref="D123:J123"/>
-    <mergeCell ref="D47:J47"/>
-    <mergeCell ref="D48:J48"/>
-    <mergeCell ref="D112:J112"/>
     <mergeCell ref="D113:J113"/>
-    <mergeCell ref="D117:J117"/>
-    <mergeCell ref="D77:J77"/>
-    <mergeCell ref="D78:J78"/>
-    <mergeCell ref="D93:J93"/>
-    <mergeCell ref="M133:S133"/>
-    <mergeCell ref="D97:J97"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="V12:AB12"/>
+    <mergeCell ref="V13:AB13"/>
+    <mergeCell ref="M12:S12"/>
+    <mergeCell ref="M8:S8"/>
+    <mergeCell ref="M7:S7"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="V7:AB7"/>
+    <mergeCell ref="V8:AB8"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="M147:S147"/>
+    <mergeCell ref="M148:S148"/>
+    <mergeCell ref="M63:S63"/>
+    <mergeCell ref="D17:J17"/>
+    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="M57:S57"/>
+    <mergeCell ref="M58:S58"/>
+    <mergeCell ref="M97:S97"/>
+    <mergeCell ref="M72:S72"/>
+    <mergeCell ref="M73:S73"/>
     <mergeCell ref="D98:J98"/>
     <mergeCell ref="D102:J102"/>
     <mergeCell ref="M87:S87"/>
@@ -6148,40 +6173,9 @@
     <mergeCell ref="M22:S22"/>
     <mergeCell ref="M122:S122"/>
     <mergeCell ref="M123:S123"/>
-    <mergeCell ref="D32:J32"/>
-    <mergeCell ref="D33:J33"/>
-    <mergeCell ref="D92:J92"/>
-    <mergeCell ref="D103:J103"/>
-    <mergeCell ref="M43:S43"/>
-    <mergeCell ref="M47:S47"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M52:S52"/>
-    <mergeCell ref="D42:J42"/>
-    <mergeCell ref="M92:S92"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="D23:J23"/>
     <mergeCell ref="D27:J27"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="V12:AB12"/>
-    <mergeCell ref="V13:AB13"/>
-    <mergeCell ref="M12:S12"/>
-    <mergeCell ref="M8:S8"/>
-    <mergeCell ref="M7:S7"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="V7:AB7"/>
-    <mergeCell ref="V8:AB8"/>
-    <mergeCell ref="D107:J107"/>
-    <mergeCell ref="D108:J108"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="M63:S63"/>
-    <mergeCell ref="D17:J17"/>
-    <mergeCell ref="D18:J18"/>
-    <mergeCell ref="M57:S57"/>
-    <mergeCell ref="M58:S58"/>
-    <mergeCell ref="M97:S97"/>
-    <mergeCell ref="M72:S72"/>
-    <mergeCell ref="M73:S73"/>
+    <mergeCell ref="D47:J47"/>
+    <mergeCell ref="D48:J48"/>
     <mergeCell ref="V17:AB17"/>
     <mergeCell ref="V18:AB18"/>
     <mergeCell ref="M17:S17"/>
@@ -6197,8 +6191,8 @@
     <mergeCell ref="D67:J67"/>
     <mergeCell ref="D68:J68"/>
     <mergeCell ref="D43:J43"/>
-    <mergeCell ref="D137:J137"/>
-    <mergeCell ref="D138:J138"/>
+    <mergeCell ref="D127:J127"/>
+    <mergeCell ref="D128:J128"/>
     <mergeCell ref="M107:S107"/>
     <mergeCell ref="M108:S108"/>
     <mergeCell ref="D82:J82"/>
@@ -6207,8 +6201,8 @@
     <mergeCell ref="M113:S113"/>
     <mergeCell ref="M82:S82"/>
     <mergeCell ref="M83:S83"/>
-    <mergeCell ref="D127:J127"/>
-    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D117:J117"/>
+    <mergeCell ref="D118:J118"/>
     <mergeCell ref="M117:S117"/>
     <mergeCell ref="M118:S118"/>
     <mergeCell ref="M103:S103"/>
@@ -6216,14 +6210,12 @@
     <mergeCell ref="M68:S68"/>
     <mergeCell ref="M102:S102"/>
     <mergeCell ref="M132:S132"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D162:J162"/>
-    <mergeCell ref="D163:J163"/>
-    <mergeCell ref="D142:J142"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D132:J132"/>
-    <mergeCell ref="D133:J133"/>
+    <mergeCell ref="D147:J147"/>
+    <mergeCell ref="D148:J148"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="D122:J122"/>
+    <mergeCell ref="D123:J123"/>
     <mergeCell ref="M167:S167"/>
     <mergeCell ref="D28:J28"/>
     <mergeCell ref="D72:J72"/>
@@ -6240,6 +6232,8 @@
     <mergeCell ref="M38:S38"/>
     <mergeCell ref="M53:S53"/>
     <mergeCell ref="M62:S62"/>
+    <mergeCell ref="D107:J107"/>
+    <mergeCell ref="D108:J108"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6255,28 +6249,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="38"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="A1" s="42"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
+      <c r="A2" s="42"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
     </row>
     <row r="4" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>

--- a/Docs/Units.xlsx
+++ b/Docs/Units.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="206">
   <si>
     <t>Name</t>
   </si>
@@ -402,9 +402,6 @@
     <t>Great Unclean one</t>
   </si>
   <si>
-    <t>Polymorphed animal</t>
-  </si>
-  <si>
     <t>Water mage</t>
   </si>
   <si>
@@ -424,9 +421,6 @@
   </si>
   <si>
     <t>Stormokinesis</t>
-  </si>
-  <si>
-    <t>A rabbit, sheep or a big sheep depending on the size</t>
   </si>
   <si>
     <t>Four 3 length line perpendicular to player in all directions 1 space away</t>
@@ -849,29 +843,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
@@ -895,13 +873,29 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1234,30 +1228,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
     </row>
     <row r="2" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
     </row>
     <row r="3" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
@@ -1441,39 +1435,39 @@
       <c r="C7" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="35"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
       <c r="L7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="41" t="s">
+      <c r="M7" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="N7" s="41"/>
-      <c r="O7" s="41"/>
-      <c r="P7" s="41"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="41"/>
-      <c r="S7" s="41"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="39"/>
+      <c r="S7" s="39"/>
       <c r="U7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V7" s="40" t="s">
+      <c r="V7" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="W7" s="40"/>
-      <c r="X7" s="40"/>
-      <c r="Y7" s="40"/>
-      <c r="Z7" s="40"/>
-      <c r="AA7" s="40"/>
-      <c r="AB7" s="40"/>
+      <c r="W7" s="38"/>
+      <c r="X7" s="38"/>
+      <c r="Y7" s="38"/>
+      <c r="Z7" s="38"/>
+      <c r="AA7" s="38"/>
+      <c r="AB7" s="38"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
@@ -1483,39 +1477,39 @@
       <c r="C8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="35"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="29"/>
       <c r="L8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="41" t="s">
+      <c r="M8" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="41"/>
-      <c r="O8" s="41"/>
-      <c r="P8" s="41"/>
-      <c r="Q8" s="41"/>
-      <c r="R8" s="41"/>
-      <c r="S8" s="41"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="39"/>
+      <c r="S8" s="39"/>
       <c r="U8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="40" t="s">
+      <c r="V8" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="W8" s="40"/>
-      <c r="X8" s="40"/>
-      <c r="Y8" s="40"/>
-      <c r="Z8" s="40"/>
-      <c r="AA8" s="40"/>
-      <c r="AB8" s="40"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="38"/>
+      <c r="Y8" s="38"/>
+      <c r="Z8" s="38"/>
+      <c r="AA8" s="38"/>
+      <c r="AB8" s="38"/>
     </row>
     <row r="9" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
       <c r="O9"/>
@@ -1597,7 +1591,7 @@
     </row>
     <row r="11" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D11" s="15">
         <v>3</v>
@@ -1645,7 +1639,7 @@
         <v>50</v>
       </c>
       <c r="U11" s="20" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="V11" s="2">
         <v>3</v>
@@ -1673,77 +1667,77 @@
       <c r="C12" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="32"/>
+      <c r="D12" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="36"/>
       <c r="L12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="41" t="s">
+      <c r="M12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="N12" s="41"/>
-      <c r="O12" s="41"/>
-      <c r="P12" s="41"/>
-      <c r="Q12" s="41"/>
-      <c r="R12" s="41"/>
-      <c r="S12" s="41"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="39"/>
+      <c r="P12" s="39"/>
+      <c r="Q12" s="39"/>
+      <c r="R12" s="39"/>
+      <c r="S12" s="39"/>
       <c r="U12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V12" s="40" t="s">
+      <c r="V12" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="W12" s="40"/>
-      <c r="X12" s="40"/>
-      <c r="Y12" s="40"/>
-      <c r="Z12" s="40"/>
-      <c r="AA12" s="40"/>
-      <c r="AB12" s="40"/>
+      <c r="W12" s="38"/>
+      <c r="X12" s="38"/>
+      <c r="Y12" s="38"/>
+      <c r="Z12" s="38"/>
+      <c r="AA12" s="38"/>
+      <c r="AB12" s="38"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="C13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="32"/>
+      <c r="D13" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="36"/>
       <c r="L13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="41" t="s">
+      <c r="M13" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="N13" s="41"/>
-      <c r="O13" s="41"/>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="41"/>
-      <c r="S13" s="41"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="39"/>
+      <c r="Q13" s="39"/>
+      <c r="R13" s="39"/>
+      <c r="S13" s="39"/>
       <c r="U13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V13" s="40" t="s">
+      <c r="V13" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="W13" s="40"/>
-      <c r="X13" s="40"/>
-      <c r="Y13" s="40"/>
-      <c r="Z13" s="40"/>
-      <c r="AA13" s="40"/>
-      <c r="AB13" s="40"/>
+      <c r="W13" s="38"/>
+      <c r="X13" s="38"/>
+      <c r="Y13" s="38"/>
+      <c r="Z13" s="38"/>
+      <c r="AA13" s="38"/>
+      <c r="AB13" s="38"/>
     </row>
     <row r="14" spans="1:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O14"/>
@@ -1825,7 +1819,7 @@
     </row>
     <row r="16" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="C16" s="15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D16" s="15">
         <v>3</v>
@@ -1901,77 +1895,77 @@
       <c r="C17" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="28" t="s">
-        <v>149</v>
-      </c>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
+      <c r="D17" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
       <c r="L17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="41" t="s">
+      <c r="M17" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="N17" s="41"/>
-      <c r="O17" s="41"/>
-      <c r="P17" s="41"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="41"/>
-      <c r="S17" s="41"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="39"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="39"/>
+      <c r="R17" s="39"/>
+      <c r="S17" s="39"/>
       <c r="U17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V17" s="40" t="s">
+      <c r="V17" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="W17" s="40"/>
-      <c r="X17" s="40"/>
-      <c r="Y17" s="40"/>
-      <c r="Z17" s="40"/>
-      <c r="AA17" s="40"/>
-      <c r="AB17" s="40"/>
+      <c r="W17" s="38"/>
+      <c r="X17" s="38"/>
+      <c r="Y17" s="38"/>
+      <c r="Z17" s="38"/>
+      <c r="AA17" s="38"/>
+      <c r="AB17" s="38"/>
     </row>
     <row r="18" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
+      <c r="D18" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
       <c r="L18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="41" t="s">
+      <c r="M18" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="41"/>
-      <c r="O18" s="41"/>
-      <c r="P18" s="41"/>
-      <c r="Q18" s="41"/>
-      <c r="R18" s="41"/>
-      <c r="S18" s="41"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="39"/>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="39"/>
+      <c r="R18" s="39"/>
+      <c r="S18" s="39"/>
       <c r="U18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V18" s="40" t="s">
+      <c r="V18" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="W18" s="40"/>
-      <c r="X18" s="40"/>
-      <c r="Y18" s="40"/>
-      <c r="Z18" s="40"/>
-      <c r="AA18" s="40"/>
-      <c r="AB18" s="40"/>
+      <c r="W18" s="38"/>
+      <c r="X18" s="38"/>
+      <c r="Y18" s="38"/>
+      <c r="Z18" s="38"/>
+      <c r="AA18" s="38"/>
+      <c r="AB18" s="38"/>
     </row>
     <row r="19" spans="3:28" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C19" s="16"/>
@@ -1985,28 +1979,28 @@
       <c r="O19"/>
     </row>
     <row r="20" spans="3:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="D20" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="F20" s="26" t="s">
+      <c r="D20" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="J20" s="26" t="s">
+      <c r="G20" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="25" t="s">
         <v>19</v>
       </c>
       <c r="L20" s="6" t="s">
@@ -2035,32 +2029,32 @@
       </c>
     </row>
     <row r="21" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="D21" s="26">
-        <v>2</v>
-      </c>
-      <c r="E21" s="26">
-        <v>1</v>
-      </c>
-      <c r="F21" s="26" t="s">
+      <c r="C21" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="D21" s="25">
+        <v>2</v>
+      </c>
+      <c r="E21" s="25">
+        <v>1</v>
+      </c>
+      <c r="F21" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G21" s="26" t="s">
+      <c r="G21" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="I21" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="J21" s="26">
+      <c r="H21" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="25">
         <v>25</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M21" s="6">
         <v>3</v>
@@ -2085,56 +2079,56 @@
       </c>
     </row>
     <row r="22" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="28" t="s">
-        <v>204</v>
-      </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
+      <c r="D22" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="40"/>
       <c r="L22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="41" t="s">
+      <c r="M22" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="N22" s="41"/>
-      <c r="O22" s="41"/>
-      <c r="P22" s="41"/>
-      <c r="Q22" s="41"/>
-      <c r="R22" s="41"/>
-      <c r="S22" s="41"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="39"/>
+      <c r="R22" s="39"/>
+      <c r="S22" s="39"/>
     </row>
     <row r="23" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
+      <c r="D23" s="40" t="s">
+        <v>198</v>
+      </c>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
       <c r="L23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="41" t="s">
+      <c r="M23" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="N23" s="41"/>
-      <c r="O23" s="41"/>
-      <c r="P23" s="41"/>
-      <c r="Q23" s="41"/>
-      <c r="R23" s="41"/>
-      <c r="S23" s="41"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="39"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="39"/>
+      <c r="R23" s="39"/>
+      <c r="S23" s="39"/>
     </row>
     <row r="25" spans="3:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="15" t="s">
@@ -2188,7 +2182,7 @@
     </row>
     <row r="26" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="15" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D26" s="15">
         <v>6</v>
@@ -2240,77 +2234,77 @@
       <c r="C27" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="32"/>
+      <c r="D27" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="36"/>
       <c r="L27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M27" s="41" t="s">
+      <c r="M27" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="N27" s="41"/>
-      <c r="O27" s="41"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="41"/>
-      <c r="S27" s="41"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="39"/>
+      <c r="R27" s="39"/>
+      <c r="S27" s="39"/>
     </row>
     <row r="28" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="30" t="s">
-        <v>172</v>
-      </c>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="32"/>
+      <c r="D28" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="36"/>
       <c r="L28" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M28" s="39" t="s">
+      <c r="M28" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="N28" s="39"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="39"/>
-      <c r="R28" s="39"/>
-      <c r="S28" s="39"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="33"/>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="33"/>
+      <c r="S28" s="33"/>
     </row>
     <row r="30" spans="3:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F30" s="13" t="s">
+      <c r="D30" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="J30" s="13" t="s">
+      <c r="G30" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="H30" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="I30" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="J30" s="26" t="s">
         <v>19</v>
       </c>
       <c r="L30" s="11" t="s">
@@ -2339,28 +2333,28 @@
       </c>
     </row>
     <row r="31" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="D31" s="13">
-        <v>3</v>
-      </c>
-      <c r="E31" s="13">
-        <v>1</v>
-      </c>
-      <c r="F31" s="13" t="s">
+      <c r="D31" s="26">
+        <v>3</v>
+      </c>
+      <c r="E31" s="26">
+        <v>1</v>
+      </c>
+      <c r="F31" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="H31" s="13" t="s">
+      <c r="H31" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="I31" s="13" t="s">
+      <c r="I31" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="J31" s="13">
+      <c r="J31" s="26">
         <v>60</v>
       </c>
       <c r="L31" s="11" t="s">
@@ -2389,56 +2383,56 @@
       </c>
     </row>
     <row r="32" spans="3:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="33" t="s">
+      <c r="D32" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="36"/>
       <c r="L32" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M32" s="36" t="s">
+      <c r="M32" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="N32" s="37"/>
-      <c r="O32" s="37"/>
-      <c r="P32" s="37"/>
-      <c r="Q32" s="37"/>
-      <c r="R32" s="37"/>
-      <c r="S32" s="38"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="32"/>
     </row>
     <row r="33" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="33" t="s">
+      <c r="D33" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="35"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="36"/>
       <c r="L33" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M33" s="36" t="s">
+      <c r="M33" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="N33" s="37"/>
-      <c r="O33" s="37"/>
-      <c r="P33" s="37"/>
-      <c r="Q33" s="37"/>
-      <c r="R33" s="37"/>
-      <c r="S33" s="38"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="31"/>
+      <c r="S33" s="32"/>
     </row>
     <row r="35" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="15" t="s">
@@ -2492,7 +2486,7 @@
     </row>
     <row r="36" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D36" s="15">
         <v>2</v>
@@ -2544,53 +2538,53 @@
       <c r="C37" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
+      <c r="D37" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="40"/>
       <c r="L37" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M37" s="36" t="s">
+      <c r="M37" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="N37" s="37"/>
-      <c r="O37" s="37"/>
-      <c r="P37" s="37"/>
-      <c r="Q37" s="37"/>
-      <c r="R37" s="37"/>
-      <c r="S37" s="38"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="31"/>
+      <c r="S37" s="32"/>
     </row>
     <row r="38" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="28"/>
+      <c r="D38" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="40"/>
+      <c r="J38" s="40"/>
       <c r="L38" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M38" s="39" t="s">
-        <v>161</v>
-      </c>
-      <c r="N38" s="39"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="39"/>
-      <c r="Q38" s="39"/>
-      <c r="R38" s="39"/>
-      <c r="S38" s="39"/>
+      <c r="M38" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="N38" s="33"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="33"/>
+      <c r="Q38" s="33"/>
+      <c r="R38" s="33"/>
+      <c r="S38" s="33"/>
     </row>
     <row r="40" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="15" t="s">
@@ -2644,7 +2638,7 @@
     </row>
     <row r="41" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D41" s="15">
         <v>3</v>
@@ -2696,53 +2690,53 @@
       <c r="C42" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D42" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="E42" s="31"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="32"/>
+      <c r="D42" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="35"/>
+      <c r="J42" s="36"/>
       <c r="L42" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M42" s="36" t="s">
-        <v>185</v>
-      </c>
-      <c r="N42" s="37"/>
-      <c r="O42" s="37"/>
-      <c r="P42" s="37"/>
-      <c r="Q42" s="37"/>
-      <c r="R42" s="37"/>
-      <c r="S42" s="38"/>
+      <c r="M42" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="N42" s="31"/>
+      <c r="O42" s="31"/>
+      <c r="P42" s="31"/>
+      <c r="Q42" s="31"/>
+      <c r="R42" s="31"/>
+      <c r="S42" s="32"/>
     </row>
     <row r="43" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="E43" s="31"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="31"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="32"/>
+      <c r="D43" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="35"/>
+      <c r="J43" s="36"/>
       <c r="L43" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M43" s="36" t="s">
+      <c r="M43" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="N43" s="37"/>
-      <c r="O43" s="37"/>
-      <c r="P43" s="37"/>
-      <c r="Q43" s="37"/>
-      <c r="R43" s="37"/>
-      <c r="S43" s="38"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+      <c r="R43" s="31"/>
+      <c r="S43" s="32"/>
     </row>
     <row r="45" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="13" t="s">
@@ -2848,53 +2842,53 @@
       <c r="C47" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="33" t="s">
+      <c r="D47" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="E47" s="34"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="34"/>
-      <c r="H47" s="34"/>
-      <c r="I47" s="34"/>
-      <c r="J47" s="35"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="29"/>
       <c r="L47" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="36" t="s">
+      <c r="M47" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="N47" s="37"/>
-      <c r="O47" s="37"/>
-      <c r="P47" s="37"/>
-      <c r="Q47" s="37"/>
-      <c r="R47" s="37"/>
-      <c r="S47" s="38"/>
+      <c r="N47" s="31"/>
+      <c r="O47" s="31"/>
+      <c r="P47" s="31"/>
+      <c r="Q47" s="31"/>
+      <c r="R47" s="31"/>
+      <c r="S47" s="32"/>
     </row>
     <row r="48" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="33" t="s">
+      <c r="D48" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="E48" s="34"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="34"/>
-      <c r="H48" s="34"/>
-      <c r="I48" s="34"/>
-      <c r="J48" s="35"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="29"/>
       <c r="L48" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M48" s="36" t="s">
+      <c r="M48" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="N48" s="37"/>
-      <c r="O48" s="37"/>
-      <c r="P48" s="37"/>
-      <c r="Q48" s="37"/>
-      <c r="R48" s="37"/>
-      <c r="S48" s="38"/>
+      <c r="N48" s="31"/>
+      <c r="O48" s="31"/>
+      <c r="P48" s="31"/>
+      <c r="Q48" s="31"/>
+      <c r="R48" s="31"/>
+      <c r="S48" s="32"/>
     </row>
     <row r="50" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="13" t="s">
@@ -2948,7 +2942,7 @@
     </row>
     <row r="51" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D51" s="13">
         <v>3</v>
@@ -3000,53 +2994,53 @@
       <c r="C52" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D52" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="E52" s="34"/>
-      <c r="F52" s="34"/>
-      <c r="G52" s="34"/>
-      <c r="H52" s="34"/>
-      <c r="I52" s="34"/>
-      <c r="J52" s="35"/>
+      <c r="D52" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="29"/>
       <c r="L52" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M52" s="39" t="s">
-        <v>188</v>
-      </c>
-      <c r="N52" s="39"/>
-      <c r="O52" s="39"/>
-      <c r="P52" s="39"/>
-      <c r="Q52" s="39"/>
-      <c r="R52" s="39"/>
-      <c r="S52" s="39"/>
+      <c r="M52" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="N52" s="33"/>
+      <c r="O52" s="33"/>
+      <c r="P52" s="33"/>
+      <c r="Q52" s="33"/>
+      <c r="R52" s="33"/>
+      <c r="S52" s="33"/>
     </row>
     <row r="53" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="E53" s="34"/>
-      <c r="F53" s="34"/>
-      <c r="G53" s="34"/>
-      <c r="H53" s="34"/>
-      <c r="I53" s="34"/>
-      <c r="J53" s="35"/>
+      <c r="D53" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="28"/>
+      <c r="I53" s="28"/>
+      <c r="J53" s="29"/>
       <c r="L53" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M53" s="39" t="s">
+      <c r="M53" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="N53" s="39"/>
-      <c r="O53" s="39"/>
-      <c r="P53" s="39"/>
-      <c r="Q53" s="39"/>
-      <c r="R53" s="39"/>
-      <c r="S53" s="39"/>
+      <c r="N53" s="33"/>
+      <c r="O53" s="33"/>
+      <c r="P53" s="33"/>
+      <c r="Q53" s="33"/>
+      <c r="R53" s="33"/>
+      <c r="S53" s="33"/>
     </row>
     <row r="55" spans="3:19" ht="30" x14ac:dyDescent="0.25">
       <c r="C55" s="13" t="s">
@@ -3100,7 +3094,7 @@
     </row>
     <row r="56" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C56" s="13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D56" s="13">
         <v>3</v>
@@ -3152,53 +3146,53 @@
       <c r="C57" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="E57" s="34"/>
-      <c r="F57" s="34"/>
-      <c r="G57" s="34"/>
-      <c r="H57" s="34"/>
-      <c r="I57" s="34"/>
-      <c r="J57" s="35"/>
+      <c r="D57" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="29"/>
       <c r="L57" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M57" s="36" t="s">
+      <c r="M57" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="N57" s="37"/>
-      <c r="O57" s="37"/>
-      <c r="P57" s="37"/>
-      <c r="Q57" s="37"/>
-      <c r="R57" s="37"/>
-      <c r="S57" s="38"/>
+      <c r="N57" s="31"/>
+      <c r="O57" s="31"/>
+      <c r="P57" s="31"/>
+      <c r="Q57" s="31"/>
+      <c r="R57" s="31"/>
+      <c r="S57" s="32"/>
     </row>
     <row r="58" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C58" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="E58" s="34"/>
-      <c r="F58" s="34"/>
-      <c r="G58" s="34"/>
-      <c r="H58" s="34"/>
-      <c r="I58" s="34"/>
-      <c r="J58" s="35"/>
+      <c r="D58" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="29"/>
       <c r="L58" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M58" s="36" t="s">
+      <c r="M58" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="N58" s="37"/>
-      <c r="O58" s="37"/>
-      <c r="P58" s="37"/>
-      <c r="Q58" s="37"/>
-      <c r="R58" s="37"/>
-      <c r="S58" s="38"/>
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
+      <c r="P58" s="31"/>
+      <c r="Q58" s="31"/>
+      <c r="R58" s="31"/>
+      <c r="S58" s="32"/>
     </row>
     <row r="60" spans="3:19" ht="30" x14ac:dyDescent="0.25">
       <c r="C60" s="13" t="s">
@@ -3252,7 +3246,7 @@
     </row>
     <row r="61" spans="3:19" ht="45" x14ac:dyDescent="0.25">
       <c r="C61" s="13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D61" s="13">
         <v>3</v>
@@ -3304,53 +3298,53 @@
       <c r="C62" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D62" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="E62" s="34"/>
-      <c r="F62" s="34"/>
-      <c r="G62" s="34"/>
-      <c r="H62" s="34"/>
-      <c r="I62" s="34"/>
-      <c r="J62" s="35"/>
+      <c r="D62" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
+      <c r="G62" s="28"/>
+      <c r="H62" s="28"/>
+      <c r="I62" s="28"/>
+      <c r="J62" s="29"/>
       <c r="L62" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M62" s="39" t="s">
+      <c r="M62" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="N62" s="39"/>
-      <c r="O62" s="39"/>
-      <c r="P62" s="39"/>
-      <c r="Q62" s="39"/>
-      <c r="R62" s="39"/>
-      <c r="S62" s="39"/>
+      <c r="N62" s="33"/>
+      <c r="O62" s="33"/>
+      <c r="P62" s="33"/>
+      <c r="Q62" s="33"/>
+      <c r="R62" s="33"/>
+      <c r="S62" s="33"/>
     </row>
     <row r="63" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="E63" s="34"/>
-      <c r="F63" s="34"/>
-      <c r="G63" s="34"/>
-      <c r="H63" s="34"/>
-      <c r="I63" s="34"/>
-      <c r="J63" s="35"/>
+      <c r="D63" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
+      <c r="G63" s="28"/>
+      <c r="H63" s="28"/>
+      <c r="I63" s="28"/>
+      <c r="J63" s="29"/>
       <c r="L63" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M63" s="39" t="s">
+      <c r="M63" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="N63" s="39"/>
-      <c r="O63" s="39"/>
-      <c r="P63" s="39"/>
-      <c r="Q63" s="39"/>
-      <c r="R63" s="39"/>
-      <c r="S63" s="39"/>
+      <c r="N63" s="33"/>
+      <c r="O63" s="33"/>
+      <c r="P63" s="33"/>
+      <c r="Q63" s="33"/>
+      <c r="R63" s="33"/>
+      <c r="S63" s="33"/>
     </row>
     <row r="65" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="13" t="s">
@@ -3404,7 +3398,7 @@
     </row>
     <row r="66" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D66" s="13">
         <v>4</v>
@@ -3443,7 +3437,7 @@
         <v>7</v>
       </c>
       <c r="Q66" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R66" s="18" t="s">
         <v>8</v>
@@ -3456,53 +3450,53 @@
       <c r="C67" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="E67" s="34"/>
-      <c r="F67" s="34"/>
-      <c r="G67" s="34"/>
-      <c r="H67" s="34"/>
-      <c r="I67" s="34"/>
-      <c r="J67" s="35"/>
+      <c r="D67" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="H67" s="28"/>
+      <c r="I67" s="28"/>
+      <c r="J67" s="29"/>
       <c r="L67" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M67" s="36" t="s">
+      <c r="M67" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="N67" s="37"/>
-      <c r="O67" s="37"/>
-      <c r="P67" s="37"/>
-      <c r="Q67" s="37"/>
-      <c r="R67" s="37"/>
-      <c r="S67" s="38"/>
+      <c r="N67" s="31"/>
+      <c r="O67" s="31"/>
+      <c r="P67" s="31"/>
+      <c r="Q67" s="31"/>
+      <c r="R67" s="31"/>
+      <c r="S67" s="32"/>
     </row>
     <row r="68" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="33" t="s">
-        <v>157</v>
-      </c>
-      <c r="E68" s="34"/>
-      <c r="F68" s="34"/>
-      <c r="G68" s="34"/>
-      <c r="H68" s="34"/>
-      <c r="I68" s="34"/>
-      <c r="J68" s="35"/>
+      <c r="D68" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="E68" s="28"/>
+      <c r="F68" s="28"/>
+      <c r="G68" s="28"/>
+      <c r="H68" s="28"/>
+      <c r="I68" s="28"/>
+      <c r="J68" s="29"/>
       <c r="L68" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M68" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="N68" s="37"/>
-      <c r="O68" s="37"/>
-      <c r="P68" s="37"/>
-      <c r="Q68" s="37"/>
-      <c r="R68" s="37"/>
-      <c r="S68" s="38"/>
+      <c r="M68" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="N68" s="31"/>
+      <c r="O68" s="31"/>
+      <c r="P68" s="31"/>
+      <c r="Q68" s="31"/>
+      <c r="R68" s="31"/>
+      <c r="S68" s="32"/>
     </row>
     <row r="70" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="13" t="s">
@@ -3556,7 +3550,7 @@
     </row>
     <row r="71" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D71" s="13">
         <v>3</v>
@@ -3595,7 +3589,7 @@
         <v>7</v>
       </c>
       <c r="Q71" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R71" s="18" t="s">
         <v>8</v>
@@ -3608,53 +3602,53 @@
       <c r="C72" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="E72" s="34"/>
-      <c r="F72" s="34"/>
-      <c r="G72" s="34"/>
-      <c r="H72" s="34"/>
-      <c r="I72" s="34"/>
-      <c r="J72" s="35"/>
+      <c r="D72" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="E72" s="28"/>
+      <c r="F72" s="28"/>
+      <c r="G72" s="28"/>
+      <c r="H72" s="28"/>
+      <c r="I72" s="28"/>
+      <c r="J72" s="29"/>
       <c r="L72" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M72" s="36" t="s">
+      <c r="M72" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="N72" s="37"/>
-      <c r="O72" s="37"/>
-      <c r="P72" s="37"/>
-      <c r="Q72" s="37"/>
-      <c r="R72" s="37"/>
-      <c r="S72" s="38"/>
+      <c r="N72" s="31"/>
+      <c r="O72" s="31"/>
+      <c r="P72" s="31"/>
+      <c r="Q72" s="31"/>
+      <c r="R72" s="31"/>
+      <c r="S72" s="32"/>
     </row>
     <row r="73" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="E73" s="34"/>
-      <c r="F73" s="34"/>
-      <c r="G73" s="34"/>
-      <c r="H73" s="34"/>
-      <c r="I73" s="34"/>
-      <c r="J73" s="35"/>
+      <c r="D73" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
+      <c r="G73" s="28"/>
+      <c r="H73" s="28"/>
+      <c r="I73" s="28"/>
+      <c r="J73" s="29"/>
       <c r="L73" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M73" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="N73" s="39"/>
-      <c r="O73" s="39"/>
-      <c r="P73" s="39"/>
-      <c r="Q73" s="39"/>
-      <c r="R73" s="39"/>
-      <c r="S73" s="39"/>
+      <c r="M73" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="N73" s="33"/>
+      <c r="O73" s="33"/>
+      <c r="P73" s="33"/>
+      <c r="Q73" s="33"/>
+      <c r="R73" s="33"/>
+      <c r="S73" s="33"/>
     </row>
     <row r="75" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="13" t="s">
@@ -3760,53 +3754,53 @@
       <c r="C77" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="33" t="s">
+      <c r="D77" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="E77" s="34"/>
-      <c r="F77" s="34"/>
-      <c r="G77" s="34"/>
-      <c r="H77" s="34"/>
-      <c r="I77" s="34"/>
-      <c r="J77" s="35"/>
+      <c r="E77" s="28"/>
+      <c r="F77" s="28"/>
+      <c r="G77" s="28"/>
+      <c r="H77" s="28"/>
+      <c r="I77" s="28"/>
+      <c r="J77" s="29"/>
       <c r="L77" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M77" s="36" t="s">
+      <c r="M77" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="N77" s="37"/>
-      <c r="O77" s="37"/>
-      <c r="P77" s="37"/>
-      <c r="Q77" s="37"/>
-      <c r="R77" s="37"/>
-      <c r="S77" s="38"/>
+      <c r="N77" s="31"/>
+      <c r="O77" s="31"/>
+      <c r="P77" s="31"/>
+      <c r="Q77" s="31"/>
+      <c r="R77" s="31"/>
+      <c r="S77" s="32"/>
     </row>
     <row r="78" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C78" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="33" t="s">
+      <c r="D78" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="E78" s="34"/>
-      <c r="F78" s="34"/>
-      <c r="G78" s="34"/>
-      <c r="H78" s="34"/>
-      <c r="I78" s="34"/>
-      <c r="J78" s="35"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="28"/>
+      <c r="G78" s="28"/>
+      <c r="H78" s="28"/>
+      <c r="I78" s="28"/>
+      <c r="J78" s="29"/>
       <c r="L78" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M78" s="36" t="s">
+      <c r="M78" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="N78" s="37"/>
-      <c r="O78" s="37"/>
-      <c r="P78" s="37"/>
-      <c r="Q78" s="37"/>
-      <c r="R78" s="37"/>
-      <c r="S78" s="38"/>
+      <c r="N78" s="31"/>
+      <c r="O78" s="31"/>
+      <c r="P78" s="31"/>
+      <c r="Q78" s="31"/>
+      <c r="R78" s="31"/>
+      <c r="S78" s="32"/>
     </row>
     <row r="80" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C80" s="23" t="s">
@@ -3860,7 +3854,7 @@
     </row>
     <row r="81" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C81" s="23" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D81" s="23">
         <v>5</v>
@@ -3912,53 +3906,53 @@
       <c r="C82" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="33" t="s">
-        <v>179</v>
-      </c>
-      <c r="E82" s="34"/>
-      <c r="F82" s="34"/>
-      <c r="G82" s="34"/>
-      <c r="H82" s="34"/>
-      <c r="I82" s="34"/>
-      <c r="J82" s="35"/>
+      <c r="D82" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="E82" s="28"/>
+      <c r="F82" s="28"/>
+      <c r="G82" s="28"/>
+      <c r="H82" s="28"/>
+      <c r="I82" s="28"/>
+      <c r="J82" s="29"/>
       <c r="L82" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M82" s="36" t="s">
+      <c r="M82" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="N82" s="37"/>
-      <c r="O82" s="37"/>
-      <c r="P82" s="37"/>
-      <c r="Q82" s="37"/>
-      <c r="R82" s="37"/>
-      <c r="S82" s="38"/>
+      <c r="N82" s="31"/>
+      <c r="O82" s="31"/>
+      <c r="P82" s="31"/>
+      <c r="Q82" s="31"/>
+      <c r="R82" s="31"/>
+      <c r="S82" s="32"/>
     </row>
     <row r="83" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C83" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D83" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="E83" s="34"/>
-      <c r="F83" s="34"/>
-      <c r="G83" s="34"/>
-      <c r="H83" s="34"/>
-      <c r="I83" s="34"/>
-      <c r="J83" s="35"/>
+      <c r="D83" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="E83" s="28"/>
+      <c r="F83" s="28"/>
+      <c r="G83" s="28"/>
+      <c r="H83" s="28"/>
+      <c r="I83" s="28"/>
+      <c r="J83" s="29"/>
       <c r="L83" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M83" s="36" t="s">
+      <c r="M83" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="N83" s="37"/>
-      <c r="O83" s="37"/>
-      <c r="P83" s="37"/>
-      <c r="Q83" s="37"/>
-      <c r="R83" s="37"/>
-      <c r="S83" s="38"/>
+      <c r="N83" s="31"/>
+      <c r="O83" s="31"/>
+      <c r="P83" s="31"/>
+      <c r="Q83" s="31"/>
+      <c r="R83" s="31"/>
+      <c r="S83" s="32"/>
     </row>
     <row r="84" spans="3:19" x14ac:dyDescent="0.25">
       <c r="O84"/>
@@ -4067,53 +4061,53 @@
       <c r="C87" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D87" s="33" t="s">
+      <c r="D87" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="E87" s="34"/>
-      <c r="F87" s="34"/>
-      <c r="G87" s="34"/>
-      <c r="H87" s="34"/>
-      <c r="I87" s="34"/>
-      <c r="J87" s="35"/>
+      <c r="E87" s="28"/>
+      <c r="F87" s="28"/>
+      <c r="G87" s="28"/>
+      <c r="H87" s="28"/>
+      <c r="I87" s="28"/>
+      <c r="J87" s="29"/>
       <c r="L87" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M87" s="36" t="s">
+      <c r="M87" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="N87" s="37"/>
-      <c r="O87" s="37"/>
-      <c r="P87" s="37"/>
-      <c r="Q87" s="37"/>
-      <c r="R87" s="37"/>
-      <c r="S87" s="38"/>
+      <c r="N87" s="31"/>
+      <c r="O87" s="31"/>
+      <c r="P87" s="31"/>
+      <c r="Q87" s="31"/>
+      <c r="R87" s="31"/>
+      <c r="S87" s="32"/>
     </row>
     <row r="88" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C88" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D88" s="33" t="s">
+      <c r="D88" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="E88" s="34"/>
-      <c r="F88" s="34"/>
-      <c r="G88" s="34"/>
-      <c r="H88" s="34"/>
-      <c r="I88" s="34"/>
-      <c r="J88" s="35"/>
+      <c r="E88" s="28"/>
+      <c r="F88" s="28"/>
+      <c r="G88" s="28"/>
+      <c r="H88" s="28"/>
+      <c r="I88" s="28"/>
+      <c r="J88" s="29"/>
       <c r="L88" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M88" s="36" t="s">
+      <c r="M88" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="N88" s="37"/>
-      <c r="O88" s="37"/>
-      <c r="P88" s="37"/>
-      <c r="Q88" s="37"/>
-      <c r="R88" s="37"/>
-      <c r="S88" s="38"/>
+      <c r="N88" s="31"/>
+      <c r="O88" s="31"/>
+      <c r="P88" s="31"/>
+      <c r="Q88" s="31"/>
+      <c r="R88" s="31"/>
+      <c r="S88" s="32"/>
     </row>
     <row r="90" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="13" t="s">
@@ -4219,53 +4213,53 @@
       <c r="C92" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D92" s="33" t="s">
+      <c r="D92" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="E92" s="34"/>
-      <c r="F92" s="34"/>
-      <c r="G92" s="34"/>
-      <c r="H92" s="34"/>
-      <c r="I92" s="34"/>
-      <c r="J92" s="35"/>
+      <c r="E92" s="28"/>
+      <c r="F92" s="28"/>
+      <c r="G92" s="28"/>
+      <c r="H92" s="28"/>
+      <c r="I92" s="28"/>
+      <c r="J92" s="29"/>
       <c r="L92" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M92" s="36" t="s">
+      <c r="M92" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="N92" s="37"/>
-      <c r="O92" s="37"/>
-      <c r="P92" s="37"/>
-      <c r="Q92" s="37"/>
-      <c r="R92" s="37"/>
-      <c r="S92" s="38"/>
+      <c r="N92" s="31"/>
+      <c r="O92" s="31"/>
+      <c r="P92" s="31"/>
+      <c r="Q92" s="31"/>
+      <c r="R92" s="31"/>
+      <c r="S92" s="32"/>
     </row>
     <row r="93" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C93" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="33" t="s">
+      <c r="D93" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="E93" s="34"/>
-      <c r="F93" s="34"/>
-      <c r="G93" s="34"/>
-      <c r="H93" s="34"/>
-      <c r="I93" s="34"/>
-      <c r="J93" s="35"/>
+      <c r="E93" s="28"/>
+      <c r="F93" s="28"/>
+      <c r="G93" s="28"/>
+      <c r="H93" s="28"/>
+      <c r="I93" s="28"/>
+      <c r="J93" s="29"/>
       <c r="L93" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M93" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="N93" s="37"/>
-      <c r="O93" s="37"/>
-      <c r="P93" s="37"/>
-      <c r="Q93" s="37"/>
-      <c r="R93" s="37"/>
-      <c r="S93" s="38"/>
+      <c r="M93" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="N93" s="31"/>
+      <c r="O93" s="31"/>
+      <c r="P93" s="31"/>
+      <c r="Q93" s="31"/>
+      <c r="R93" s="31"/>
+      <c r="S93" s="32"/>
     </row>
     <row r="95" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C95" s="13" t="s">
@@ -4371,53 +4365,53 @@
       <c r="C97" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="33" t="s">
+      <c r="D97" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="E97" s="34"/>
-      <c r="F97" s="34"/>
-      <c r="G97" s="34"/>
-      <c r="H97" s="34"/>
-      <c r="I97" s="34"/>
-      <c r="J97" s="35"/>
+      <c r="E97" s="28"/>
+      <c r="F97" s="28"/>
+      <c r="G97" s="28"/>
+      <c r="H97" s="28"/>
+      <c r="I97" s="28"/>
+      <c r="J97" s="29"/>
       <c r="L97" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M97" s="36" t="s">
+      <c r="M97" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="N97" s="37"/>
-      <c r="O97" s="37"/>
-      <c r="P97" s="37"/>
-      <c r="Q97" s="37"/>
-      <c r="R97" s="37"/>
-      <c r="S97" s="38"/>
+      <c r="N97" s="31"/>
+      <c r="O97" s="31"/>
+      <c r="P97" s="31"/>
+      <c r="Q97" s="31"/>
+      <c r="R97" s="31"/>
+      <c r="S97" s="32"/>
     </row>
     <row r="98" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C98" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D98" s="33" t="s">
+      <c r="D98" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="E98" s="34"/>
-      <c r="F98" s="34"/>
-      <c r="G98" s="34"/>
-      <c r="H98" s="34"/>
-      <c r="I98" s="34"/>
-      <c r="J98" s="35"/>
+      <c r="E98" s="28"/>
+      <c r="F98" s="28"/>
+      <c r="G98" s="28"/>
+      <c r="H98" s="28"/>
+      <c r="I98" s="28"/>
+      <c r="J98" s="29"/>
       <c r="L98" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M98" s="36" t="s">
+      <c r="M98" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="N98" s="37"/>
-      <c r="O98" s="37"/>
-      <c r="P98" s="37"/>
-      <c r="Q98" s="37"/>
-      <c r="R98" s="37"/>
-      <c r="S98" s="38"/>
+      <c r="N98" s="31"/>
+      <c r="O98" s="31"/>
+      <c r="P98" s="31"/>
+      <c r="Q98" s="31"/>
+      <c r="R98" s="31"/>
+      <c r="S98" s="32"/>
     </row>
     <row r="99" spans="3:19" x14ac:dyDescent="0.25">
       <c r="O99"/>
@@ -4526,53 +4520,53 @@
       <c r="C102" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D102" s="33" t="s">
+      <c r="D102" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="E102" s="34"/>
-      <c r="F102" s="34"/>
-      <c r="G102" s="34"/>
-      <c r="H102" s="34"/>
-      <c r="I102" s="34"/>
-      <c r="J102" s="35"/>
+      <c r="E102" s="28"/>
+      <c r="F102" s="28"/>
+      <c r="G102" s="28"/>
+      <c r="H102" s="28"/>
+      <c r="I102" s="28"/>
+      <c r="J102" s="29"/>
       <c r="L102" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M102" s="36" t="s">
+      <c r="M102" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="N102" s="37"/>
-      <c r="O102" s="37"/>
-      <c r="P102" s="37"/>
-      <c r="Q102" s="37"/>
-      <c r="R102" s="37"/>
-      <c r="S102" s="38"/>
+      <c r="N102" s="31"/>
+      <c r="O102" s="31"/>
+      <c r="P102" s="31"/>
+      <c r="Q102" s="31"/>
+      <c r="R102" s="31"/>
+      <c r="S102" s="32"/>
     </row>
     <row r="103" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C103" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D103" s="33" t="s">
+      <c r="D103" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="E103" s="34"/>
-      <c r="F103" s="34"/>
-      <c r="G103" s="34"/>
-      <c r="H103" s="34"/>
-      <c r="I103" s="34"/>
-      <c r="J103" s="35"/>
+      <c r="E103" s="28"/>
+      <c r="F103" s="28"/>
+      <c r="G103" s="28"/>
+      <c r="H103" s="28"/>
+      <c r="I103" s="28"/>
+      <c r="J103" s="29"/>
       <c r="L103" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M103" s="36" t="s">
+      <c r="M103" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="N103" s="37"/>
-      <c r="O103" s="37"/>
-      <c r="P103" s="37"/>
-      <c r="Q103" s="37"/>
-      <c r="R103" s="37"/>
-      <c r="S103" s="38"/>
+      <c r="N103" s="31"/>
+      <c r="O103" s="31"/>
+      <c r="P103" s="31"/>
+      <c r="Q103" s="31"/>
+      <c r="R103" s="31"/>
+      <c r="S103" s="32"/>
     </row>
     <row r="104" spans="3:19" x14ac:dyDescent="0.25">
       <c r="O104"/>
@@ -4653,7 +4647,7 @@
         <v>100</v>
       </c>
       <c r="L106" s="21" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M106" s="21">
         <v>3</v>
@@ -4681,53 +4675,53 @@
       <c r="C107" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="33" t="s">
+      <c r="D107" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="E107" s="34"/>
-      <c r="F107" s="34"/>
-      <c r="G107" s="34"/>
-      <c r="H107" s="34"/>
-      <c r="I107" s="34"/>
-      <c r="J107" s="35"/>
+      <c r="E107" s="28"/>
+      <c r="F107" s="28"/>
+      <c r="G107" s="28"/>
+      <c r="H107" s="28"/>
+      <c r="I107" s="28"/>
+      <c r="J107" s="29"/>
       <c r="L107" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M107" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="N107" s="39"/>
-      <c r="O107" s="39"/>
-      <c r="P107" s="39"/>
-      <c r="Q107" s="39"/>
-      <c r="R107" s="39"/>
-      <c r="S107" s="39"/>
+      <c r="M107" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="N107" s="33"/>
+      <c r="O107" s="33"/>
+      <c r="P107" s="33"/>
+      <c r="Q107" s="33"/>
+      <c r="R107" s="33"/>
+      <c r="S107" s="33"/>
     </row>
     <row r="108" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C108" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="33" t="s">
+      <c r="D108" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="E108" s="34"/>
-      <c r="F108" s="34"/>
-      <c r="G108" s="34"/>
-      <c r="H108" s="34"/>
-      <c r="I108" s="34"/>
-      <c r="J108" s="35"/>
+      <c r="E108" s="28"/>
+      <c r="F108" s="28"/>
+      <c r="G108" s="28"/>
+      <c r="H108" s="28"/>
+      <c r="I108" s="28"/>
+      <c r="J108" s="29"/>
       <c r="L108" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M108" s="39" t="s">
-        <v>175</v>
-      </c>
-      <c r="N108" s="39"/>
-      <c r="O108" s="39"/>
-      <c r="P108" s="39"/>
-      <c r="Q108" s="39"/>
-      <c r="R108" s="39"/>
-      <c r="S108" s="39"/>
+      <c r="M108" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="N108" s="33"/>
+      <c r="O108" s="33"/>
+      <c r="P108" s="33"/>
+      <c r="Q108" s="33"/>
+      <c r="R108" s="33"/>
+      <c r="S108" s="33"/>
     </row>
     <row r="110" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C110" s="13" t="s">
@@ -4833,77 +4827,77 @@
       <c r="C112" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D112" s="33" t="s">
+      <c r="D112" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="E112" s="34"/>
-      <c r="F112" s="34"/>
-      <c r="G112" s="34"/>
-      <c r="H112" s="34"/>
-      <c r="I112" s="34"/>
-      <c r="J112" s="35"/>
+      <c r="E112" s="28"/>
+      <c r="F112" s="28"/>
+      <c r="G112" s="28"/>
+      <c r="H112" s="28"/>
+      <c r="I112" s="28"/>
+      <c r="J112" s="29"/>
       <c r="L112" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M112" s="36" t="s">
+      <c r="M112" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="N112" s="37"/>
-      <c r="O112" s="37"/>
-      <c r="P112" s="37"/>
-      <c r="Q112" s="37"/>
-      <c r="R112" s="37"/>
-      <c r="S112" s="38"/>
+      <c r="N112" s="31"/>
+      <c r="O112" s="31"/>
+      <c r="P112" s="31"/>
+      <c r="Q112" s="31"/>
+      <c r="R112" s="31"/>
+      <c r="S112" s="32"/>
     </row>
     <row r="113" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C113" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D113" s="33" t="s">
+      <c r="D113" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="E113" s="34"/>
-      <c r="F113" s="34"/>
-      <c r="G113" s="34"/>
-      <c r="H113" s="34"/>
-      <c r="I113" s="34"/>
-      <c r="J113" s="35"/>
+      <c r="E113" s="28"/>
+      <c r="F113" s="28"/>
+      <c r="G113" s="28"/>
+      <c r="H113" s="28"/>
+      <c r="I113" s="28"/>
+      <c r="J113" s="29"/>
       <c r="L113" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M113" s="36" t="s">
+      <c r="M113" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="N113" s="37"/>
-      <c r="O113" s="37"/>
-      <c r="P113" s="37"/>
-      <c r="Q113" s="37"/>
-      <c r="R113" s="37"/>
-      <c r="S113" s="38"/>
+      <c r="N113" s="31"/>
+      <c r="O113" s="31"/>
+      <c r="P113" s="31"/>
+      <c r="Q113" s="31"/>
+      <c r="R113" s="31"/>
+      <c r="S113" s="32"/>
     </row>
     <row r="115" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C115" s="24" t="s">
+      <c r="C115" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="D115" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E115" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="F115" s="24" t="s">
+      <c r="D115" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E115" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F115" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="G115" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="H115" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="I115" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="J115" s="24" t="s">
+      <c r="G115" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="H115" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="I115" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J115" s="23" t="s">
         <v>19</v>
       </c>
       <c r="L115" s="21" t="s">
@@ -4932,32 +4926,32 @@
       </c>
     </row>
     <row r="116" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C116" s="24" t="s">
+      <c r="C116" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="D116" s="23">
+        <v>1</v>
+      </c>
+      <c r="E116" s="23">
+        <v>1</v>
+      </c>
+      <c r="F116" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G116" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="H116" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="I116" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="J116" s="23">
+        <v>10</v>
+      </c>
+      <c r="L116" s="21" t="s">
         <v>128</v>
-      </c>
-      <c r="D116" s="24">
-        <v>2</v>
-      </c>
-      <c r="E116" s="24">
-        <v>0</v>
-      </c>
-      <c r="F116" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="G116" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="H116" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="I116" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="J116" s="24">
-        <v>10</v>
-      </c>
-      <c r="L116" s="21" t="s">
-        <v>129</v>
       </c>
       <c r="M116" s="21">
         <v>3</v>
@@ -4975,63 +4969,63 @@
         <v>35</v>
       </c>
       <c r="R116" s="21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S116" s="21">
         <v>25</v>
       </c>
     </row>
     <row r="117" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C117" s="24" t="s">
+      <c r="C117" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D117" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="E117" s="34"/>
-      <c r="F117" s="34"/>
-      <c r="G117" s="34"/>
-      <c r="H117" s="34"/>
-      <c r="I117" s="34"/>
-      <c r="J117" s="35"/>
+      <c r="D117" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="E117" s="42"/>
+      <c r="F117" s="42"/>
+      <c r="G117" s="42"/>
+      <c r="H117" s="42"/>
+      <c r="I117" s="42"/>
+      <c r="J117" s="42"/>
       <c r="L117" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M117" s="36" t="s">
-        <v>131</v>
-      </c>
-      <c r="N117" s="37"/>
-      <c r="O117" s="37"/>
-      <c r="P117" s="37"/>
-      <c r="Q117" s="37"/>
-      <c r="R117" s="37"/>
-      <c r="S117" s="38"/>
+      <c r="M117" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="N117" s="31"/>
+      <c r="O117" s="31"/>
+      <c r="P117" s="31"/>
+      <c r="Q117" s="31"/>
+      <c r="R117" s="31"/>
+      <c r="S117" s="32"/>
     </row>
     <row r="118" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C118" s="24" t="s">
+      <c r="C118" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D118" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="E118" s="34"/>
-      <c r="F118" s="34"/>
-      <c r="G118" s="34"/>
-      <c r="H118" s="34"/>
-      <c r="I118" s="34"/>
-      <c r="J118" s="35"/>
+      <c r="D118" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="E118" s="42"/>
+      <c r="F118" s="42"/>
+      <c r="G118" s="42"/>
+      <c r="H118" s="42"/>
+      <c r="I118" s="42"/>
+      <c r="J118" s="42"/>
       <c r="L118" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M118" s="36" t="s">
-        <v>169</v>
-      </c>
-      <c r="N118" s="37"/>
-      <c r="O118" s="37"/>
-      <c r="P118" s="37"/>
-      <c r="Q118" s="37"/>
-      <c r="R118" s="37"/>
-      <c r="S118" s="38"/>
+      <c r="M118" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="N118" s="31"/>
+      <c r="O118" s="31"/>
+      <c r="P118" s="31"/>
+      <c r="Q118" s="31"/>
+      <c r="R118" s="31"/>
+      <c r="S118" s="32"/>
     </row>
     <row r="120" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C120" s="23" t="s">
@@ -5085,7 +5079,7 @@
     </row>
     <row r="121" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C121" s="23" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D121" s="23">
         <v>2</v>
@@ -5109,7 +5103,7 @@
         <v>30</v>
       </c>
       <c r="L121" s="22" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M121" s="22">
         <v>2</v>
@@ -5137,53 +5131,53 @@
       <c r="C122" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D122" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="E122" s="27"/>
-      <c r="F122" s="27"/>
-      <c r="G122" s="27"/>
-      <c r="H122" s="27"/>
-      <c r="I122" s="27"/>
-      <c r="J122" s="27"/>
+      <c r="D122" s="42" t="s">
+        <v>200</v>
+      </c>
+      <c r="E122" s="42"/>
+      <c r="F122" s="42"/>
+      <c r="G122" s="42"/>
+      <c r="H122" s="42"/>
+      <c r="I122" s="42"/>
+      <c r="J122" s="42"/>
       <c r="L122" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M122" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="N122" s="39"/>
-      <c r="O122" s="39"/>
-      <c r="P122" s="39"/>
-      <c r="Q122" s="39"/>
-      <c r="R122" s="39"/>
-      <c r="S122" s="39"/>
+      <c r="M122" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="N122" s="33"/>
+      <c r="O122" s="33"/>
+      <c r="P122" s="33"/>
+      <c r="Q122" s="33"/>
+      <c r="R122" s="33"/>
+      <c r="S122" s="33"/>
     </row>
     <row r="123" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C123" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D123" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="E123" s="27"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="27"/>
-      <c r="H123" s="27"/>
-      <c r="I123" s="27"/>
-      <c r="J123" s="27"/>
+      <c r="D123" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="E123" s="42"/>
+      <c r="F123" s="42"/>
+      <c r="G123" s="42"/>
+      <c r="H123" s="42"/>
+      <c r="I123" s="42"/>
+      <c r="J123" s="42"/>
       <c r="L123" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="M123" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="N123" s="39"/>
-      <c r="O123" s="39"/>
-      <c r="P123" s="39"/>
-      <c r="Q123" s="39"/>
-      <c r="R123" s="39"/>
-      <c r="S123" s="39"/>
+      <c r="M123" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="N123" s="33"/>
+      <c r="O123" s="33"/>
+      <c r="P123" s="33"/>
+      <c r="Q123" s="33"/>
+      <c r="R123" s="33"/>
+      <c r="S123" s="33"/>
     </row>
     <row r="124" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C124" s="16"/>
@@ -5247,7 +5241,7 @@
     </row>
     <row r="126" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C126" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D126" s="13">
         <v>4</v>
@@ -5265,7 +5259,7 @@
         <v>8</v>
       </c>
       <c r="I126" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J126" s="13">
         <v>50</v>
@@ -5299,53 +5293,53 @@
       <c r="C127" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D127" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="E127" s="34"/>
-      <c r="F127" s="34"/>
-      <c r="G127" s="34"/>
-      <c r="H127" s="34"/>
-      <c r="I127" s="34"/>
-      <c r="J127" s="35"/>
+      <c r="D127" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="E127" s="28"/>
+      <c r="F127" s="28"/>
+      <c r="G127" s="28"/>
+      <c r="H127" s="28"/>
+      <c r="I127" s="28"/>
+      <c r="J127" s="29"/>
       <c r="L127" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M127" s="36" t="s">
+      <c r="M127" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="N127" s="37"/>
-      <c r="O127" s="37"/>
-      <c r="P127" s="37"/>
-      <c r="Q127" s="37"/>
-      <c r="R127" s="37"/>
-      <c r="S127" s="38"/>
+      <c r="N127" s="31"/>
+      <c r="O127" s="31"/>
+      <c r="P127" s="31"/>
+      <c r="Q127" s="31"/>
+      <c r="R127" s="31"/>
+      <c r="S127" s="32"/>
     </row>
     <row r="128" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C128" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D128" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="E128" s="34"/>
-      <c r="F128" s="34"/>
-      <c r="G128" s="34"/>
-      <c r="H128" s="34"/>
-      <c r="I128" s="34"/>
-      <c r="J128" s="35"/>
+      <c r="D128" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E128" s="28"/>
+      <c r="F128" s="28"/>
+      <c r="G128" s="28"/>
+      <c r="H128" s="28"/>
+      <c r="I128" s="28"/>
+      <c r="J128" s="29"/>
       <c r="L128" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="M128" s="36" t="s">
+      <c r="M128" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="N128" s="37"/>
-      <c r="O128" s="37"/>
-      <c r="P128" s="37"/>
-      <c r="Q128" s="37"/>
-      <c r="R128" s="37"/>
-      <c r="S128" s="38"/>
+      <c r="N128" s="31"/>
+      <c r="O128" s="31"/>
+      <c r="P128" s="31"/>
+      <c r="Q128" s="31"/>
+      <c r="R128" s="31"/>
+      <c r="S128" s="32"/>
     </row>
     <row r="130" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C130" s="23" t="s">
@@ -5399,7 +5393,7 @@
     </row>
     <row r="131" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C131" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D131" s="23">
         <v>5</v>
@@ -5417,7 +5411,7 @@
         <v>8</v>
       </c>
       <c r="I131" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J131" s="23">
         <v>70</v>
@@ -5451,53 +5445,53 @@
       <c r="C132" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D132" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="E132" s="34"/>
-      <c r="F132" s="34"/>
-      <c r="G132" s="34"/>
-      <c r="H132" s="34"/>
-      <c r="I132" s="34"/>
-      <c r="J132" s="35"/>
+      <c r="D132" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="E132" s="28"/>
+      <c r="F132" s="28"/>
+      <c r="G132" s="28"/>
+      <c r="H132" s="28"/>
+      <c r="I132" s="28"/>
+      <c r="J132" s="29"/>
       <c r="L132" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M132" s="36" t="s">
+      <c r="M132" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="N132" s="37"/>
-      <c r="O132" s="37"/>
-      <c r="P132" s="37"/>
-      <c r="Q132" s="37"/>
-      <c r="R132" s="37"/>
-      <c r="S132" s="38"/>
+      <c r="N132" s="31"/>
+      <c r="O132" s="31"/>
+      <c r="P132" s="31"/>
+      <c r="Q132" s="31"/>
+      <c r="R132" s="31"/>
+      <c r="S132" s="32"/>
     </row>
     <row r="133" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C133" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D133" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E133" s="34"/>
-      <c r="F133" s="34"/>
-      <c r="G133" s="34"/>
-      <c r="H133" s="34"/>
-      <c r="I133" s="34"/>
-      <c r="J133" s="35"/>
+      <c r="D133" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="E133" s="28"/>
+      <c r="F133" s="28"/>
+      <c r="G133" s="28"/>
+      <c r="H133" s="28"/>
+      <c r="I133" s="28"/>
+      <c r="J133" s="29"/>
       <c r="L133" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="M133" s="36" t="s">
+      <c r="M133" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="N133" s="37"/>
-      <c r="O133" s="37"/>
-      <c r="P133" s="37"/>
-      <c r="Q133" s="37"/>
-      <c r="R133" s="37"/>
-      <c r="S133" s="38"/>
+      <c r="N133" s="31"/>
+      <c r="O133" s="31"/>
+      <c r="P133" s="31"/>
+      <c r="Q133" s="31"/>
+      <c r="R133" s="31"/>
+      <c r="S133" s="32"/>
     </row>
     <row r="134" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M134"/>
@@ -5558,7 +5552,7 @@
     </row>
     <row r="136" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C136" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D136" s="23">
         <v>2</v>
@@ -5582,7 +5576,7 @@
         <v>25</v>
       </c>
       <c r="L136" s="22" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M136" s="22">
         <v>3</v>
@@ -5610,53 +5604,53 @@
       <c r="C137" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D137" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="E137" s="34"/>
-      <c r="F137" s="34"/>
-      <c r="G137" s="34"/>
-      <c r="H137" s="34"/>
-      <c r="I137" s="34"/>
-      <c r="J137" s="35"/>
+      <c r="D137" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="E137" s="28"/>
+      <c r="F137" s="28"/>
+      <c r="G137" s="28"/>
+      <c r="H137" s="28"/>
+      <c r="I137" s="28"/>
+      <c r="J137" s="29"/>
       <c r="L137" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M137" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="N137" s="37"/>
-      <c r="O137" s="37"/>
-      <c r="P137" s="37"/>
-      <c r="Q137" s="37"/>
-      <c r="R137" s="37"/>
-      <c r="S137" s="38"/>
+      <c r="M137" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="N137" s="31"/>
+      <c r="O137" s="31"/>
+      <c r="P137" s="31"/>
+      <c r="Q137" s="31"/>
+      <c r="R137" s="31"/>
+      <c r="S137" s="32"/>
     </row>
     <row r="138" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C138" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D138" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E138" s="34"/>
-      <c r="F138" s="34"/>
-      <c r="G138" s="34"/>
-      <c r="H138" s="34"/>
-      <c r="I138" s="34"/>
-      <c r="J138" s="35"/>
+      <c r="D138" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="E138" s="28"/>
+      <c r="F138" s="28"/>
+      <c r="G138" s="28"/>
+      <c r="H138" s="28"/>
+      <c r="I138" s="28"/>
+      <c r="J138" s="29"/>
       <c r="L138" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="M138" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="N138" s="37"/>
-      <c r="O138" s="37"/>
-      <c r="P138" s="37"/>
-      <c r="Q138" s="37"/>
-      <c r="R138" s="37"/>
-      <c r="S138" s="38"/>
+      <c r="M138" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="N138" s="31"/>
+      <c r="O138" s="31"/>
+      <c r="P138" s="31"/>
+      <c r="Q138" s="31"/>
+      <c r="R138" s="31"/>
+      <c r="S138" s="32"/>
     </row>
     <row r="139" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M139"/>
@@ -5690,34 +5684,34 @@
       <c r="J140" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="L140" s="25" t="s">
+      <c r="L140" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="M140" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="N140" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O140" s="25" t="s">
+      <c r="M140" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="N140" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="O140" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="P140" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q140" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="R140" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="S140" s="25" t="s">
+      <c r="P140" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q140" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="R140" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="S140" s="24" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="141" spans="3:19" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C141" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D141" s="23">
         <v>1</v>
@@ -5740,28 +5734,28 @@
       <c r="J141" s="23">
         <v>10</v>
       </c>
-      <c r="L141" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="M141" s="25">
-        <v>2</v>
-      </c>
-      <c r="N141" s="25">
-        <v>1</v>
-      </c>
-      <c r="O141" s="25" t="s">
+      <c r="L141" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="M141" s="24">
+        <v>2</v>
+      </c>
+      <c r="N141" s="24">
+        <v>1</v>
+      </c>
+      <c r="O141" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="P141" s="25" t="s">
+      <c r="P141" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="Q141" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="R141" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="S141" s="25">
+      <c r="Q141" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="R141" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="S141" s="24">
         <v>25</v>
       </c>
     </row>
@@ -5769,291 +5763,219 @@
       <c r="C142" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D142" s="33" t="s">
-        <v>192</v>
-      </c>
-      <c r="E142" s="34"/>
-      <c r="F142" s="34"/>
-      <c r="G142" s="34"/>
-      <c r="H142" s="34"/>
-      <c r="I142" s="34"/>
-      <c r="J142" s="35"/>
-      <c r="L142" s="25" t="s">
+      <c r="D142" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="E142" s="28"/>
+      <c r="F142" s="28"/>
+      <c r="G142" s="28"/>
+      <c r="H142" s="28"/>
+      <c r="I142" s="28"/>
+      <c r="J142" s="29"/>
+      <c r="L142" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="M142" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="N142" s="37"/>
-      <c r="O142" s="37"/>
-      <c r="P142" s="37"/>
-      <c r="Q142" s="37"/>
-      <c r="R142" s="37"/>
-      <c r="S142" s="38"/>
+      <c r="M142" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="N142" s="31"/>
+      <c r="O142" s="31"/>
+      <c r="P142" s="31"/>
+      <c r="Q142" s="31"/>
+      <c r="R142" s="31"/>
+      <c r="S142" s="32"/>
     </row>
     <row r="143" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C143" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D143" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E143" s="34"/>
-      <c r="F143" s="34"/>
-      <c r="G143" s="34"/>
-      <c r="H143" s="34"/>
-      <c r="I143" s="34"/>
-      <c r="J143" s="35"/>
-      <c r="L143" s="25" t="s">
+      <c r="D143" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="E143" s="28"/>
+      <c r="F143" s="28"/>
+      <c r="G143" s="28"/>
+      <c r="H143" s="28"/>
+      <c r="I143" s="28"/>
+      <c r="J143" s="29"/>
+      <c r="L143" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="M143" s="36" t="s">
+      <c r="M143" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="N143" s="37"/>
-      <c r="O143" s="37"/>
-      <c r="P143" s="37"/>
-      <c r="Q143" s="37"/>
-      <c r="R143" s="37"/>
-      <c r="S143" s="38"/>
-    </row>
-    <row r="145" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C145" s="23" t="s">
+      <c r="N143" s="31"/>
+      <c r="O143" s="31"/>
+      <c r="P143" s="31"/>
+      <c r="Q143" s="31"/>
+      <c r="R143" s="31"/>
+      <c r="S143" s="32"/>
+    </row>
+    <row r="145" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L145" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D145" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E145" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F145" s="23" t="s">
+      <c r="M145" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="N145" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="O145" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="G145" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="H145" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I145" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="J145" s="23" t="s">
+      <c r="P145" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q145" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="R145" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="S145" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="L145" s="25" t="s">
+    </row>
+    <row r="146" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L146" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="M146" s="24">
+        <v>2</v>
+      </c>
+      <c r="N146" s="24">
+        <v>1</v>
+      </c>
+      <c r="O146" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P146" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q146" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="R146" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="S146" s="24">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="147" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L147" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="M147" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="N147" s="33"/>
+      <c r="O147" s="33"/>
+      <c r="P147" s="33"/>
+      <c r="Q147" s="33"/>
+      <c r="R147" s="33"/>
+      <c r="S147" s="33"/>
+    </row>
+    <row r="148" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L148" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="M148" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="N148" s="33"/>
+      <c r="O148" s="33"/>
+      <c r="P148" s="33"/>
+      <c r="Q148" s="33"/>
+      <c r="R148" s="33"/>
+      <c r="S148" s="33"/>
+    </row>
+    <row r="150" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L150" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="M145" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="N145" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O145" s="25" t="s">
+      <c r="M150" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="N150" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="O150" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="P145" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q145" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="R145" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="S145" s="25" t="s">
+      <c r="P150" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q150" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="R150" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="S150" s="24" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="146" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C146" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="D146" s="23">
-        <v>1</v>
-      </c>
-      <c r="E146" s="23">
-        <v>1</v>
-      </c>
-      <c r="F146" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G146" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="H146" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="I146" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="J146" s="23">
-        <v>10</v>
-      </c>
-      <c r="L146" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="M146" s="25">
-        <v>2</v>
-      </c>
-      <c r="N146" s="25">
-        <v>1</v>
-      </c>
-      <c r="O146" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="P146" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q146" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="R146" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="S146" s="25">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="147" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C147" s="23" t="s">
+    <row r="151" spans="12:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L151" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="M151" s="24">
+        <v>6</v>
+      </c>
+      <c r="N151" s="24">
+        <v>1</v>
+      </c>
+      <c r="O151" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P151" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q151" s="24">
+        <v>0</v>
+      </c>
+      <c r="R151" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="S151" s="24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="152" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L152" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D147" s="27" t="s">
-        <v>192</v>
-      </c>
-      <c r="E147" s="27"/>
-      <c r="F147" s="27"/>
-      <c r="G147" s="27"/>
-      <c r="H147" s="27"/>
-      <c r="I147" s="27"/>
-      <c r="J147" s="27"/>
-      <c r="L147" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="M147" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="N147" s="39"/>
-      <c r="O147" s="39"/>
-      <c r="P147" s="39"/>
-      <c r="Q147" s="39"/>
-      <c r="R147" s="39"/>
-      <c r="S147" s="39"/>
-    </row>
-    <row r="148" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C148" s="23" t="s">
+      <c r="M152" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="N152" s="31"/>
+      <c r="O152" s="31"/>
+      <c r="P152" s="31"/>
+      <c r="Q152" s="31"/>
+      <c r="R152" s="31"/>
+      <c r="S152" s="32"/>
+    </row>
+    <row r="153" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L153" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="D148" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="E148" s="27"/>
-      <c r="F148" s="27"/>
-      <c r="G148" s="27"/>
-      <c r="H148" s="27"/>
-      <c r="I148" s="27"/>
-      <c r="J148" s="27"/>
-      <c r="L148" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="M148" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="N148" s="39"/>
-      <c r="O148" s="39"/>
-      <c r="P148" s="39"/>
-      <c r="Q148" s="39"/>
-      <c r="R148" s="39"/>
-      <c r="S148" s="39"/>
-    </row>
-    <row r="150" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L150" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="M150" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="N150" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O150" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="P150" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q150" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="R150" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="S150" s="25" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="151" spans="3:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L151" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="M151" s="25">
-        <v>6</v>
-      </c>
-      <c r="N151" s="25">
-        <v>1</v>
-      </c>
-      <c r="O151" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="P151" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q151" s="25">
-        <v>0</v>
-      </c>
-      <c r="R151" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="S151" s="25">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="152" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L152" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="M152" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="N152" s="37"/>
-      <c r="O152" s="37"/>
-      <c r="P152" s="37"/>
-      <c r="Q152" s="37"/>
-      <c r="R152" s="37"/>
-      <c r="S152" s="38"/>
-    </row>
-    <row r="153" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L153" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="M153" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="N153" s="37"/>
-      <c r="O153" s="37"/>
-      <c r="P153" s="37"/>
-      <c r="Q153" s="37"/>
-      <c r="R153" s="37"/>
-      <c r="S153" s="38"/>
-    </row>
-    <row r="155" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="M153" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="N153" s="31"/>
+      <c r="O153" s="31"/>
+      <c r="P153" s="31"/>
+      <c r="Q153" s="31"/>
+      <c r="R153" s="31"/>
+      <c r="S153" s="32"/>
+    </row>
+    <row r="155" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="161" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="162" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="163" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6079,23 +6001,23 @@
     </row>
     <row r="167" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L167"/>
-      <c r="M167" s="29"/>
-      <c r="N167" s="29"/>
-      <c r="O167" s="29"/>
-      <c r="P167" s="29"/>
-      <c r="Q167" s="29"/>
-      <c r="R167" s="29"/>
-      <c r="S167" s="29"/>
+      <c r="M167" s="41"/>
+      <c r="N167" s="41"/>
+      <c r="O167" s="41"/>
+      <c r="P167" s="41"/>
+      <c r="Q167" s="41"/>
+      <c r="R167" s="41"/>
+      <c r="S167" s="41"/>
     </row>
     <row r="168" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L168"/>
-      <c r="M168" s="29"/>
-      <c r="N168" s="29"/>
-      <c r="O168" s="29"/>
-      <c r="P168" s="29"/>
-      <c r="Q168" s="29"/>
-      <c r="R168" s="29"/>
-      <c r="S168" s="29"/>
+      <c r="M168" s="41"/>
+      <c r="N168" s="41"/>
+      <c r="O168" s="41"/>
+      <c r="P168" s="41"/>
+      <c r="Q168" s="41"/>
+      <c r="R168" s="41"/>
+      <c r="S168" s="41"/>
     </row>
     <row r="170" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="171" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6106,16 +6028,89 @@
     <row r="177" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="178" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="127">
-    <mergeCell ref="D32:J32"/>
-    <mergeCell ref="D33:J33"/>
-    <mergeCell ref="D112:J112"/>
-    <mergeCell ref="D77:J77"/>
-    <mergeCell ref="D78:J78"/>
-    <mergeCell ref="D93:J93"/>
-    <mergeCell ref="M133:S133"/>
-    <mergeCell ref="D97:J97"/>
-    <mergeCell ref="M152:S152"/>
+  <mergeCells count="125">
+    <mergeCell ref="M167:S167"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="D72:J72"/>
+    <mergeCell ref="D73:J73"/>
+    <mergeCell ref="D52:J52"/>
+    <mergeCell ref="D53:J53"/>
+    <mergeCell ref="D57:J57"/>
+    <mergeCell ref="D58:J58"/>
+    <mergeCell ref="D62:J62"/>
+    <mergeCell ref="M127:S127"/>
+    <mergeCell ref="M128:S128"/>
+    <mergeCell ref="D37:J37"/>
+    <mergeCell ref="D38:J38"/>
+    <mergeCell ref="M38:S38"/>
+    <mergeCell ref="M53:S53"/>
+    <mergeCell ref="M62:S62"/>
+    <mergeCell ref="D107:J107"/>
+    <mergeCell ref="D108:J108"/>
+    <mergeCell ref="M168:S168"/>
+    <mergeCell ref="D63:J63"/>
+    <mergeCell ref="D67:J67"/>
+    <mergeCell ref="D68:J68"/>
+    <mergeCell ref="D43:J43"/>
+    <mergeCell ref="D127:J127"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="M107:S107"/>
+    <mergeCell ref="M108:S108"/>
+    <mergeCell ref="D82:J82"/>
+    <mergeCell ref="D83:J83"/>
+    <mergeCell ref="M112:S112"/>
+    <mergeCell ref="M113:S113"/>
+    <mergeCell ref="M82:S82"/>
+    <mergeCell ref="M83:S83"/>
+    <mergeCell ref="M117:S117"/>
+    <mergeCell ref="M118:S118"/>
+    <mergeCell ref="M103:S103"/>
+    <mergeCell ref="M98:S98"/>
+    <mergeCell ref="M68:S68"/>
+    <mergeCell ref="M102:S102"/>
+    <mergeCell ref="M132:S132"/>
+    <mergeCell ref="V17:AB17"/>
+    <mergeCell ref="V18:AB18"/>
+    <mergeCell ref="M17:S17"/>
+    <mergeCell ref="M18:S18"/>
+    <mergeCell ref="M32:S32"/>
+    <mergeCell ref="M37:S37"/>
+    <mergeCell ref="M23:S23"/>
+    <mergeCell ref="M27:S27"/>
+    <mergeCell ref="M28:S28"/>
+    <mergeCell ref="M33:S33"/>
+    <mergeCell ref="D17:J17"/>
+    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="M57:S57"/>
+    <mergeCell ref="M58:S58"/>
+    <mergeCell ref="M97:S97"/>
+    <mergeCell ref="M72:S72"/>
+    <mergeCell ref="M73:S73"/>
+    <mergeCell ref="D98:J98"/>
+    <mergeCell ref="D102:J102"/>
+    <mergeCell ref="M87:S87"/>
+    <mergeCell ref="M88:S88"/>
+    <mergeCell ref="M77:S77"/>
+    <mergeCell ref="M78:S78"/>
+    <mergeCell ref="M22:S22"/>
+    <mergeCell ref="D27:J27"/>
+    <mergeCell ref="D47:J47"/>
+    <mergeCell ref="D48:J48"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="V12:AB12"/>
+    <mergeCell ref="V13:AB13"/>
+    <mergeCell ref="M12:S12"/>
+    <mergeCell ref="M8:S8"/>
+    <mergeCell ref="M7:S7"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="V7:AB7"/>
+    <mergeCell ref="V8:AB8"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
     <mergeCell ref="M153:S153"/>
     <mergeCell ref="D92:J92"/>
     <mergeCell ref="D103:J103"/>
@@ -6139,101 +6134,26 @@
     <mergeCell ref="M93:S93"/>
     <mergeCell ref="M67:S67"/>
     <mergeCell ref="D113:J113"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="V12:AB12"/>
-    <mergeCell ref="V13:AB13"/>
-    <mergeCell ref="M12:S12"/>
-    <mergeCell ref="M8:S8"/>
-    <mergeCell ref="M7:S7"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="V7:AB7"/>
-    <mergeCell ref="V8:AB8"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
     <mergeCell ref="M147:S147"/>
+    <mergeCell ref="D32:J32"/>
+    <mergeCell ref="D33:J33"/>
+    <mergeCell ref="D112:J112"/>
+    <mergeCell ref="D77:J77"/>
+    <mergeCell ref="D78:J78"/>
+    <mergeCell ref="D93:J93"/>
+    <mergeCell ref="M133:S133"/>
+    <mergeCell ref="D97:J97"/>
+    <mergeCell ref="M152:S152"/>
     <mergeCell ref="M148:S148"/>
     <mergeCell ref="M63:S63"/>
-    <mergeCell ref="D17:J17"/>
-    <mergeCell ref="D18:J18"/>
-    <mergeCell ref="M57:S57"/>
-    <mergeCell ref="M58:S58"/>
-    <mergeCell ref="M97:S97"/>
-    <mergeCell ref="M72:S72"/>
-    <mergeCell ref="M73:S73"/>
-    <mergeCell ref="D98:J98"/>
-    <mergeCell ref="D102:J102"/>
-    <mergeCell ref="M87:S87"/>
-    <mergeCell ref="M88:S88"/>
-    <mergeCell ref="M77:S77"/>
-    <mergeCell ref="M78:S78"/>
     <mergeCell ref="M137:S137"/>
     <mergeCell ref="M138:S138"/>
-    <mergeCell ref="M22:S22"/>
     <mergeCell ref="M122:S122"/>
     <mergeCell ref="M123:S123"/>
-    <mergeCell ref="D27:J27"/>
-    <mergeCell ref="D47:J47"/>
-    <mergeCell ref="D48:J48"/>
-    <mergeCell ref="V17:AB17"/>
-    <mergeCell ref="V18:AB18"/>
-    <mergeCell ref="M17:S17"/>
-    <mergeCell ref="M18:S18"/>
-    <mergeCell ref="M32:S32"/>
-    <mergeCell ref="M37:S37"/>
-    <mergeCell ref="M23:S23"/>
-    <mergeCell ref="M27:S27"/>
-    <mergeCell ref="M28:S28"/>
-    <mergeCell ref="M33:S33"/>
-    <mergeCell ref="M168:S168"/>
-    <mergeCell ref="D63:J63"/>
-    <mergeCell ref="D67:J67"/>
-    <mergeCell ref="D68:J68"/>
-    <mergeCell ref="D43:J43"/>
-    <mergeCell ref="D127:J127"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="M107:S107"/>
-    <mergeCell ref="M108:S108"/>
-    <mergeCell ref="D82:J82"/>
-    <mergeCell ref="D83:J83"/>
-    <mergeCell ref="M112:S112"/>
-    <mergeCell ref="M113:S113"/>
-    <mergeCell ref="M82:S82"/>
-    <mergeCell ref="M83:S83"/>
     <mergeCell ref="D117:J117"/>
     <mergeCell ref="D118:J118"/>
-    <mergeCell ref="M117:S117"/>
-    <mergeCell ref="M118:S118"/>
-    <mergeCell ref="M103:S103"/>
-    <mergeCell ref="M98:S98"/>
-    <mergeCell ref="M68:S68"/>
-    <mergeCell ref="M102:S102"/>
-    <mergeCell ref="M132:S132"/>
-    <mergeCell ref="D147:J147"/>
-    <mergeCell ref="D148:J148"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="D23:J23"/>
     <mergeCell ref="D122:J122"/>
     <mergeCell ref="D123:J123"/>
-    <mergeCell ref="M167:S167"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="D72:J72"/>
-    <mergeCell ref="D73:J73"/>
-    <mergeCell ref="D52:J52"/>
-    <mergeCell ref="D53:J53"/>
-    <mergeCell ref="D57:J57"/>
-    <mergeCell ref="D58:J58"/>
-    <mergeCell ref="D62:J62"/>
-    <mergeCell ref="M127:S127"/>
-    <mergeCell ref="M128:S128"/>
-    <mergeCell ref="D37:J37"/>
-    <mergeCell ref="D38:J38"/>
-    <mergeCell ref="M38:S38"/>
-    <mergeCell ref="M53:S53"/>
-    <mergeCell ref="M62:S62"/>
-    <mergeCell ref="D107:J107"/>
-    <mergeCell ref="D108:J108"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6249,28 +6169,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="42"/>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
+      <c r="A1" s="37"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
     </row>
     <row r="4" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>

--- a/Docs/Units.xlsx
+++ b/Docs/Units.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="209">
   <si>
     <t>Name</t>
   </si>
@@ -267,9 +267,6 @@
     <t>"Torch" or "Lantern" golems from Dragon age</t>
   </si>
   <si>
-    <t>Teleportation beacon</t>
-  </si>
-  <si>
     <t>Driller bunker</t>
   </si>
   <si>
@@ -294,9 +291,6 @@
     <t>Reflecting, Fragile</t>
   </si>
   <si>
-    <t>Fragile</t>
-  </si>
-  <si>
     <t>Fragile, Infiltrating</t>
   </si>
   <si>
@@ -396,9 +390,6 @@
     <t>Woundable</t>
   </si>
   <si>
-    <t>Slimey, Resistant:Poison, Putrid, Woundable</t>
-  </si>
-  <si>
     <t>Great Unclean one</t>
   </si>
   <si>
@@ -450,12 +441,6 @@
     <t>3, normal</t>
   </si>
   <si>
-    <t>Protected, Oozing, Slippery</t>
-  </si>
-  <si>
-    <t>Resistant:Poison, Slimey, Slippery</t>
-  </si>
-  <si>
     <t>Siren</t>
   </si>
   <si>
@@ -543,9 +528,6 @@
     <t>Engineer peasant</t>
   </si>
   <si>
-    <t>Oozing</t>
-  </si>
-  <si>
     <t>Flesh constuct</t>
   </si>
   <si>
@@ -612,9 +594,6 @@
     <t>The Nurgle sloppity guy</t>
   </si>
   <si>
-    <t>Explosive (1)</t>
-  </si>
-  <si>
     <t>Gladiator</t>
   </si>
   <si>
@@ -627,13 +606,43 @@
     <t>Bomb squig made out of mushrooms</t>
   </si>
   <si>
-    <t>Oliokinesis, Oozing</t>
-  </si>
-  <si>
     <t>Bombshroom</t>
   </si>
   <si>
     <t>Corn knight</t>
+  </si>
+  <si>
+    <t>Cheap</t>
+  </si>
+  <si>
+    <t>Fragile, Cheap</t>
+  </si>
+  <si>
+    <t>Crystal warrior</t>
+  </si>
+  <si>
+    <t>Diamondback bu skinny</t>
+  </si>
+  <si>
+    <t>Oliokinesis, Oily</t>
+  </si>
+  <si>
+    <t>Protected, Oily, Slippery</t>
+  </si>
+  <si>
+    <t>Oily</t>
+  </si>
+  <si>
+    <t>Resistant:Poison, Toxic, Slippery</t>
+  </si>
+  <si>
+    <t>Toxic, Resistant:Poison, Putrid, Woundable</t>
+  </si>
+  <si>
+    <t>Beacon</t>
+  </si>
+  <si>
+    <t>Putrid (1), Cheap</t>
   </si>
 </sst>
 </file>
@@ -774,7 +783,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -831,9 +840,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -852,13 +858,17 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
@@ -873,6 +883,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -880,6 +893,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -892,10 +914,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1228,30 +1246,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
     </row>
     <row r="2" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="37"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
+      <c r="A2" s="42"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
     </row>
     <row r="3" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
@@ -1278,28 +1296,28 @@
       <c r="A5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="13" t="s">
+      <c r="C5" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="27" t="s">
         <v>19</v>
       </c>
       <c r="L5" s="6" t="s">
@@ -1355,28 +1373,28 @@
       <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" s="13">
-        <v>3</v>
-      </c>
-      <c r="E6" s="13">
-        <v>1</v>
-      </c>
-      <c r="F6" s="13" t="s">
+      <c r="C6" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="D6" s="27">
+        <v>1</v>
+      </c>
+      <c r="E6" s="27">
+        <v>2</v>
+      </c>
+      <c r="F6" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="J6" s="13">
+      <c r="H6" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" s="27">
         <v>50</v>
       </c>
       <c r="L6" s="6" t="s">
@@ -1430,114 +1448,115 @@
     </row>
     <row r="7" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="29"/>
+      <c r="D7" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="38"/>
       <c r="L7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="39" t="s">
+      <c r="M7" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
+      <c r="N7" s="44"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="44"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="44"/>
       <c r="U7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V7" s="38" t="s">
+      <c r="V7" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="W7" s="38"/>
-      <c r="X7" s="38"/>
-      <c r="Y7" s="38"/>
-      <c r="Z7" s="38"/>
-      <c r="AA7" s="38"/>
-      <c r="AB7" s="38"/>
+      <c r="W7" s="43"/>
+      <c r="X7" s="43"/>
+      <c r="Y7" s="43"/>
+      <c r="Z7" s="43"/>
+      <c r="AA7" s="43"/>
+      <c r="AB7" s="43"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="5"/>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="29"/>
+      <c r="D8" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="38"/>
       <c r="L8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="N8" s="39"/>
-      <c r="O8" s="39"/>
-      <c r="P8" s="39"/>
-      <c r="Q8" s="39"/>
-      <c r="R8" s="39"/>
-      <c r="S8" s="39"/>
+      <c r="M8" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="34"/>
+      <c r="S8" s="34"/>
       <c r="U8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="W8" s="38"/>
-      <c r="X8" s="38"/>
-      <c r="Y8" s="38"/>
-      <c r="Z8" s="38"/>
-      <c r="AA8" s="38"/>
-      <c r="AB8" s="38"/>
-    </row>
-    <row r="9" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="V8" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="W8" s="35"/>
+      <c r="X8" s="35"/>
+      <c r="Y8" s="35"/>
+      <c r="Z8" s="35"/>
+      <c r="AA8" s="35"/>
+      <c r="AB8" s="35"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="O9"/>
+      <c r="Q9" s="26"/>
       <c r="X9"/>
     </row>
     <row r="10" spans="1:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="C10" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="15" t="s">
+      <c r="C10" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="27" t="s">
         <v>19</v>
       </c>
       <c r="L10" s="6" t="s">
@@ -1590,28 +1609,28 @@
       </c>
     </row>
     <row r="11" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="D11" s="15">
-        <v>3</v>
-      </c>
-      <c r="E11" s="15">
-        <v>1</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="15" t="s">
+      <c r="C11" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="27">
+        <v>2</v>
+      </c>
+      <c r="E11" s="27">
+        <v>1</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" s="15">
+      <c r="H11" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="27">
         <v>40</v>
       </c>
       <c r="L11" s="6" t="s">
@@ -1638,8 +1657,8 @@
       <c r="S11" s="6">
         <v>50</v>
       </c>
-      <c r="U11" s="20" t="s">
-        <v>179</v>
+      <c r="U11" s="30" t="s">
+        <v>173</v>
       </c>
       <c r="V11" s="2">
         <v>3</v>
@@ -1664,108 +1683,108 @@
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="34" t="s">
-        <v>187</v>
-      </c>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="36"/>
+      <c r="D12" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="38"/>
       <c r="L12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="39" t="s">
+      <c r="M12" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="39"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
       <c r="U12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V12" s="38" t="s">
+      <c r="V12" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="38"/>
-      <c r="AB12" s="38"/>
+      <c r="W12" s="43"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="43"/>
+      <c r="Z12" s="43"/>
+      <c r="AA12" s="43"/>
+      <c r="AB12" s="43"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="34" t="s">
-        <v>188</v>
-      </c>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="36"/>
+      <c r="D13" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="38"/>
       <c r="L13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="39" t="s">
+      <c r="M13" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="N13" s="39"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="39"/>
-      <c r="Q13" s="39"/>
-      <c r="R13" s="39"/>
-      <c r="S13" s="39"/>
+      <c r="N13" s="44"/>
+      <c r="O13" s="44"/>
+      <c r="P13" s="44"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
       <c r="U13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V13" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="W13" s="38"/>
-      <c r="X13" s="38"/>
-      <c r="Y13" s="38"/>
-      <c r="Z13" s="38"/>
-      <c r="AA13" s="38"/>
-      <c r="AB13" s="38"/>
+      <c r="V13" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="W13" s="43"/>
+      <c r="X13" s="43"/>
+      <c r="Y13" s="43"/>
+      <c r="Z13" s="43"/>
+      <c r="AA13" s="43"/>
+      <c r="AB13" s="43"/>
     </row>
     <row r="14" spans="1:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O14"/>
       <c r="X14"/>
     </row>
     <row r="15" spans="1:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="C15" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J15" s="15" t="s">
+      <c r="C15" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="24" t="s">
         <v>19</v>
       </c>
       <c r="L15" s="6" t="s">
@@ -1818,29 +1837,29 @@
       </c>
     </row>
     <row r="16" spans="1:28" ht="45" x14ac:dyDescent="0.25">
-      <c r="C16" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="D16" s="15">
-        <v>3</v>
-      </c>
-      <c r="E16" s="15">
-        <v>1</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="15" t="s">
+      <c r="C16" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="D16" s="24">
+        <v>2</v>
+      </c>
+      <c r="E16" s="24">
+        <v>1</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="15">
-        <v>40</v>
+      <c r="H16" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="24">
+        <v>25</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>32</v>
@@ -1892,80 +1911,80 @@
       </c>
     </row>
     <row r="17" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="40" t="s">
-        <v>147</v>
-      </c>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="40"/>
+      <c r="D17" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
       <c r="L17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="39" t="s">
+      <c r="M17" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="N17" s="39"/>
-      <c r="O17" s="39"/>
-      <c r="P17" s="39"/>
-      <c r="Q17" s="39"/>
-      <c r="R17" s="39"/>
-      <c r="S17" s="39"/>
+      <c r="N17" s="44"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="44"/>
+      <c r="S17" s="44"/>
       <c r="U17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V17" s="38" t="s">
+      <c r="V17" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="W17" s="38"/>
-      <c r="X17" s="38"/>
-      <c r="Y17" s="38"/>
-      <c r="Z17" s="38"/>
-      <c r="AA17" s="38"/>
-      <c r="AB17" s="38"/>
+      <c r="W17" s="43"/>
+      <c r="X17" s="43"/>
+      <c r="Y17" s="43"/>
+      <c r="Z17" s="43"/>
+      <c r="AA17" s="43"/>
+      <c r="AB17" s="43"/>
     </row>
     <row r="18" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="40" t="s">
-        <v>148</v>
-      </c>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="40"/>
+      <c r="D18" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
       <c r="L18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="39" t="s">
+      <c r="M18" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="39"/>
-      <c r="O18" s="39"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="39"/>
-      <c r="R18" s="39"/>
-      <c r="S18" s="39"/>
+      <c r="N18" s="44"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="44"/>
+      <c r="Q18" s="44"/>
+      <c r="R18" s="44"/>
+      <c r="S18" s="44"/>
       <c r="U18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V18" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="W18" s="38"/>
-      <c r="X18" s="38"/>
-      <c r="Y18" s="38"/>
-      <c r="Z18" s="38"/>
-      <c r="AA18" s="38"/>
-      <c r="AB18" s="38"/>
+      <c r="V18" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="W18" s="35"/>
+      <c r="X18" s="35"/>
+      <c r="Y18" s="35"/>
+      <c r="Z18" s="35"/>
+      <c r="AA18" s="35"/>
+      <c r="AB18" s="35"/>
     </row>
     <row r="19" spans="3:28" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C19" s="16"/>
@@ -2030,31 +2049,31 @@
     </row>
     <row r="21" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="25" t="s">
-        <v>204</v>
+        <v>115</v>
       </c>
       <c r="D21" s="25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="25">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="G21" s="25" t="s">
         <v>7</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="I21" s="25" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="J21" s="25">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="M21" s="6">
         <v>3</v>
@@ -2082,53 +2101,53 @@
       <c r="C22" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="40" t="s">
-        <v>202</v>
-      </c>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
+      <c r="D22" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="38"/>
       <c r="L22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="39" t="s">
+      <c r="M22" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="N22" s="39"/>
-      <c r="O22" s="39"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="39"/>
-      <c r="R22" s="39"/>
-      <c r="S22" s="39"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="44"/>
+      <c r="P22" s="44"/>
+      <c r="Q22" s="44"/>
+      <c r="R22" s="44"/>
+      <c r="S22" s="44"/>
     </row>
     <row r="23" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="40" t="s">
-        <v>198</v>
-      </c>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40"/>
+      <c r="D23" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="38"/>
       <c r="L23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="N23" s="39"/>
-      <c r="O23" s="39"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="39"/>
-      <c r="R23" s="39"/>
-      <c r="S23" s="39"/>
+      <c r="M23" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="44"/>
+      <c r="R23" s="44"/>
+      <c r="S23" s="44"/>
     </row>
     <row r="25" spans="3:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="15" t="s">
@@ -2182,10 +2201,10 @@
     </row>
     <row r="26" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="15" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
         <v>1</v>
@@ -2194,16 +2213,16 @@
         <v>44</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>8</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="J26" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>46</v>
@@ -2234,77 +2253,77 @@
       <c r="C27" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="36"/>
+      <c r="D27" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
       <c r="L27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M27" s="39" t="s">
+      <c r="M27" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="N27" s="39"/>
-      <c r="O27" s="39"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="39"/>
-      <c r="R27" s="39"/>
-      <c r="S27" s="39"/>
+      <c r="N27" s="44"/>
+      <c r="O27" s="44"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="44"/>
+      <c r="R27" s="44"/>
+      <c r="S27" s="44"/>
     </row>
     <row r="28" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="36"/>
+      <c r="D28" s="45" t="s">
+        <v>143</v>
+      </c>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
       <c r="L28" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M28" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="N28" s="33"/>
-      <c r="O28" s="33"/>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="33"/>
-      <c r="R28" s="33"/>
-      <c r="S28" s="33"/>
+      <c r="M28" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
     </row>
     <row r="30" spans="3:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="F30" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="H30" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="I30" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="J30" s="26" t="s">
+      <c r="C30" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="J30" s="13" t="s">
         <v>19</v>
       </c>
       <c r="L30" s="11" t="s">
@@ -2333,29 +2352,29 @@
       </c>
     </row>
     <row r="31" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="D31" s="26">
-        <v>3</v>
-      </c>
-      <c r="E31" s="26">
-        <v>1</v>
-      </c>
-      <c r="F31" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="G31" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="H31" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="I31" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="J31" s="26">
-        <v>60</v>
+      <c r="C31" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" s="13">
+        <v>12</v>
+      </c>
+      <c r="E31" s="13">
+        <v>2</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J31" s="13">
+        <v>80</v>
       </c>
       <c r="L31" s="11" t="s">
         <v>43</v>
@@ -2383,80 +2402,80 @@
       </c>
     </row>
     <row r="32" spans="3:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="26" t="s">
+      <c r="C32" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="36"/>
+      <c r="D32" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="40"/>
+      <c r="J32" s="41"/>
       <c r="L32" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M32" s="30" t="s">
+      <c r="M32" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="33"/>
     </row>
     <row r="33" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="26" t="s">
+      <c r="C33" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="35"/>
-      <c r="J33" s="36"/>
+      <c r="D33" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="41"/>
       <c r="L33" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M33" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="31"/>
-      <c r="Q33" s="31"/>
-      <c r="R33" s="31"/>
-      <c r="S33" s="32"/>
+      <c r="M33" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="33"/>
     </row>
     <row r="35" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G35" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H35" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I35" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J35" s="15" t="s">
+      <c r="C35" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="F35" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="29" t="s">
         <v>19</v>
       </c>
       <c r="L35" s="11" t="s">
@@ -2485,29 +2504,29 @@
       </c>
     </row>
     <row r="36" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="D36" s="15">
-        <v>2</v>
-      </c>
-      <c r="E36" s="15">
-        <v>1</v>
-      </c>
-      <c r="F36" s="15" t="s">
+      <c r="C36" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="D36" s="29">
+        <v>3</v>
+      </c>
+      <c r="E36" s="29">
+        <v>1</v>
+      </c>
+      <c r="F36" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="G36" s="15" t="s">
+      <c r="G36" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I36" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J36" s="15">
-        <v>25</v>
+      <c r="H36" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I36" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="J36" s="29">
+        <v>35</v>
       </c>
       <c r="L36" s="11" t="s">
         <v>49</v>
@@ -2535,80 +2554,80 @@
       </c>
     </row>
     <row r="37" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="40" t="s">
-        <v>182</v>
+      <c r="D37" s="39" t="s">
+        <v>137</v>
       </c>
       <c r="E37" s="40"/>
       <c r="F37" s="40"/>
       <c r="G37" s="40"/>
       <c r="H37" s="40"/>
       <c r="I37" s="40"/>
-      <c r="J37" s="40"/>
+      <c r="J37" s="41"/>
       <c r="L37" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M37" s="30" t="s">
+      <c r="M37" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="N37" s="31"/>
-      <c r="O37" s="31"/>
-      <c r="P37" s="31"/>
-      <c r="Q37" s="31"/>
-      <c r="R37" s="31"/>
-      <c r="S37" s="32"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+      <c r="R37" s="32"/>
+      <c r="S37" s="33"/>
     </row>
     <row r="38" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="40" t="s">
-        <v>175</v>
+      <c r="D38" s="39" t="s">
+        <v>144</v>
       </c>
       <c r="E38" s="40"/>
       <c r="F38" s="40"/>
       <c r="G38" s="40"/>
       <c r="H38" s="40"/>
       <c r="I38" s="40"/>
-      <c r="J38" s="40"/>
+      <c r="J38" s="41"/>
       <c r="L38" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M38" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="N38" s="33"/>
-      <c r="O38" s="33"/>
-      <c r="P38" s="33"/>
-      <c r="Q38" s="33"/>
-      <c r="R38" s="33"/>
-      <c r="S38" s="33"/>
+      <c r="M38" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="N38" s="34"/>
+      <c r="O38" s="34"/>
+      <c r="P38" s="34"/>
+      <c r="Q38" s="34"/>
+      <c r="R38" s="34"/>
+      <c r="S38" s="34"/>
     </row>
     <row r="40" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F40" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G40" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H40" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I40" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J40" s="15" t="s">
+      <c r="C40" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="D40" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="F40" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="H40" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I40" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="J40" s="29" t="s">
         <v>19</v>
       </c>
       <c r="L40" s="11" t="s">
@@ -2637,29 +2656,29 @@
       </c>
     </row>
     <row r="41" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="D41" s="15">
-        <v>3</v>
-      </c>
-      <c r="E41" s="15">
-        <v>1</v>
-      </c>
-      <c r="F41" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" s="15" t="s">
+      <c r="C41" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="D41" s="29">
+        <v>3</v>
+      </c>
+      <c r="E41" s="29">
+        <v>2</v>
+      </c>
+      <c r="F41" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="H41" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I41" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="J41" s="15">
-        <v>35</v>
+      <c r="H41" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="J41" s="29">
+        <v>30</v>
       </c>
       <c r="L41" s="11" t="s">
         <v>51</v>
@@ -2687,80 +2706,80 @@
       </c>
     </row>
     <row r="42" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D42" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="35"/>
-      <c r="I42" s="35"/>
-      <c r="J42" s="36"/>
+      <c r="D42" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="40"/>
+      <c r="I42" s="40"/>
+      <c r="J42" s="41"/>
       <c r="L42" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M42" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="N42" s="31"/>
-      <c r="O42" s="31"/>
-      <c r="P42" s="31"/>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="31"/>
-      <c r="S42" s="32"/>
+      <c r="M42" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="32"/>
+      <c r="Q42" s="32"/>
+      <c r="R42" s="32"/>
+      <c r="S42" s="33"/>
     </row>
     <row r="43" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="34" t="s">
-        <v>203</v>
-      </c>
-      <c r="E43" s="35"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="35"/>
-      <c r="I43" s="35"/>
-      <c r="J43" s="36"/>
+      <c r="D43" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="40"/>
+      <c r="I43" s="40"/>
+      <c r="J43" s="41"/>
       <c r="L43" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M43" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="N43" s="31"/>
-      <c r="O43" s="31"/>
-      <c r="P43" s="31"/>
-      <c r="Q43" s="31"/>
-      <c r="R43" s="31"/>
-      <c r="S43" s="32"/>
+      <c r="M43" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="N43" s="32"/>
+      <c r="O43" s="32"/>
+      <c r="P43" s="32"/>
+      <c r="Q43" s="32"/>
+      <c r="R43" s="32"/>
+      <c r="S43" s="33"/>
     </row>
     <row r="45" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I45" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45" s="13" t="s">
+      <c r="C45" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="D45" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="F45" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="29" t="s">
         <v>19</v>
       </c>
       <c r="L45" s="11" t="s">
@@ -2789,29 +2808,29 @@
       </c>
     </row>
     <row r="46" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="D46" s="13">
-        <v>12</v>
-      </c>
-      <c r="E46" s="13">
-        <v>2</v>
-      </c>
-      <c r="F46" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G46" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="H46" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I46" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="J46" s="13">
-        <v>80</v>
+      <c r="C46" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="D46" s="29">
+        <v>3</v>
+      </c>
+      <c r="E46" s="29">
+        <v>1</v>
+      </c>
+      <c r="F46" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="H46" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="J46" s="29">
+        <v>30</v>
       </c>
       <c r="L46" s="11" t="s">
         <v>53</v>
@@ -2839,80 +2858,80 @@
       </c>
     </row>
     <row r="47" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="28"/>
-      <c r="J47" s="29"/>
+      <c r="D47" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="E47" s="40"/>
+      <c r="F47" s="40"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="40"/>
+      <c r="I47" s="40"/>
+      <c r="J47" s="41"/>
       <c r="L47" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="30" t="s">
+      <c r="M47" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="N47" s="31"/>
-      <c r="O47" s="31"/>
-      <c r="P47" s="31"/>
-      <c r="Q47" s="31"/>
-      <c r="R47" s="31"/>
-      <c r="S47" s="32"/>
+      <c r="N47" s="32"/>
+      <c r="O47" s="32"/>
+      <c r="P47" s="32"/>
+      <c r="Q47" s="32"/>
+      <c r="R47" s="32"/>
+      <c r="S47" s="33"/>
     </row>
     <row r="48" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C48" s="13" t="s">
+      <c r="C48" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="28"/>
-      <c r="J48" s="29"/>
+      <c r="D48" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="40"/>
+      <c r="I48" s="40"/>
+      <c r="J48" s="41"/>
       <c r="L48" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M48" s="30" t="s">
+      <c r="M48" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="N48" s="31"/>
-      <c r="O48" s="31"/>
-      <c r="P48" s="31"/>
-      <c r="Q48" s="31"/>
-      <c r="R48" s="31"/>
-      <c r="S48" s="32"/>
+      <c r="N48" s="32"/>
+      <c r="O48" s="32"/>
+      <c r="P48" s="32"/>
+      <c r="Q48" s="32"/>
+      <c r="R48" s="32"/>
+      <c r="S48" s="33"/>
     </row>
     <row r="50" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C50" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G50" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H50" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I50" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="J50" s="13" t="s">
+      <c r="C50" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="H50" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I50" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="J50" s="29" t="s">
         <v>19</v>
       </c>
       <c r="L50" s="11" t="s">
@@ -2941,29 +2960,29 @@
       </c>
     </row>
     <row r="51" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C51" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="D51" s="13">
-        <v>3</v>
-      </c>
-      <c r="E51" s="13">
-        <v>1</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G51" s="13" t="s">
+      <c r="C51" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="D51" s="29">
+        <v>4</v>
+      </c>
+      <c r="E51" s="29">
+        <v>2</v>
+      </c>
+      <c r="F51" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="H51" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="I51" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J51" s="13">
-        <v>35</v>
+      <c r="H51" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="I51" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="J51" s="29">
+        <v>40</v>
       </c>
       <c r="L51" s="11" t="s">
         <v>57</v>
@@ -2991,80 +3010,80 @@
       </c>
     </row>
     <row r="52" spans="3:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D52" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="29"/>
+      <c r="D52" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="40"/>
+      <c r="I52" s="40"/>
+      <c r="J52" s="41"/>
       <c r="L52" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M52" s="33" t="s">
-        <v>186</v>
-      </c>
-      <c r="N52" s="33"/>
-      <c r="O52" s="33"/>
-      <c r="P52" s="33"/>
-      <c r="Q52" s="33"/>
-      <c r="R52" s="33"/>
-      <c r="S52" s="33"/>
+      <c r="M52" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="N52" s="34"/>
+      <c r="O52" s="34"/>
+      <c r="P52" s="34"/>
+      <c r="Q52" s="34"/>
+      <c r="R52" s="34"/>
+      <c r="S52" s="34"/>
     </row>
     <row r="53" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="E53" s="28"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="29"/>
+      <c r="D53" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="E53" s="40"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="40"/>
+      <c r="I53" s="40"/>
+      <c r="J53" s="41"/>
       <c r="L53" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M53" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="N53" s="33"/>
-      <c r="O53" s="33"/>
-      <c r="P53" s="33"/>
-      <c r="Q53" s="33"/>
-      <c r="R53" s="33"/>
-      <c r="S53" s="33"/>
+      <c r="M53" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="N53" s="34"/>
+      <c r="O53" s="34"/>
+      <c r="P53" s="34"/>
+      <c r="Q53" s="34"/>
+      <c r="R53" s="34"/>
+      <c r="S53" s="34"/>
     </row>
     <row r="55" spans="3:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="C55" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D55" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F55" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G55" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H55" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I55" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="J55" s="13" t="s">
+      <c r="C55" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="D55" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="E55" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G55" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="H55" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I55" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="J55" s="29" t="s">
         <v>19</v>
       </c>
       <c r="L55" s="17" t="s">
@@ -3093,28 +3112,28 @@
       </c>
     </row>
     <row r="56" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C56" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="D56" s="13">
-        <v>3</v>
-      </c>
-      <c r="E56" s="13">
-        <v>2</v>
-      </c>
-      <c r="F56" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G56" s="13" t="s">
+      <c r="C56" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D56" s="29">
+        <v>3</v>
+      </c>
+      <c r="E56" s="29">
+        <v>1</v>
+      </c>
+      <c r="F56" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="H56" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I56" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J56" s="13">
+      <c r="H56" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I56" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="J56" s="29">
         <v>30</v>
       </c>
       <c r="L56" s="17" t="s">
@@ -3143,80 +3162,80 @@
       </c>
     </row>
     <row r="57" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="13" t="s">
+      <c r="C57" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="E57" s="28"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="28"/>
-      <c r="I57" s="28"/>
-      <c r="J57" s="29"/>
+      <c r="D57" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="E57" s="40"/>
+      <c r="F57" s="40"/>
+      <c r="G57" s="40"/>
+      <c r="H57" s="40"/>
+      <c r="I57" s="40"/>
+      <c r="J57" s="41"/>
       <c r="L57" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M57" s="30" t="s">
+      <c r="M57" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="N57" s="31"/>
-      <c r="O57" s="31"/>
-      <c r="P57" s="31"/>
-      <c r="Q57" s="31"/>
-      <c r="R57" s="31"/>
-      <c r="S57" s="32"/>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C58" s="13" t="s">
+      <c r="N57" s="32"/>
+      <c r="O57" s="32"/>
+      <c r="P57" s="32"/>
+      <c r="Q57" s="32"/>
+      <c r="R57" s="32"/>
+      <c r="S57" s="33"/>
+    </row>
+    <row r="58" spans="3:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C58" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="E58" s="28"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="28"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="28"/>
-      <c r="J58" s="29"/>
+      <c r="D58" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="E58" s="40"/>
+      <c r="F58" s="40"/>
+      <c r="G58" s="40"/>
+      <c r="H58" s="40"/>
+      <c r="I58" s="40"/>
+      <c r="J58" s="41"/>
       <c r="L58" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M58" s="30" t="s">
+      <c r="M58" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="N58" s="31"/>
-      <c r="O58" s="31"/>
-      <c r="P58" s="31"/>
-      <c r="Q58" s="31"/>
-      <c r="R58" s="31"/>
-      <c r="S58" s="32"/>
+      <c r="N58" s="32"/>
+      <c r="O58" s="32"/>
+      <c r="P58" s="32"/>
+      <c r="Q58" s="32"/>
+      <c r="R58" s="32"/>
+      <c r="S58" s="33"/>
     </row>
     <row r="60" spans="3:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="C60" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F60" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G60" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I60" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="J60" s="13" t="s">
+      <c r="C60" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D60" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E60" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F60" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I60" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="J60" s="22" t="s">
         <v>19</v>
       </c>
       <c r="L60" s="17" t="s">
@@ -3245,29 +3264,29 @@
       </c>
     </row>
     <row r="61" spans="3:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="C61" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="D61" s="13">
-        <v>3</v>
-      </c>
-      <c r="E61" s="13">
-        <v>1</v>
-      </c>
-      <c r="F61" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="G61" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="H61" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I61" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J61" s="13">
-        <v>30</v>
+      <c r="C61" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="D61" s="22">
+        <v>5</v>
+      </c>
+      <c r="E61" s="22">
+        <v>1</v>
+      </c>
+      <c r="F61" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G61" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H61" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="I61" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J61" s="22">
+        <v>50</v>
       </c>
       <c r="L61" s="17" t="s">
         <v>58</v>
@@ -3295,80 +3314,80 @@
       </c>
     </row>
     <row r="62" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C62" s="13" t="s">
+      <c r="C62" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D62" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="E62" s="28"/>
-      <c r="F62" s="28"/>
-      <c r="G62" s="28"/>
-      <c r="H62" s="28"/>
-      <c r="I62" s="28"/>
-      <c r="J62" s="29"/>
+      <c r="D62" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="E62" s="40"/>
+      <c r="F62" s="40"/>
+      <c r="G62" s="40"/>
+      <c r="H62" s="40"/>
+      <c r="I62" s="40"/>
+      <c r="J62" s="41"/>
       <c r="L62" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M62" s="33" t="s">
+      <c r="M62" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="N62" s="33"/>
-      <c r="O62" s="33"/>
-      <c r="P62" s="33"/>
-      <c r="Q62" s="33"/>
-      <c r="R62" s="33"/>
-      <c r="S62" s="33"/>
+      <c r="N62" s="34"/>
+      <c r="O62" s="34"/>
+      <c r="P62" s="34"/>
+      <c r="Q62" s="34"/>
+      <c r="R62" s="34"/>
+      <c r="S62" s="34"/>
     </row>
     <row r="63" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C63" s="13" t="s">
+      <c r="C63" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="E63" s="28"/>
-      <c r="F63" s="28"/>
-      <c r="G63" s="28"/>
-      <c r="H63" s="28"/>
-      <c r="I63" s="28"/>
-      <c r="J63" s="29"/>
+      <c r="D63" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="E63" s="40"/>
+      <c r="F63" s="40"/>
+      <c r="G63" s="40"/>
+      <c r="H63" s="40"/>
+      <c r="I63" s="40"/>
+      <c r="J63" s="41"/>
       <c r="L63" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M63" s="33" t="s">
+      <c r="M63" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="N63" s="33"/>
-      <c r="O63" s="33"/>
-      <c r="P63" s="33"/>
-      <c r="Q63" s="33"/>
-      <c r="R63" s="33"/>
-      <c r="S63" s="33"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="34"/>
+      <c r="R63" s="34"/>
+      <c r="S63" s="34"/>
     </row>
     <row r="65" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F65" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G65" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H65" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I65" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="J65" s="13" t="s">
+      <c r="C65" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D65" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E65" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F65" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G65" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="H65" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I65" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="J65" s="22" t="s">
         <v>19</v>
       </c>
       <c r="L65" s="18" t="s">
@@ -3397,32 +3416,32 @@
       </c>
     </row>
     <row r="66" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="D66" s="13">
-        <v>4</v>
-      </c>
-      <c r="E66" s="13">
-        <v>2</v>
-      </c>
-      <c r="F66" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="13" t="s">
+      <c r="C66" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D66" s="22">
+        <v>3</v>
+      </c>
+      <c r="E66" s="22">
+        <v>1</v>
+      </c>
+      <c r="F66" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="G66" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="H66" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I66" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="J66" s="13">
-        <v>40</v>
+      <c r="H66" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J66" s="22">
+        <v>45</v>
       </c>
       <c r="L66" s="18" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M66" s="18">
         <v>3</v>
@@ -3437,7 +3456,7 @@
         <v>7</v>
       </c>
       <c r="Q66" s="18" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="R66" s="18" t="s">
         <v>8</v>
@@ -3447,56 +3466,56 @@
       </c>
     </row>
     <row r="67" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="E67" s="28"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="28"/>
-      <c r="J67" s="29"/>
+      <c r="D67" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="E67" s="40"/>
+      <c r="F67" s="40"/>
+      <c r="G67" s="40"/>
+      <c r="H67" s="40"/>
+      <c r="I67" s="40"/>
+      <c r="J67" s="41"/>
       <c r="L67" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M67" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="N67" s="31"/>
-      <c r="O67" s="31"/>
-      <c r="P67" s="31"/>
-      <c r="Q67" s="31"/>
-      <c r="R67" s="31"/>
-      <c r="S67" s="32"/>
+      <c r="M67" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="N67" s="32"/>
+      <c r="O67" s="32"/>
+      <c r="P67" s="32"/>
+      <c r="Q67" s="32"/>
+      <c r="R67" s="32"/>
+      <c r="S67" s="33"/>
     </row>
     <row r="68" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="E68" s="28"/>
-      <c r="F68" s="28"/>
-      <c r="G68" s="28"/>
-      <c r="H68" s="28"/>
-      <c r="I68" s="28"/>
-      <c r="J68" s="29"/>
+      <c r="D68" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="E68" s="40"/>
+      <c r="F68" s="40"/>
+      <c r="G68" s="40"/>
+      <c r="H68" s="40"/>
+      <c r="I68" s="40"/>
+      <c r="J68" s="41"/>
       <c r="L68" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M68" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="N68" s="31"/>
-      <c r="O68" s="31"/>
-      <c r="P68" s="31"/>
-      <c r="Q68" s="31"/>
-      <c r="R68" s="31"/>
-      <c r="S68" s="32"/>
+      <c r="M68" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="N68" s="32"/>
+      <c r="O68" s="32"/>
+      <c r="P68" s="32"/>
+      <c r="Q68" s="32"/>
+      <c r="R68" s="32"/>
+      <c r="S68" s="33"/>
     </row>
     <row r="70" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="13" t="s">
@@ -3550,25 +3569,25 @@
     </row>
     <row r="71" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="13" t="s">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="D71" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E71" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G71" s="13" t="s">
         <v>7</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J71" s="13">
         <v>30</v>
@@ -3589,7 +3608,7 @@
         <v>7</v>
       </c>
       <c r="Q71" s="18" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="R71" s="18" t="s">
         <v>8</v>
@@ -3602,53 +3621,53 @@
       <c r="C72" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="E72" s="28"/>
-      <c r="F72" s="28"/>
-      <c r="G72" s="28"/>
-      <c r="H72" s="28"/>
-      <c r="I72" s="28"/>
-      <c r="J72" s="29"/>
+      <c r="D72" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="E72" s="40"/>
+      <c r="F72" s="40"/>
+      <c r="G72" s="40"/>
+      <c r="H72" s="40"/>
+      <c r="I72" s="40"/>
+      <c r="J72" s="41"/>
       <c r="L72" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M72" s="30" t="s">
+      <c r="M72" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="N72" s="31"/>
-      <c r="O72" s="31"/>
-      <c r="P72" s="31"/>
-      <c r="Q72" s="31"/>
-      <c r="R72" s="31"/>
-      <c r="S72" s="32"/>
+      <c r="N72" s="32"/>
+      <c r="O72" s="32"/>
+      <c r="P72" s="32"/>
+      <c r="Q72" s="32"/>
+      <c r="R72" s="32"/>
+      <c r="S72" s="33"/>
     </row>
     <row r="73" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="E73" s="28"/>
-      <c r="F73" s="28"/>
-      <c r="G73" s="28"/>
-      <c r="H73" s="28"/>
-      <c r="I73" s="28"/>
-      <c r="J73" s="29"/>
+      <c r="D73" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="E73" s="40"/>
+      <c r="F73" s="40"/>
+      <c r="G73" s="40"/>
+      <c r="H73" s="40"/>
+      <c r="I73" s="40"/>
+      <c r="J73" s="41"/>
       <c r="L73" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M73" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="N73" s="33"/>
-      <c r="O73" s="33"/>
-      <c r="P73" s="33"/>
-      <c r="Q73" s="33"/>
-      <c r="R73" s="33"/>
-      <c r="S73" s="33"/>
+      <c r="M73" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="N73" s="34"/>
+      <c r="O73" s="34"/>
+      <c r="P73" s="34"/>
+      <c r="Q73" s="34"/>
+      <c r="R73" s="34"/>
+      <c r="S73" s="34"/>
     </row>
     <row r="75" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="13" t="s">
@@ -3702,19 +3721,19 @@
     </row>
     <row r="76" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C76" s="13" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="D76" s="13">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E76" s="13">
         <v>1</v>
       </c>
       <c r="F76" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G76" s="13" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H76" s="13" t="s">
         <v>8</v>
@@ -3723,7 +3742,7 @@
         <v>8</v>
       </c>
       <c r="J76" s="13">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="L76" s="19" t="s">
         <v>78</v>
@@ -3754,77 +3773,77 @@
       <c r="C77" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="E77" s="28"/>
-      <c r="F77" s="28"/>
-      <c r="G77" s="28"/>
-      <c r="H77" s="28"/>
-      <c r="I77" s="28"/>
-      <c r="J77" s="29"/>
+      <c r="D77" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="E77" s="40"/>
+      <c r="F77" s="40"/>
+      <c r="G77" s="40"/>
+      <c r="H77" s="40"/>
+      <c r="I77" s="40"/>
+      <c r="J77" s="41"/>
       <c r="L77" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M77" s="30" t="s">
+      <c r="M77" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="N77" s="31"/>
-      <c r="O77" s="31"/>
-      <c r="P77" s="31"/>
-      <c r="Q77" s="31"/>
-      <c r="R77" s="31"/>
-      <c r="S77" s="32"/>
+      <c r="N77" s="32"/>
+      <c r="O77" s="32"/>
+      <c r="P77" s="32"/>
+      <c r="Q77" s="32"/>
+      <c r="R77" s="32"/>
+      <c r="S77" s="33"/>
     </row>
     <row r="78" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C78" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="E78" s="28"/>
-      <c r="F78" s="28"/>
-      <c r="G78" s="28"/>
-      <c r="H78" s="28"/>
-      <c r="I78" s="28"/>
-      <c r="J78" s="29"/>
+      <c r="D78" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="E78" s="40"/>
+      <c r="F78" s="40"/>
+      <c r="G78" s="40"/>
+      <c r="H78" s="40"/>
+      <c r="I78" s="40"/>
+      <c r="J78" s="41"/>
       <c r="L78" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M78" s="30" t="s">
+      <c r="M78" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="N78" s="31"/>
-      <c r="O78" s="31"/>
-      <c r="P78" s="31"/>
-      <c r="Q78" s="31"/>
-      <c r="R78" s="31"/>
-      <c r="S78" s="32"/>
+      <c r="N78" s="32"/>
+      <c r="O78" s="32"/>
+      <c r="P78" s="32"/>
+      <c r="Q78" s="32"/>
+      <c r="R78" s="32"/>
+      <c r="S78" s="33"/>
     </row>
     <row r="80" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C80" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D80" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E80" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F80" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G80" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="H80" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I80" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="J80" s="23" t="s">
+      <c r="C80" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F80" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G80" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H80" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="I80" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="J80" s="13" t="s">
         <v>19</v>
       </c>
       <c r="L80" s="19" t="s">
@@ -3853,32 +3872,32 @@
       </c>
     </row>
     <row r="81" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C81" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="D81" s="23">
-        <v>5</v>
-      </c>
-      <c r="E81" s="23">
-        <v>1</v>
-      </c>
-      <c r="F81" s="23" t="s">
+      <c r="C81" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D81" s="13">
+        <v>2</v>
+      </c>
+      <c r="E81" s="13">
+        <v>1</v>
+      </c>
+      <c r="F81" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G81" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="H81" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="I81" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="J81" s="23">
+      <c r="G81" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H81" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="13">
         <v>50</v>
       </c>
       <c r="L81" s="19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M81" s="19">
         <v>2</v>
@@ -3903,83 +3922,83 @@
       </c>
     </row>
     <row r="82" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C82" s="23" t="s">
+      <c r="C82" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="E82" s="28"/>
-      <c r="F82" s="28"/>
-      <c r="G82" s="28"/>
-      <c r="H82" s="28"/>
-      <c r="I82" s="28"/>
-      <c r="J82" s="29"/>
+      <c r="D82" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="E82" s="40"/>
+      <c r="F82" s="40"/>
+      <c r="G82" s="40"/>
+      <c r="H82" s="40"/>
+      <c r="I82" s="40"/>
+      <c r="J82" s="41"/>
       <c r="L82" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M82" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="N82" s="31"/>
-      <c r="O82" s="31"/>
-      <c r="P82" s="31"/>
-      <c r="Q82" s="31"/>
-      <c r="R82" s="31"/>
-      <c r="S82" s="32"/>
+      <c r="M82" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="N82" s="32"/>
+      <c r="O82" s="32"/>
+      <c r="P82" s="32"/>
+      <c r="Q82" s="32"/>
+      <c r="R82" s="32"/>
+      <c r="S82" s="33"/>
     </row>
     <row r="83" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C83" s="23" t="s">
+      <c r="C83" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D83" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="E83" s="28"/>
-      <c r="F83" s="28"/>
-      <c r="G83" s="28"/>
-      <c r="H83" s="28"/>
-      <c r="I83" s="28"/>
-      <c r="J83" s="29"/>
+      <c r="D83" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="E83" s="40"/>
+      <c r="F83" s="40"/>
+      <c r="G83" s="40"/>
+      <c r="H83" s="40"/>
+      <c r="I83" s="40"/>
+      <c r="J83" s="41"/>
       <c r="L83" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M83" s="30" t="s">
+      <c r="M83" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="N83" s="31"/>
-      <c r="O83" s="31"/>
-      <c r="P83" s="31"/>
-      <c r="Q83" s="31"/>
-      <c r="R83" s="31"/>
-      <c r="S83" s="32"/>
+      <c r="N83" s="32"/>
+      <c r="O83" s="32"/>
+      <c r="P83" s="32"/>
+      <c r="Q83" s="32"/>
+      <c r="R83" s="32"/>
+      <c r="S83" s="33"/>
     </row>
     <row r="84" spans="3:19" x14ac:dyDescent="0.25">
       <c r="O84"/>
     </row>
     <row r="85" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C85" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D85" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E85" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F85" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G85" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="H85" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I85" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="J85" s="23" t="s">
+      <c r="C85" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F85" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G85" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H85" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="I85" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="J85" s="13" t="s">
         <v>19</v>
       </c>
       <c r="L85" s="19" t="s">
@@ -4008,32 +4027,32 @@
       </c>
     </row>
     <row r="86" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C86" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="D86" s="23">
-        <v>3</v>
-      </c>
-      <c r="E86" s="23">
-        <v>1</v>
-      </c>
-      <c r="F86" s="23" t="s">
+      <c r="C86" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D86" s="13">
+        <v>12</v>
+      </c>
+      <c r="E86" s="13">
+        <v>3</v>
+      </c>
+      <c r="F86" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G86" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="H86" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="I86" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="J86" s="23">
-        <v>45</v>
+      <c r="G86" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="H86" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="I86" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J86" s="13">
+        <v>100</v>
       </c>
       <c r="L86" s="19" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M86" s="19">
         <v>1</v>
@@ -4058,56 +4077,56 @@
       </c>
     </row>
     <row r="87" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C87" s="23" t="s">
+      <c r="C87" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D87" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="E87" s="28"/>
-      <c r="F87" s="28"/>
-      <c r="G87" s="28"/>
-      <c r="H87" s="28"/>
-      <c r="I87" s="28"/>
-      <c r="J87" s="29"/>
+      <c r="D87" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="E87" s="40"/>
+      <c r="F87" s="40"/>
+      <c r="G87" s="40"/>
+      <c r="H87" s="40"/>
+      <c r="I87" s="40"/>
+      <c r="J87" s="41"/>
       <c r="L87" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M87" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="N87" s="31"/>
-      <c r="O87" s="31"/>
-      <c r="P87" s="31"/>
-      <c r="Q87" s="31"/>
-      <c r="R87" s="31"/>
-      <c r="S87" s="32"/>
+      <c r="M87" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="N87" s="32"/>
+      <c r="O87" s="32"/>
+      <c r="P87" s="32"/>
+      <c r="Q87" s="32"/>
+      <c r="R87" s="32"/>
+      <c r="S87" s="33"/>
     </row>
     <row r="88" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C88" s="23" t="s">
+      <c r="C88" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D88" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="E88" s="28"/>
-      <c r="F88" s="28"/>
-      <c r="G88" s="28"/>
-      <c r="H88" s="28"/>
-      <c r="I88" s="28"/>
-      <c r="J88" s="29"/>
+      <c r="D88" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="E88" s="40"/>
+      <c r="F88" s="40"/>
+      <c r="G88" s="40"/>
+      <c r="H88" s="40"/>
+      <c r="I88" s="40"/>
+      <c r="J88" s="41"/>
       <c r="L88" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M88" s="30" t="s">
+      <c r="M88" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="N88" s="31"/>
-      <c r="O88" s="31"/>
-      <c r="P88" s="31"/>
-      <c r="Q88" s="31"/>
-      <c r="R88" s="31"/>
-      <c r="S88" s="32"/>
+      <c r="N88" s="32"/>
+      <c r="O88" s="32"/>
+      <c r="P88" s="32"/>
+      <c r="Q88" s="32"/>
+      <c r="R88" s="32"/>
+      <c r="S88" s="33"/>
     </row>
     <row r="90" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="13" t="s">
@@ -4161,16 +4180,16 @@
     </row>
     <row r="91" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C91" s="13" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="D91" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F91" s="13" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G91" s="13" t="s">
         <v>7</v>
@@ -4182,10 +4201,10 @@
         <v>8</v>
       </c>
       <c r="J91" s="13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L91" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M91" s="19">
         <v>5</v>
@@ -4213,77 +4232,77 @@
       <c r="C92" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D92" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="E92" s="28"/>
-      <c r="F92" s="28"/>
-      <c r="G92" s="28"/>
-      <c r="H92" s="28"/>
-      <c r="I92" s="28"/>
-      <c r="J92" s="29"/>
+      <c r="D92" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E92" s="40"/>
+      <c r="F92" s="40"/>
+      <c r="G92" s="40"/>
+      <c r="H92" s="40"/>
+      <c r="I92" s="40"/>
+      <c r="J92" s="41"/>
       <c r="L92" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M92" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="N92" s="31"/>
-      <c r="O92" s="31"/>
-      <c r="P92" s="31"/>
-      <c r="Q92" s="31"/>
-      <c r="R92" s="31"/>
-      <c r="S92" s="32"/>
+      <c r="M92" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="N92" s="32"/>
+      <c r="O92" s="32"/>
+      <c r="P92" s="32"/>
+      <c r="Q92" s="32"/>
+      <c r="R92" s="32"/>
+      <c r="S92" s="33"/>
     </row>
     <row r="93" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C93" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="E93" s="28"/>
-      <c r="F93" s="28"/>
-      <c r="G93" s="28"/>
-      <c r="H93" s="28"/>
-      <c r="I93" s="28"/>
-      <c r="J93" s="29"/>
+      <c r="D93" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="E93" s="40"/>
+      <c r="F93" s="40"/>
+      <c r="G93" s="40"/>
+      <c r="H93" s="40"/>
+      <c r="I93" s="40"/>
+      <c r="J93" s="41"/>
       <c r="L93" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M93" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="N93" s="31"/>
-      <c r="O93" s="31"/>
-      <c r="P93" s="31"/>
-      <c r="Q93" s="31"/>
-      <c r="R93" s="31"/>
-      <c r="S93" s="32"/>
+      <c r="M93" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="N93" s="32"/>
+      <c r="O93" s="32"/>
+      <c r="P93" s="32"/>
+      <c r="Q93" s="32"/>
+      <c r="R93" s="32"/>
+      <c r="S93" s="33"/>
     </row>
     <row r="95" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C95" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D95" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E95" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F95" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G95" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H95" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I95" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="J95" s="13" t="s">
+      <c r="C95" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D95" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E95" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F95" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G95" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="H95" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I95" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="J95" s="22" t="s">
         <v>19</v>
       </c>
       <c r="L95" s="19" t="s">
@@ -4312,29 +4331,29 @@
       </c>
     </row>
     <row r="96" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C96" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="D96" s="13">
+      <c r="C96" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="D96" s="22">
+        <v>1</v>
+      </c>
+      <c r="E96" s="22">
+        <v>1</v>
+      </c>
+      <c r="F96" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G96" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E96" s="13">
-        <v>1</v>
-      </c>
-      <c r="F96" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G96" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="H96" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I96" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="J96" s="13">
-        <v>50</v>
+      <c r="H96" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="22">
+        <v>10</v>
       </c>
       <c r="L96" s="19" t="s">
         <v>65</v>
@@ -4362,83 +4381,83 @@
       </c>
     </row>
     <row r="97" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C97" s="13" t="s">
+      <c r="C97" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E97" s="28"/>
-      <c r="F97" s="28"/>
-      <c r="G97" s="28"/>
-      <c r="H97" s="28"/>
-      <c r="I97" s="28"/>
-      <c r="J97" s="29"/>
+      <c r="D97" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="E97" s="35"/>
+      <c r="F97" s="35"/>
+      <c r="G97" s="35"/>
+      <c r="H97" s="35"/>
+      <c r="I97" s="35"/>
+      <c r="J97" s="35"/>
       <c r="L97" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M97" s="30" t="s">
+      <c r="M97" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="N97" s="31"/>
-      <c r="O97" s="31"/>
-      <c r="P97" s="31"/>
-      <c r="Q97" s="31"/>
-      <c r="R97" s="31"/>
-      <c r="S97" s="32"/>
+      <c r="N97" s="32"/>
+      <c r="O97" s="32"/>
+      <c r="P97" s="32"/>
+      <c r="Q97" s="32"/>
+      <c r="R97" s="32"/>
+      <c r="S97" s="33"/>
     </row>
     <row r="98" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C98" s="13" t="s">
+      <c r="C98" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D98" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="E98" s="28"/>
-      <c r="F98" s="28"/>
-      <c r="G98" s="28"/>
-      <c r="H98" s="28"/>
-      <c r="I98" s="28"/>
-      <c r="J98" s="29"/>
+      <c r="D98" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="E98" s="35"/>
+      <c r="F98" s="35"/>
+      <c r="G98" s="35"/>
+      <c r="H98" s="35"/>
+      <c r="I98" s="35"/>
+      <c r="J98" s="35"/>
       <c r="L98" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M98" s="30" t="s">
+      <c r="M98" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="N98" s="31"/>
-      <c r="O98" s="31"/>
-      <c r="P98" s="31"/>
-      <c r="Q98" s="31"/>
-      <c r="R98" s="31"/>
-      <c r="S98" s="32"/>
+      <c r="N98" s="32"/>
+      <c r="O98" s="32"/>
+      <c r="P98" s="32"/>
+      <c r="Q98" s="32"/>
+      <c r="R98" s="32"/>
+      <c r="S98" s="33"/>
     </row>
     <row r="99" spans="3:19" x14ac:dyDescent="0.25">
       <c r="O99"/>
     </row>
     <row r="100" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C100" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D100" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F100" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G100" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I100" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="13" t="s">
+      <c r="C100" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D100" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E100" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F100" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G100" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="22" t="s">
         <v>19</v>
       </c>
       <c r="L100" s="19" t="s">
@@ -4467,29 +4486,29 @@
       </c>
     </row>
     <row r="101" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C101" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="D101" s="13">
-        <v>2</v>
-      </c>
-      <c r="E101" s="13">
-        <v>1</v>
-      </c>
-      <c r="F101" s="13" t="s">
+      <c r="C101" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="D101" s="22">
+        <v>2</v>
+      </c>
+      <c r="E101" s="22">
+        <v>2</v>
+      </c>
+      <c r="F101" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G101" s="13" t="s">
+      <c r="G101" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="H101" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I101" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="J101" s="13">
-        <v>50</v>
+      <c r="H101" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="22">
+        <v>30</v>
       </c>
       <c r="L101" s="19" t="s">
         <v>68</v>
@@ -4517,58 +4536,66 @@
       </c>
     </row>
     <row r="102" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C102" s="13" t="s">
+      <c r="C102" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D102" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="E102" s="28"/>
-      <c r="F102" s="28"/>
-      <c r="G102" s="28"/>
-      <c r="H102" s="28"/>
-      <c r="I102" s="28"/>
-      <c r="J102" s="29"/>
+      <c r="D102" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="E102" s="35"/>
+      <c r="F102" s="35"/>
+      <c r="G102" s="35"/>
+      <c r="H102" s="35"/>
+      <c r="I102" s="35"/>
+      <c r="J102" s="35"/>
       <c r="L102" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M102" s="30" t="s">
+      <c r="M102" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="N102" s="31"/>
-      <c r="O102" s="31"/>
-      <c r="P102" s="31"/>
-      <c r="Q102" s="31"/>
-      <c r="R102" s="31"/>
-      <c r="S102" s="32"/>
+      <c r="N102" s="32"/>
+      <c r="O102" s="32"/>
+      <c r="P102" s="32"/>
+      <c r="Q102" s="32"/>
+      <c r="R102" s="32"/>
+      <c r="S102" s="33"/>
     </row>
     <row r="103" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C103" s="13" t="s">
+      <c r="C103" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D103" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="E103" s="28"/>
-      <c r="F103" s="28"/>
-      <c r="G103" s="28"/>
-      <c r="H103" s="28"/>
-      <c r="I103" s="28"/>
-      <c r="J103" s="29"/>
+      <c r="D103" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="E103" s="35"/>
+      <c r="F103" s="35"/>
+      <c r="G103" s="35"/>
+      <c r="H103" s="35"/>
+      <c r="I103" s="35"/>
+      <c r="J103" s="35"/>
       <c r="L103" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M103" s="30" t="s">
+      <c r="M103" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="N103" s="31"/>
-      <c r="O103" s="31"/>
-      <c r="P103" s="31"/>
-      <c r="Q103" s="31"/>
-      <c r="R103" s="31"/>
-      <c r="S103" s="32"/>
+      <c r="N103" s="32"/>
+      <c r="O103" s="32"/>
+      <c r="P103" s="32"/>
+      <c r="Q103" s="32"/>
+      <c r="R103" s="32"/>
+      <c r="S103" s="33"/>
     </row>
     <row r="104" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C104" s="16"/>
+      <c r="D104" s="16"/>
+      <c r="E104" s="16"/>
+      <c r="F104" s="14"/>
+      <c r="G104" s="16"/>
+      <c r="H104" s="16"/>
+      <c r="I104" s="16"/>
+      <c r="J104" s="16"/>
       <c r="O104"/>
     </row>
     <row r="105" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -4596,78 +4623,78 @@
       <c r="J105" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="L105" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="M105" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="N105" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="O105" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="P105" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q105" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="R105" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="S105" s="21" t="s">
+      <c r="L105" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="M105" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="N105" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="O105" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="P105" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q105" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="R105" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="S105" s="20" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="106" spans="3:19" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C106" s="13" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="D106" s="13">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E106" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F106" s="13" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="G106" s="13" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="H106" s="13" t="s">
         <v>8</v>
       </c>
       <c r="I106" s="13" t="s">
-        <v>8</v>
+        <v>132</v>
       </c>
       <c r="J106" s="13">
-        <v>100</v>
-      </c>
-      <c r="L106" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="M106" s="21">
-        <v>3</v>
-      </c>
-      <c r="N106" s="21">
-        <v>1</v>
-      </c>
-      <c r="O106" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="L106" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="M106" s="20">
+        <v>3</v>
+      </c>
+      <c r="N106" s="20">
+        <v>1</v>
+      </c>
+      <c r="O106" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="P106" s="21" t="s">
+      <c r="P106" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="Q106" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="R106" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="S106" s="21">
+      <c r="Q106" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="R106" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="S106" s="20">
         <v>15</v>
       </c>
     </row>
@@ -4675,519 +4702,509 @@
       <c r="C107" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="E107" s="28"/>
-      <c r="F107" s="28"/>
-      <c r="G107" s="28"/>
-      <c r="H107" s="28"/>
-      <c r="I107" s="28"/>
-      <c r="J107" s="29"/>
-      <c r="L107" s="21" t="s">
+      <c r="D107" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="E107" s="40"/>
+      <c r="F107" s="40"/>
+      <c r="G107" s="40"/>
+      <c r="H107" s="40"/>
+      <c r="I107" s="40"/>
+      <c r="J107" s="41"/>
+      <c r="L107" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M107" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="N107" s="33"/>
-      <c r="O107" s="33"/>
-      <c r="P107" s="33"/>
-      <c r="Q107" s="33"/>
-      <c r="R107" s="33"/>
-      <c r="S107" s="33"/>
+      <c r="M107" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="N107" s="34"/>
+      <c r="O107" s="34"/>
+      <c r="P107" s="34"/>
+      <c r="Q107" s="34"/>
+      <c r="R107" s="34"/>
+      <c r="S107" s="34"/>
     </row>
     <row r="108" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C108" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="27" t="s">
+      <c r="D108" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="E108" s="40"/>
+      <c r="F108" s="40"/>
+      <c r="G108" s="40"/>
+      <c r="H108" s="40"/>
+      <c r="I108" s="40"/>
+      <c r="J108" s="41"/>
+      <c r="L108" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="M108" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="N108" s="34"/>
+      <c r="O108" s="34"/>
+      <c r="P108" s="34"/>
+      <c r="Q108" s="34"/>
+      <c r="R108" s="34"/>
+      <c r="S108" s="34"/>
+    </row>
+    <row r="110" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C110" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D110" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E110" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F110" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G110" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="H110" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I110" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="J110" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="L110" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="M110" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="N110" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="O110" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="P110" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q110" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="R110" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="S110" s="20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C111" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="D111" s="22">
+        <v>5</v>
+      </c>
+      <c r="E111" s="22">
+        <v>1</v>
+      </c>
+      <c r="F111" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="G111" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="H111" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="I111" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="J111" s="22">
+        <v>70</v>
+      </c>
+      <c r="L111" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="M111" s="20">
+        <v>1</v>
+      </c>
+      <c r="N111" s="20">
+        <v>1</v>
+      </c>
+      <c r="O111" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="P111" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q111" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="R111" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="S111" s="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C112" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="E112" s="40"/>
+      <c r="F112" s="40"/>
+      <c r="G112" s="40"/>
+      <c r="H112" s="40"/>
+      <c r="I112" s="40"/>
+      <c r="J112" s="41"/>
+      <c r="L112" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="M112" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="N112" s="32"/>
+      <c r="O112" s="32"/>
+      <c r="P112" s="32"/>
+      <c r="Q112" s="32"/>
+      <c r="R112" s="32"/>
+      <c r="S112" s="33"/>
+    </row>
+    <row r="113" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C113" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D113" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="E113" s="40"/>
+      <c r="F113" s="40"/>
+      <c r="G113" s="40"/>
+      <c r="H113" s="40"/>
+      <c r="I113" s="40"/>
+      <c r="J113" s="41"/>
+      <c r="L113" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="M113" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="N113" s="32"/>
+      <c r="O113" s="32"/>
+      <c r="P113" s="32"/>
+      <c r="Q113" s="32"/>
+      <c r="R113" s="32"/>
+      <c r="S113" s="33"/>
+    </row>
+    <row r="115" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C115" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D115" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E115" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F115" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G115" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="H115" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I115" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="J115" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="L115" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="M115" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="N115" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="O115" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="P115" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q115" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="R115" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="S115" s="20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C116" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="D116" s="22">
+        <v>2</v>
+      </c>
+      <c r="E116" s="22">
+        <v>1</v>
+      </c>
+      <c r="F116" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G116" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="H116" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="I116" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J116" s="22">
+        <v>25</v>
+      </c>
+      <c r="L116" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="M116" s="20">
+        <v>3</v>
+      </c>
+      <c r="N116" s="20">
+        <v>1</v>
+      </c>
+      <c r="O116" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="P116" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q116" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="R116" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="E108" s="28"/>
-      <c r="F108" s="28"/>
-      <c r="G108" s="28"/>
-      <c r="H108" s="28"/>
-      <c r="I108" s="28"/>
-      <c r="J108" s="29"/>
-      <c r="L108" s="21" t="s">
+      <c r="S116" s="20">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="117" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C117" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D117" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="E117" s="40"/>
+      <c r="F117" s="40"/>
+      <c r="G117" s="40"/>
+      <c r="H117" s="40"/>
+      <c r="I117" s="40"/>
+      <c r="J117" s="41"/>
+      <c r="L117" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="M117" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="N117" s="32"/>
+      <c r="O117" s="32"/>
+      <c r="P117" s="32"/>
+      <c r="Q117" s="32"/>
+      <c r="R117" s="32"/>
+      <c r="S117" s="33"/>
+    </row>
+    <row r="118" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C118" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="M108" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="N108" s="33"/>
-      <c r="O108" s="33"/>
-      <c r="P108" s="33"/>
-      <c r="Q108" s="33"/>
-      <c r="R108" s="33"/>
-      <c r="S108" s="33"/>
-    </row>
-    <row r="110" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C110" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D110" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E110" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F110" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G110" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H110" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I110" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="J110" s="13" t="s">
+      <c r="D118" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="E118" s="40"/>
+      <c r="F118" s="40"/>
+      <c r="G118" s="40"/>
+      <c r="H118" s="40"/>
+      <c r="I118" s="40"/>
+      <c r="J118" s="41"/>
+      <c r="L118" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="M118" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="N118" s="32"/>
+      <c r="O118" s="32"/>
+      <c r="P118" s="32"/>
+      <c r="Q118" s="32"/>
+      <c r="R118" s="32"/>
+      <c r="S118" s="33"/>
+    </row>
+    <row r="120" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C120" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D120" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E120" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F120" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G120" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="H120" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I120" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="J120" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="L110" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="M110" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="N110" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="O110" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="P110" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q110" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="R110" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="S110" s="21" t="s">
+      <c r="L120" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="M120" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="N120" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O120" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="P120" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q120" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="R120" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="S120" s="21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="111" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C111" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="D111" s="13">
-        <v>2</v>
-      </c>
-      <c r="E111" s="13">
-        <v>1</v>
-      </c>
-      <c r="F111" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G111" s="13" t="s">
+    <row r="121" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C121" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="D121" s="22">
+        <v>1</v>
+      </c>
+      <c r="E121" s="22">
+        <v>1</v>
+      </c>
+      <c r="F121" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G121" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="H111" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I111" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="J111" s="13">
+      <c r="H121" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="I121" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J121" s="22">
+        <v>10</v>
+      </c>
+      <c r="L121" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="M121" s="21">
+        <v>2</v>
+      </c>
+      <c r="N121" s="21">
+        <v>1</v>
+      </c>
+      <c r="O121" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="P121" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q121" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="R121" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="S121" s="21">
         <v>40</v>
       </c>
-      <c r="L111" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="M111" s="21">
-        <v>1</v>
-      </c>
-      <c r="N111" s="21">
-        <v>1</v>
-      </c>
-      <c r="O111" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="P111" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q111" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="R111" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="S111" s="21">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="112" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C112" s="13" t="s">
+    </row>
+    <row r="122" spans="3:19" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C122" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D112" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="E112" s="28"/>
-      <c r="F112" s="28"/>
-      <c r="G112" s="28"/>
-      <c r="H112" s="28"/>
-      <c r="I112" s="28"/>
-      <c r="J112" s="29"/>
-      <c r="L112" s="21" t="s">
+      <c r="D122" s="39" t="s">
+        <v>184</v>
+      </c>
+      <c r="E122" s="40"/>
+      <c r="F122" s="40"/>
+      <c r="G122" s="40"/>
+      <c r="H122" s="40"/>
+      <c r="I122" s="40"/>
+      <c r="J122" s="41"/>
+      <c r="L122" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M112" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="N112" s="31"/>
-      <c r="O112" s="31"/>
-      <c r="P112" s="31"/>
-      <c r="Q112" s="31"/>
-      <c r="R112" s="31"/>
-      <c r="S112" s="32"/>
-    </row>
-    <row r="113" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C113" s="13" t="s">
+      <c r="M122" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="N122" s="34"/>
+      <c r="O122" s="34"/>
+      <c r="P122" s="34"/>
+      <c r="Q122" s="34"/>
+      <c r="R122" s="34"/>
+      <c r="S122" s="34"/>
+    </row>
+    <row r="123" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C123" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D113" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="E113" s="28"/>
-      <c r="F113" s="28"/>
-      <c r="G113" s="28"/>
-      <c r="H113" s="28"/>
-      <c r="I113" s="28"/>
-      <c r="J113" s="29"/>
-      <c r="L113" s="21" t="s">
+      <c r="D123" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="E123" s="40"/>
+      <c r="F123" s="40"/>
+      <c r="G123" s="40"/>
+      <c r="H123" s="40"/>
+      <c r="I123" s="40"/>
+      <c r="J123" s="41"/>
+      <c r="L123" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M113" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="N113" s="31"/>
-      <c r="O113" s="31"/>
-      <c r="P113" s="31"/>
-      <c r="Q113" s="31"/>
-      <c r="R113" s="31"/>
-      <c r="S113" s="32"/>
-    </row>
-    <row r="115" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C115" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D115" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E115" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F115" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G115" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="H115" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I115" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="J115" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L115" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="M115" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="N115" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="O115" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="P115" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q115" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="R115" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="S115" s="21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="116" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C116" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="D116" s="23">
-        <v>1</v>
-      </c>
-      <c r="E116" s="23">
-        <v>1</v>
-      </c>
-      <c r="F116" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G116" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="H116" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="I116" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="J116" s="23">
-        <v>10</v>
-      </c>
-      <c r="L116" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="M116" s="21">
-        <v>3</v>
-      </c>
-      <c r="N116" s="21">
-        <v>1</v>
-      </c>
-      <c r="O116" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="P116" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q116" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="R116" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="S116" s="21">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="117" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C117" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D117" s="42" t="s">
-        <v>190</v>
-      </c>
-      <c r="E117" s="42"/>
-      <c r="F117" s="42"/>
-      <c r="G117" s="42"/>
-      <c r="H117" s="42"/>
-      <c r="I117" s="42"/>
-      <c r="J117" s="42"/>
-      <c r="L117" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="M117" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="N117" s="31"/>
-      <c r="O117" s="31"/>
-      <c r="P117" s="31"/>
-      <c r="Q117" s="31"/>
-      <c r="R117" s="31"/>
-      <c r="S117" s="32"/>
-    </row>
-    <row r="118" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C118" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D118" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="E118" s="42"/>
-      <c r="F118" s="42"/>
-      <c r="G118" s="42"/>
-      <c r="H118" s="42"/>
-      <c r="I118" s="42"/>
-      <c r="J118" s="42"/>
-      <c r="L118" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="M118" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="N118" s="31"/>
-      <c r="O118" s="31"/>
-      <c r="P118" s="31"/>
-      <c r="Q118" s="31"/>
-      <c r="R118" s="31"/>
-      <c r="S118" s="32"/>
-    </row>
-    <row r="120" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C120" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D120" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E120" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F120" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G120" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="H120" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I120" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="J120" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L120" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="M120" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="N120" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="O120" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="P120" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q120" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="R120" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="S120" s="22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="121" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C121" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="D121" s="23">
-        <v>2</v>
-      </c>
-      <c r="E121" s="23">
-        <v>2</v>
-      </c>
-      <c r="F121" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G121" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="H121" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="I121" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="J121" s="23">
-        <v>30</v>
-      </c>
-      <c r="L121" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="M121" s="22">
-        <v>2</v>
-      </c>
-      <c r="N121" s="22">
-        <v>1</v>
-      </c>
-      <c r="O121" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="P121" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q121" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="R121" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="S121" s="22">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="122" spans="3:19" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C122" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D122" s="42" t="s">
-        <v>200</v>
-      </c>
-      <c r="E122" s="42"/>
-      <c r="F122" s="42"/>
-      <c r="G122" s="42"/>
-      <c r="H122" s="42"/>
-      <c r="I122" s="42"/>
-      <c r="J122" s="42"/>
-      <c r="L122" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="M122" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="N122" s="33"/>
-      <c r="O122" s="33"/>
-      <c r="P122" s="33"/>
-      <c r="Q122" s="33"/>
-      <c r="R122" s="33"/>
-      <c r="S122" s="33"/>
-    </row>
-    <row r="123" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C123" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D123" s="42" t="s">
-        <v>201</v>
-      </c>
-      <c r="E123" s="42"/>
-      <c r="F123" s="42"/>
-      <c r="G123" s="42"/>
-      <c r="H123" s="42"/>
-      <c r="I123" s="42"/>
-      <c r="J123" s="42"/>
-      <c r="L123" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="M123" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="N123" s="33"/>
-      <c r="O123" s="33"/>
-      <c r="P123" s="33"/>
-      <c r="Q123" s="33"/>
-      <c r="R123" s="33"/>
-      <c r="S123" s="33"/>
-    </row>
-    <row r="124" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C124" s="16"/>
-      <c r="D124" s="16"/>
-      <c r="E124" s="16"/>
-      <c r="F124" s="14"/>
-      <c r="G124" s="16"/>
-      <c r="H124" s="16"/>
-      <c r="I124" s="16"/>
-      <c r="J124" s="16"/>
+      <c r="M123" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="N123" s="34"/>
+      <c r="O123" s="34"/>
+      <c r="P123" s="34"/>
+      <c r="Q123" s="34"/>
+      <c r="R123" s="34"/>
+      <c r="S123" s="34"/>
     </row>
     <row r="125" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C125" s="13" t="s">
@@ -5214,43 +5231,43 @@
       <c r="J125" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="L125" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="M125" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="N125" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="O125" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="P125" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q125" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="R125" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="S125" s="22" t="s">
+      <c r="L125" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="M125" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="N125" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O125" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="P125" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q125" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="R125" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="S125" s="21" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="126" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C126" s="13" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="D126" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E126" s="13">
         <v>1</v>
       </c>
       <c r="F126" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G126" s="13" t="s">
         <v>7</v>
@@ -5259,33 +5276,33 @@
         <v>8</v>
       </c>
       <c r="I126" s="13" t="s">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="J126" s="13">
         <v>50</v>
       </c>
-      <c r="L126" s="22" t="s">
+      <c r="L126" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="M126" s="22">
-        <v>3</v>
-      </c>
-      <c r="N126" s="22">
-        <v>1</v>
-      </c>
-      <c r="O126" s="22" t="s">
+      <c r="M126" s="21">
+        <v>3</v>
+      </c>
+      <c r="N126" s="21">
+        <v>1</v>
+      </c>
+      <c r="O126" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="P126" s="22" t="s">
+      <c r="P126" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="Q126" s="22" t="s">
+      <c r="Q126" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="R126" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="S126" s="22">
+      <c r="R126" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="S126" s="21">
         <v>40</v>
       </c>
     </row>
@@ -5293,771 +5310,827 @@
       <c r="C127" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D127" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="E127" s="28"/>
-      <c r="F127" s="28"/>
-      <c r="G127" s="28"/>
-      <c r="H127" s="28"/>
-      <c r="I127" s="28"/>
-      <c r="J127" s="29"/>
-      <c r="L127" s="22" t="s">
+      <c r="D127" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="E127" s="40"/>
+      <c r="F127" s="40"/>
+      <c r="G127" s="40"/>
+      <c r="H127" s="40"/>
+      <c r="I127" s="40"/>
+      <c r="J127" s="41"/>
+      <c r="L127" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M127" s="30" t="s">
+      <c r="M127" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="N127" s="31"/>
-      <c r="O127" s="31"/>
-      <c r="P127" s="31"/>
-      <c r="Q127" s="31"/>
-      <c r="R127" s="31"/>
-      <c r="S127" s="32"/>
+      <c r="N127" s="32"/>
+      <c r="O127" s="32"/>
+      <c r="P127" s="32"/>
+      <c r="Q127" s="32"/>
+      <c r="R127" s="32"/>
+      <c r="S127" s="33"/>
     </row>
     <row r="128" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C128" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D128" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="E128" s="28"/>
-      <c r="F128" s="28"/>
-      <c r="G128" s="28"/>
-      <c r="H128" s="28"/>
-      <c r="I128" s="28"/>
-      <c r="J128" s="29"/>
-      <c r="L128" s="22" t="s">
+      <c r="D128" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="E128" s="40"/>
+      <c r="F128" s="40"/>
+      <c r="G128" s="40"/>
+      <c r="H128" s="40"/>
+      <c r="I128" s="40"/>
+      <c r="J128" s="41"/>
+      <c r="L128" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M128" s="30" t="s">
+      <c r="M128" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="N128" s="31"/>
-      <c r="O128" s="31"/>
-      <c r="P128" s="31"/>
-      <c r="Q128" s="31"/>
-      <c r="R128" s="31"/>
-      <c r="S128" s="32"/>
-    </row>
-    <row r="130" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C130" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D130" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E130" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F130" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G130" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="H130" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I130" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="J130" s="23" t="s">
+      <c r="N128" s="32"/>
+      <c r="O128" s="32"/>
+      <c r="P128" s="32"/>
+      <c r="Q128" s="32"/>
+      <c r="R128" s="32"/>
+      <c r="S128" s="33"/>
+    </row>
+    <row r="130" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L130" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="M130" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="N130" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O130" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="P130" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q130" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="R130" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="S130" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="L130" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="M130" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="N130" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="O130" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="P130" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q130" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="R130" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="S130" s="22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="131" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C131" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="D131" s="23">
-        <v>5</v>
-      </c>
-      <c r="E131" s="23">
-        <v>1</v>
-      </c>
-      <c r="F131" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="G131" s="23" t="s">
+    </row>
+    <row r="131" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L131" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="M131" s="21">
+        <v>3</v>
+      </c>
+      <c r="N131" s="21">
+        <v>1</v>
+      </c>
+      <c r="O131" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="P131" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="H131" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="I131" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="J131" s="23">
-        <v>70</v>
-      </c>
-      <c r="L131" s="22" t="s">
+      <c r="Q131" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="R131" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="S131" s="21">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="132" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L132" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="M132" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="N132" s="32"/>
+      <c r="O132" s="32"/>
+      <c r="P132" s="32"/>
+      <c r="Q132" s="32"/>
+      <c r="R132" s="32"/>
+      <c r="S132" s="33"/>
+    </row>
+    <row r="133" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L133" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="M133" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="M131" s="22">
-        <v>3</v>
-      </c>
-      <c r="N131" s="22">
-        <v>1</v>
-      </c>
-      <c r="O131" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="P131" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q131" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="R131" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="S131" s="22">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="132" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C132" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D132" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="E132" s="28"/>
-      <c r="F132" s="28"/>
-      <c r="G132" s="28"/>
-      <c r="H132" s="28"/>
-      <c r="I132" s="28"/>
-      <c r="J132" s="29"/>
-      <c r="L132" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="M132" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="N132" s="31"/>
-      <c r="O132" s="31"/>
-      <c r="P132" s="31"/>
-      <c r="Q132" s="31"/>
-      <c r="R132" s="31"/>
-      <c r="S132" s="32"/>
-    </row>
-    <row r="133" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C133" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D133" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="E133" s="28"/>
-      <c r="F133" s="28"/>
-      <c r="G133" s="28"/>
-      <c r="H133" s="28"/>
-      <c r="I133" s="28"/>
-      <c r="J133" s="29"/>
-      <c r="L133" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="M133" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="N133" s="31"/>
-      <c r="O133" s="31"/>
-      <c r="P133" s="31"/>
-      <c r="Q133" s="31"/>
-      <c r="R133" s="31"/>
-      <c r="S133" s="32"/>
-    </row>
-    <row r="134" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N133" s="32"/>
+      <c r="O133" s="32"/>
+      <c r="P133" s="32"/>
+      <c r="Q133" s="32"/>
+      <c r="R133" s="32"/>
+      <c r="S133" s="33"/>
+    </row>
+    <row r="134" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M134"/>
       <c r="N134"/>
       <c r="O134"/>
       <c r="P134"/>
       <c r="Q134"/>
     </row>
-    <row r="135" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D135" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E135" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F135" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G135" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="H135" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I135" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="J135" s="23" t="s">
+    <row r="135" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L135" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="M135" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="N135" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O135" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="P135" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q135" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="R135" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="S135" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="L135" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="M135" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="N135" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="O135" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="P135" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q135" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="R135" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="S135" s="22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="136" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="D136" s="23">
-        <v>2</v>
-      </c>
-      <c r="E136" s="23">
-        <v>1</v>
-      </c>
-      <c r="F136" s="23" t="s">
+    </row>
+    <row r="136" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L136" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="M136" s="21">
+        <v>3</v>
+      </c>
+      <c r="N136" s="21">
+        <v>1</v>
+      </c>
+      <c r="O136" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="G136" s="23" t="s">
+      <c r="P136" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="H136" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="I136" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="J136" s="23">
-        <v>25</v>
-      </c>
-      <c r="L136" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="M136" s="22">
-        <v>3</v>
-      </c>
-      <c r="N136" s="22">
-        <v>1</v>
-      </c>
-      <c r="O136" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="P136" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q136" s="22" t="s">
+      <c r="Q136" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="R136" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="S136" s="22">
+      <c r="R136" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="S136" s="21">
         <v>50</v>
       </c>
     </row>
-    <row r="137" spans="3:19" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C137" s="23" t="s">
+    <row r="137" spans="12:19" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L137" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D137" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="E137" s="28"/>
-      <c r="F137" s="28"/>
-      <c r="G137" s="28"/>
-      <c r="H137" s="28"/>
-      <c r="I137" s="28"/>
-      <c r="J137" s="29"/>
-      <c r="L137" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="M137" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="N137" s="31"/>
-      <c r="O137" s="31"/>
-      <c r="P137" s="31"/>
-      <c r="Q137" s="31"/>
-      <c r="R137" s="31"/>
-      <c r="S137" s="32"/>
-    </row>
-    <row r="138" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C138" s="23" t="s">
+      <c r="M137" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="N137" s="32"/>
+      <c r="O137" s="32"/>
+      <c r="P137" s="32"/>
+      <c r="Q137" s="32"/>
+      <c r="R137" s="32"/>
+      <c r="S137" s="33"/>
+    </row>
+    <row r="138" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L138" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D138" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="E138" s="28"/>
-      <c r="F138" s="28"/>
-      <c r="G138" s="28"/>
-      <c r="H138" s="28"/>
-      <c r="I138" s="28"/>
-      <c r="J138" s="29"/>
-      <c r="L138" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="M138" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="N138" s="31"/>
-      <c r="O138" s="31"/>
-      <c r="P138" s="31"/>
-      <c r="Q138" s="31"/>
-      <c r="R138" s="31"/>
-      <c r="S138" s="32"/>
-    </row>
-    <row r="139" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M138" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="N138" s="32"/>
+      <c r="O138" s="32"/>
+      <c r="P138" s="32"/>
+      <c r="Q138" s="32"/>
+      <c r="R138" s="32"/>
+      <c r="S138" s="33"/>
+    </row>
+    <row r="139" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M139"/>
       <c r="N139"/>
       <c r="O139"/>
       <c r="P139"/>
       <c r="Q139"/>
     </row>
-    <row r="140" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C140" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D140" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E140" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F140" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G140" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="H140" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I140" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="J140" s="23" t="s">
+    <row r="140" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L140" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="M140" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="N140" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="O140" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="P140" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q140" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="R140" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="S140" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="L140" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="M140" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="N140" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="O140" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="P140" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q140" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="R140" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="S140" s="24" t="s">
+    </row>
+    <row r="141" spans="12:19" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L141" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="M141" s="23">
+        <v>2</v>
+      </c>
+      <c r="N141" s="23">
+        <v>1</v>
+      </c>
+      <c r="O141" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="P141" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q141" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="R141" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="S141" s="23">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="142" spans="12:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L142" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="M142" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="N142" s="32"/>
+      <c r="O142" s="32"/>
+      <c r="P142" s="32"/>
+      <c r="Q142" s="32"/>
+      <c r="R142" s="32"/>
+      <c r="S142" s="33"/>
+    </row>
+    <row r="143" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L143" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="M143" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="N143" s="34"/>
+      <c r="O143" s="34"/>
+      <c r="P143" s="34"/>
+      <c r="Q143" s="34"/>
+      <c r="R143" s="34"/>
+      <c r="S143" s="34"/>
+    </row>
+    <row r="145" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L145" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="M145" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="N145" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="O145" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="P145" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q145" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="R145" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="S145" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="141" spans="3:19" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C141" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="D141" s="23">
-        <v>1</v>
-      </c>
-      <c r="E141" s="23">
-        <v>1</v>
-      </c>
-      <c r="F141" s="23" t="s">
+    <row r="146" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L146" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="M146" s="23">
+        <v>2</v>
+      </c>
+      <c r="N146" s="23">
+        <v>1</v>
+      </c>
+      <c r="O146" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="G141" s="23" t="s">
+      <c r="P146" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="H141" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="I141" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="J141" s="23">
+      <c r="Q146" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="R146" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="S146" s="23">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="147" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L147" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="M147" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="N147" s="34"/>
+      <c r="O147" s="34"/>
+      <c r="P147" s="34"/>
+      <c r="Q147" s="34"/>
+      <c r="R147" s="34"/>
+      <c r="S147" s="34"/>
+    </row>
+    <row r="148" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L148" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="M148" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="L141" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="M141" s="24">
-        <v>2</v>
-      </c>
-      <c r="N141" s="24">
-        <v>1</v>
-      </c>
-      <c r="O141" s="24" t="s">
+      <c r="N148" s="34"/>
+      <c r="O148" s="34"/>
+      <c r="P148" s="34"/>
+      <c r="Q148" s="34"/>
+      <c r="R148" s="34"/>
+      <c r="S148" s="34"/>
+    </row>
+    <row r="150" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L150" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="M150" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="N150" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="O150" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="P150" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q150" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="R150" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="S150" s="23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="151" spans="12:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L151" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="M151" s="23">
+        <v>6</v>
+      </c>
+      <c r="N151" s="23">
+        <v>1</v>
+      </c>
+      <c r="O151" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="P151" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q151" s="23">
+        <v>0</v>
+      </c>
+      <c r="R151" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="S151" s="23">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="152" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L152" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="M152" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="N152" s="32"/>
+      <c r="O152" s="32"/>
+      <c r="P152" s="32"/>
+      <c r="Q152" s="32"/>
+      <c r="R152" s="32"/>
+      <c r="S152" s="33"/>
+    </row>
+    <row r="153" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L153" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="M153" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="N153" s="32"/>
+      <c r="O153" s="32"/>
+      <c r="P153" s="32"/>
+      <c r="Q153" s="32"/>
+      <c r="R153" s="32"/>
+      <c r="S153" s="33"/>
+    </row>
+    <row r="155" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L155" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="M155" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="N155" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="O155" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="P155" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q155" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="R155" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="S155" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="156" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L156" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="M156" s="28">
+        <v>2</v>
+      </c>
+      <c r="N156" s="28">
+        <v>1</v>
+      </c>
+      <c r="O156" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="P156" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q156" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="R156" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="S156" s="28">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="157" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L157" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="M157" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="N157" s="34"/>
+      <c r="O157" s="34"/>
+      <c r="P157" s="34"/>
+      <c r="Q157" s="34"/>
+      <c r="R157" s="34"/>
+      <c r="S157" s="34"/>
+    </row>
+    <row r="158" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L158" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="M158" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="N158" s="34"/>
+      <c r="O158" s="34"/>
+      <c r="P158" s="34"/>
+      <c r="Q158" s="34"/>
+      <c r="R158" s="34"/>
+      <c r="S158" s="34"/>
+    </row>
+    <row r="160" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L160" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="M160" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="N160" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="O160" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="P160" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q160" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="R160" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="S160" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L161" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="M161" s="28">
+        <v>3</v>
+      </c>
+      <c r="N161" s="28">
+        <v>1</v>
+      </c>
+      <c r="O161" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="P161" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q161" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="R161" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="S161" s="28">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="162" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L162" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="M162" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="N162" s="32"/>
+      <c r="O162" s="32"/>
+      <c r="P162" s="32"/>
+      <c r="Q162" s="32"/>
+      <c r="R162" s="32"/>
+      <c r="S162" s="33"/>
+    </row>
+    <row r="163" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L163" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="M163" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="N163" s="32"/>
+      <c r="O163" s="32"/>
+      <c r="P163" s="32"/>
+      <c r="Q163" s="32"/>
+      <c r="R163" s="32"/>
+      <c r="S163" s="33"/>
+    </row>
+    <row r="165" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L165" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="M165" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="N165" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="O165" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="P165" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q165" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="R165" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="S165" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="166" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L166" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="M166" s="28">
+        <v>3</v>
+      </c>
+      <c r="N166" s="28">
+        <v>1</v>
+      </c>
+      <c r="O166" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="P141" s="24" t="s">
+      <c r="P166" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="Q141" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="R141" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="S141" s="24">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="142" spans="3:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C142" s="23" t="s">
+      <c r="Q166" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="R166" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="S166" s="28">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="167" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L167" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D142" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="E142" s="28"/>
-      <c r="F142" s="28"/>
-      <c r="G142" s="28"/>
-      <c r="H142" s="28"/>
-      <c r="I142" s="28"/>
-      <c r="J142" s="29"/>
-      <c r="L142" s="24" t="s">
+      <c r="M167" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="N167" s="32"/>
+      <c r="O167" s="32"/>
+      <c r="P167" s="32"/>
+      <c r="Q167" s="32"/>
+      <c r="R167" s="32"/>
+      <c r="S167" s="33"/>
+    </row>
+    <row r="168" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L168" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="M168" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="N168" s="32"/>
+      <c r="O168" s="32"/>
+      <c r="P168" s="32"/>
+      <c r="Q168" s="32"/>
+      <c r="R168" s="32"/>
+      <c r="S168" s="33"/>
+    </row>
+    <row r="170" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L170" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="M170" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="N170" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="O170" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="P170" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q170" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="R170" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="S170" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="171" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L171" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="M171" s="28">
+        <v>6</v>
+      </c>
+      <c r="N171" s="28">
+        <v>1</v>
+      </c>
+      <c r="O171" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="P171" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q171" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="R171" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="S171" s="28">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="172" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L172" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="M142" s="30" t="s">
-        <v>181</v>
-      </c>
-      <c r="N142" s="31"/>
-      <c r="O142" s="31"/>
-      <c r="P142" s="31"/>
-      <c r="Q142" s="31"/>
-      <c r="R142" s="31"/>
-      <c r="S142" s="32"/>
-    </row>
-    <row r="143" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C143" s="23" t="s">
+      <c r="M172" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="N172" s="32"/>
+      <c r="O172" s="32"/>
+      <c r="P172" s="32"/>
+      <c r="Q172" s="32"/>
+      <c r="R172" s="32"/>
+      <c r="S172" s="33"/>
+    </row>
+    <row r="173" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L173" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D143" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="E143" s="28"/>
-      <c r="F143" s="28"/>
-      <c r="G143" s="28"/>
-      <c r="H143" s="28"/>
-      <c r="I143" s="28"/>
-      <c r="J143" s="29"/>
-      <c r="L143" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="M143" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="N143" s="31"/>
-      <c r="O143" s="31"/>
-      <c r="P143" s="31"/>
-      <c r="Q143" s="31"/>
-      <c r="R143" s="31"/>
-      <c r="S143" s="32"/>
-    </row>
-    <row r="145" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L145" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="M145" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="N145" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="O145" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="P145" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q145" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="R145" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="S145" s="24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="146" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L146" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="M146" s="24">
-        <v>2</v>
-      </c>
-      <c r="N146" s="24">
-        <v>1</v>
-      </c>
-      <c r="O146" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="P146" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q146" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="R146" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="S146" s="24">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="147" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L147" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="M147" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="N147" s="33"/>
-      <c r="O147" s="33"/>
-      <c r="P147" s="33"/>
-      <c r="Q147" s="33"/>
-      <c r="R147" s="33"/>
-      <c r="S147" s="33"/>
-    </row>
-    <row r="148" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L148" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="M148" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="N148" s="33"/>
-      <c r="O148" s="33"/>
-      <c r="P148" s="33"/>
-      <c r="Q148" s="33"/>
-      <c r="R148" s="33"/>
-      <c r="S148" s="33"/>
-    </row>
-    <row r="150" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L150" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="M150" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="N150" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="O150" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="P150" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q150" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="R150" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="S150" s="24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="151" spans="12:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L151" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="M151" s="24">
-        <v>6</v>
-      </c>
-      <c r="N151" s="24">
-        <v>1</v>
-      </c>
-      <c r="O151" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P151" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q151" s="24">
-        <v>0</v>
-      </c>
-      <c r="R151" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="S151" s="24">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="152" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L152" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="M152" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="N152" s="31"/>
-      <c r="O152" s="31"/>
-      <c r="P152" s="31"/>
-      <c r="Q152" s="31"/>
-      <c r="R152" s="31"/>
-      <c r="S152" s="32"/>
-    </row>
-    <row r="153" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L153" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="M153" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="N153" s="31"/>
-      <c r="O153" s="31"/>
-      <c r="P153" s="31"/>
-      <c r="Q153" s="31"/>
-      <c r="R153" s="31"/>
-      <c r="S153" s="32"/>
-    </row>
-    <row r="155" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L165"/>
-      <c r="M165"/>
-      <c r="N165"/>
-      <c r="O165"/>
-      <c r="P165"/>
-      <c r="Q165"/>
-      <c r="R165"/>
-      <c r="S165"/>
-    </row>
-    <row r="166" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L166"/>
-      <c r="M166"/>
-      <c r="N166"/>
-      <c r="O166"/>
-      <c r="P166"/>
-      <c r="Q166"/>
-      <c r="R166"/>
-      <c r="S166"/>
-    </row>
-    <row r="167" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L167"/>
-      <c r="M167" s="41"/>
-      <c r="N167" s="41"/>
-      <c r="O167" s="41"/>
-      <c r="P167" s="41"/>
-      <c r="Q167" s="41"/>
-      <c r="R167" s="41"/>
-      <c r="S167" s="41"/>
-    </row>
-    <row r="168" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L168"/>
-      <c r="M168" s="41"/>
-      <c r="N168" s="41"/>
-      <c r="O168" s="41"/>
-      <c r="P168" s="41"/>
-      <c r="Q168" s="41"/>
-      <c r="R168" s="41"/>
-      <c r="S168" s="41"/>
-    </row>
-    <row r="170" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="M173" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="N173" s="32"/>
+      <c r="O173" s="32"/>
+      <c r="P173" s="32"/>
+      <c r="Q173" s="32"/>
+      <c r="R173" s="32"/>
+      <c r="S173" s="33"/>
+    </row>
     <row r="175" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="176" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="177" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="178" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="125">
-    <mergeCell ref="M167:S167"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="D72:J72"/>
-    <mergeCell ref="D73:J73"/>
-    <mergeCell ref="D52:J52"/>
-    <mergeCell ref="D53:J53"/>
+    <mergeCell ref="M173:S173"/>
     <mergeCell ref="D57:J57"/>
     <mergeCell ref="D58:J58"/>
-    <mergeCell ref="D62:J62"/>
+    <mergeCell ref="D37:J37"/>
+    <mergeCell ref="D38:J38"/>
+    <mergeCell ref="D42:J42"/>
+    <mergeCell ref="D43:J43"/>
+    <mergeCell ref="D47:J47"/>
     <mergeCell ref="M127:S127"/>
     <mergeCell ref="M128:S128"/>
-    <mergeCell ref="D37:J37"/>
-    <mergeCell ref="D38:J38"/>
+    <mergeCell ref="M157:S157"/>
+    <mergeCell ref="M158:S158"/>
     <mergeCell ref="M38:S38"/>
     <mergeCell ref="M53:S53"/>
     <mergeCell ref="M62:S62"/>
+    <mergeCell ref="D87:J87"/>
+    <mergeCell ref="D88:J88"/>
+    <mergeCell ref="M162:S162"/>
+    <mergeCell ref="M92:S92"/>
+    <mergeCell ref="M142:S142"/>
+    <mergeCell ref="M143:S143"/>
+    <mergeCell ref="D122:J122"/>
+    <mergeCell ref="D123:J123"/>
+    <mergeCell ref="D48:J48"/>
+    <mergeCell ref="D52:J52"/>
+    <mergeCell ref="D53:J53"/>
+    <mergeCell ref="M163:S163"/>
     <mergeCell ref="D107:J107"/>
     <mergeCell ref="D108:J108"/>
-    <mergeCell ref="M168:S168"/>
-    <mergeCell ref="D63:J63"/>
-    <mergeCell ref="D67:J67"/>
-    <mergeCell ref="D68:J68"/>
-    <mergeCell ref="D43:J43"/>
-    <mergeCell ref="D127:J127"/>
-    <mergeCell ref="D128:J128"/>
     <mergeCell ref="M107:S107"/>
     <mergeCell ref="M108:S108"/>
-    <mergeCell ref="D82:J82"/>
-    <mergeCell ref="D83:J83"/>
+    <mergeCell ref="D62:J62"/>
+    <mergeCell ref="D63:J63"/>
     <mergeCell ref="M112:S112"/>
     <mergeCell ref="M113:S113"/>
     <mergeCell ref="M82:S82"/>
@@ -6069,6 +6142,8 @@
     <mergeCell ref="M68:S68"/>
     <mergeCell ref="M102:S102"/>
     <mergeCell ref="M132:S132"/>
+    <mergeCell ref="M153:S153"/>
+    <mergeCell ref="D83:J83"/>
     <mergeCell ref="V17:AB17"/>
     <mergeCell ref="V18:AB18"/>
     <mergeCell ref="M17:S17"/>
@@ -6079,27 +6154,32 @@
     <mergeCell ref="M27:S27"/>
     <mergeCell ref="M28:S28"/>
     <mergeCell ref="M33:S33"/>
-    <mergeCell ref="D17:J17"/>
-    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="D27:J27"/>
+    <mergeCell ref="D28:J28"/>
     <mergeCell ref="M57:S57"/>
     <mergeCell ref="M58:S58"/>
     <mergeCell ref="M97:S97"/>
     <mergeCell ref="M72:S72"/>
     <mergeCell ref="M73:S73"/>
-    <mergeCell ref="D98:J98"/>
-    <mergeCell ref="D102:J102"/>
+    <mergeCell ref="D78:J78"/>
+    <mergeCell ref="D82:J82"/>
     <mergeCell ref="M87:S87"/>
     <mergeCell ref="M88:S88"/>
     <mergeCell ref="M77:S77"/>
     <mergeCell ref="M78:S78"/>
     <mergeCell ref="M22:S22"/>
-    <mergeCell ref="D27:J27"/>
-    <mergeCell ref="D47:J47"/>
-    <mergeCell ref="D48:J48"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="D23:J23"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="M172:S172"/>
+    <mergeCell ref="D32:J32"/>
+    <mergeCell ref="D33:J33"/>
+    <mergeCell ref="D17:J17"/>
+    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="D72:J72"/>
+    <mergeCell ref="M43:S43"/>
+    <mergeCell ref="M47:S47"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M52:S52"/>
+    <mergeCell ref="M167:S167"/>
+    <mergeCell ref="M168:S168"/>
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="V12:AB12"/>
     <mergeCell ref="V13:AB13"/>
@@ -6111,38 +6191,23 @@
     <mergeCell ref="V8:AB8"/>
     <mergeCell ref="D7:J7"/>
     <mergeCell ref="D8:J8"/>
-    <mergeCell ref="M153:S153"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="D23:J23"/>
     <mergeCell ref="D92:J92"/>
-    <mergeCell ref="D103:J103"/>
-    <mergeCell ref="M43:S43"/>
-    <mergeCell ref="M47:S47"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M52:S52"/>
-    <mergeCell ref="D42:J42"/>
-    <mergeCell ref="M92:S92"/>
-    <mergeCell ref="M142:S142"/>
-    <mergeCell ref="M143:S143"/>
-    <mergeCell ref="D142:J142"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D137:J137"/>
-    <mergeCell ref="D138:J138"/>
-    <mergeCell ref="D132:J132"/>
-    <mergeCell ref="D133:J133"/>
-    <mergeCell ref="D87:J87"/>
-    <mergeCell ref="D88:J88"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D73:J73"/>
+    <mergeCell ref="M133:S133"/>
+    <mergeCell ref="D77:J77"/>
+    <mergeCell ref="D117:J117"/>
+    <mergeCell ref="D112:J112"/>
+    <mergeCell ref="D113:J113"/>
+    <mergeCell ref="D67:J67"/>
+    <mergeCell ref="D68:J68"/>
     <mergeCell ref="M42:S42"/>
     <mergeCell ref="M93:S93"/>
     <mergeCell ref="M67:S67"/>
-    <mergeCell ref="D113:J113"/>
-    <mergeCell ref="M147:S147"/>
-    <mergeCell ref="D32:J32"/>
-    <mergeCell ref="D33:J33"/>
-    <mergeCell ref="D112:J112"/>
-    <mergeCell ref="D77:J77"/>
-    <mergeCell ref="D78:J78"/>
     <mergeCell ref="D93:J93"/>
-    <mergeCell ref="M133:S133"/>
-    <mergeCell ref="D97:J97"/>
     <mergeCell ref="M152:S152"/>
     <mergeCell ref="M148:S148"/>
     <mergeCell ref="M63:S63"/>
@@ -6150,10 +6215,14 @@
     <mergeCell ref="M138:S138"/>
     <mergeCell ref="M122:S122"/>
     <mergeCell ref="M123:S123"/>
-    <mergeCell ref="D117:J117"/>
+    <mergeCell ref="D97:J97"/>
+    <mergeCell ref="D98:J98"/>
+    <mergeCell ref="D102:J102"/>
+    <mergeCell ref="D103:J103"/>
+    <mergeCell ref="M147:S147"/>
     <mergeCell ref="D118:J118"/>
-    <mergeCell ref="D122:J122"/>
-    <mergeCell ref="D123:J123"/>
+    <mergeCell ref="D127:J127"/>
+    <mergeCell ref="D128:J128"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6169,28 +6238,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="37"/>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
+      <c r="A1" s="42"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="37"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
+      <c r="A2" s="42"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
     </row>
     <row r="4" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>

--- a/Docs/Units.xlsx
+++ b/Docs/Units.xlsx
@@ -447,9 +447,6 @@
     <t>Darkest dungeon siren</t>
   </si>
   <si>
-    <t>Captivating</t>
-  </si>
-  <si>
     <t>Pushing, Merging</t>
   </si>
   <si>
@@ -643,6 +640,9 @@
   </si>
   <si>
     <t>Putrid (1), Cheap</t>
+  </si>
+  <si>
+    <t>Captivating, Evading</t>
   </si>
 </sst>
 </file>
@@ -855,9 +855,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -871,6 +868,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -878,21 +878,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
@@ -904,16 +889,31 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1221,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB178"/>
+  <dimension ref="A1:AB183"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.85546875" style="1"/>
@@ -1296,28 +1296,28 @@
       <c r="A5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="27" t="s">
+      <c r="C5" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="27" t="s">
+      <c r="G5" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="15" t="s">
         <v>19</v>
       </c>
       <c r="L5" s="6" t="s">
@@ -1373,29 +1373,29 @@
       <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="D6" s="27">
-        <v>1</v>
-      </c>
-      <c r="E6" s="27">
-        <v>2</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="27" t="s">
+      <c r="C6" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="15">
+        <v>3</v>
+      </c>
+      <c r="E6" s="15">
+        <v>0</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="J6" s="27">
-        <v>50</v>
+      <c r="H6" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="15">
+        <v>40</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>26</v>
@@ -1450,113 +1450,113 @@
       <c r="A7" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="36" t="s">
-        <v>201</v>
-      </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="D7" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
       <c r="L7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="44" t="s">
+      <c r="M7" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
       <c r="U7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V7" s="43" t="s">
+      <c r="V7" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="W7" s="43"/>
-      <c r="X7" s="43"/>
-      <c r="Y7" s="43"/>
-      <c r="Z7" s="43"/>
-      <c r="AA7" s="43"/>
-      <c r="AB7" s="43"/>
+      <c r="W7" s="38"/>
+      <c r="X7" s="38"/>
+      <c r="Y7" s="38"/>
+      <c r="Z7" s="38"/>
+      <c r="AA7" s="38"/>
+      <c r="AB7" s="38"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="5"/>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="36" t="s">
-        <v>199</v>
-      </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="38"/>
+      <c r="D8" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
       <c r="L8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="34"/>
-      <c r="S8" s="34"/>
+      <c r="M8" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="N8" s="37"/>
+      <c r="O8" s="37"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="37"/>
+      <c r="R8" s="37"/>
+      <c r="S8" s="37"/>
       <c r="U8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="35" t="s">
-        <v>198</v>
-      </c>
-      <c r="W8" s="35"/>
-      <c r="X8" s="35"/>
-      <c r="Y8" s="35"/>
-      <c r="Z8" s="35"/>
-      <c r="AA8" s="35"/>
-      <c r="AB8" s="35"/>
+      <c r="V8" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="W8" s="39"/>
+      <c r="X8" s="39"/>
+      <c r="Y8" s="39"/>
+      <c r="Z8" s="39"/>
+      <c r="AA8" s="39"/>
+      <c r="AB8" s="39"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="O9"/>
-      <c r="Q9" s="26"/>
+      <c r="Q9" s="25"/>
       <c r="X9"/>
     </row>
     <row r="10" spans="1:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="C10" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F10" s="27" t="s">
+      <c r="C10" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="27" t="s">
+      <c r="G10" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="26" t="s">
         <v>19</v>
       </c>
       <c r="L10" s="6" t="s">
@@ -1609,28 +1609,28 @@
       </c>
     </row>
     <row r="11" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="27">
-        <v>2</v>
-      </c>
-      <c r="E11" s="27">
-        <v>1</v>
-      </c>
-      <c r="F11" s="27" t="s">
+      <c r="D11" s="26">
+        <v>2</v>
+      </c>
+      <c r="E11" s="26">
+        <v>1</v>
+      </c>
+      <c r="F11" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G11" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="I11" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" s="27">
+      <c r="H11" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="26">
         <v>40</v>
       </c>
       <c r="L11" s="6" t="s">
@@ -1657,8 +1657,8 @@
       <c r="S11" s="6">
         <v>50</v>
       </c>
-      <c r="U11" s="30" t="s">
-        <v>173</v>
+      <c r="U11" s="29" t="s">
+        <v>172</v>
       </c>
       <c r="V11" s="2">
         <v>3</v>
@@ -1683,110 +1683,86 @@
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="38"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="45"/>
       <c r="L12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="44" t="s">
+      <c r="M12" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="N12" s="44"/>
-      <c r="O12" s="44"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="44"/>
-      <c r="R12" s="44"/>
-      <c r="S12" s="44"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="40"/>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="40"/>
+      <c r="S12" s="40"/>
       <c r="U12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V12" s="43" t="s">
+      <c r="V12" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="W12" s="43"/>
-      <c r="X12" s="43"/>
-      <c r="Y12" s="43"/>
-      <c r="Z12" s="43"/>
-      <c r="AA12" s="43"/>
-      <c r="AB12" s="43"/>
+      <c r="W12" s="38"/>
+      <c r="X12" s="38"/>
+      <c r="Y12" s="38"/>
+      <c r="Z12" s="38"/>
+      <c r="AA12" s="38"/>
+      <c r="AB12" s="38"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="36" t="s">
-        <v>207</v>
-      </c>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="38"/>
+      <c r="D13" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="45"/>
       <c r="L13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="44" t="s">
+      <c r="M13" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="N13" s="44"/>
-      <c r="O13" s="44"/>
-      <c r="P13" s="44"/>
-      <c r="Q13" s="44"/>
-      <c r="R13" s="44"/>
-      <c r="S13" s="44"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="40"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="40"/>
+      <c r="S13" s="40"/>
       <c r="U13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V13" s="43" t="s">
+      <c r="V13" s="38" t="s">
         <v>108</v>
       </c>
-      <c r="W13" s="43"/>
-      <c r="X13" s="43"/>
-      <c r="Y13" s="43"/>
-      <c r="Z13" s="43"/>
-      <c r="AA13" s="43"/>
-      <c r="AB13" s="43"/>
+      <c r="W13" s="38"/>
+      <c r="X13" s="38"/>
+      <c r="Y13" s="38"/>
+      <c r="Z13" s="38"/>
+      <c r="AA13" s="38"/>
+      <c r="AB13" s="38"/>
     </row>
     <row r="14" spans="1:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O14"/>
       <c r="X14"/>
     </row>
     <row r="15" spans="1:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="C15" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="F15" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="J15" s="24" t="s">
-        <v>19</v>
-      </c>
       <c r="L15" s="6" t="s">
         <v>0</v>
       </c>
@@ -1837,30 +1813,6 @@
       </c>
     </row>
     <row r="16" spans="1:28" ht="45" x14ac:dyDescent="0.25">
-      <c r="C16" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="D16" s="24">
-        <v>2</v>
-      </c>
-      <c r="E16" s="24">
-        <v>1</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="24">
-        <v>25</v>
-      </c>
       <c r="L16" s="6" t="s">
         <v>32</v>
       </c>
@@ -1911,80 +1863,56 @@
       </c>
     </row>
     <row r="17" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="C17" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="45" t="s">
-        <v>195</v>
-      </c>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
       <c r="L17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="44" t="s">
+      <c r="M17" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="N17" s="44"/>
-      <c r="O17" s="44"/>
-      <c r="P17" s="44"/>
-      <c r="Q17" s="44"/>
-      <c r="R17" s="44"/>
-      <c r="S17" s="44"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="40"/>
+      <c r="P17" s="40"/>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="40"/>
+      <c r="S17" s="40"/>
       <c r="U17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V17" s="43" t="s">
+      <c r="V17" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="W17" s="43"/>
-      <c r="X17" s="43"/>
-      <c r="Y17" s="43"/>
-      <c r="Z17" s="43"/>
-      <c r="AA17" s="43"/>
-      <c r="AB17" s="43"/>
+      <c r="W17" s="38"/>
+      <c r="X17" s="38"/>
+      <c r="Y17" s="38"/>
+      <c r="Z17" s="38"/>
+      <c r="AA17" s="38"/>
+      <c r="AB17" s="38"/>
     </row>
     <row r="18" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="C18" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
       <c r="L18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="44" t="s">
+      <c r="M18" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="44"/>
-      <c r="O18" s="44"/>
-      <c r="P18" s="44"/>
-      <c r="Q18" s="44"/>
-      <c r="R18" s="44"/>
-      <c r="S18" s="44"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="40"/>
+      <c r="P18" s="40"/>
+      <c r="Q18" s="40"/>
+      <c r="R18" s="40"/>
+      <c r="S18" s="40"/>
       <c r="U18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V18" s="35" t="s">
-        <v>198</v>
-      </c>
-      <c r="W18" s="35"/>
-      <c r="X18" s="35"/>
-      <c r="Y18" s="35"/>
-      <c r="Z18" s="35"/>
-      <c r="AA18" s="35"/>
-      <c r="AB18" s="35"/>
+      <c r="V18" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="W18" s="39"/>
+      <c r="X18" s="39"/>
+      <c r="Y18" s="39"/>
+      <c r="Z18" s="39"/>
+      <c r="AA18" s="39"/>
+      <c r="AB18" s="39"/>
     </row>
     <row r="19" spans="3:28" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C19" s="16"/>
@@ -1998,28 +1926,28 @@
       <c r="O19"/>
     </row>
     <row r="20" spans="3:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="C20" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="F20" s="25" t="s">
+      <c r="C20" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="J20" s="25" t="s">
+      <c r="G20" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="24" t="s">
         <v>19</v>
       </c>
       <c r="L20" s="6" t="s">
@@ -2048,32 +1976,32 @@
       </c>
     </row>
     <row r="21" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="D21" s="25">
-        <v>3</v>
-      </c>
-      <c r="E21" s="25">
-        <v>1</v>
-      </c>
-      <c r="F21" s="25" t="s">
+      <c r="D21" s="24">
+        <v>3</v>
+      </c>
+      <c r="E21" s="24">
+        <v>1</v>
+      </c>
+      <c r="F21" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="G21" s="25" t="s">
+      <c r="G21" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="25" t="s">
+      <c r="H21" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="I21" s="25" t="s">
+      <c r="I21" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="J21" s="25">
+      <c r="J21" s="24">
         <v>60</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M21" s="6">
         <v>3</v>
@@ -2098,82 +2026,58 @@
       </c>
     </row>
     <row r="22" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="36" t="s">
+      <c r="D22" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="38"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="45"/>
       <c r="L22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="44" t="s">
+      <c r="M22" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="N22" s="44"/>
-      <c r="O22" s="44"/>
-      <c r="P22" s="44"/>
-      <c r="Q22" s="44"/>
-      <c r="R22" s="44"/>
-      <c r="S22" s="44"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="40"/>
+      <c r="P22" s="40"/>
+      <c r="Q22" s="40"/>
+      <c r="R22" s="40"/>
+      <c r="S22" s="40"/>
     </row>
     <row r="23" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="36" t="s">
+      <c r="D23" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="38"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="45"/>
       <c r="L23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="44" t="s">
+      <c r="M23" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="N23" s="44"/>
-      <c r="O23" s="44"/>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="44"/>
-      <c r="R23" s="44"/>
-      <c r="S23" s="44"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="40"/>
+      <c r="P23" s="40"/>
+      <c r="Q23" s="40"/>
+      <c r="R23" s="40"/>
+      <c r="S23" s="40"/>
     </row>
     <row r="25" spans="3:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J25" s="15" t="s">
-        <v>19</v>
-      </c>
       <c r="L25" s="6" t="s">
         <v>0</v>
       </c>
@@ -2200,30 +2104,6 @@
       </c>
     </row>
     <row r="26" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="D26" s="15">
-        <v>3</v>
-      </c>
-      <c r="E26" s="15">
-        <v>1</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="G26" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="H26" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I26" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J26" s="15">
-        <v>40</v>
-      </c>
       <c r="L26" s="6" t="s">
         <v>46</v>
       </c>
@@ -2250,56 +2130,32 @@
       </c>
     </row>
     <row r="27" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="45" t="s">
-        <v>142</v>
-      </c>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
       <c r="L27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M27" s="44" t="s">
+      <c r="M27" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="N27" s="44"/>
-      <c r="O27" s="44"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="44"/>
-      <c r="R27" s="44"/>
-      <c r="S27" s="44"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="40"/>
+      <c r="S27" s="40"/>
     </row>
     <row r="28" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" s="45" t="s">
-        <v>143</v>
-      </c>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="45"/>
       <c r="L28" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
+      <c r="N28" s="37"/>
+      <c r="O28" s="37"/>
+      <c r="P28" s="37"/>
+      <c r="Q28" s="37"/>
+      <c r="R28" s="37"/>
+      <c r="S28" s="37"/>
     </row>
     <row r="30" spans="3:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="13" t="s">
@@ -2405,15 +2261,15 @@
       <c r="C32" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="39" t="s">
+      <c r="D32" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="40"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="41"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="36"/>
       <c r="L32" s="11" t="s">
         <v>11</v>
       </c>
@@ -2431,15 +2287,15 @@
       <c r="C33" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="39" t="s">
+      <c r="D33" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="40"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="41"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="36"/>
       <c r="L33" s="11" t="s">
         <v>17</v>
       </c>
@@ -2454,28 +2310,28 @@
       <c r="S33" s="33"/>
     </row>
     <row r="35" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="D35" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="F35" s="29" t="s">
+      <c r="C35" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F35" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="G35" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="H35" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I35" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="J35" s="29" t="s">
+      <c r="G35" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="28" t="s">
         <v>19</v>
       </c>
       <c r="L35" s="11" t="s">
@@ -2504,28 +2360,28 @@
       </c>
     </row>
     <row r="36" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="29" t="s">
+      <c r="C36" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="D36" s="29">
-        <v>3</v>
-      </c>
-      <c r="E36" s="29">
-        <v>1</v>
-      </c>
-      <c r="F36" s="29" t="s">
+      <c r="D36" s="28">
+        <v>3</v>
+      </c>
+      <c r="E36" s="28">
+        <v>1</v>
+      </c>
+      <c r="F36" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="G36" s="29" t="s">
+      <c r="G36" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="29" t="s">
+      <c r="H36" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="I36" s="29" t="s">
+      <c r="I36" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="J36" s="29">
+      <c r="J36" s="28">
         <v>35</v>
       </c>
       <c r="L36" s="11" t="s">
@@ -2554,18 +2410,18 @@
       </c>
     </row>
     <row r="37" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="29" t="s">
+      <c r="C37" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="39" t="s">
+      <c r="D37" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="40"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="41"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="36"/>
       <c r="L37" s="11" t="s">
         <v>11</v>
       </c>
@@ -2580,54 +2436,54 @@
       <c r="S37" s="33"/>
     </row>
     <row r="38" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="29" t="s">
+      <c r="C38" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="41"/>
+      <c r="D38" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" s="35"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="36"/>
       <c r="L38" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M38" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="N38" s="34"/>
-      <c r="O38" s="34"/>
-      <c r="P38" s="34"/>
-      <c r="Q38" s="34"/>
-      <c r="R38" s="34"/>
-      <c r="S38" s="34"/>
+      <c r="M38" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="N38" s="37"/>
+      <c r="O38" s="37"/>
+      <c r="P38" s="37"/>
+      <c r="Q38" s="37"/>
+      <c r="R38" s="37"/>
+      <c r="S38" s="37"/>
     </row>
     <row r="40" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="D40" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="F40" s="29" t="s">
+      <c r="C40" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F40" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="G40" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="H40" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I40" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="J40" s="29" t="s">
+      <c r="G40" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="H40" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="I40" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="J40" s="28" t="s">
         <v>19</v>
       </c>
       <c r="L40" s="11" t="s">
@@ -2656,28 +2512,28 @@
       </c>
     </row>
     <row r="41" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="29" t="s">
+      <c r="C41" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="D41" s="29">
-        <v>3</v>
-      </c>
-      <c r="E41" s="29">
-        <v>2</v>
-      </c>
-      <c r="F41" s="29" t="s">
+      <c r="D41" s="28">
+        <v>3</v>
+      </c>
+      <c r="E41" s="28">
+        <v>2</v>
+      </c>
+      <c r="F41" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="G41" s="29" t="s">
+      <c r="G41" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="H41" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="I41" s="29" t="s">
+      <c r="H41" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="J41" s="29">
+      <c r="J41" s="28">
         <v>30</v>
       </c>
       <c r="L41" s="11" t="s">
@@ -2706,23 +2562,23 @@
       </c>
     </row>
     <row r="42" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="29" t="s">
+      <c r="C42" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D42" s="39" t="s">
+      <c r="D42" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="E42" s="40"/>
-      <c r="F42" s="40"/>
-      <c r="G42" s="40"/>
-      <c r="H42" s="40"/>
-      <c r="I42" s="40"/>
-      <c r="J42" s="41"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="35"/>
+      <c r="J42" s="36"/>
       <c r="L42" s="11" t="s">
         <v>11</v>
       </c>
       <c r="M42" s="31" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N42" s="32"/>
       <c r="O42" s="32"/>
@@ -2732,18 +2588,18 @@
       <c r="S42" s="33"/>
     </row>
     <row r="43" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="29" t="s">
+      <c r="C43" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="E43" s="40"/>
-      <c r="F43" s="40"/>
-      <c r="G43" s="40"/>
-      <c r="H43" s="40"/>
-      <c r="I43" s="40"/>
-      <c r="J43" s="41"/>
+      <c r="D43" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="35"/>
+      <c r="J43" s="36"/>
       <c r="L43" s="11" t="s">
         <v>17</v>
       </c>
@@ -2758,28 +2614,28 @@
       <c r="S43" s="33"/>
     </row>
     <row r="45" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="D45" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="F45" s="29" t="s">
+      <c r="C45" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="D45" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F45" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="G45" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I45" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45" s="29" t="s">
+      <c r="G45" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="28" t="s">
         <v>19</v>
       </c>
       <c r="L45" s="11" t="s">
@@ -2808,28 +2664,28 @@
       </c>
     </row>
     <row r="46" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="D46" s="29">
-        <v>3</v>
-      </c>
-      <c r="E46" s="29">
-        <v>1</v>
-      </c>
-      <c r="F46" s="29" t="s">
+      <c r="C46" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D46" s="28">
+        <v>3</v>
+      </c>
+      <c r="E46" s="28">
+        <v>1</v>
+      </c>
+      <c r="F46" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="G46" s="29" t="s">
+      <c r="G46" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="H46" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="I46" s="29" t="s">
+      <c r="H46" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="J46" s="29">
+      <c r="J46" s="28">
         <v>30</v>
       </c>
       <c r="L46" s="11" t="s">
@@ -2858,18 +2714,18 @@
       </c>
     </row>
     <row r="47" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="29" t="s">
+      <c r="C47" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="E47" s="40"/>
-      <c r="F47" s="40"/>
-      <c r="G47" s="40"/>
-      <c r="H47" s="40"/>
-      <c r="I47" s="40"/>
-      <c r="J47" s="41"/>
+      <c r="D47" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="E47" s="35"/>
+      <c r="F47" s="35"/>
+      <c r="G47" s="35"/>
+      <c r="H47" s="35"/>
+      <c r="I47" s="35"/>
+      <c r="J47" s="36"/>
       <c r="L47" s="11" t="s">
         <v>11</v>
       </c>
@@ -2884,18 +2740,18 @@
       <c r="S47" s="33"/>
     </row>
     <row r="48" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C48" s="29" t="s">
+      <c r="C48" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="E48" s="40"/>
-      <c r="F48" s="40"/>
-      <c r="G48" s="40"/>
-      <c r="H48" s="40"/>
-      <c r="I48" s="40"/>
-      <c r="J48" s="41"/>
+      <c r="D48" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E48" s="35"/>
+      <c r="F48" s="35"/>
+      <c r="G48" s="35"/>
+      <c r="H48" s="35"/>
+      <c r="I48" s="35"/>
+      <c r="J48" s="36"/>
       <c r="L48" s="11" t="s">
         <v>17</v>
       </c>
@@ -2910,28 +2766,28 @@
       <c r="S48" s="33"/>
     </row>
     <row r="50" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C50" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="D50" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="F50" s="29" t="s">
+      <c r="C50" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="G50" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="H50" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I50" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="J50" s="29" t="s">
+      <c r="G50" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="H50" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="I50" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="J50" s="28" t="s">
         <v>19</v>
       </c>
       <c r="L50" s="11" t="s">
@@ -2960,28 +2816,28 @@
       </c>
     </row>
     <row r="51" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C51" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="D51" s="29">
-        <v>4</v>
-      </c>
-      <c r="E51" s="29">
-        <v>2</v>
-      </c>
-      <c r="F51" s="29" t="s">
+      <c r="C51" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="D51" s="28">
+        <v>4</v>
+      </c>
+      <c r="E51" s="28">
+        <v>2</v>
+      </c>
+      <c r="F51" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="G51" s="29" t="s">
+      <c r="G51" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="H51" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="I51" s="29" t="s">
+      <c r="H51" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="I51" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="J51" s="29">
+      <c r="J51" s="28">
         <v>40</v>
       </c>
       <c r="L51" s="11" t="s">
@@ -3010,80 +2866,80 @@
       </c>
     </row>
     <row r="52" spans="3:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C52" s="29" t="s">
+      <c r="C52" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D52" s="39" t="s">
-        <v>149</v>
-      </c>
-      <c r="E52" s="40"/>
-      <c r="F52" s="40"/>
-      <c r="G52" s="40"/>
-      <c r="H52" s="40"/>
-      <c r="I52" s="40"/>
-      <c r="J52" s="41"/>
+      <c r="D52" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="E52" s="35"/>
+      <c r="F52" s="35"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="35"/>
+      <c r="I52" s="35"/>
+      <c r="J52" s="36"/>
       <c r="L52" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M52" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="N52" s="34"/>
-      <c r="O52" s="34"/>
-      <c r="P52" s="34"/>
-      <c r="Q52" s="34"/>
-      <c r="R52" s="34"/>
-      <c r="S52" s="34"/>
+      <c r="M52" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="N52" s="37"/>
+      <c r="O52" s="37"/>
+      <c r="P52" s="37"/>
+      <c r="Q52" s="37"/>
+      <c r="R52" s="37"/>
+      <c r="S52" s="37"/>
     </row>
     <row r="53" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C53" s="29" t="s">
+      <c r="C53" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="E53" s="40"/>
-      <c r="F53" s="40"/>
-      <c r="G53" s="40"/>
-      <c r="H53" s="40"/>
-      <c r="I53" s="40"/>
-      <c r="J53" s="41"/>
+      <c r="D53" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="E53" s="35"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="36"/>
       <c r="L53" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M53" s="34" t="s">
-        <v>199</v>
-      </c>
-      <c r="N53" s="34"/>
-      <c r="O53" s="34"/>
-      <c r="P53" s="34"/>
-      <c r="Q53" s="34"/>
-      <c r="R53" s="34"/>
-      <c r="S53" s="34"/>
+      <c r="M53" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="N53" s="37"/>
+      <c r="O53" s="37"/>
+      <c r="P53" s="37"/>
+      <c r="Q53" s="37"/>
+      <c r="R53" s="37"/>
+      <c r="S53" s="37"/>
     </row>
     <row r="55" spans="3:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="C55" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="D55" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="E55" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="F55" s="29" t="s">
+      <c r="C55" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="D55" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E55" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="G55" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="H55" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I55" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="J55" s="29" t="s">
+      <c r="G55" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="H55" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="I55" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="J55" s="28" t="s">
         <v>19</v>
       </c>
       <c r="L55" s="17" t="s">
@@ -3112,28 +2968,28 @@
       </c>
     </row>
     <row r="56" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C56" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="D56" s="29">
-        <v>3</v>
-      </c>
-      <c r="E56" s="29">
-        <v>1</v>
-      </c>
-      <c r="F56" s="29" t="s">
+      <c r="C56" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="D56" s="28">
+        <v>3</v>
+      </c>
+      <c r="E56" s="28">
+        <v>1</v>
+      </c>
+      <c r="F56" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="G56" s="29" t="s">
+      <c r="G56" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="H56" s="29" t="s">
+      <c r="H56" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="I56" s="29" t="s">
+      <c r="I56" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="J56" s="29">
+      <c r="J56" s="28">
         <v>30</v>
       </c>
       <c r="L56" s="17" t="s">
@@ -3162,18 +3018,18 @@
       </c>
     </row>
     <row r="57" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="29" t="s">
+      <c r="C57" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="39" t="s">
-        <v>158</v>
-      </c>
-      <c r="E57" s="40"/>
-      <c r="F57" s="40"/>
-      <c r="G57" s="40"/>
-      <c r="H57" s="40"/>
-      <c r="I57" s="40"/>
-      <c r="J57" s="41"/>
+      <c r="D57" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="35"/>
+      <c r="J57" s="36"/>
       <c r="L57" s="17" t="s">
         <v>11</v>
       </c>
@@ -3188,18 +3044,18 @@
       <c r="S57" s="33"/>
     </row>
     <row r="58" spans="3:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C58" s="29" t="s">
+      <c r="C58" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="E58" s="40"/>
-      <c r="F58" s="40"/>
-      <c r="G58" s="40"/>
-      <c r="H58" s="40"/>
-      <c r="I58" s="40"/>
-      <c r="J58" s="41"/>
+      <c r="D58" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="35"/>
+      <c r="I58" s="35"/>
+      <c r="J58" s="36"/>
       <c r="L58" s="17" t="s">
         <v>17</v>
       </c>
@@ -3265,7 +3121,7 @@
     </row>
     <row r="61" spans="3:19" ht="45" x14ac:dyDescent="0.25">
       <c r="C61" s="22" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D61" s="22">
         <v>5</v>
@@ -3317,53 +3173,53 @@
       <c r="C62" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D62" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="E62" s="40"/>
-      <c r="F62" s="40"/>
-      <c r="G62" s="40"/>
-      <c r="H62" s="40"/>
-      <c r="I62" s="40"/>
-      <c r="J62" s="41"/>
+      <c r="D62" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="E62" s="35"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="35"/>
+      <c r="I62" s="35"/>
+      <c r="J62" s="36"/>
       <c r="L62" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M62" s="34" t="s">
+      <c r="M62" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="N62" s="34"/>
-      <c r="O62" s="34"/>
-      <c r="P62" s="34"/>
-      <c r="Q62" s="34"/>
-      <c r="R62" s="34"/>
-      <c r="S62" s="34"/>
+      <c r="N62" s="37"/>
+      <c r="O62" s="37"/>
+      <c r="P62" s="37"/>
+      <c r="Q62" s="37"/>
+      <c r="R62" s="37"/>
+      <c r="S62" s="37"/>
     </row>
     <row r="63" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="39" t="s">
-        <v>172</v>
-      </c>
-      <c r="E63" s="40"/>
-      <c r="F63" s="40"/>
-      <c r="G63" s="40"/>
-      <c r="H63" s="40"/>
-      <c r="I63" s="40"/>
-      <c r="J63" s="41"/>
+      <c r="D63" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="E63" s="35"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="35"/>
+      <c r="I63" s="35"/>
+      <c r="J63" s="36"/>
       <c r="L63" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M63" s="34" t="s">
+      <c r="M63" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="N63" s="34"/>
-      <c r="O63" s="34"/>
-      <c r="P63" s="34"/>
-      <c r="Q63" s="34"/>
-      <c r="R63" s="34"/>
-      <c r="S63" s="34"/>
+      <c r="N63" s="37"/>
+      <c r="O63" s="37"/>
+      <c r="P63" s="37"/>
+      <c r="Q63" s="37"/>
+      <c r="R63" s="37"/>
+      <c r="S63" s="37"/>
     </row>
     <row r="65" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="22" t="s">
@@ -3469,15 +3325,15 @@
       <c r="C67" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="39" t="s">
+      <c r="D67" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="E67" s="40"/>
-      <c r="F67" s="40"/>
-      <c r="G67" s="40"/>
-      <c r="H67" s="40"/>
-      <c r="I67" s="40"/>
-      <c r="J67" s="41"/>
+      <c r="E67" s="35"/>
+      <c r="F67" s="35"/>
+      <c r="G67" s="35"/>
+      <c r="H67" s="35"/>
+      <c r="I67" s="35"/>
+      <c r="J67" s="36"/>
       <c r="L67" s="18" t="s">
         <v>11</v>
       </c>
@@ -3495,20 +3351,20 @@
       <c r="C68" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="39" t="s">
+      <c r="D68" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="E68" s="40"/>
-      <c r="F68" s="40"/>
-      <c r="G68" s="40"/>
-      <c r="H68" s="40"/>
-      <c r="I68" s="40"/>
-      <c r="J68" s="41"/>
+      <c r="E68" s="35"/>
+      <c r="F68" s="35"/>
+      <c r="G68" s="35"/>
+      <c r="H68" s="35"/>
+      <c r="I68" s="35"/>
+      <c r="J68" s="36"/>
       <c r="L68" s="18" t="s">
         <v>17</v>
       </c>
       <c r="M68" s="31" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N68" s="32"/>
       <c r="O68" s="32"/>
@@ -3621,15 +3477,15 @@
       <c r="C72" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="39" t="s">
+      <c r="D72" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="E72" s="40"/>
-      <c r="F72" s="40"/>
-      <c r="G72" s="40"/>
-      <c r="H72" s="40"/>
-      <c r="I72" s="40"/>
-      <c r="J72" s="41"/>
+      <c r="E72" s="35"/>
+      <c r="F72" s="35"/>
+      <c r="G72" s="35"/>
+      <c r="H72" s="35"/>
+      <c r="I72" s="35"/>
+      <c r="J72" s="36"/>
       <c r="L72" s="18" t="s">
         <v>11</v>
       </c>
@@ -3647,27 +3503,27 @@
       <c r="C73" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="39" t="s">
+      <c r="D73" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="40"/>
-      <c r="F73" s="40"/>
-      <c r="G73" s="40"/>
-      <c r="H73" s="40"/>
-      <c r="I73" s="40"/>
-      <c r="J73" s="41"/>
+      <c r="E73" s="35"/>
+      <c r="F73" s="35"/>
+      <c r="G73" s="35"/>
+      <c r="H73" s="35"/>
+      <c r="I73" s="35"/>
+      <c r="J73" s="36"/>
       <c r="L73" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M73" s="34" t="s">
-        <v>203</v>
-      </c>
-      <c r="N73" s="34"/>
-      <c r="O73" s="34"/>
-      <c r="P73" s="34"/>
-      <c r="Q73" s="34"/>
-      <c r="R73" s="34"/>
-      <c r="S73" s="34"/>
+      <c r="M73" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="N73" s="37"/>
+      <c r="O73" s="37"/>
+      <c r="P73" s="37"/>
+      <c r="Q73" s="37"/>
+      <c r="R73" s="37"/>
+      <c r="S73" s="37"/>
     </row>
     <row r="75" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="13" t="s">
@@ -3773,15 +3629,15 @@
       <c r="C77" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="39" t="s">
+      <c r="D77" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="E77" s="40"/>
-      <c r="F77" s="40"/>
-      <c r="G77" s="40"/>
-      <c r="H77" s="40"/>
-      <c r="I77" s="40"/>
-      <c r="J77" s="41"/>
+      <c r="E77" s="35"/>
+      <c r="F77" s="35"/>
+      <c r="G77" s="35"/>
+      <c r="H77" s="35"/>
+      <c r="I77" s="35"/>
+      <c r="J77" s="36"/>
       <c r="L77" s="19" t="s">
         <v>11</v>
       </c>
@@ -3799,15 +3655,15 @@
       <c r="C78" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="39" t="s">
+      <c r="D78" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="E78" s="40"/>
-      <c r="F78" s="40"/>
-      <c r="G78" s="40"/>
-      <c r="H78" s="40"/>
-      <c r="I78" s="40"/>
-      <c r="J78" s="41"/>
+      <c r="E78" s="35"/>
+      <c r="F78" s="35"/>
+      <c r="G78" s="35"/>
+      <c r="H78" s="35"/>
+      <c r="I78" s="35"/>
+      <c r="J78" s="36"/>
       <c r="L78" s="19" t="s">
         <v>17</v>
       </c>
@@ -3925,15 +3781,15 @@
       <c r="C82" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="39" t="s">
+      <c r="D82" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E82" s="40"/>
-      <c r="F82" s="40"/>
-      <c r="G82" s="40"/>
-      <c r="H82" s="40"/>
-      <c r="I82" s="40"/>
-      <c r="J82" s="41"/>
+      <c r="E82" s="35"/>
+      <c r="F82" s="35"/>
+      <c r="G82" s="35"/>
+      <c r="H82" s="35"/>
+      <c r="I82" s="35"/>
+      <c r="J82" s="36"/>
       <c r="L82" s="19" t="s">
         <v>11</v>
       </c>
@@ -3951,15 +3807,15 @@
       <c r="C83" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D83" s="39" t="s">
+      <c r="D83" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="E83" s="40"/>
-      <c r="F83" s="40"/>
-      <c r="G83" s="40"/>
-      <c r="H83" s="40"/>
-      <c r="I83" s="40"/>
-      <c r="J83" s="41"/>
+      <c r="E83" s="35"/>
+      <c r="F83" s="35"/>
+      <c r="G83" s="35"/>
+      <c r="H83" s="35"/>
+      <c r="I83" s="35"/>
+      <c r="J83" s="36"/>
       <c r="L83" s="19" t="s">
         <v>17</v>
       </c>
@@ -4080,15 +3936,15 @@
       <c r="C87" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D87" s="39" t="s">
+      <c r="D87" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="E87" s="40"/>
-      <c r="F87" s="40"/>
-      <c r="G87" s="40"/>
-      <c r="H87" s="40"/>
-      <c r="I87" s="40"/>
-      <c r="J87" s="41"/>
+      <c r="E87" s="35"/>
+      <c r="F87" s="35"/>
+      <c r="G87" s="35"/>
+      <c r="H87" s="35"/>
+      <c r="I87" s="35"/>
+      <c r="J87" s="36"/>
       <c r="L87" s="19" t="s">
         <v>11</v>
       </c>
@@ -4106,15 +3962,15 @@
       <c r="C88" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D88" s="39" t="s">
-        <v>206</v>
-      </c>
-      <c r="E88" s="40"/>
-      <c r="F88" s="40"/>
-      <c r="G88" s="40"/>
-      <c r="H88" s="40"/>
-      <c r="I88" s="40"/>
-      <c r="J88" s="41"/>
+      <c r="D88" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="E88" s="35"/>
+      <c r="F88" s="35"/>
+      <c r="G88" s="35"/>
+      <c r="H88" s="35"/>
+      <c r="I88" s="35"/>
+      <c r="J88" s="36"/>
       <c r="L88" s="19" t="s">
         <v>17</v>
       </c>
@@ -4232,15 +4088,15 @@
       <c r="C92" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D92" s="39" t="s">
+      <c r="D92" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="E92" s="40"/>
-      <c r="F92" s="40"/>
-      <c r="G92" s="40"/>
-      <c r="H92" s="40"/>
-      <c r="I92" s="40"/>
-      <c r="J92" s="41"/>
+      <c r="E92" s="35"/>
+      <c r="F92" s="35"/>
+      <c r="G92" s="35"/>
+      <c r="H92" s="35"/>
+      <c r="I92" s="35"/>
+      <c r="J92" s="36"/>
       <c r="L92" s="19" t="s">
         <v>11</v>
       </c>
@@ -4258,20 +4114,20 @@
       <c r="C93" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="39" t="s">
+      <c r="D93" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="E93" s="40"/>
-      <c r="F93" s="40"/>
-      <c r="G93" s="40"/>
-      <c r="H93" s="40"/>
-      <c r="I93" s="40"/>
-      <c r="J93" s="41"/>
+      <c r="E93" s="35"/>
+      <c r="F93" s="35"/>
+      <c r="G93" s="35"/>
+      <c r="H93" s="35"/>
+      <c r="I93" s="35"/>
+      <c r="J93" s="36"/>
       <c r="L93" s="19" t="s">
         <v>17</v>
       </c>
       <c r="M93" s="31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N93" s="32"/>
       <c r="O93" s="32"/>
@@ -4332,7 +4188,7 @@
     </row>
     <row r="96" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C96" s="22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D96" s="22">
         <v>1</v>
@@ -4384,15 +4240,15 @@
       <c r="C97" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="E97" s="35"/>
-      <c r="F97" s="35"/>
-      <c r="G97" s="35"/>
-      <c r="H97" s="35"/>
-      <c r="I97" s="35"/>
-      <c r="J97" s="35"/>
+      <c r="D97" s="39" t="s">
+        <v>183</v>
+      </c>
+      <c r="E97" s="39"/>
+      <c r="F97" s="39"/>
+      <c r="G97" s="39"/>
+      <c r="H97" s="39"/>
+      <c r="I97" s="39"/>
+      <c r="J97" s="39"/>
       <c r="L97" s="19" t="s">
         <v>11</v>
       </c>
@@ -4410,15 +4266,15 @@
       <c r="C98" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D98" s="35" t="s">
-        <v>185</v>
-      </c>
-      <c r="E98" s="35"/>
-      <c r="F98" s="35"/>
-      <c r="G98" s="35"/>
-      <c r="H98" s="35"/>
-      <c r="I98" s="35"/>
-      <c r="J98" s="35"/>
+      <c r="D98" s="39" t="s">
+        <v>184</v>
+      </c>
+      <c r="E98" s="39"/>
+      <c r="F98" s="39"/>
+      <c r="G98" s="39"/>
+      <c r="H98" s="39"/>
+      <c r="I98" s="39"/>
+      <c r="J98" s="39"/>
       <c r="L98" s="19" t="s">
         <v>17</v>
       </c>
@@ -4487,7 +4343,7 @@
     </row>
     <row r="101" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C101" s="22" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D101" s="22">
         <v>2</v>
@@ -4539,15 +4395,15 @@
       <c r="C102" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D102" s="35" t="s">
-        <v>193</v>
-      </c>
-      <c r="E102" s="35"/>
-      <c r="F102" s="35"/>
-      <c r="G102" s="35"/>
-      <c r="H102" s="35"/>
-      <c r="I102" s="35"/>
-      <c r="J102" s="35"/>
+      <c r="D102" s="39" t="s">
+        <v>192</v>
+      </c>
+      <c r="E102" s="39"/>
+      <c r="F102" s="39"/>
+      <c r="G102" s="39"/>
+      <c r="H102" s="39"/>
+      <c r="I102" s="39"/>
+      <c r="J102" s="39"/>
       <c r="L102" s="19" t="s">
         <v>11</v>
       </c>
@@ -4565,15 +4421,15 @@
       <c r="C103" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D103" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="E103" s="35"/>
-      <c r="F103" s="35"/>
-      <c r="G103" s="35"/>
-      <c r="H103" s="35"/>
-      <c r="I103" s="35"/>
-      <c r="J103" s="35"/>
+      <c r="D103" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="E103" s="39"/>
+      <c r="F103" s="39"/>
+      <c r="G103" s="39"/>
+      <c r="H103" s="39"/>
+      <c r="I103" s="39"/>
+      <c r="J103" s="39"/>
       <c r="L103" s="19" t="s">
         <v>17</v>
       </c>
@@ -4674,7 +4530,7 @@
         <v>50</v>
       </c>
       <c r="L106" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M106" s="20">
         <v>3</v>
@@ -4702,53 +4558,53 @@
       <c r="C107" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="39" t="s">
+      <c r="D107" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="E107" s="40"/>
-      <c r="F107" s="40"/>
-      <c r="G107" s="40"/>
-      <c r="H107" s="40"/>
-      <c r="I107" s="40"/>
-      <c r="J107" s="41"/>
+      <c r="E107" s="35"/>
+      <c r="F107" s="35"/>
+      <c r="G107" s="35"/>
+      <c r="H107" s="35"/>
+      <c r="I107" s="35"/>
+      <c r="J107" s="36"/>
       <c r="L107" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M107" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="N107" s="34"/>
-      <c r="O107" s="34"/>
-      <c r="P107" s="34"/>
-      <c r="Q107" s="34"/>
-      <c r="R107" s="34"/>
-      <c r="S107" s="34"/>
+      <c r="M107" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="N107" s="37"/>
+      <c r="O107" s="37"/>
+      <c r="P107" s="37"/>
+      <c r="Q107" s="37"/>
+      <c r="R107" s="37"/>
+      <c r="S107" s="37"/>
     </row>
     <row r="108" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C108" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="39" t="s">
+      <c r="D108" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="E108" s="40"/>
-      <c r="F108" s="40"/>
-      <c r="G108" s="40"/>
-      <c r="H108" s="40"/>
-      <c r="I108" s="40"/>
-      <c r="J108" s="41"/>
+      <c r="E108" s="35"/>
+      <c r="F108" s="35"/>
+      <c r="G108" s="35"/>
+      <c r="H108" s="35"/>
+      <c r="I108" s="35"/>
+      <c r="J108" s="36"/>
       <c r="L108" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="M108" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="N108" s="34"/>
-      <c r="O108" s="34"/>
-      <c r="P108" s="34"/>
-      <c r="Q108" s="34"/>
-      <c r="R108" s="34"/>
-      <c r="S108" s="34"/>
+      <c r="M108" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="N108" s="37"/>
+      <c r="O108" s="37"/>
+      <c r="P108" s="37"/>
+      <c r="Q108" s="37"/>
+      <c r="R108" s="37"/>
+      <c r="S108" s="37"/>
     </row>
     <row r="110" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C110" s="22" t="s">
@@ -4802,7 +4658,7 @@
     </row>
     <row r="111" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C111" s="22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D111" s="22">
         <v>5</v>
@@ -4820,7 +4676,7 @@
         <v>8</v>
       </c>
       <c r="I111" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J111" s="22">
         <v>70</v>
@@ -4854,15 +4710,15 @@
       <c r="C112" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D112" s="39" t="s">
-        <v>191</v>
-      </c>
-      <c r="E112" s="40"/>
-      <c r="F112" s="40"/>
-      <c r="G112" s="40"/>
-      <c r="H112" s="40"/>
-      <c r="I112" s="40"/>
-      <c r="J112" s="41"/>
+      <c r="D112" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="E112" s="35"/>
+      <c r="F112" s="35"/>
+      <c r="G112" s="35"/>
+      <c r="H112" s="35"/>
+      <c r="I112" s="35"/>
+      <c r="J112" s="36"/>
       <c r="L112" s="20" t="s">
         <v>11</v>
       </c>
@@ -4880,15 +4736,15 @@
       <c r="C113" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D113" s="39" t="s">
-        <v>185</v>
-      </c>
-      <c r="E113" s="40"/>
-      <c r="F113" s="40"/>
-      <c r="G113" s="40"/>
-      <c r="H113" s="40"/>
-      <c r="I113" s="40"/>
-      <c r="J113" s="41"/>
+      <c r="D113" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="E113" s="35"/>
+      <c r="F113" s="35"/>
+      <c r="G113" s="35"/>
+      <c r="H113" s="35"/>
+      <c r="I113" s="35"/>
+      <c r="J113" s="36"/>
       <c r="L113" s="20" t="s">
         <v>17</v>
       </c>
@@ -4954,7 +4810,7 @@
     </row>
     <row r="116" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C116" s="22" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D116" s="22">
         <v>2</v>
@@ -5006,15 +4862,15 @@
       <c r="C117" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D117" s="39" t="s">
-        <v>188</v>
-      </c>
-      <c r="E117" s="40"/>
-      <c r="F117" s="40"/>
-      <c r="G117" s="40"/>
-      <c r="H117" s="40"/>
-      <c r="I117" s="40"/>
-      <c r="J117" s="41"/>
+      <c r="D117" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E117" s="35"/>
+      <c r="F117" s="35"/>
+      <c r="G117" s="35"/>
+      <c r="H117" s="35"/>
+      <c r="I117" s="35"/>
+      <c r="J117" s="36"/>
       <c r="L117" s="20" t="s">
         <v>11</v>
       </c>
@@ -5032,20 +4888,20 @@
       <c r="C118" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D118" s="39" t="s">
-        <v>185</v>
-      </c>
-      <c r="E118" s="40"/>
-      <c r="F118" s="40"/>
-      <c r="G118" s="40"/>
-      <c r="H118" s="40"/>
-      <c r="I118" s="40"/>
-      <c r="J118" s="41"/>
+      <c r="D118" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="E118" s="35"/>
+      <c r="F118" s="35"/>
+      <c r="G118" s="35"/>
+      <c r="H118" s="35"/>
+      <c r="I118" s="35"/>
+      <c r="J118" s="36"/>
       <c r="L118" s="20" t="s">
         <v>17</v>
       </c>
       <c r="M118" s="31" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N118" s="32"/>
       <c r="O118" s="32"/>
@@ -5106,7 +4962,7 @@
     </row>
     <row r="121" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C121" s="22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D121" s="22">
         <v>1</v>
@@ -5130,7 +4986,7 @@
         <v>10</v>
       </c>
       <c r="L121" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M121" s="21">
         <v>2</v>
@@ -5158,53 +5014,53 @@
       <c r="C122" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D122" s="39" t="s">
-        <v>184</v>
-      </c>
-      <c r="E122" s="40"/>
-      <c r="F122" s="40"/>
-      <c r="G122" s="40"/>
-      <c r="H122" s="40"/>
-      <c r="I122" s="40"/>
-      <c r="J122" s="41"/>
+      <c r="D122" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="E122" s="35"/>
+      <c r="F122" s="35"/>
+      <c r="G122" s="35"/>
+      <c r="H122" s="35"/>
+      <c r="I122" s="35"/>
+      <c r="J122" s="36"/>
       <c r="L122" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M122" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="N122" s="34"/>
-      <c r="O122" s="34"/>
-      <c r="P122" s="34"/>
-      <c r="Q122" s="34"/>
-      <c r="R122" s="34"/>
-      <c r="S122" s="34"/>
+      <c r="M122" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="N122" s="37"/>
+      <c r="O122" s="37"/>
+      <c r="P122" s="37"/>
+      <c r="Q122" s="37"/>
+      <c r="R122" s="37"/>
+      <c r="S122" s="37"/>
     </row>
     <row r="123" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C123" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D123" s="39" t="s">
-        <v>185</v>
-      </c>
-      <c r="E123" s="40"/>
-      <c r="F123" s="40"/>
-      <c r="G123" s="40"/>
-      <c r="H123" s="40"/>
-      <c r="I123" s="40"/>
-      <c r="J123" s="41"/>
+      <c r="D123" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="E123" s="35"/>
+      <c r="F123" s="35"/>
+      <c r="G123" s="35"/>
+      <c r="H123" s="35"/>
+      <c r="I123" s="35"/>
+      <c r="J123" s="36"/>
       <c r="L123" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M123" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="N123" s="34"/>
-      <c r="O123" s="34"/>
-      <c r="P123" s="34"/>
-      <c r="Q123" s="34"/>
-      <c r="R123" s="34"/>
-      <c r="S123" s="34"/>
+      <c r="M123" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="N123" s="37"/>
+      <c r="O123" s="37"/>
+      <c r="P123" s="37"/>
+      <c r="Q123" s="37"/>
+      <c r="R123" s="37"/>
+      <c r="S123" s="37"/>
     </row>
     <row r="125" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C125" s="13" t="s">
@@ -5310,15 +5166,15 @@
       <c r="C127" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D127" s="39" t="s">
+      <c r="D127" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="E127" s="40"/>
-      <c r="F127" s="40"/>
-      <c r="G127" s="40"/>
-      <c r="H127" s="40"/>
-      <c r="I127" s="40"/>
-      <c r="J127" s="41"/>
+      <c r="E127" s="35"/>
+      <c r="F127" s="35"/>
+      <c r="G127" s="35"/>
+      <c r="H127" s="35"/>
+      <c r="I127" s="35"/>
+      <c r="J127" s="36"/>
       <c r="L127" s="21" t="s">
         <v>11</v>
       </c>
@@ -5336,15 +5192,15 @@
       <c r="C128" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D128" s="39" t="s">
+      <c r="D128" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="E128" s="40"/>
-      <c r="F128" s="40"/>
-      <c r="G128" s="40"/>
-      <c r="H128" s="40"/>
-      <c r="I128" s="40"/>
-      <c r="J128" s="41"/>
+      <c r="E128" s="35"/>
+      <c r="F128" s="35"/>
+      <c r="G128" s="35"/>
+      <c r="H128" s="35"/>
+      <c r="I128" s="35"/>
+      <c r="J128" s="36"/>
       <c r="L128" s="21" t="s">
         <v>17</v>
       </c>
@@ -5560,7 +5416,7 @@
     </row>
     <row r="141" spans="12:19" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L141" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M141" s="23">
         <v>2</v>
@@ -5589,7 +5445,7 @@
         <v>11</v>
       </c>
       <c r="M142" s="31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N142" s="32"/>
       <c r="O142" s="32"/>
@@ -5602,15 +5458,15 @@
       <c r="L143" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="M143" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="N143" s="34"/>
-      <c r="O143" s="34"/>
-      <c r="P143" s="34"/>
-      <c r="Q143" s="34"/>
-      <c r="R143" s="34"/>
-      <c r="S143" s="34"/>
+      <c r="M143" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="N143" s="37"/>
+      <c r="O143" s="37"/>
+      <c r="P143" s="37"/>
+      <c r="Q143" s="37"/>
+      <c r="R143" s="37"/>
+      <c r="S143" s="37"/>
     </row>
     <row r="145" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L145" s="23" t="s">
@@ -5640,7 +5496,7 @@
     </row>
     <row r="146" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L146" s="23" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M146" s="23">
         <v>2</v>
@@ -5668,29 +5524,29 @@
       <c r="L147" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="M147" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="N147" s="34"/>
-      <c r="O147" s="34"/>
-      <c r="P147" s="34"/>
-      <c r="Q147" s="34"/>
-      <c r="R147" s="34"/>
-      <c r="S147" s="34"/>
+      <c r="M147" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="N147" s="37"/>
+      <c r="O147" s="37"/>
+      <c r="P147" s="37"/>
+      <c r="Q147" s="37"/>
+      <c r="R147" s="37"/>
+      <c r="S147" s="37"/>
     </row>
     <row r="148" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L148" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="M148" s="34" t="s">
+      <c r="M148" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="N148" s="34"/>
-      <c r="O148" s="34"/>
-      <c r="P148" s="34"/>
-      <c r="Q148" s="34"/>
-      <c r="R148" s="34"/>
-      <c r="S148" s="34"/>
+      <c r="N148" s="37"/>
+      <c r="O148" s="37"/>
+      <c r="P148" s="37"/>
+      <c r="Q148" s="37"/>
+      <c r="R148" s="37"/>
+      <c r="S148" s="37"/>
     </row>
     <row r="150" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L150" s="23" t="s">
@@ -5763,7 +5619,7 @@
         <v>17</v>
       </c>
       <c r="M153" s="31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N153" s="32"/>
       <c r="O153" s="32"/>
@@ -5773,143 +5629,143 @@
       <c r="S153" s="33"/>
     </row>
     <row r="155" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L155" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="M155" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="N155" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="O155" s="28" t="s">
+      <c r="L155" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="M155" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="N155" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="O155" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="P155" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q155" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="R155" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="S155" s="28" t="s">
+      <c r="P155" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q155" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="R155" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="S155" s="27" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="156" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L156" s="28" t="s">
-        <v>169</v>
-      </c>
-      <c r="M156" s="28">
-        <v>2</v>
-      </c>
-      <c r="N156" s="28">
-        <v>1</v>
-      </c>
-      <c r="O156" s="28" t="s">
+      <c r="L156" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="M156" s="27">
+        <v>2</v>
+      </c>
+      <c r="N156" s="27">
+        <v>1</v>
+      </c>
+      <c r="O156" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="P156" s="28" t="s">
+      <c r="P156" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="Q156" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="R156" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="S156" s="28">
+      <c r="Q156" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="R156" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="S156" s="27">
         <v>25</v>
       </c>
     </row>
     <row r="157" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L157" s="28" t="s">
+      <c r="L157" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="M157" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="N157" s="34"/>
-      <c r="O157" s="34"/>
-      <c r="P157" s="34"/>
-      <c r="Q157" s="34"/>
-      <c r="R157" s="34"/>
-      <c r="S157" s="34"/>
+      <c r="M157" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="N157" s="37"/>
+      <c r="O157" s="37"/>
+      <c r="P157" s="37"/>
+      <c r="Q157" s="37"/>
+      <c r="R157" s="37"/>
+      <c r="S157" s="37"/>
     </row>
     <row r="158" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L158" s="28" t="s">
+      <c r="L158" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="M158" s="34" t="s">
-        <v>204</v>
-      </c>
-      <c r="N158" s="34"/>
-      <c r="O158" s="34"/>
-      <c r="P158" s="34"/>
-      <c r="Q158" s="34"/>
-      <c r="R158" s="34"/>
-      <c r="S158" s="34"/>
+      <c r="M158" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="N158" s="37"/>
+      <c r="O158" s="37"/>
+      <c r="P158" s="37"/>
+      <c r="Q158" s="37"/>
+      <c r="R158" s="37"/>
+      <c r="S158" s="37"/>
     </row>
     <row r="160" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L160" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="M160" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="N160" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="O160" s="28" t="s">
+      <c r="L160" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="M160" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="N160" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="O160" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="P160" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q160" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="R160" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="S160" s="28" t="s">
+      <c r="P160" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q160" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="R160" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="S160" s="27" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="161" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L161" s="28" t="s">
+      <c r="L161" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="M161" s="28">
-        <v>3</v>
-      </c>
-      <c r="N161" s="28">
-        <v>1</v>
-      </c>
-      <c r="O161" s="28" t="s">
+      <c r="M161" s="27">
+        <v>3</v>
+      </c>
+      <c r="N161" s="27">
+        <v>1</v>
+      </c>
+      <c r="O161" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="P161" s="28" t="s">
+      <c r="P161" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="Q161" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="R161" s="28" t="s">
+      <c r="Q161" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="R161" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="S161" s="28">
+      <c r="S161" s="27">
         <v>35</v>
       </c>
     </row>
     <row r="162" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L162" s="28" t="s">
+      <c r="L162" s="27" t="s">
         <v>11</v>
       </c>
       <c r="M162" s="31" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N162" s="32"/>
       <c r="O162" s="32"/>
@@ -5919,11 +5775,11 @@
       <c r="S162" s="33"/>
     </row>
     <row r="163" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L163" s="28" t="s">
+      <c r="L163" s="27" t="s">
         <v>17</v>
       </c>
       <c r="M163" s="31" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N163" s="32"/>
       <c r="O163" s="32"/>
@@ -5933,63 +5789,63 @@
       <c r="S163" s="33"/>
     </row>
     <row r="165" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L165" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="M165" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="N165" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="O165" s="28" t="s">
+      <c r="L165" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="M165" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="N165" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="O165" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="P165" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q165" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="R165" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="S165" s="28" t="s">
+      <c r="P165" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q165" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="R165" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="S165" s="27" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="166" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L166" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="M166" s="28">
-        <v>3</v>
-      </c>
-      <c r="N166" s="28">
-        <v>1</v>
-      </c>
-      <c r="O166" s="28" t="s">
+      <c r="L166" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="M166" s="27">
+        <v>3</v>
+      </c>
+      <c r="N166" s="27">
+        <v>1</v>
+      </c>
+      <c r="O166" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="P166" s="28" t="s">
+      <c r="P166" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="Q166" s="28" t="s">
+      <c r="Q166" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="R166" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="S166" s="28">
+      <c r="R166" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="S166" s="27">
         <v>40</v>
       </c>
     </row>
     <row r="167" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L167" s="28" t="s">
+      <c r="L167" s="27" t="s">
         <v>11</v>
       </c>
       <c r="M167" s="31" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N167" s="32"/>
       <c r="O167" s="32"/>
@@ -5999,11 +5855,11 @@
       <c r="S167" s="33"/>
     </row>
     <row r="168" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L168" s="28" t="s">
+      <c r="L168" s="27" t="s">
         <v>17</v>
       </c>
       <c r="M168" s="31" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N168" s="32"/>
       <c r="O168" s="32"/>
@@ -6013,63 +5869,63 @@
       <c r="S168" s="33"/>
     </row>
     <row r="170" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L170" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="M170" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="N170" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="O170" s="28" t="s">
+      <c r="L170" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="M170" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="N170" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="O170" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="P170" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q170" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="R170" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="S170" s="28" t="s">
+      <c r="P170" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q170" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="R170" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="S170" s="27" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="171" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L171" s="28" t="s">
+      <c r="L171" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="M171" s="27">
+        <v>6</v>
+      </c>
+      <c r="N171" s="27">
+        <v>1</v>
+      </c>
+      <c r="O171" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="P171" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q171" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="R171" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="S171" s="27">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="172" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L172" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="M172" s="31" t="s">
         <v>163</v>
-      </c>
-      <c r="M171" s="28">
-        <v>6</v>
-      </c>
-      <c r="N171" s="28">
-        <v>1</v>
-      </c>
-      <c r="O171" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="P171" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q171" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="R171" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="S171" s="28">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="172" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L172" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="M172" s="31" t="s">
-        <v>164</v>
       </c>
       <c r="N172" s="32"/>
       <c r="O172" s="32"/>
@@ -6079,11 +5935,11 @@
       <c r="S172" s="33"/>
     </row>
     <row r="173" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L173" s="28" t="s">
+      <c r="L173" s="27" t="s">
         <v>17</v>
       </c>
       <c r="M173" s="31" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N173" s="32"/>
       <c r="O173" s="32"/>
@@ -6092,12 +5948,269 @@
       <c r="R173" s="32"/>
       <c r="S173" s="33"/>
     </row>
-    <row r="175" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L175" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="M175" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="N175" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="O175" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="P175" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q175" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="R175" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="S175" s="30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="176" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L176" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="M176" s="30">
+        <v>2</v>
+      </c>
+      <c r="N176" s="30">
+        <v>1</v>
+      </c>
+      <c r="O176" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="P176" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q176" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="R176" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="S176" s="30">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="177" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L177" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="M177" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="N177" s="37"/>
+      <c r="O177" s="37"/>
+      <c r="P177" s="37"/>
+      <c r="Q177" s="37"/>
+      <c r="R177" s="37"/>
+      <c r="S177" s="37"/>
+    </row>
+    <row r="178" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L178" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="M178" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="N178" s="37"/>
+      <c r="O178" s="37"/>
+      <c r="P178" s="37"/>
+      <c r="Q178" s="37"/>
+      <c r="R178" s="37"/>
+      <c r="S178" s="37"/>
+    </row>
+    <row r="180" spans="12:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="L180" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="M180" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="N180" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="O180" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="P180" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q180" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="R180" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="S180" s="30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="181" spans="12:19" x14ac:dyDescent="0.25">
+      <c r="L181" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="M181" s="30">
+        <v>1</v>
+      </c>
+      <c r="N181" s="30">
+        <v>2</v>
+      </c>
+      <c r="O181" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="P181" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q181" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="R181" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="S181" s="30">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="182" spans="12:19" x14ac:dyDescent="0.25">
+      <c r="L182" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="M182" s="31" t="s">
+        <v>200</v>
+      </c>
+      <c r="N182" s="32"/>
+      <c r="O182" s="32"/>
+      <c r="P182" s="32"/>
+      <c r="Q182" s="32"/>
+      <c r="R182" s="32"/>
+      <c r="S182" s="33"/>
+    </row>
+    <row r="183" spans="12:19" x14ac:dyDescent="0.25">
+      <c r="L183" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="M183" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="N183" s="32"/>
+      <c r="O183" s="32"/>
+      <c r="P183" s="32"/>
+      <c r="Q183" s="32"/>
+      <c r="R183" s="32"/>
+      <c r="S183" s="33"/>
+    </row>
   </sheetData>
   <mergeCells count="125">
+    <mergeCell ref="M137:S137"/>
+    <mergeCell ref="M138:S138"/>
+    <mergeCell ref="M122:S122"/>
+    <mergeCell ref="M123:S123"/>
+    <mergeCell ref="D97:J97"/>
+    <mergeCell ref="D98:J98"/>
+    <mergeCell ref="D102:J102"/>
+    <mergeCell ref="D103:J103"/>
+    <mergeCell ref="M147:S147"/>
+    <mergeCell ref="D118:J118"/>
+    <mergeCell ref="D127:J127"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="V12:AB12"/>
+    <mergeCell ref="V13:AB13"/>
+    <mergeCell ref="M12:S12"/>
+    <mergeCell ref="M8:S8"/>
+    <mergeCell ref="M7:S7"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="V7:AB7"/>
+    <mergeCell ref="V8:AB8"/>
+    <mergeCell ref="M182:S182"/>
+    <mergeCell ref="M183:S183"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="M172:S172"/>
+    <mergeCell ref="D32:J32"/>
+    <mergeCell ref="D33:J33"/>
+    <mergeCell ref="M177:S177"/>
+    <mergeCell ref="M178:S178"/>
+    <mergeCell ref="D72:J72"/>
+    <mergeCell ref="M43:S43"/>
+    <mergeCell ref="M47:S47"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M52:S52"/>
+    <mergeCell ref="M167:S167"/>
+    <mergeCell ref="M168:S168"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="D92:J92"/>
+    <mergeCell ref="D73:J73"/>
+    <mergeCell ref="M133:S133"/>
+    <mergeCell ref="D77:J77"/>
+    <mergeCell ref="D117:J117"/>
+    <mergeCell ref="D112:J112"/>
+    <mergeCell ref="D113:J113"/>
+    <mergeCell ref="D67:J67"/>
+    <mergeCell ref="D68:J68"/>
+    <mergeCell ref="M42:S42"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="M57:S57"/>
+    <mergeCell ref="M58:S58"/>
+    <mergeCell ref="M97:S97"/>
+    <mergeCell ref="M72:S72"/>
+    <mergeCell ref="M73:S73"/>
+    <mergeCell ref="D78:J78"/>
+    <mergeCell ref="D82:J82"/>
+    <mergeCell ref="M87:S87"/>
+    <mergeCell ref="M88:S88"/>
+    <mergeCell ref="M77:S77"/>
+    <mergeCell ref="M78:S78"/>
+    <mergeCell ref="M93:S93"/>
+    <mergeCell ref="M67:S67"/>
+    <mergeCell ref="D93:J93"/>
+    <mergeCell ref="M63:S63"/>
+    <mergeCell ref="V17:AB17"/>
+    <mergeCell ref="V18:AB18"/>
+    <mergeCell ref="M17:S17"/>
+    <mergeCell ref="M18:S18"/>
+    <mergeCell ref="M32:S32"/>
+    <mergeCell ref="M37:S37"/>
+    <mergeCell ref="M23:S23"/>
+    <mergeCell ref="M27:S27"/>
+    <mergeCell ref="M28:S28"/>
+    <mergeCell ref="M33:S33"/>
+    <mergeCell ref="M22:S22"/>
+    <mergeCell ref="D52:J52"/>
+    <mergeCell ref="D53:J53"/>
+    <mergeCell ref="M163:S163"/>
+    <mergeCell ref="D107:J107"/>
+    <mergeCell ref="D108:J108"/>
+    <mergeCell ref="M107:S107"/>
+    <mergeCell ref="M108:S108"/>
+    <mergeCell ref="D62:J62"/>
+    <mergeCell ref="D63:J63"/>
+    <mergeCell ref="M112:S112"/>
+    <mergeCell ref="M113:S113"/>
+    <mergeCell ref="M82:S82"/>
+    <mergeCell ref="M83:S83"/>
+    <mergeCell ref="M117:S117"/>
+    <mergeCell ref="M118:S118"/>
+    <mergeCell ref="M103:S103"/>
+    <mergeCell ref="M98:S98"/>
+    <mergeCell ref="M68:S68"/>
+    <mergeCell ref="M102:S102"/>
+    <mergeCell ref="M132:S132"/>
+    <mergeCell ref="M153:S153"/>
+    <mergeCell ref="D83:J83"/>
+    <mergeCell ref="M152:S152"/>
+    <mergeCell ref="M148:S148"/>
     <mergeCell ref="M173:S173"/>
     <mergeCell ref="D57:J57"/>
     <mergeCell ref="D58:J58"/>
@@ -6122,107 +6235,6 @@
     <mergeCell ref="D122:J122"/>
     <mergeCell ref="D123:J123"/>
     <mergeCell ref="D48:J48"/>
-    <mergeCell ref="D52:J52"/>
-    <mergeCell ref="D53:J53"/>
-    <mergeCell ref="M163:S163"/>
-    <mergeCell ref="D107:J107"/>
-    <mergeCell ref="D108:J108"/>
-    <mergeCell ref="M107:S107"/>
-    <mergeCell ref="M108:S108"/>
-    <mergeCell ref="D62:J62"/>
-    <mergeCell ref="D63:J63"/>
-    <mergeCell ref="M112:S112"/>
-    <mergeCell ref="M113:S113"/>
-    <mergeCell ref="M82:S82"/>
-    <mergeCell ref="M83:S83"/>
-    <mergeCell ref="M117:S117"/>
-    <mergeCell ref="M118:S118"/>
-    <mergeCell ref="M103:S103"/>
-    <mergeCell ref="M98:S98"/>
-    <mergeCell ref="M68:S68"/>
-    <mergeCell ref="M102:S102"/>
-    <mergeCell ref="M132:S132"/>
-    <mergeCell ref="M153:S153"/>
-    <mergeCell ref="D83:J83"/>
-    <mergeCell ref="V17:AB17"/>
-    <mergeCell ref="V18:AB18"/>
-    <mergeCell ref="M17:S17"/>
-    <mergeCell ref="M18:S18"/>
-    <mergeCell ref="M32:S32"/>
-    <mergeCell ref="M37:S37"/>
-    <mergeCell ref="M23:S23"/>
-    <mergeCell ref="M27:S27"/>
-    <mergeCell ref="M28:S28"/>
-    <mergeCell ref="M33:S33"/>
-    <mergeCell ref="D27:J27"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="M57:S57"/>
-    <mergeCell ref="M58:S58"/>
-    <mergeCell ref="M97:S97"/>
-    <mergeCell ref="M72:S72"/>
-    <mergeCell ref="M73:S73"/>
-    <mergeCell ref="D78:J78"/>
-    <mergeCell ref="D82:J82"/>
-    <mergeCell ref="M87:S87"/>
-    <mergeCell ref="M88:S88"/>
-    <mergeCell ref="M77:S77"/>
-    <mergeCell ref="M78:S78"/>
-    <mergeCell ref="M22:S22"/>
-    <mergeCell ref="M172:S172"/>
-    <mergeCell ref="D32:J32"/>
-    <mergeCell ref="D33:J33"/>
-    <mergeCell ref="D17:J17"/>
-    <mergeCell ref="D18:J18"/>
-    <mergeCell ref="D72:J72"/>
-    <mergeCell ref="M43:S43"/>
-    <mergeCell ref="M47:S47"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M52:S52"/>
-    <mergeCell ref="M167:S167"/>
-    <mergeCell ref="M168:S168"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="V12:AB12"/>
-    <mergeCell ref="V13:AB13"/>
-    <mergeCell ref="M12:S12"/>
-    <mergeCell ref="M8:S8"/>
-    <mergeCell ref="M7:S7"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="V7:AB7"/>
-    <mergeCell ref="V8:AB8"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="D23:J23"/>
-    <mergeCell ref="D92:J92"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D73:J73"/>
-    <mergeCell ref="M133:S133"/>
-    <mergeCell ref="D77:J77"/>
-    <mergeCell ref="D117:J117"/>
-    <mergeCell ref="D112:J112"/>
-    <mergeCell ref="D113:J113"/>
-    <mergeCell ref="D67:J67"/>
-    <mergeCell ref="D68:J68"/>
-    <mergeCell ref="M42:S42"/>
-    <mergeCell ref="M93:S93"/>
-    <mergeCell ref="M67:S67"/>
-    <mergeCell ref="D93:J93"/>
-    <mergeCell ref="M152:S152"/>
-    <mergeCell ref="M148:S148"/>
-    <mergeCell ref="M63:S63"/>
-    <mergeCell ref="M137:S137"/>
-    <mergeCell ref="M138:S138"/>
-    <mergeCell ref="M122:S122"/>
-    <mergeCell ref="M123:S123"/>
-    <mergeCell ref="D97:J97"/>
-    <mergeCell ref="D98:J98"/>
-    <mergeCell ref="D102:J102"/>
-    <mergeCell ref="D103:J103"/>
-    <mergeCell ref="M147:S147"/>
-    <mergeCell ref="D118:J118"/>
-    <mergeCell ref="D127:J127"/>
-    <mergeCell ref="D128:J128"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Docs/Units.xlsx
+++ b/Docs/Units.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="212">
   <si>
     <t>Name</t>
   </si>
@@ -643,6 +643,15 @@
   </si>
   <si>
     <t>Captivating, Evading</t>
+  </si>
+  <si>
+    <t>Dark princess' ride</t>
+  </si>
+  <si>
+    <t>Genderbent old Vect miniature</t>
+  </si>
+  <si>
+    <t>Charging, Bloodthirsty</t>
   </si>
 </sst>
 </file>
@@ -783,7 +792,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -871,6 +880,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -904,9 +919,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -914,6 +926,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1221,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB183"/>
+  <dimension ref="A1:AB188"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.85546875" style="1"/>
@@ -1246,30 +1261,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
     </row>
     <row r="2" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
     </row>
     <row r="3" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
@@ -1453,39 +1468,39 @@
       <c r="C7" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
       <c r="L7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="40" t="s">
+      <c r="M7" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="40"/>
-      <c r="S7" s="40"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
       <c r="U7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V7" s="38" t="s">
+      <c r="V7" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="W7" s="38"/>
-      <c r="X7" s="38"/>
-      <c r="Y7" s="38"/>
-      <c r="Z7" s="38"/>
-      <c r="AA7" s="38"/>
-      <c r="AB7" s="38"/>
+      <c r="W7" s="40"/>
+      <c r="X7" s="40"/>
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="40"/>
+      <c r="AA7" s="40"/>
+      <c r="AB7" s="40"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
@@ -1495,39 +1510,39 @@
       <c r="C8" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="D8" s="43" t="s">
         <v>208</v>
       </c>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
       <c r="L8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="37" t="s">
+      <c r="M8" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="37"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="39"/>
+      <c r="S8" s="39"/>
       <c r="U8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="39" t="s">
+      <c r="V8" s="41" t="s">
         <v>197</v>
       </c>
-      <c r="W8" s="39"/>
-      <c r="X8" s="39"/>
-      <c r="Y8" s="39"/>
-      <c r="Z8" s="39"/>
-      <c r="AA8" s="39"/>
-      <c r="AB8" s="39"/>
+      <c r="W8" s="41"/>
+      <c r="X8" s="41"/>
+      <c r="Y8" s="41"/>
+      <c r="Z8" s="41"/>
+      <c r="AA8" s="41"/>
+      <c r="AB8" s="41"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="O9"/>
@@ -1686,83 +1701,107 @@
       <c r="C12" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="46"/>
       <c r="L12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="40" t="s">
+      <c r="M12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="N12" s="40"/>
-      <c r="O12" s="40"/>
-      <c r="P12" s="40"/>
-      <c r="Q12" s="40"/>
-      <c r="R12" s="40"/>
-      <c r="S12" s="40"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="42"/>
+      <c r="S12" s="42"/>
       <c r="U12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V12" s="38" t="s">
+      <c r="V12" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="38"/>
-      <c r="AB12" s="38"/>
+      <c r="W12" s="40"/>
+      <c r="X12" s="40"/>
+      <c r="Y12" s="40"/>
+      <c r="Z12" s="40"/>
+      <c r="AA12" s="40"/>
+      <c r="AB12" s="40"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="C13" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="43" t="s">
+      <c r="D13" s="44" t="s">
         <v>206</v>
       </c>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="46"/>
       <c r="L13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="40" t="s">
+      <c r="M13" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="40"/>
-      <c r="Q13" s="40"/>
-      <c r="R13" s="40"/>
-      <c r="S13" s="40"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="42"/>
       <c r="U13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V13" s="38" t="s">
+      <c r="V13" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="W13" s="38"/>
-      <c r="X13" s="38"/>
-      <c r="Y13" s="38"/>
-      <c r="Z13" s="38"/>
-      <c r="AA13" s="38"/>
-      <c r="AB13" s="38"/>
+      <c r="W13" s="40"/>
+      <c r="X13" s="40"/>
+      <c r="Y13" s="40"/>
+      <c r="Z13" s="40"/>
+      <c r="AA13" s="40"/>
+      <c r="AB13" s="40"/>
     </row>
     <row r="14" spans="1:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O14"/>
       <c r="X14"/>
     </row>
     <row r="15" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="C15" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="32" t="s">
+        <v>19</v>
+      </c>
       <c r="L15" s="6" t="s">
         <v>0</v>
       </c>
@@ -1813,6 +1852,30 @@
       </c>
     </row>
     <row r="16" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+      <c r="C16" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="32">
+        <v>2</v>
+      </c>
+      <c r="E16" s="32">
+        <v>1</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="32">
+        <v>40</v>
+      </c>
       <c r="L16" s="6" t="s">
         <v>32</v>
       </c>
@@ -1863,56 +1926,80 @@
       </c>
     </row>
     <row r="17" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="C17" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="46"/>
       <c r="L17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="40" t="s">
+      <c r="M17" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N17" s="40"/>
-      <c r="O17" s="40"/>
-      <c r="P17" s="40"/>
-      <c r="Q17" s="40"/>
-      <c r="R17" s="40"/>
-      <c r="S17" s="40"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="42"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="42"/>
+      <c r="R17" s="42"/>
+      <c r="S17" s="42"/>
       <c r="U17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V17" s="38" t="s">
+      <c r="V17" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="W17" s="38"/>
-      <c r="X17" s="38"/>
-      <c r="Y17" s="38"/>
-      <c r="Z17" s="38"/>
-      <c r="AA17" s="38"/>
-      <c r="AB17" s="38"/>
+      <c r="W17" s="40"/>
+      <c r="X17" s="40"/>
+      <c r="Y17" s="40"/>
+      <c r="Z17" s="40"/>
+      <c r="AA17" s="40"/>
+      <c r="AB17" s="40"/>
     </row>
     <row r="18" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="C18" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="46"/>
       <c r="L18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="40" t="s">
+      <c r="M18" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="40"/>
-      <c r="O18" s="40"/>
-      <c r="P18" s="40"/>
-      <c r="Q18" s="40"/>
-      <c r="R18" s="40"/>
-      <c r="S18" s="40"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="42"/>
+      <c r="R18" s="42"/>
+      <c r="S18" s="42"/>
       <c r="U18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V18" s="39" t="s">
+      <c r="V18" s="41" t="s">
         <v>197</v>
       </c>
-      <c r="W18" s="39"/>
-      <c r="X18" s="39"/>
-      <c r="Y18" s="39"/>
-      <c r="Z18" s="39"/>
-      <c r="AA18" s="39"/>
-      <c r="AB18" s="39"/>
+      <c r="W18" s="41"/>
+      <c r="X18" s="41"/>
+      <c r="Y18" s="41"/>
+      <c r="Z18" s="41"/>
+      <c r="AA18" s="41"/>
+      <c r="AB18" s="41"/>
     </row>
     <row r="19" spans="3:28" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C19" s="16"/>
@@ -2029,55 +2116,82 @@
       <c r="C22" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="43" t="s">
+      <c r="D22" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="46"/>
       <c r="L22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="40" t="s">
+      <c r="M22" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="N22" s="40"/>
-      <c r="O22" s="40"/>
-      <c r="P22" s="40"/>
-      <c r="Q22" s="40"/>
-      <c r="R22" s="40"/>
-      <c r="S22" s="40"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="42"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="42"/>
+      <c r="R22" s="42"/>
+      <c r="S22" s="42"/>
     </row>
     <row r="23" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="43" t="s">
+      <c r="D23" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="46"/>
       <c r="L23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="40" t="s">
+      <c r="M23" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="N23" s="40"/>
-      <c r="O23" s="40"/>
-      <c r="P23" s="40"/>
-      <c r="Q23" s="40"/>
-      <c r="R23" s="40"/>
-      <c r="S23" s="40"/>
+      <c r="N23" s="42"/>
+      <c r="O23" s="42"/>
+      <c r="P23" s="42"/>
+      <c r="Q23" s="42"/>
+      <c r="R23" s="42"/>
+      <c r="S23" s="42"/>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="J24" s="25"/>
     </row>
     <row r="25" spans="3:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="H25" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I25" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="J25" s="32" t="s">
+        <v>19</v>
+      </c>
       <c r="L25" s="6" t="s">
         <v>0</v>
       </c>
@@ -2103,7 +2217,31 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="D26" s="32">
+        <v>5</v>
+      </c>
+      <c r="E26" s="32">
+        <v>1</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="32">
+        <v>50</v>
+      </c>
       <c r="L26" s="6" t="s">
         <v>46</v>
       </c>
@@ -2130,32 +2268,56 @@
       </c>
     </row>
     <row r="27" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>210</v>
+      </c>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="46"/>
       <c r="L27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M27" s="40" t="s">
+      <c r="M27" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="N27" s="40"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="40"/>
-      <c r="S27" s="40"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="42"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="42"/>
+      <c r="R27" s="42"/>
+      <c r="S27" s="42"/>
     </row>
     <row r="28" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="46"/>
       <c r="L28" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M28" s="37" t="s">
+      <c r="M28" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="N28" s="37"/>
-      <c r="O28" s="37"/>
-      <c r="P28" s="37"/>
-      <c r="Q28" s="37"/>
-      <c r="R28" s="37"/>
-      <c r="S28" s="37"/>
+      <c r="N28" s="39"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="39"/>
+      <c r="R28" s="39"/>
+      <c r="S28" s="39"/>
     </row>
     <row r="30" spans="3:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="13" t="s">
@@ -2261,53 +2423,53 @@
       <c r="C32" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="34" t="s">
+      <c r="D32" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="36"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="37"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="38"/>
       <c r="L32" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M32" s="31" t="s">
+      <c r="M32" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="N32" s="32"/>
-      <c r="O32" s="32"/>
-      <c r="P32" s="32"/>
-      <c r="Q32" s="32"/>
-      <c r="R32" s="32"/>
-      <c r="S32" s="33"/>
+      <c r="N32" s="34"/>
+      <c r="O32" s="34"/>
+      <c r="P32" s="34"/>
+      <c r="Q32" s="34"/>
+      <c r="R32" s="34"/>
+      <c r="S32" s="35"/>
     </row>
     <row r="33" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="34" t="s">
+      <c r="D33" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="35"/>
-      <c r="J33" s="36"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="38"/>
       <c r="L33" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M33" s="31" t="s">
+      <c r="M33" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="N33" s="32"/>
-      <c r="O33" s="32"/>
-      <c r="P33" s="32"/>
-      <c r="Q33" s="32"/>
-      <c r="R33" s="32"/>
-      <c r="S33" s="33"/>
+      <c r="N33" s="34"/>
+      <c r="O33" s="34"/>
+      <c r="P33" s="34"/>
+      <c r="Q33" s="34"/>
+      <c r="R33" s="34"/>
+      <c r="S33" s="35"/>
     </row>
     <row r="35" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="28" t="s">
@@ -2413,53 +2575,53 @@
       <c r="C37" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="34" t="s">
+      <c r="D37" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="36"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="37"/>
+      <c r="I37" s="37"/>
+      <c r="J37" s="38"/>
       <c r="L37" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M37" s="31" t="s">
+      <c r="M37" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="N37" s="32"/>
-      <c r="O37" s="32"/>
-      <c r="P37" s="32"/>
-      <c r="Q37" s="32"/>
-      <c r="R37" s="32"/>
-      <c r="S37" s="33"/>
+      <c r="N37" s="34"/>
+      <c r="O37" s="34"/>
+      <c r="P37" s="34"/>
+      <c r="Q37" s="34"/>
+      <c r="R37" s="34"/>
+      <c r="S37" s="35"/>
     </row>
     <row r="38" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="34" t="s">
+      <c r="D38" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35"/>
-      <c r="J38" s="36"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="37"/>
+      <c r="H38" s="37"/>
+      <c r="I38" s="37"/>
+      <c r="J38" s="38"/>
       <c r="L38" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M38" s="37" t="s">
+      <c r="M38" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="N38" s="37"/>
-      <c r="O38" s="37"/>
-      <c r="P38" s="37"/>
-      <c r="Q38" s="37"/>
-      <c r="R38" s="37"/>
-      <c r="S38" s="37"/>
+      <c r="N38" s="39"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="39"/>
+      <c r="Q38" s="39"/>
+      <c r="R38" s="39"/>
+      <c r="S38" s="39"/>
     </row>
     <row r="40" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="28" t="s">
@@ -2565,53 +2727,53 @@
       <c r="C42" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D42" s="34" t="s">
+      <c r="D42" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="35"/>
-      <c r="I42" s="35"/>
-      <c r="J42" s="36"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="37"/>
+      <c r="I42" s="37"/>
+      <c r="J42" s="38"/>
       <c r="L42" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M42" s="31" t="s">
+      <c r="M42" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="N42" s="32"/>
-      <c r="O42" s="32"/>
-      <c r="P42" s="32"/>
-      <c r="Q42" s="32"/>
-      <c r="R42" s="32"/>
-      <c r="S42" s="33"/>
+      <c r="N42" s="34"/>
+      <c r="O42" s="34"/>
+      <c r="P42" s="34"/>
+      <c r="Q42" s="34"/>
+      <c r="R42" s="34"/>
+      <c r="S42" s="35"/>
     </row>
     <row r="43" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="34" t="s">
+      <c r="D43" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="E43" s="35"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="35"/>
-      <c r="I43" s="35"/>
-      <c r="J43" s="36"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="37"/>
+      <c r="I43" s="37"/>
+      <c r="J43" s="38"/>
       <c r="L43" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M43" s="31" t="s">
+      <c r="M43" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="N43" s="32"/>
-      <c r="O43" s="32"/>
-      <c r="P43" s="32"/>
-      <c r="Q43" s="32"/>
-      <c r="R43" s="32"/>
-      <c r="S43" s="33"/>
+      <c r="N43" s="34"/>
+      <c r="O43" s="34"/>
+      <c r="P43" s="34"/>
+      <c r="Q43" s="34"/>
+      <c r="R43" s="34"/>
+      <c r="S43" s="35"/>
     </row>
     <row r="45" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="28" t="s">
@@ -2717,53 +2879,53 @@
       <c r="C47" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="34" t="s">
+      <c r="D47" s="36" t="s">
         <v>147</v>
       </c>
-      <c r="E47" s="35"/>
-      <c r="F47" s="35"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="35"/>
-      <c r="I47" s="35"/>
-      <c r="J47" s="36"/>
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="37"/>
+      <c r="I47" s="37"/>
+      <c r="J47" s="38"/>
       <c r="L47" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="31" t="s">
+      <c r="M47" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="N47" s="32"/>
-      <c r="O47" s="32"/>
-      <c r="P47" s="32"/>
-      <c r="Q47" s="32"/>
-      <c r="R47" s="32"/>
-      <c r="S47" s="33"/>
+      <c r="N47" s="34"/>
+      <c r="O47" s="34"/>
+      <c r="P47" s="34"/>
+      <c r="Q47" s="34"/>
+      <c r="R47" s="34"/>
+      <c r="S47" s="35"/>
     </row>
     <row r="48" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="34" t="s">
+      <c r="D48" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="E48" s="35"/>
-      <c r="F48" s="35"/>
-      <c r="G48" s="35"/>
-      <c r="H48" s="35"/>
-      <c r="I48" s="35"/>
-      <c r="J48" s="36"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="37"/>
+      <c r="H48" s="37"/>
+      <c r="I48" s="37"/>
+      <c r="J48" s="38"/>
       <c r="L48" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M48" s="31" t="s">
+      <c r="M48" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="N48" s="32"/>
-      <c r="O48" s="32"/>
-      <c r="P48" s="32"/>
-      <c r="Q48" s="32"/>
-      <c r="R48" s="32"/>
-      <c r="S48" s="33"/>
+      <c r="N48" s="34"/>
+      <c r="O48" s="34"/>
+      <c r="P48" s="34"/>
+      <c r="Q48" s="34"/>
+      <c r="R48" s="34"/>
+      <c r="S48" s="35"/>
     </row>
     <row r="50" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="28" t="s">
@@ -2869,53 +3031,53 @@
       <c r="C52" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D52" s="34" t="s">
+      <c r="D52" s="36" t="s">
         <v>148</v>
       </c>
-      <c r="E52" s="35"/>
-      <c r="F52" s="35"/>
-      <c r="G52" s="35"/>
-      <c r="H52" s="35"/>
-      <c r="I52" s="35"/>
-      <c r="J52" s="36"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="37"/>
+      <c r="H52" s="37"/>
+      <c r="I52" s="37"/>
+      <c r="J52" s="38"/>
       <c r="L52" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M52" s="37" t="s">
+      <c r="M52" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="N52" s="37"/>
-      <c r="O52" s="37"/>
-      <c r="P52" s="37"/>
-      <c r="Q52" s="37"/>
-      <c r="R52" s="37"/>
-      <c r="S52" s="37"/>
+      <c r="N52" s="39"/>
+      <c r="O52" s="39"/>
+      <c r="P52" s="39"/>
+      <c r="Q52" s="39"/>
+      <c r="R52" s="39"/>
+      <c r="S52" s="39"/>
     </row>
     <row r="53" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="34" t="s">
+      <c r="D53" s="36" t="s">
         <v>149</v>
       </c>
-      <c r="E53" s="35"/>
-      <c r="F53" s="35"/>
-      <c r="G53" s="35"/>
-      <c r="H53" s="35"/>
-      <c r="I53" s="35"/>
-      <c r="J53" s="36"/>
+      <c r="E53" s="37"/>
+      <c r="F53" s="37"/>
+      <c r="G53" s="37"/>
+      <c r="H53" s="37"/>
+      <c r="I53" s="37"/>
+      <c r="J53" s="38"/>
       <c r="L53" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M53" s="37" t="s">
+      <c r="M53" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="N53" s="37"/>
-      <c r="O53" s="37"/>
-      <c r="P53" s="37"/>
-      <c r="Q53" s="37"/>
-      <c r="R53" s="37"/>
-      <c r="S53" s="37"/>
+      <c r="N53" s="39"/>
+      <c r="O53" s="39"/>
+      <c r="P53" s="39"/>
+      <c r="Q53" s="39"/>
+      <c r="R53" s="39"/>
+      <c r="S53" s="39"/>
     </row>
     <row r="55" spans="3:19" ht="30" x14ac:dyDescent="0.25">
       <c r="C55" s="28" t="s">
@@ -3021,53 +3183,53 @@
       <c r="C57" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="34" t="s">
+      <c r="D57" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="E57" s="35"/>
-      <c r="F57" s="35"/>
-      <c r="G57" s="35"/>
-      <c r="H57" s="35"/>
-      <c r="I57" s="35"/>
-      <c r="J57" s="36"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="37"/>
+      <c r="G57" s="37"/>
+      <c r="H57" s="37"/>
+      <c r="I57" s="37"/>
+      <c r="J57" s="38"/>
       <c r="L57" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M57" s="31" t="s">
+      <c r="M57" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="N57" s="32"/>
-      <c r="O57" s="32"/>
-      <c r="P57" s="32"/>
-      <c r="Q57" s="32"/>
-      <c r="R57" s="32"/>
-      <c r="S57" s="33"/>
+      <c r="N57" s="34"/>
+      <c r="O57" s="34"/>
+      <c r="P57" s="34"/>
+      <c r="Q57" s="34"/>
+      <c r="R57" s="34"/>
+      <c r="S57" s="35"/>
     </row>
     <row r="58" spans="3:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C58" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="34" t="s">
+      <c r="D58" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="35"/>
-      <c r="H58" s="35"/>
-      <c r="I58" s="35"/>
-      <c r="J58" s="36"/>
+      <c r="E58" s="37"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="37"/>
+      <c r="H58" s="37"/>
+      <c r="I58" s="37"/>
+      <c r="J58" s="38"/>
       <c r="L58" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M58" s="31" t="s">
+      <c r="M58" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="N58" s="32"/>
-      <c r="O58" s="32"/>
-      <c r="P58" s="32"/>
-      <c r="Q58" s="32"/>
-      <c r="R58" s="32"/>
-      <c r="S58" s="33"/>
+      <c r="N58" s="34"/>
+      <c r="O58" s="34"/>
+      <c r="P58" s="34"/>
+      <c r="Q58" s="34"/>
+      <c r="R58" s="34"/>
+      <c r="S58" s="35"/>
     </row>
     <row r="60" spans="3:19" ht="30" x14ac:dyDescent="0.25">
       <c r="C60" s="22" t="s">
@@ -3173,53 +3335,53 @@
       <c r="C62" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D62" s="34" t="s">
+      <c r="D62" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="E62" s="35"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="35"/>
-      <c r="I62" s="35"/>
-      <c r="J62" s="36"/>
+      <c r="E62" s="37"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="37"/>
+      <c r="H62" s="37"/>
+      <c r="I62" s="37"/>
+      <c r="J62" s="38"/>
       <c r="L62" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M62" s="37" t="s">
+      <c r="M62" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="N62" s="37"/>
-      <c r="O62" s="37"/>
-      <c r="P62" s="37"/>
-      <c r="Q62" s="37"/>
-      <c r="R62" s="37"/>
-      <c r="S62" s="37"/>
+      <c r="N62" s="39"/>
+      <c r="O62" s="39"/>
+      <c r="P62" s="39"/>
+      <c r="Q62" s="39"/>
+      <c r="R62" s="39"/>
+      <c r="S62" s="39"/>
     </row>
     <row r="63" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="34" t="s">
+      <c r="D63" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="E63" s="35"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="35"/>
-      <c r="H63" s="35"/>
-      <c r="I63" s="35"/>
-      <c r="J63" s="36"/>
+      <c r="E63" s="37"/>
+      <c r="F63" s="37"/>
+      <c r="G63" s="37"/>
+      <c r="H63" s="37"/>
+      <c r="I63" s="37"/>
+      <c r="J63" s="38"/>
       <c r="L63" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M63" s="37" t="s">
+      <c r="M63" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="N63" s="37"/>
-      <c r="O63" s="37"/>
-      <c r="P63" s="37"/>
-      <c r="Q63" s="37"/>
-      <c r="R63" s="37"/>
-      <c r="S63" s="37"/>
+      <c r="N63" s="39"/>
+      <c r="O63" s="39"/>
+      <c r="P63" s="39"/>
+      <c r="Q63" s="39"/>
+      <c r="R63" s="39"/>
+      <c r="S63" s="39"/>
     </row>
     <row r="65" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="22" t="s">
@@ -3325,53 +3487,53 @@
       <c r="C67" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="34" t="s">
+      <c r="D67" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="E67" s="35"/>
-      <c r="F67" s="35"/>
-      <c r="G67" s="35"/>
-      <c r="H67" s="35"/>
-      <c r="I67" s="35"/>
-      <c r="J67" s="36"/>
+      <c r="E67" s="37"/>
+      <c r="F67" s="37"/>
+      <c r="G67" s="37"/>
+      <c r="H67" s="37"/>
+      <c r="I67" s="37"/>
+      <c r="J67" s="38"/>
       <c r="L67" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M67" s="31" t="s">
+      <c r="M67" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="N67" s="32"/>
-      <c r="O67" s="32"/>
-      <c r="P67" s="32"/>
-      <c r="Q67" s="32"/>
-      <c r="R67" s="32"/>
-      <c r="S67" s="33"/>
+      <c r="N67" s="34"/>
+      <c r="O67" s="34"/>
+      <c r="P67" s="34"/>
+      <c r="Q67" s="34"/>
+      <c r="R67" s="34"/>
+      <c r="S67" s="35"/>
     </row>
     <row r="68" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="34" t="s">
+      <c r="D68" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="E68" s="35"/>
-      <c r="F68" s="35"/>
-      <c r="G68" s="35"/>
-      <c r="H68" s="35"/>
-      <c r="I68" s="35"/>
-      <c r="J68" s="36"/>
+      <c r="E68" s="37"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="37"/>
+      <c r="H68" s="37"/>
+      <c r="I68" s="37"/>
+      <c r="J68" s="38"/>
       <c r="L68" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M68" s="31" t="s">
+      <c r="M68" s="33" t="s">
         <v>204</v>
       </c>
-      <c r="N68" s="32"/>
-      <c r="O68" s="32"/>
-      <c r="P68" s="32"/>
-      <c r="Q68" s="32"/>
-      <c r="R68" s="32"/>
-      <c r="S68" s="33"/>
+      <c r="N68" s="34"/>
+      <c r="O68" s="34"/>
+      <c r="P68" s="34"/>
+      <c r="Q68" s="34"/>
+      <c r="R68" s="34"/>
+      <c r="S68" s="35"/>
     </row>
     <row r="70" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="13" t="s">
@@ -3477,79 +3639,55 @@
       <c r="C72" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="34" t="s">
+      <c r="D72" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="E72" s="35"/>
-      <c r="F72" s="35"/>
-      <c r="G72" s="35"/>
-      <c r="H72" s="35"/>
-      <c r="I72" s="35"/>
-      <c r="J72" s="36"/>
+      <c r="E72" s="37"/>
+      <c r="F72" s="37"/>
+      <c r="G72" s="37"/>
+      <c r="H72" s="37"/>
+      <c r="I72" s="37"/>
+      <c r="J72" s="38"/>
       <c r="L72" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M72" s="31" t="s">
+      <c r="M72" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="N72" s="32"/>
-      <c r="O72" s="32"/>
-      <c r="P72" s="32"/>
-      <c r="Q72" s="32"/>
-      <c r="R72" s="32"/>
-      <c r="S72" s="33"/>
+      <c r="N72" s="34"/>
+      <c r="O72" s="34"/>
+      <c r="P72" s="34"/>
+      <c r="Q72" s="34"/>
+      <c r="R72" s="34"/>
+      <c r="S72" s="35"/>
     </row>
     <row r="73" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="34" t="s">
+      <c r="D73" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="35"/>
-      <c r="F73" s="35"/>
-      <c r="G73" s="35"/>
-      <c r="H73" s="35"/>
-      <c r="I73" s="35"/>
-      <c r="J73" s="36"/>
+      <c r="E73" s="37"/>
+      <c r="F73" s="37"/>
+      <c r="G73" s="37"/>
+      <c r="H73" s="37"/>
+      <c r="I73" s="37"/>
+      <c r="J73" s="38"/>
       <c r="L73" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M73" s="37" t="s">
+      <c r="M73" s="39" t="s">
         <v>202</v>
       </c>
-      <c r="N73" s="37"/>
-      <c r="O73" s="37"/>
-      <c r="P73" s="37"/>
-      <c r="Q73" s="37"/>
-      <c r="R73" s="37"/>
-      <c r="S73" s="37"/>
+      <c r="N73" s="39"/>
+      <c r="O73" s="39"/>
+      <c r="P73" s="39"/>
+      <c r="Q73" s="39"/>
+      <c r="R73" s="39"/>
+      <c r="S73" s="39"/>
     </row>
     <row r="75" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C75" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D75" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E75" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F75" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G75" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H75" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I75" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="J75" s="13" t="s">
-        <v>19</v>
-      </c>
       <c r="L75" s="19" t="s">
         <v>0</v>
       </c>
@@ -3576,30 +3714,6 @@
       </c>
     </row>
     <row r="76" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C76" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D76" s="13">
-        <v>7</v>
-      </c>
-      <c r="E76" s="13">
-        <v>1</v>
-      </c>
-      <c r="F76" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G76" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="H76" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I76" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="J76" s="13">
-        <v>50</v>
-      </c>
       <c r="L76" s="19" t="s">
         <v>78</v>
       </c>
@@ -3626,56 +3740,32 @@
       </c>
     </row>
     <row r="77" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C77" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D77" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="E77" s="35"/>
-      <c r="F77" s="35"/>
-      <c r="G77" s="35"/>
-      <c r="H77" s="35"/>
-      <c r="I77" s="35"/>
-      <c r="J77" s="36"/>
       <c r="L77" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M77" s="31" t="s">
+      <c r="M77" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="N77" s="32"/>
-      <c r="O77" s="32"/>
-      <c r="P77" s="32"/>
-      <c r="Q77" s="32"/>
-      <c r="R77" s="32"/>
-      <c r="S77" s="33"/>
+      <c r="N77" s="34"/>
+      <c r="O77" s="34"/>
+      <c r="P77" s="34"/>
+      <c r="Q77" s="34"/>
+      <c r="R77" s="34"/>
+      <c r="S77" s="35"/>
     </row>
     <row r="78" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C78" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D78" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="E78" s="35"/>
-      <c r="F78" s="35"/>
-      <c r="G78" s="35"/>
-      <c r="H78" s="35"/>
-      <c r="I78" s="35"/>
-      <c r="J78" s="36"/>
       <c r="L78" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M78" s="31" t="s">
+      <c r="M78" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="N78" s="32"/>
-      <c r="O78" s="32"/>
-      <c r="P78" s="32"/>
-      <c r="Q78" s="32"/>
-      <c r="R78" s="32"/>
-      <c r="S78" s="33"/>
+      <c r="N78" s="34"/>
+      <c r="O78" s="34"/>
+      <c r="P78" s="34"/>
+      <c r="Q78" s="34"/>
+      <c r="R78" s="34"/>
+      <c r="S78" s="35"/>
     </row>
     <row r="80" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C80" s="13" t="s">
@@ -3781,53 +3871,53 @@
       <c r="C82" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="34" t="s">
+      <c r="D82" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="E82" s="35"/>
-      <c r="F82" s="35"/>
-      <c r="G82" s="35"/>
-      <c r="H82" s="35"/>
-      <c r="I82" s="35"/>
-      <c r="J82" s="36"/>
+      <c r="E82" s="37"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="37"/>
+      <c r="H82" s="37"/>
+      <c r="I82" s="37"/>
+      <c r="J82" s="38"/>
       <c r="L82" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M82" s="31" t="s">
+      <c r="M82" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="N82" s="32"/>
-      <c r="O82" s="32"/>
-      <c r="P82" s="32"/>
-      <c r="Q82" s="32"/>
-      <c r="R82" s="32"/>
-      <c r="S82" s="33"/>
+      <c r="N82" s="34"/>
+      <c r="O82" s="34"/>
+      <c r="P82" s="34"/>
+      <c r="Q82" s="34"/>
+      <c r="R82" s="34"/>
+      <c r="S82" s="35"/>
     </row>
     <row r="83" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C83" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D83" s="34" t="s">
+      <c r="D83" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="E83" s="35"/>
-      <c r="F83" s="35"/>
-      <c r="G83" s="35"/>
-      <c r="H83" s="35"/>
-      <c r="I83" s="35"/>
-      <c r="J83" s="36"/>
+      <c r="E83" s="37"/>
+      <c r="F83" s="37"/>
+      <c r="G83" s="37"/>
+      <c r="H83" s="37"/>
+      <c r="I83" s="37"/>
+      <c r="J83" s="38"/>
       <c r="L83" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M83" s="31" t="s">
+      <c r="M83" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="N83" s="32"/>
-      <c r="O83" s="32"/>
-      <c r="P83" s="32"/>
-      <c r="Q83" s="32"/>
-      <c r="R83" s="32"/>
-      <c r="S83" s="33"/>
+      <c r="N83" s="34"/>
+      <c r="O83" s="34"/>
+      <c r="P83" s="34"/>
+      <c r="Q83" s="34"/>
+      <c r="R83" s="34"/>
+      <c r="S83" s="35"/>
     </row>
     <row r="84" spans="3:19" x14ac:dyDescent="0.25">
       <c r="O84"/>
@@ -3936,79 +4026,55 @@
       <c r="C87" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D87" s="34" t="s">
+      <c r="D87" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="E87" s="35"/>
-      <c r="F87" s="35"/>
-      <c r="G87" s="35"/>
-      <c r="H87" s="35"/>
-      <c r="I87" s="35"/>
-      <c r="J87" s="36"/>
+      <c r="E87" s="37"/>
+      <c r="F87" s="37"/>
+      <c r="G87" s="37"/>
+      <c r="H87" s="37"/>
+      <c r="I87" s="37"/>
+      <c r="J87" s="38"/>
       <c r="L87" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M87" s="31" t="s">
+      <c r="M87" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="N87" s="32"/>
-      <c r="O87" s="32"/>
-      <c r="P87" s="32"/>
-      <c r="Q87" s="32"/>
-      <c r="R87" s="32"/>
-      <c r="S87" s="33"/>
+      <c r="N87" s="34"/>
+      <c r="O87" s="34"/>
+      <c r="P87" s="34"/>
+      <c r="Q87" s="34"/>
+      <c r="R87" s="34"/>
+      <c r="S87" s="35"/>
     </row>
     <row r="88" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C88" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D88" s="34" t="s">
+      <c r="D88" s="36" t="s">
         <v>205</v>
       </c>
-      <c r="E88" s="35"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="35"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="35"/>
-      <c r="J88" s="36"/>
+      <c r="E88" s="37"/>
+      <c r="F88" s="37"/>
+      <c r="G88" s="37"/>
+      <c r="H88" s="37"/>
+      <c r="I88" s="37"/>
+      <c r="J88" s="38"/>
       <c r="L88" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M88" s="31" t="s">
+      <c r="M88" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="N88" s="32"/>
-      <c r="O88" s="32"/>
-      <c r="P88" s="32"/>
-      <c r="Q88" s="32"/>
-      <c r="R88" s="32"/>
-      <c r="S88" s="33"/>
+      <c r="N88" s="34"/>
+      <c r="O88" s="34"/>
+      <c r="P88" s="34"/>
+      <c r="Q88" s="34"/>
+      <c r="R88" s="34"/>
+      <c r="S88" s="35"/>
     </row>
     <row r="90" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C90" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D90" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E90" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F90" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G90" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H90" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I90" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="J90" s="13" t="s">
-        <v>19</v>
-      </c>
       <c r="L90" s="19" t="s">
         <v>0</v>
       </c>
@@ -4035,30 +4101,6 @@
       </c>
     </row>
     <row r="91" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C91" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="D91" s="13">
-        <v>2</v>
-      </c>
-      <c r="E91" s="13">
-        <v>1</v>
-      </c>
-      <c r="F91" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G91" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="H91" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I91" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="13">
-        <v>40</v>
-      </c>
       <c r="L91" s="19" t="s">
         <v>89</v>
       </c>
@@ -4085,56 +4127,32 @@
       </c>
     </row>
     <row r="92" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C92" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D92" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="E92" s="35"/>
-      <c r="F92" s="35"/>
-      <c r="G92" s="35"/>
-      <c r="H92" s="35"/>
-      <c r="I92" s="35"/>
-      <c r="J92" s="36"/>
       <c r="L92" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M92" s="31" t="s">
+      <c r="M92" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="N92" s="32"/>
-      <c r="O92" s="32"/>
-      <c r="P92" s="32"/>
-      <c r="Q92" s="32"/>
-      <c r="R92" s="32"/>
-      <c r="S92" s="33"/>
+      <c r="N92" s="34"/>
+      <c r="O92" s="34"/>
+      <c r="P92" s="34"/>
+      <c r="Q92" s="34"/>
+      <c r="R92" s="34"/>
+      <c r="S92" s="35"/>
     </row>
     <row r="93" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C93" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D93" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="E93" s="35"/>
-      <c r="F93" s="35"/>
-      <c r="G93" s="35"/>
-      <c r="H93" s="35"/>
-      <c r="I93" s="35"/>
-      <c r="J93" s="36"/>
       <c r="L93" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M93" s="31" t="s">
+      <c r="M93" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="N93" s="32"/>
-      <c r="O93" s="32"/>
-      <c r="P93" s="32"/>
-      <c r="Q93" s="32"/>
-      <c r="R93" s="32"/>
-      <c r="S93" s="33"/>
+      <c r="N93" s="34"/>
+      <c r="O93" s="34"/>
+      <c r="P93" s="34"/>
+      <c r="Q93" s="34"/>
+      <c r="R93" s="34"/>
+      <c r="S93" s="35"/>
     </row>
     <row r="95" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C95" s="22" t="s">
@@ -4240,53 +4258,53 @@
       <c r="C97" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="39" t="s">
+      <c r="D97" s="41" t="s">
         <v>183</v>
       </c>
-      <c r="E97" s="39"/>
-      <c r="F97" s="39"/>
-      <c r="G97" s="39"/>
-      <c r="H97" s="39"/>
-      <c r="I97" s="39"/>
-      <c r="J97" s="39"/>
+      <c r="E97" s="41"/>
+      <c r="F97" s="41"/>
+      <c r="G97" s="41"/>
+      <c r="H97" s="41"/>
+      <c r="I97" s="41"/>
+      <c r="J97" s="41"/>
       <c r="L97" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M97" s="31" t="s">
+      <c r="M97" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="N97" s="32"/>
-      <c r="O97" s="32"/>
-      <c r="P97" s="32"/>
-      <c r="Q97" s="32"/>
-      <c r="R97" s="32"/>
-      <c r="S97" s="33"/>
+      <c r="N97" s="34"/>
+      <c r="O97" s="34"/>
+      <c r="P97" s="34"/>
+      <c r="Q97" s="34"/>
+      <c r="R97" s="34"/>
+      <c r="S97" s="35"/>
     </row>
     <row r="98" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C98" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D98" s="39" t="s">
+      <c r="D98" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="E98" s="39"/>
-      <c r="F98" s="39"/>
-      <c r="G98" s="39"/>
-      <c r="H98" s="39"/>
-      <c r="I98" s="39"/>
-      <c r="J98" s="39"/>
+      <c r="E98" s="41"/>
+      <c r="F98" s="41"/>
+      <c r="G98" s="41"/>
+      <c r="H98" s="41"/>
+      <c r="I98" s="41"/>
+      <c r="J98" s="41"/>
       <c r="L98" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M98" s="31" t="s">
+      <c r="M98" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="N98" s="32"/>
-      <c r="O98" s="32"/>
-      <c r="P98" s="32"/>
-      <c r="Q98" s="32"/>
-      <c r="R98" s="32"/>
-      <c r="S98" s="33"/>
+      <c r="N98" s="34"/>
+      <c r="O98" s="34"/>
+      <c r="P98" s="34"/>
+      <c r="Q98" s="34"/>
+      <c r="R98" s="34"/>
+      <c r="S98" s="35"/>
     </row>
     <row r="99" spans="3:19" x14ac:dyDescent="0.25">
       <c r="O99"/>
@@ -4395,53 +4413,53 @@
       <c r="C102" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D102" s="39" t="s">
+      <c r="D102" s="41" t="s">
         <v>192</v>
       </c>
-      <c r="E102" s="39"/>
-      <c r="F102" s="39"/>
-      <c r="G102" s="39"/>
-      <c r="H102" s="39"/>
-      <c r="I102" s="39"/>
-      <c r="J102" s="39"/>
+      <c r="E102" s="41"/>
+      <c r="F102" s="41"/>
+      <c r="G102" s="41"/>
+      <c r="H102" s="41"/>
+      <c r="I102" s="41"/>
+      <c r="J102" s="41"/>
       <c r="L102" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M102" s="31" t="s">
+      <c r="M102" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="N102" s="32"/>
-      <c r="O102" s="32"/>
-      <c r="P102" s="32"/>
-      <c r="Q102" s="32"/>
-      <c r="R102" s="32"/>
-      <c r="S102" s="33"/>
+      <c r="N102" s="34"/>
+      <c r="O102" s="34"/>
+      <c r="P102" s="34"/>
+      <c r="Q102" s="34"/>
+      <c r="R102" s="34"/>
+      <c r="S102" s="35"/>
     </row>
     <row r="103" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C103" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D103" s="39" t="s">
+      <c r="D103" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="E103" s="39"/>
-      <c r="F103" s="39"/>
-      <c r="G103" s="39"/>
-      <c r="H103" s="39"/>
-      <c r="I103" s="39"/>
-      <c r="J103" s="39"/>
+      <c r="E103" s="41"/>
+      <c r="F103" s="41"/>
+      <c r="G103" s="41"/>
+      <c r="H103" s="41"/>
+      <c r="I103" s="41"/>
+      <c r="J103" s="41"/>
       <c r="L103" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M103" s="31" t="s">
+      <c r="M103" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="N103" s="32"/>
-      <c r="O103" s="32"/>
-      <c r="P103" s="32"/>
-      <c r="Q103" s="32"/>
-      <c r="R103" s="32"/>
-      <c r="S103" s="33"/>
+      <c r="N103" s="34"/>
+      <c r="O103" s="34"/>
+      <c r="P103" s="34"/>
+      <c r="Q103" s="34"/>
+      <c r="R103" s="34"/>
+      <c r="S103" s="35"/>
     </row>
     <row r="104" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C104" s="16"/>
@@ -4558,53 +4576,53 @@
       <c r="C107" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="34" t="s">
+      <c r="D107" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="E107" s="35"/>
-      <c r="F107" s="35"/>
-      <c r="G107" s="35"/>
-      <c r="H107" s="35"/>
-      <c r="I107" s="35"/>
-      <c r="J107" s="36"/>
+      <c r="E107" s="37"/>
+      <c r="F107" s="37"/>
+      <c r="G107" s="37"/>
+      <c r="H107" s="37"/>
+      <c r="I107" s="37"/>
+      <c r="J107" s="38"/>
       <c r="L107" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M107" s="37" t="s">
+      <c r="M107" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="N107" s="37"/>
-      <c r="O107" s="37"/>
-      <c r="P107" s="37"/>
-      <c r="Q107" s="37"/>
-      <c r="R107" s="37"/>
-      <c r="S107" s="37"/>
+      <c r="N107" s="39"/>
+      <c r="O107" s="39"/>
+      <c r="P107" s="39"/>
+      <c r="Q107" s="39"/>
+      <c r="R107" s="39"/>
+      <c r="S107" s="39"/>
     </row>
     <row r="108" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C108" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="34" t="s">
+      <c r="D108" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="E108" s="35"/>
-      <c r="F108" s="35"/>
-      <c r="G108" s="35"/>
-      <c r="H108" s="35"/>
-      <c r="I108" s="35"/>
-      <c r="J108" s="36"/>
+      <c r="E108" s="37"/>
+      <c r="F108" s="37"/>
+      <c r="G108" s="37"/>
+      <c r="H108" s="37"/>
+      <c r="I108" s="37"/>
+      <c r="J108" s="38"/>
       <c r="L108" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="M108" s="37" t="s">
+      <c r="M108" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="N108" s="37"/>
-      <c r="O108" s="37"/>
-      <c r="P108" s="37"/>
-      <c r="Q108" s="37"/>
-      <c r="R108" s="37"/>
-      <c r="S108" s="37"/>
+      <c r="N108" s="39"/>
+      <c r="O108" s="39"/>
+      <c r="P108" s="39"/>
+      <c r="Q108" s="39"/>
+      <c r="R108" s="39"/>
+      <c r="S108" s="39"/>
     </row>
     <row r="110" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C110" s="22" t="s">
@@ -4710,53 +4728,53 @@
       <c r="C112" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D112" s="34" t="s">
+      <c r="D112" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="E112" s="35"/>
-      <c r="F112" s="35"/>
-      <c r="G112" s="35"/>
-      <c r="H112" s="35"/>
-      <c r="I112" s="35"/>
-      <c r="J112" s="36"/>
+      <c r="E112" s="37"/>
+      <c r="F112" s="37"/>
+      <c r="G112" s="37"/>
+      <c r="H112" s="37"/>
+      <c r="I112" s="37"/>
+      <c r="J112" s="38"/>
       <c r="L112" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M112" s="31" t="s">
+      <c r="M112" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="N112" s="32"/>
-      <c r="O112" s="32"/>
-      <c r="P112" s="32"/>
-      <c r="Q112" s="32"/>
-      <c r="R112" s="32"/>
-      <c r="S112" s="33"/>
+      <c r="N112" s="34"/>
+      <c r="O112" s="34"/>
+      <c r="P112" s="34"/>
+      <c r="Q112" s="34"/>
+      <c r="R112" s="34"/>
+      <c r="S112" s="35"/>
     </row>
     <row r="113" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C113" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D113" s="34" t="s">
+      <c r="D113" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="E113" s="35"/>
-      <c r="F113" s="35"/>
-      <c r="G113" s="35"/>
-      <c r="H113" s="35"/>
-      <c r="I113" s="35"/>
-      <c r="J113" s="36"/>
+      <c r="E113" s="37"/>
+      <c r="F113" s="37"/>
+      <c r="G113" s="37"/>
+      <c r="H113" s="37"/>
+      <c r="I113" s="37"/>
+      <c r="J113" s="38"/>
       <c r="L113" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="M113" s="31" t="s">
+      <c r="M113" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="N113" s="32"/>
-      <c r="O113" s="32"/>
-      <c r="P113" s="32"/>
-      <c r="Q113" s="32"/>
-      <c r="R113" s="32"/>
-      <c r="S113" s="33"/>
+      <c r="N113" s="34"/>
+      <c r="O113" s="34"/>
+      <c r="P113" s="34"/>
+      <c r="Q113" s="34"/>
+      <c r="R113" s="34"/>
+      <c r="S113" s="35"/>
     </row>
     <row r="115" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C115" s="22" t="s">
@@ -4862,53 +4880,53 @@
       <c r="C117" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D117" s="34" t="s">
+      <c r="D117" s="36" t="s">
         <v>187</v>
       </c>
-      <c r="E117" s="35"/>
-      <c r="F117" s="35"/>
-      <c r="G117" s="35"/>
-      <c r="H117" s="35"/>
-      <c r="I117" s="35"/>
-      <c r="J117" s="36"/>
+      <c r="E117" s="37"/>
+      <c r="F117" s="37"/>
+      <c r="G117" s="37"/>
+      <c r="H117" s="37"/>
+      <c r="I117" s="37"/>
+      <c r="J117" s="38"/>
       <c r="L117" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M117" s="31" t="s">
+      <c r="M117" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="N117" s="32"/>
-      <c r="O117" s="32"/>
-      <c r="P117" s="32"/>
-      <c r="Q117" s="32"/>
-      <c r="R117" s="32"/>
-      <c r="S117" s="33"/>
+      <c r="N117" s="34"/>
+      <c r="O117" s="34"/>
+      <c r="P117" s="34"/>
+      <c r="Q117" s="34"/>
+      <c r="R117" s="34"/>
+      <c r="S117" s="35"/>
     </row>
     <row r="118" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C118" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D118" s="34" t="s">
+      <c r="D118" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="E118" s="35"/>
-      <c r="F118" s="35"/>
-      <c r="G118" s="35"/>
-      <c r="H118" s="35"/>
-      <c r="I118" s="35"/>
-      <c r="J118" s="36"/>
+      <c r="E118" s="37"/>
+      <c r="F118" s="37"/>
+      <c r="G118" s="37"/>
+      <c r="H118" s="37"/>
+      <c r="I118" s="37"/>
+      <c r="J118" s="38"/>
       <c r="L118" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="M118" s="31" t="s">
+      <c r="M118" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="N118" s="32"/>
-      <c r="O118" s="32"/>
-      <c r="P118" s="32"/>
-      <c r="Q118" s="32"/>
-      <c r="R118" s="32"/>
-      <c r="S118" s="33"/>
+      <c r="N118" s="34"/>
+      <c r="O118" s="34"/>
+      <c r="P118" s="34"/>
+      <c r="Q118" s="34"/>
+      <c r="R118" s="34"/>
+      <c r="S118" s="35"/>
     </row>
     <row r="120" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C120" s="22" t="s">
@@ -5014,53 +5032,53 @@
       <c r="C122" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D122" s="34" t="s">
+      <c r="D122" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="E122" s="35"/>
-      <c r="F122" s="35"/>
-      <c r="G122" s="35"/>
-      <c r="H122" s="35"/>
-      <c r="I122" s="35"/>
-      <c r="J122" s="36"/>
+      <c r="E122" s="37"/>
+      <c r="F122" s="37"/>
+      <c r="G122" s="37"/>
+      <c r="H122" s="37"/>
+      <c r="I122" s="37"/>
+      <c r="J122" s="38"/>
       <c r="L122" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M122" s="37" t="s">
+      <c r="M122" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="N122" s="37"/>
-      <c r="O122" s="37"/>
-      <c r="P122" s="37"/>
-      <c r="Q122" s="37"/>
-      <c r="R122" s="37"/>
-      <c r="S122" s="37"/>
+      <c r="N122" s="39"/>
+      <c r="O122" s="39"/>
+      <c r="P122" s="39"/>
+      <c r="Q122" s="39"/>
+      <c r="R122" s="39"/>
+      <c r="S122" s="39"/>
     </row>
     <row r="123" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C123" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D123" s="34" t="s">
+      <c r="D123" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="E123" s="35"/>
-      <c r="F123" s="35"/>
-      <c r="G123" s="35"/>
-      <c r="H123" s="35"/>
-      <c r="I123" s="35"/>
-      <c r="J123" s="36"/>
+      <c r="E123" s="37"/>
+      <c r="F123" s="37"/>
+      <c r="G123" s="37"/>
+      <c r="H123" s="37"/>
+      <c r="I123" s="37"/>
+      <c r="J123" s="38"/>
       <c r="L123" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M123" s="37" t="s">
+      <c r="M123" s="39" t="s">
         <v>152</v>
       </c>
-      <c r="N123" s="37"/>
-      <c r="O123" s="37"/>
-      <c r="P123" s="37"/>
-      <c r="Q123" s="37"/>
-      <c r="R123" s="37"/>
-      <c r="S123" s="37"/>
+      <c r="N123" s="39"/>
+      <c r="O123" s="39"/>
+      <c r="P123" s="39"/>
+      <c r="Q123" s="39"/>
+      <c r="R123" s="39"/>
+      <c r="S123" s="39"/>
     </row>
     <row r="125" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C125" s="13" t="s">
@@ -5166,53 +5184,53 @@
       <c r="C127" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D127" s="34" t="s">
+      <c r="D127" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="E127" s="35"/>
-      <c r="F127" s="35"/>
-      <c r="G127" s="35"/>
-      <c r="H127" s="35"/>
-      <c r="I127" s="35"/>
-      <c r="J127" s="36"/>
+      <c r="E127" s="37"/>
+      <c r="F127" s="37"/>
+      <c r="G127" s="37"/>
+      <c r="H127" s="37"/>
+      <c r="I127" s="37"/>
+      <c r="J127" s="38"/>
       <c r="L127" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M127" s="31" t="s">
+      <c r="M127" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="N127" s="32"/>
-      <c r="O127" s="32"/>
-      <c r="P127" s="32"/>
-      <c r="Q127" s="32"/>
-      <c r="R127" s="32"/>
-      <c r="S127" s="33"/>
+      <c r="N127" s="34"/>
+      <c r="O127" s="34"/>
+      <c r="P127" s="34"/>
+      <c r="Q127" s="34"/>
+      <c r="R127" s="34"/>
+      <c r="S127" s="35"/>
     </row>
     <row r="128" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C128" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D128" s="34" t="s">
+      <c r="D128" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="E128" s="35"/>
-      <c r="F128" s="35"/>
-      <c r="G128" s="35"/>
-      <c r="H128" s="35"/>
-      <c r="I128" s="35"/>
-      <c r="J128" s="36"/>
+      <c r="E128" s="37"/>
+      <c r="F128" s="37"/>
+      <c r="G128" s="37"/>
+      <c r="H128" s="37"/>
+      <c r="I128" s="37"/>
+      <c r="J128" s="38"/>
       <c r="L128" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M128" s="31" t="s">
+      <c r="M128" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="N128" s="32"/>
-      <c r="O128" s="32"/>
-      <c r="P128" s="32"/>
-      <c r="Q128" s="32"/>
-      <c r="R128" s="32"/>
-      <c r="S128" s="33"/>
+      <c r="N128" s="34"/>
+      <c r="O128" s="34"/>
+      <c r="P128" s="34"/>
+      <c r="Q128" s="34"/>
+      <c r="R128" s="34"/>
+      <c r="S128" s="35"/>
     </row>
     <row r="130" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L130" s="21" t="s">
@@ -5270,29 +5288,29 @@
       <c r="L132" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M132" s="31" t="s">
+      <c r="M132" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="N132" s="32"/>
-      <c r="O132" s="32"/>
-      <c r="P132" s="32"/>
-      <c r="Q132" s="32"/>
-      <c r="R132" s="32"/>
-      <c r="S132" s="33"/>
+      <c r="N132" s="34"/>
+      <c r="O132" s="34"/>
+      <c r="P132" s="34"/>
+      <c r="Q132" s="34"/>
+      <c r="R132" s="34"/>
+      <c r="S132" s="35"/>
     </row>
     <row r="133" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L133" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M133" s="31" t="s">
+      <c r="M133" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="N133" s="32"/>
-      <c r="O133" s="32"/>
-      <c r="P133" s="32"/>
-      <c r="Q133" s="32"/>
-      <c r="R133" s="32"/>
-      <c r="S133" s="33"/>
+      <c r="N133" s="34"/>
+      <c r="O133" s="34"/>
+      <c r="P133" s="34"/>
+      <c r="Q133" s="34"/>
+      <c r="R133" s="34"/>
+      <c r="S133" s="35"/>
     </row>
     <row r="134" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M134"/>
@@ -5357,29 +5375,29 @@
       <c r="L137" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M137" s="31" t="s">
+      <c r="M137" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="N137" s="32"/>
-      <c r="O137" s="32"/>
-      <c r="P137" s="32"/>
-      <c r="Q137" s="32"/>
-      <c r="R137" s="32"/>
-      <c r="S137" s="33"/>
+      <c r="N137" s="34"/>
+      <c r="O137" s="34"/>
+      <c r="P137" s="34"/>
+      <c r="Q137" s="34"/>
+      <c r="R137" s="34"/>
+      <c r="S137" s="35"/>
     </row>
     <row r="138" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L138" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M138" s="31" t="s">
+      <c r="M138" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="N138" s="32"/>
-      <c r="O138" s="32"/>
-      <c r="P138" s="32"/>
-      <c r="Q138" s="32"/>
-      <c r="R138" s="32"/>
-      <c r="S138" s="33"/>
+      <c r="N138" s="34"/>
+      <c r="O138" s="34"/>
+      <c r="P138" s="34"/>
+      <c r="Q138" s="34"/>
+      <c r="R138" s="34"/>
+      <c r="S138" s="35"/>
     </row>
     <row r="139" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M139"/>
@@ -5444,29 +5462,29 @@
       <c r="L142" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="M142" s="31" t="s">
+      <c r="M142" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="N142" s="32"/>
-      <c r="O142" s="32"/>
-      <c r="P142" s="32"/>
-      <c r="Q142" s="32"/>
-      <c r="R142" s="32"/>
-      <c r="S142" s="33"/>
+      <c r="N142" s="34"/>
+      <c r="O142" s="34"/>
+      <c r="P142" s="34"/>
+      <c r="Q142" s="34"/>
+      <c r="R142" s="34"/>
+      <c r="S142" s="35"/>
     </row>
     <row r="143" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L143" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="M143" s="37" t="s">
+      <c r="M143" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="N143" s="37"/>
-      <c r="O143" s="37"/>
-      <c r="P143" s="37"/>
-      <c r="Q143" s="37"/>
-      <c r="R143" s="37"/>
-      <c r="S143" s="37"/>
+      <c r="N143" s="39"/>
+      <c r="O143" s="39"/>
+      <c r="P143" s="39"/>
+      <c r="Q143" s="39"/>
+      <c r="R143" s="39"/>
+      <c r="S143" s="39"/>
     </row>
     <row r="145" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L145" s="23" t="s">
@@ -5524,29 +5542,29 @@
       <c r="L147" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="M147" s="37" t="s">
+      <c r="M147" s="39" t="s">
         <v>178</v>
       </c>
-      <c r="N147" s="37"/>
-      <c r="O147" s="37"/>
-      <c r="P147" s="37"/>
-      <c r="Q147" s="37"/>
-      <c r="R147" s="37"/>
-      <c r="S147" s="37"/>
+      <c r="N147" s="39"/>
+      <c r="O147" s="39"/>
+      <c r="P147" s="39"/>
+      <c r="Q147" s="39"/>
+      <c r="R147" s="39"/>
+      <c r="S147" s="39"/>
     </row>
     <row r="148" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L148" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="M148" s="37" t="s">
+      <c r="M148" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="N148" s="37"/>
-      <c r="O148" s="37"/>
-      <c r="P148" s="37"/>
-      <c r="Q148" s="37"/>
-      <c r="R148" s="37"/>
-      <c r="S148" s="37"/>
+      <c r="N148" s="39"/>
+      <c r="O148" s="39"/>
+      <c r="P148" s="39"/>
+      <c r="Q148" s="39"/>
+      <c r="R148" s="39"/>
+      <c r="S148" s="39"/>
     </row>
     <row r="150" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L150" s="23" t="s">
@@ -5604,29 +5622,29 @@
       <c r="L152" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="M152" s="31" t="s">
+      <c r="M152" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="N152" s="32"/>
-      <c r="O152" s="32"/>
-      <c r="P152" s="32"/>
-      <c r="Q152" s="32"/>
-      <c r="R152" s="32"/>
-      <c r="S152" s="33"/>
+      <c r="N152" s="34"/>
+      <c r="O152" s="34"/>
+      <c r="P152" s="34"/>
+      <c r="Q152" s="34"/>
+      <c r="R152" s="34"/>
+      <c r="S152" s="35"/>
     </row>
     <row r="153" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L153" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="M153" s="31" t="s">
+      <c r="M153" s="33" t="s">
         <v>160</v>
       </c>
-      <c r="N153" s="32"/>
-      <c r="O153" s="32"/>
-      <c r="P153" s="32"/>
-      <c r="Q153" s="32"/>
-      <c r="R153" s="32"/>
-      <c r="S153" s="33"/>
+      <c r="N153" s="34"/>
+      <c r="O153" s="34"/>
+      <c r="P153" s="34"/>
+      <c r="Q153" s="34"/>
+      <c r="R153" s="34"/>
+      <c r="S153" s="35"/>
     </row>
     <row r="155" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L155" s="27" t="s">
@@ -5684,29 +5702,29 @@
       <c r="L157" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="M157" s="37" t="s">
+      <c r="M157" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="N157" s="37"/>
-      <c r="O157" s="37"/>
-      <c r="P157" s="37"/>
-      <c r="Q157" s="37"/>
-      <c r="R157" s="37"/>
-      <c r="S157" s="37"/>
+      <c r="N157" s="39"/>
+      <c r="O157" s="39"/>
+      <c r="P157" s="39"/>
+      <c r="Q157" s="39"/>
+      <c r="R157" s="39"/>
+      <c r="S157" s="39"/>
     </row>
     <row r="158" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L158" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="M158" s="37" t="s">
+      <c r="M158" s="39" t="s">
         <v>203</v>
       </c>
-      <c r="N158" s="37"/>
-      <c r="O158" s="37"/>
-      <c r="P158" s="37"/>
-      <c r="Q158" s="37"/>
-      <c r="R158" s="37"/>
-      <c r="S158" s="37"/>
+      <c r="N158" s="39"/>
+      <c r="O158" s="39"/>
+      <c r="P158" s="39"/>
+      <c r="Q158" s="39"/>
+      <c r="R158" s="39"/>
+      <c r="S158" s="39"/>
     </row>
     <row r="160" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L160" s="27" t="s">
@@ -5764,29 +5782,29 @@
       <c r="L162" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="M162" s="31" t="s">
+      <c r="M162" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="N162" s="32"/>
-      <c r="O162" s="32"/>
-      <c r="P162" s="32"/>
-      <c r="Q162" s="32"/>
-      <c r="R162" s="32"/>
-      <c r="S162" s="33"/>
+      <c r="N162" s="34"/>
+      <c r="O162" s="34"/>
+      <c r="P162" s="34"/>
+      <c r="Q162" s="34"/>
+      <c r="R162" s="34"/>
+      <c r="S162" s="35"/>
     </row>
     <row r="163" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L163" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="M163" s="31" t="s">
+      <c r="M163" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="N163" s="32"/>
-      <c r="O163" s="32"/>
-      <c r="P163" s="32"/>
-      <c r="Q163" s="32"/>
-      <c r="R163" s="32"/>
-      <c r="S163" s="33"/>
+      <c r="N163" s="34"/>
+      <c r="O163" s="34"/>
+      <c r="P163" s="34"/>
+      <c r="Q163" s="34"/>
+      <c r="R163" s="34"/>
+      <c r="S163" s="35"/>
     </row>
     <row r="165" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L165" s="27" t="s">
@@ -5844,29 +5862,29 @@
       <c r="L167" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="M167" s="31" t="s">
+      <c r="M167" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="N167" s="32"/>
-      <c r="O167" s="32"/>
-      <c r="P167" s="32"/>
-      <c r="Q167" s="32"/>
-      <c r="R167" s="32"/>
-      <c r="S167" s="33"/>
+      <c r="N167" s="34"/>
+      <c r="O167" s="34"/>
+      <c r="P167" s="34"/>
+      <c r="Q167" s="34"/>
+      <c r="R167" s="34"/>
+      <c r="S167" s="35"/>
     </row>
     <row r="168" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L168" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="M168" s="31" t="s">
+      <c r="M168" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="N168" s="32"/>
-      <c r="O168" s="32"/>
-      <c r="P168" s="32"/>
-      <c r="Q168" s="32"/>
-      <c r="R168" s="32"/>
-      <c r="S168" s="33"/>
+      <c r="N168" s="34"/>
+      <c r="O168" s="34"/>
+      <c r="P168" s="34"/>
+      <c r="Q168" s="34"/>
+      <c r="R168" s="34"/>
+      <c r="S168" s="35"/>
     </row>
     <row r="170" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L170" s="27" t="s">
@@ -5924,29 +5942,29 @@
       <c r="L172" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="M172" s="31" t="s">
+      <c r="M172" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="N172" s="32"/>
-      <c r="O172" s="32"/>
-      <c r="P172" s="32"/>
-      <c r="Q172" s="32"/>
-      <c r="R172" s="32"/>
-      <c r="S172" s="33"/>
+      <c r="N172" s="34"/>
+      <c r="O172" s="34"/>
+      <c r="P172" s="34"/>
+      <c r="Q172" s="34"/>
+      <c r="R172" s="34"/>
+      <c r="S172" s="35"/>
     </row>
     <row r="173" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L173" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="M173" s="31" t="s">
+      <c r="M173" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="N173" s="32"/>
-      <c r="O173" s="32"/>
-      <c r="P173" s="32"/>
-      <c r="Q173" s="32"/>
-      <c r="R173" s="32"/>
-      <c r="S173" s="33"/>
+      <c r="N173" s="34"/>
+      <c r="O173" s="34"/>
+      <c r="P173" s="34"/>
+      <c r="Q173" s="34"/>
+      <c r="R173" s="34"/>
+      <c r="S173" s="35"/>
     </row>
     <row r="175" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L175" s="30" t="s">
@@ -6004,29 +6022,29 @@
       <c r="L177" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M177" s="37" t="s">
+      <c r="M177" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="N177" s="37"/>
-      <c r="O177" s="37"/>
-      <c r="P177" s="37"/>
-      <c r="Q177" s="37"/>
-      <c r="R177" s="37"/>
-      <c r="S177" s="37"/>
+      <c r="N177" s="39"/>
+      <c r="O177" s="39"/>
+      <c r="P177" s="39"/>
+      <c r="Q177" s="39"/>
+      <c r="R177" s="39"/>
+      <c r="S177" s="39"/>
     </row>
     <row r="178" spans="12:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L178" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="M178" s="37" t="s">
+      <c r="M178" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="N178" s="37"/>
-      <c r="O178" s="37"/>
-      <c r="P178" s="37"/>
-      <c r="Q178" s="37"/>
-      <c r="R178" s="37"/>
-      <c r="S178" s="37"/>
+      <c r="N178" s="39"/>
+      <c r="O178" s="39"/>
+      <c r="P178" s="39"/>
+      <c r="Q178" s="39"/>
+      <c r="R178" s="39"/>
+      <c r="S178" s="39"/>
     </row>
     <row r="180" spans="12:19" ht="30" x14ac:dyDescent="0.25">
       <c r="L180" s="30" t="s">
@@ -6084,32 +6102,112 @@
       <c r="L182" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M182" s="31" t="s">
+      <c r="M182" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="N182" s="32"/>
-      <c r="O182" s="32"/>
-      <c r="P182" s="32"/>
-      <c r="Q182" s="32"/>
-      <c r="R182" s="32"/>
-      <c r="S182" s="33"/>
+      <c r="N182" s="34"/>
+      <c r="O182" s="34"/>
+      <c r="P182" s="34"/>
+      <c r="Q182" s="34"/>
+      <c r="R182" s="34"/>
+      <c r="S182" s="35"/>
     </row>
     <row r="183" spans="12:19" x14ac:dyDescent="0.25">
       <c r="L183" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="M183" s="31" t="s">
+      <c r="M183" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="N183" s="32"/>
-      <c r="O183" s="32"/>
-      <c r="P183" s="32"/>
-      <c r="Q183" s="32"/>
-      <c r="R183" s="32"/>
-      <c r="S183" s="33"/>
+      <c r="N183" s="34"/>
+      <c r="O183" s="34"/>
+      <c r="P183" s="34"/>
+      <c r="Q183" s="34"/>
+      <c r="R183" s="34"/>
+      <c r="S183" s="35"/>
+    </row>
+    <row r="185" spans="12:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="L185" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="M185" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="N185" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="O185" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="P185" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q185" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="R185" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="S185" s="31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="186" spans="12:19" x14ac:dyDescent="0.25">
+      <c r="L186" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="M186" s="31">
+        <v>7</v>
+      </c>
+      <c r="N186" s="31">
+        <v>1</v>
+      </c>
+      <c r="O186" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="P186" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q186" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="R186" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="S186" s="31">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="187" spans="12:19" x14ac:dyDescent="0.25">
+      <c r="L187" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="M187" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="N187" s="34"/>
+      <c r="O187" s="34"/>
+      <c r="P187" s="34"/>
+      <c r="Q187" s="34"/>
+      <c r="R187" s="34"/>
+      <c r="S187" s="35"/>
+    </row>
+    <row r="188" spans="12:19" x14ac:dyDescent="0.25">
+      <c r="L188" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="M188" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="N188" s="34"/>
+      <c r="O188" s="34"/>
+      <c r="P188" s="34"/>
+      <c r="Q188" s="34"/>
+      <c r="R188" s="34"/>
+      <c r="S188" s="35"/>
     </row>
   </sheetData>
-  <mergeCells count="125">
+  <mergeCells count="127">
     <mergeCell ref="M137:S137"/>
     <mergeCell ref="M138:S138"/>
     <mergeCell ref="M122:S122"/>
@@ -6122,6 +6220,7 @@
     <mergeCell ref="D118:J118"/>
     <mergeCell ref="D127:J127"/>
     <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D113:J113"/>
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="V12:AB12"/>
     <mergeCell ref="V13:AB13"/>
@@ -6149,15 +6248,12 @@
     <mergeCell ref="M168:S168"/>
     <mergeCell ref="D22:J22"/>
     <mergeCell ref="D23:J23"/>
-    <mergeCell ref="D92:J92"/>
+    <mergeCell ref="D17:J17"/>
     <mergeCell ref="D73:J73"/>
     <mergeCell ref="M133:S133"/>
-    <mergeCell ref="D77:J77"/>
+    <mergeCell ref="M187:S187"/>
     <mergeCell ref="D117:J117"/>
     <mergeCell ref="D112:J112"/>
-    <mergeCell ref="D113:J113"/>
-    <mergeCell ref="D67:J67"/>
-    <mergeCell ref="D68:J68"/>
     <mergeCell ref="M42:S42"/>
     <mergeCell ref="D7:J7"/>
     <mergeCell ref="D8:J8"/>
@@ -6166,7 +6262,7 @@
     <mergeCell ref="M97:S97"/>
     <mergeCell ref="M72:S72"/>
     <mergeCell ref="M73:S73"/>
-    <mergeCell ref="D78:J78"/>
+    <mergeCell ref="M188:S188"/>
     <mergeCell ref="D82:J82"/>
     <mergeCell ref="M87:S87"/>
     <mergeCell ref="M88:S88"/>
@@ -6174,8 +6270,12 @@
     <mergeCell ref="M78:S78"/>
     <mergeCell ref="M93:S93"/>
     <mergeCell ref="M67:S67"/>
-    <mergeCell ref="D93:J93"/>
+    <mergeCell ref="D18:J18"/>
     <mergeCell ref="M63:S63"/>
+    <mergeCell ref="D52:J52"/>
+    <mergeCell ref="D53:J53"/>
+    <mergeCell ref="D27:J27"/>
+    <mergeCell ref="D28:J28"/>
     <mergeCell ref="V17:AB17"/>
     <mergeCell ref="V18:AB18"/>
     <mergeCell ref="M17:S17"/>
@@ -6187,8 +6287,6 @@
     <mergeCell ref="M28:S28"/>
     <mergeCell ref="M33:S33"/>
     <mergeCell ref="M22:S22"/>
-    <mergeCell ref="D52:J52"/>
-    <mergeCell ref="D53:J53"/>
     <mergeCell ref="M163:S163"/>
     <mergeCell ref="D107:J107"/>
     <mergeCell ref="D108:J108"/>
@@ -6211,6 +6309,8 @@
     <mergeCell ref="D83:J83"/>
     <mergeCell ref="M152:S152"/>
     <mergeCell ref="M148:S148"/>
+    <mergeCell ref="D67:J67"/>
+    <mergeCell ref="D68:J68"/>
     <mergeCell ref="M173:S173"/>
     <mergeCell ref="D57:J57"/>
     <mergeCell ref="D58:J58"/>
@@ -6250,28 +6350,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="42"/>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
+      <c r="A1" s="47"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
     </row>
     <row r="4" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
